--- a/rosters/.versions/2026-06/previous.xlsx
+++ b/rosters/.versions/2026-06/previous.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="157" documentId="8_{33A3BB0B-4D98-43E4-AA73-C01E96E70C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{956ECAEB-130D-4730-B6E0-D458C1ECB924}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="2" activeTab="7" xr2:uid="{9736B67C-D61B-41E1-B07B-429B3D8AE9CC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="7" activeTab="7" xr2:uid="{9736B67C-D61B-41E1-B07B-429B3D8AE9CC}"/>
   </bookViews>
   <sheets>
     <sheet name="Setting " sheetId="1" state="hidden" r:id="rId1"/>
@@ -5853,58 +5853,13 @@
     <xf numFmtId="0" fontId="18" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5916,10 +5871,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5928,10 +5883,25 @@
     <xf numFmtId="0" fontId="4" fillId="12" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5940,26 +5910,104 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -5976,53 +6024,20 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6049,21 +6064,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7523,91 +7523,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:40" ht="9" customHeight="1">
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="140"/>
-      <c r="N1" s="140"/>
-      <c r="O1" s="140"/>
-      <c r="P1" s="140"/>
-      <c r="Q1" s="140"/>
-      <c r="R1" s="140"/>
-      <c r="S1" s="140"/>
-      <c r="T1" s="140"/>
-      <c r="U1" s="140"/>
-      <c r="V1" s="140"/>
-      <c r="W1" s="140"/>
-      <c r="X1" s="140"/>
-      <c r="Y1" s="140"/>
-      <c r="Z1" s="140"/>
-      <c r="AA1" s="140"/>
-      <c r="AB1" s="140"/>
-      <c r="AC1" s="140"/>
-      <c r="AD1" s="140"/>
-      <c r="AE1" s="140"/>
-      <c r="AF1" s="140"/>
-      <c r="AG1" s="140"/>
-      <c r="AH1" s="140"/>
-      <c r="AI1" s="140"/>
+      <c r="E1" s="137"/>
+      <c r="F1" s="137"/>
+      <c r="G1" s="137"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="137"/>
+      <c r="M1" s="137"/>
+      <c r="N1" s="137"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="137"/>
+      <c r="Q1" s="137"/>
+      <c r="R1" s="137"/>
+      <c r="S1" s="137"/>
+      <c r="T1" s="137"/>
+      <c r="U1" s="137"/>
+      <c r="V1" s="137"/>
+      <c r="W1" s="137"/>
+      <c r="X1" s="137"/>
+      <c r="Y1" s="137"/>
+      <c r="Z1" s="137"/>
+      <c r="AA1" s="137"/>
+      <c r="AB1" s="137"/>
+      <c r="AC1" s="137"/>
+      <c r="AD1" s="137"/>
+      <c r="AE1" s="137"/>
+      <c r="AF1" s="137"/>
+      <c r="AG1" s="137"/>
+      <c r="AH1" s="137"/>
+      <c r="AI1" s="137"/>
     </row>
     <row r="2" spans="2:40" ht="28.5">
-      <c r="B2" s="147" t="s">
+      <c r="B2" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="147"/>
+      <c r="C2" s="135"/>
       <c r="D2" s="9"/>
-      <c r="E2" s="148" t="s">
+      <c r="E2" s="136" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="148"/>
-      <c r="G2" s="148"/>
-      <c r="H2" s="148"/>
-      <c r="I2" s="148"/>
-      <c r="J2" s="148"/>
-      <c r="K2" s="148"/>
-      <c r="L2" s="148"/>
-      <c r="M2" s="148"/>
-      <c r="N2" s="148"/>
-      <c r="O2" s="148"/>
-      <c r="P2" s="148"/>
-      <c r="Q2" s="148"/>
-      <c r="R2" s="148"/>
-      <c r="S2" s="148"/>
-      <c r="T2" s="148"/>
-      <c r="U2" s="148"/>
-      <c r="V2" s="148"/>
-      <c r="W2" s="148" t="s">
+      <c r="F2" s="136"/>
+      <c r="G2" s="136"/>
+      <c r="H2" s="136"/>
+      <c r="I2" s="136"/>
+      <c r="J2" s="136"/>
+      <c r="K2" s="136"/>
+      <c r="L2" s="136"/>
+      <c r="M2" s="136"/>
+      <c r="N2" s="136"/>
+      <c r="O2" s="136"/>
+      <c r="P2" s="136"/>
+      <c r="Q2" s="136"/>
+      <c r="R2" s="136"/>
+      <c r="S2" s="136"/>
+      <c r="T2" s="136"/>
+      <c r="U2" s="136"/>
+      <c r="V2" s="136"/>
+      <c r="W2" s="136" t="s">
         <v>28</v>
       </c>
-      <c r="X2" s="148"/>
-      <c r="Y2" s="148"/>
-      <c r="Z2" s="148"/>
-      <c r="AA2" s="148"/>
-      <c r="AB2" s="148"/>
-      <c r="AC2" s="148">
+      <c r="X2" s="136"/>
+      <c r="Y2" s="136"/>
+      <c r="Z2" s="136"/>
+      <c r="AA2" s="136"/>
+      <c r="AB2" s="136"/>
+      <c r="AC2" s="136">
         <v>2025</v>
       </c>
-      <c r="AD2" s="148"/>
-      <c r="AE2" s="148"/>
-      <c r="AF2" s="148"/>
+      <c r="AD2" s="136"/>
+      <c r="AE2" s="136"/>
+      <c r="AF2" s="136"/>
       <c r="AG2" s="5"/>
       <c r="AH2" s="5"/>
       <c r="AI2" s="5"/>
-      <c r="AK2" s="144" t="s">
+      <c r="AK2" s="130" t="s">
         <v>34</v>
       </c>
-      <c r="AL2" s="144"/>
-      <c r="AM2" s="144"/>
-      <c r="AN2" s="144"/>
+      <c r="AL2" s="130"/>
+      <c r="AM2" s="130"/>
+      <c r="AN2" s="130"/>
     </row>
     <row r="3" spans="2:40">
-      <c r="B3" s="147"/>
-      <c r="C3" s="147"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="135"/>
       <c r="D3" s="10"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -7640,58 +7640,58 @@
       <c r="AG3" s="3"/>
       <c r="AH3" s="3"/>
       <c r="AI3" s="3"/>
-      <c r="AK3" s="144"/>
-      <c r="AL3" s="144"/>
-      <c r="AM3" s="144"/>
-      <c r="AN3" s="144"/>
+      <c r="AK3" s="130"/>
+      <c r="AL3" s="130"/>
+      <c r="AM3" s="130"/>
+      <c r="AN3" s="130"/>
     </row>
     <row r="4" spans="2:40">
-      <c r="B4" s="147"/>
-      <c r="C4" s="147"/>
+      <c r="B4" s="135"/>
+      <c r="C4" s="135"/>
       <c r="D4" s="10"/>
-      <c r="E4" s="141" t="s">
+      <c r="E4" s="131" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="141"/>
-      <c r="G4" s="141"/>
-      <c r="H4" s="141"/>
-      <c r="I4" s="141"/>
+      <c r="F4" s="131"/>
+      <c r="G4" s="131"/>
+      <c r="H4" s="131"/>
+      <c r="I4" s="131"/>
       <c r="J4" s="3">
         <v>1</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
-      <c r="M4" s="142" t="s">
+      <c r="M4" s="133" t="s">
         <v>36</v>
       </c>
-      <c r="N4" s="142"/>
-      <c r="O4" s="142"/>
-      <c r="P4" s="143">
+      <c r="N4" s="133"/>
+      <c r="O4" s="133"/>
+      <c r="P4" s="138">
         <f>IFERROR(DATEVALUE(J4&amp;W2&amp;AC2),"")</f>
         <v>45901</v>
       </c>
-      <c r="Q4" s="143"/>
-      <c r="R4" s="143"/>
+      <c r="Q4" s="138"/>
+      <c r="R4" s="138"/>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
-      <c r="U4" s="142" t="s">
+      <c r="U4" s="133" t="s">
         <v>37</v>
       </c>
-      <c r="V4" s="142"/>
-      <c r="W4" s="142"/>
-      <c r="X4" s="143">
+      <c r="V4" s="133"/>
+      <c r="W4" s="133"/>
+      <c r="X4" s="138">
         <f>IFERROR(EOMONTH(P4,0)+J4-1,"")</f>
         <v>45930</v>
       </c>
-      <c r="Y4" s="143"/>
-      <c r="Z4" s="143"/>
+      <c r="Y4" s="138"/>
+      <c r="Z4" s="138"/>
       <c r="AA4" s="3"/>
       <c r="AB4" s="3"/>
-      <c r="AC4" s="142" t="s">
+      <c r="AC4" s="133" t="s">
         <v>38</v>
       </c>
-      <c r="AD4" s="142"/>
-      <c r="AE4" s="142"/>
+      <c r="AD4" s="133"/>
+      <c r="AE4" s="133"/>
       <c r="AF4" s="3">
         <f>COUNTIF(E6:AI6,"*?")</f>
         <v>30</v>
@@ -7699,10 +7699,10 @@
       <c r="AG4" s="3"/>
       <c r="AH4" s="3"/>
       <c r="AI4" s="3"/>
-      <c r="AK4" s="144"/>
-      <c r="AL4" s="144"/>
-      <c r="AM4" s="144"/>
-      <c r="AN4" s="144"/>
+      <c r="AK4" s="130"/>
+      <c r="AL4" s="130"/>
+      <c r="AM4" s="130"/>
+      <c r="AN4" s="130"/>
     </row>
     <row r="5" spans="2:40" ht="6.75" customHeight="1">
       <c r="B5" s="6"/>
@@ -7741,10 +7741,10 @@
       <c r="AI5" s="3"/>
     </row>
     <row r="6" spans="2:40" ht="27.75">
-      <c r="B6" s="146" t="s">
+      <c r="B6" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="146" t="s">
+      <c r="C6" s="134" t="s">
         <v>40</v>
       </c>
       <c r="D6" s="12"/>
@@ -7873,22 +7873,22 @@
         <v/>
       </c>
       <c r="AJ6" s="14"/>
-      <c r="AK6" s="145" t="s">
+      <c r="AK6" s="132" t="s">
         <v>41</v>
       </c>
-      <c r="AL6" s="145" t="s">
+      <c r="AL6" s="132" t="s">
         <v>42</v>
       </c>
-      <c r="AM6" s="145" t="s">
+      <c r="AM6" s="132" t="s">
         <v>43</v>
       </c>
-      <c r="AN6" s="145" t="s">
+      <c r="AN6" s="132" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="7" spans="2:40">
-      <c r="B7" s="146"/>
-      <c r="C7" s="146"/>
+      <c r="B7" s="134"/>
+      <c r="C7" s="134"/>
       <c r="D7" s="12"/>
       <c r="E7" s="15">
         <f>P4</f>
@@ -8015,10 +8015,10 @@
         <v/>
       </c>
       <c r="AJ7" s="14"/>
-      <c r="AK7" s="145"/>
-      <c r="AL7" s="145"/>
-      <c r="AM7" s="145"/>
-      <c r="AN7" s="145"/>
+      <c r="AK7" s="132"/>
+      <c r="AL7" s="132"/>
+      <c r="AM7" s="132"/>
+      <c r="AN7" s="132"/>
     </row>
     <row r="8" spans="2:40">
       <c r="B8" s="3" t="s">
@@ -12471,10 +12471,10 @@
       </c>
     </row>
     <row r="39" spans="2:40">
-      <c r="B39" s="141" t="s">
+      <c r="B39" s="131" t="s">
         <v>75</v>
       </c>
-      <c r="C39" s="141"/>
+      <c r="C39" s="131"/>
       <c r="E39" s="6">
         <f t="shared" ref="E39:AI39" ca="1" si="37">COUNTIF(E$8:E$37,"M*")</f>
         <v>8</v>
@@ -12601,10 +12601,10 @@
       </c>
     </row>
     <row r="40" spans="2:40">
-      <c r="B40" s="141" t="s">
+      <c r="B40" s="131" t="s">
         <v>76</v>
       </c>
-      <c r="C40" s="141"/>
+      <c r="C40" s="131"/>
       <c r="E40" s="6">
         <f t="shared" ref="E40:AI40" ca="1" si="38">COUNTIF(E$8:E$37,"A*")</f>
         <v>4</v>
@@ -12731,10 +12731,10 @@
       </c>
     </row>
     <row r="41" spans="2:40">
-      <c r="B41" s="141" t="s">
+      <c r="B41" s="131" t="s">
         <v>77</v>
       </c>
-      <c r="C41" s="141"/>
+      <c r="C41" s="131"/>
       <c r="E41" s="6">
         <f t="shared" ref="E41:AI41" ca="1" si="39">COUNTIF(E$8:E$37,"N*")</f>
         <v>8</v>
@@ -12861,10 +12861,10 @@
       </c>
     </row>
     <row r="42" spans="2:40">
-      <c r="B42" s="141" t="s">
+      <c r="B42" s="131" t="s">
         <v>78</v>
       </c>
-      <c r="C42" s="141"/>
+      <c r="C42" s="131"/>
       <c r="E42" s="6">
         <f t="shared" ref="E42:AI42" ca="1" si="40">COUNTIF(E$8:E$37,"O*")</f>
         <v>10</v>
@@ -12998,6 +12998,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="E1:AI1"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="U4:W4"/>
+    <mergeCell ref="X4:Z4"/>
     <mergeCell ref="AK2:AN4"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="B42:C42"/>
@@ -13014,12 +13020,6 @@
     <mergeCell ref="E2:V2"/>
     <mergeCell ref="W2:AB2"/>
     <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="E1:AI1"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="M4:O4"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="U4:W4"/>
-    <mergeCell ref="X4:Z4"/>
   </mergeCells>
   <conditionalFormatting sqref="E8:AI37 AK8:AN37 E39:AI42">
     <cfRule type="expression" dxfId="112" priority="4">
@@ -13083,61 +13083,61 @@
   <sheetData>
     <row r="1" spans="2:42" ht="16.5" thickBot="1"/>
     <row r="2" spans="2:42" ht="39" customHeight="1" thickBot="1">
-      <c r="F2" s="134" t="s">
+      <c r="F2" s="139" t="s">
         <v>79</v>
       </c>
-      <c r="G2" s="135"/>
-      <c r="H2" s="135"/>
-      <c r="I2" s="135"/>
-      <c r="J2" s="135"/>
-      <c r="K2" s="135"/>
-      <c r="L2" s="135"/>
-      <c r="M2" s="135"/>
-      <c r="N2" s="135"/>
-      <c r="O2" s="135"/>
-      <c r="P2" s="135"/>
-      <c r="Q2" s="135"/>
-      <c r="R2" s="135"/>
-      <c r="S2" s="135"/>
-      <c r="T2" s="135"/>
-      <c r="U2" s="135"/>
-      <c r="V2" s="135"/>
-      <c r="W2" s="135"/>
-      <c r="X2" s="135"/>
-      <c r="Y2" s="135"/>
-      <c r="Z2" s="135"/>
-      <c r="AA2" s="135"/>
-      <c r="AB2" s="135"/>
-      <c r="AC2" s="135"/>
-      <c r="AD2" s="135"/>
-      <c r="AE2" s="135"/>
-      <c r="AF2" s="135"/>
-      <c r="AG2" s="135"/>
-      <c r="AH2" s="135"/>
-      <c r="AI2" s="135"/>
-      <c r="AJ2" s="136"/>
-      <c r="AL2" s="137" t="s">
+      <c r="G2" s="140"/>
+      <c r="H2" s="140"/>
+      <c r="I2" s="140"/>
+      <c r="J2" s="140"/>
+      <c r="K2" s="140"/>
+      <c r="L2" s="140"/>
+      <c r="M2" s="140"/>
+      <c r="N2" s="140"/>
+      <c r="O2" s="140"/>
+      <c r="P2" s="140"/>
+      <c r="Q2" s="140"/>
+      <c r="R2" s="140"/>
+      <c r="S2" s="140"/>
+      <c r="T2" s="140"/>
+      <c r="U2" s="140"/>
+      <c r="V2" s="140"/>
+      <c r="W2" s="140"/>
+      <c r="X2" s="140"/>
+      <c r="Y2" s="140"/>
+      <c r="Z2" s="140"/>
+      <c r="AA2" s="140"/>
+      <c r="AB2" s="140"/>
+      <c r="AC2" s="140"/>
+      <c r="AD2" s="140"/>
+      <c r="AE2" s="140"/>
+      <c r="AF2" s="140"/>
+      <c r="AG2" s="140"/>
+      <c r="AH2" s="140"/>
+      <c r="AI2" s="140"/>
+      <c r="AJ2" s="141"/>
+      <c r="AL2" s="114" t="s">
         <v>80</v>
       </c>
-      <c r="AM2" s="137" t="s">
+      <c r="AM2" s="114" t="s">
         <v>81</v>
       </c>
-      <c r="AN2" s="137" t="s">
+      <c r="AN2" s="114" t="s">
         <v>82</v>
       </c>
-      <c r="AO2" s="137" t="s">
+      <c r="AO2" s="114" t="s">
         <v>83</v>
       </c>
-      <c r="AP2" s="137" t="s">
+      <c r="AP2" s="114" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="3" spans="2:42" ht="39.75" thickBot="1">
-      <c r="B3" s="127" t="s">
+      <c r="B3" s="122" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="127"/>
-      <c r="D3" s="127"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="122"/>
       <c r="F3" s="43" t="s">
         <v>86</v>
       </c>
@@ -13229,16 +13229,16 @@
         <v>87</v>
       </c>
       <c r="AJ3" s="43"/>
-      <c r="AL3" s="138"/>
-      <c r="AM3" s="138"/>
-      <c r="AN3" s="138"/>
-      <c r="AO3" s="138"/>
-      <c r="AP3" s="138"/>
+      <c r="AL3" s="115"/>
+      <c r="AM3" s="115"/>
+      <c r="AN3" s="115"/>
+      <c r="AO3" s="115"/>
+      <c r="AP3" s="115"/>
     </row>
     <row r="4" spans="2:42" ht="19.5" customHeight="1" thickBot="1">
-      <c r="B4" s="127"/>
-      <c r="C4" s="127"/>
-      <c r="D4" s="127"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
       <c r="F4" s="40">
         <v>1</v>
       </c>
@@ -13330,20 +13330,20 @@
         <v>30</v>
       </c>
       <c r="AJ4" s="68"/>
-      <c r="AL4" s="139"/>
-      <c r="AM4" s="139"/>
-      <c r="AN4" s="139"/>
-      <c r="AO4" s="139"/>
-      <c r="AP4" s="139"/>
+      <c r="AL4" s="116"/>
+      <c r="AM4" s="116"/>
+      <c r="AN4" s="116"/>
+      <c r="AO4" s="116"/>
+      <c r="AP4" s="116"/>
     </row>
     <row r="5" spans="2:42" ht="19.5" customHeight="1">
       <c r="B5" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="C5" s="126" t="s">
+      <c r="C5" s="142" t="s">
         <v>94</v>
       </c>
-      <c r="D5" s="126"/>
+      <c r="D5" s="142"/>
       <c r="F5" s="84" t="s">
         <v>95</v>
       </c>
@@ -13460,10 +13460,10 @@
       <c r="B6" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="126" t="s">
+      <c r="C6" s="142" t="s">
         <v>99</v>
       </c>
-      <c r="D6" s="126"/>
+      <c r="D6" s="142"/>
       <c r="F6" s="75" t="s">
         <v>97</v>
       </c>
@@ -13580,10 +13580,10 @@
       <c r="B7" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="C7" s="126" t="s">
+      <c r="C7" s="142" t="s">
         <v>100</v>
       </c>
-      <c r="D7" s="126"/>
+      <c r="D7" s="142"/>
       <c r="F7" s="75" t="s">
         <v>101</v>
       </c>
@@ -13700,10 +13700,10 @@
       <c r="B8" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="C8" s="126" t="s">
+      <c r="C8" s="142" t="s">
         <v>103</v>
       </c>
-      <c r="D8" s="126"/>
+      <c r="D8" s="142"/>
       <c r="F8" s="75" t="s">
         <v>96</v>
       </c>
@@ -13820,10 +13820,10 @@
       <c r="B9" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="C9" s="126" t="s">
+      <c r="C9" s="142" t="s">
         <v>105</v>
       </c>
-      <c r="D9" s="126"/>
+      <c r="D9" s="142"/>
       <c r="F9" s="90" t="s">
         <v>106</v>
       </c>
@@ -13940,10 +13940,10 @@
       <c r="B10" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="C10" s="126" t="s">
+      <c r="C10" s="142" t="s">
         <v>109</v>
       </c>
-      <c r="D10" s="126"/>
+      <c r="D10" s="142"/>
       <c r="F10" s="75" t="s">
         <v>96</v>
       </c>
@@ -14060,10 +14060,10 @@
       <c r="B11" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="C11" s="126" t="s">
+      <c r="C11" s="142" t="s">
         <v>110</v>
       </c>
-      <c r="D11" s="126"/>
+      <c r="D11" s="142"/>
       <c r="F11" s="75" t="s">
         <v>95</v>
       </c>
@@ -14180,10 +14180,10 @@
       <c r="B12" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="126" t="s">
+      <c r="C12" s="142" t="s">
         <v>111</v>
       </c>
-      <c r="D12" s="126"/>
+      <c r="D12" s="142"/>
       <c r="F12" s="75" t="s">
         <v>107</v>
       </c>
@@ -14300,10 +14300,10 @@
       <c r="B13" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="C13" s="126" t="s">
+      <c r="C13" s="142" t="s">
         <v>112</v>
       </c>
-      <c r="D13" s="126"/>
+      <c r="D13" s="142"/>
       <c r="F13" s="75" t="s">
         <v>108</v>
       </c>
@@ -14421,10 +14421,10 @@
       <c r="B14" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="C14" s="126" t="s">
+      <c r="C14" s="142" t="s">
         <v>113</v>
       </c>
-      <c r="D14" s="126"/>
+      <c r="D14" s="142"/>
       <c r="F14" s="88" t="s">
         <v>95</v>
       </c>
@@ -14541,10 +14541,10 @@
       <c r="B15" s="35" t="s">
         <v>114</v>
       </c>
-      <c r="C15" s="128" t="s">
+      <c r="C15" s="144" t="s">
         <v>115</v>
       </c>
-      <c r="D15" s="129"/>
+      <c r="D15" s="145"/>
       <c r="E15" s="53"/>
       <c r="F15" s="72" t="s">
         <v>101</v>
@@ -14662,10 +14662,10 @@
       <c r="B16" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C16" s="126" t="s">
+      <c r="C16" s="142" t="s">
         <v>117</v>
       </c>
-      <c r="D16" s="133"/>
+      <c r="D16" s="143"/>
       <c r="E16" s="53"/>
       <c r="F16" s="74" t="s">
         <v>102</v>
@@ -14783,10 +14783,10 @@
       <c r="B17" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C17" s="126" t="s">
+      <c r="C17" s="142" t="s">
         <v>118</v>
       </c>
-      <c r="D17" s="133"/>
+      <c r="D17" s="143"/>
       <c r="E17" s="53"/>
       <c r="F17" s="75" t="s">
         <v>95</v>
@@ -14904,10 +14904,10 @@
       <c r="B18" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C18" s="126" t="s">
+      <c r="C18" s="142" t="s">
         <v>119</v>
       </c>
-      <c r="D18" s="133"/>
+      <c r="D18" s="143"/>
       <c r="E18" s="53"/>
       <c r="F18" s="75" t="s">
         <v>98</v>
@@ -15025,10 +15025,10 @@
       <c r="B19" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C19" s="126" t="s">
+      <c r="C19" s="142" t="s">
         <v>120</v>
       </c>
-      <c r="D19" s="133"/>
+      <c r="D19" s="143"/>
       <c r="E19" s="53"/>
       <c r="F19" s="75" t="s">
         <v>96</v>
@@ -15146,10 +15146,10 @@
       <c r="B20" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C20" s="126" t="s">
+      <c r="C20" s="142" t="s">
         <v>121</v>
       </c>
-      <c r="D20" s="133"/>
+      <c r="D20" s="143"/>
       <c r="E20" s="53"/>
       <c r="F20" s="75" t="s">
         <v>96</v>
@@ -15267,10 +15267,10 @@
       <c r="B21" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C21" s="126" t="s">
+      <c r="C21" s="142" t="s">
         <v>122</v>
       </c>
-      <c r="D21" s="133"/>
+      <c r="D21" s="143"/>
       <c r="E21" s="53"/>
       <c r="F21" s="75" t="s">
         <v>101</v>
@@ -15388,10 +15388,10 @@
       <c r="B22" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C22" s="126" t="s">
+      <c r="C22" s="142" t="s">
         <v>123</v>
       </c>
-      <c r="D22" s="133"/>
+      <c r="D22" s="143"/>
       <c r="E22" s="53"/>
       <c r="F22" s="75" t="s">
         <v>102</v>
@@ -15509,10 +15509,10 @@
       <c r="B23" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C23" s="126" t="s">
+      <c r="C23" s="142" t="s">
         <v>124</v>
       </c>
-      <c r="D23" s="133"/>
+      <c r="D23" s="143"/>
       <c r="E23" s="53"/>
       <c r="F23" s="74" t="s">
         <v>95</v>
@@ -15630,10 +15630,10 @@
       <c r="B24" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C24" s="126" t="s">
+      <c r="C24" s="142" t="s">
         <v>125</v>
       </c>
-      <c r="D24" s="133"/>
+      <c r="D24" s="143"/>
       <c r="E24" s="53"/>
       <c r="F24" s="75" t="s">
         <v>116</v>
@@ -15751,10 +15751,10 @@
       <c r="B25" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C25" s="96" t="s">
+      <c r="C25" s="112" t="s">
         <v>126</v>
       </c>
-      <c r="D25" s="130"/>
+      <c r="D25" s="146"/>
       <c r="E25" s="53"/>
       <c r="F25" s="75" t="s">
         <v>116</v>
@@ -15872,10 +15872,10 @@
       <c r="B26" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C26" s="96" t="s">
+      <c r="C26" s="112" t="s">
         <v>127</v>
       </c>
-      <c r="D26" s="130"/>
+      <c r="D26" s="146"/>
       <c r="E26" s="53"/>
       <c r="F26" s="75" t="s">
         <v>96</v>
@@ -15993,10 +15993,10 @@
       <c r="B27" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C27" s="96" t="s">
+      <c r="C27" s="112" t="s">
         <v>128</v>
       </c>
-      <c r="D27" s="130"/>
+      <c r="D27" s="146"/>
       <c r="E27" s="53"/>
       <c r="F27" s="75" t="s">
         <v>96</v>
@@ -16114,10 +16114,10 @@
       <c r="B28" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C28" s="96" t="s">
+      <c r="C28" s="112" t="s">
         <v>129</v>
       </c>
-      <c r="D28" s="130"/>
+      <c r="D28" s="146"/>
       <c r="E28" s="53"/>
       <c r="F28" s="75" t="s">
         <v>101</v>
@@ -16235,10 +16235,10 @@
       <c r="B29" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C29" s="131" t="s">
+      <c r="C29" s="147" t="s">
         <v>130</v>
       </c>
-      <c r="D29" s="132"/>
+      <c r="D29" s="148"/>
       <c r="E29" s="53"/>
       <c r="F29" s="74" t="s">
         <v>96</v>
@@ -16356,10 +16356,10 @@
       <c r="B30" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C30" s="126" t="s">
+      <c r="C30" s="142" t="s">
         <v>132</v>
       </c>
-      <c r="D30" s="126"/>
+      <c r="D30" s="142"/>
       <c r="F30" s="73" t="s">
         <v>102</v>
       </c>
@@ -16476,10 +16476,10 @@
       <c r="B31" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C31" s="126" t="s">
+      <c r="C31" s="142" t="s">
         <v>133</v>
       </c>
-      <c r="D31" s="126"/>
+      <c r="D31" s="142"/>
       <c r="F31" s="75" t="s">
         <v>102</v>
       </c>
@@ -16596,10 +16596,10 @@
       <c r="B32" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C32" s="126" t="s">
+      <c r="C32" s="142" t="s">
         <v>134</v>
       </c>
-      <c r="D32" s="126"/>
+      <c r="D32" s="142"/>
       <c r="F32" s="75" t="s">
         <v>98</v>
       </c>
@@ -16716,10 +16716,10 @@
       <c r="B33" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C33" s="126" t="s">
+      <c r="C33" s="142" t="s">
         <v>136</v>
       </c>
-      <c r="D33" s="126"/>
+      <c r="D33" s="142"/>
       <c r="F33" s="75" t="s">
         <v>95</v>
       </c>
@@ -16836,10 +16836,10 @@
       <c r="B34" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C34" s="126" t="s">
+      <c r="C34" s="142" t="s">
         <v>137</v>
       </c>
-      <c r="D34" s="126"/>
+      <c r="D34" s="142"/>
       <c r="F34" s="75" t="s">
         <v>96</v>
       </c>
@@ -16956,10 +16956,10 @@
       <c r="B35" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C35" s="126" t="s">
+      <c r="C35" s="142" t="s">
         <v>138</v>
       </c>
-      <c r="D35" s="126"/>
+      <c r="D35" s="142"/>
       <c r="F35" s="75" t="s">
         <v>96</v>
       </c>
@@ -17076,10 +17076,10 @@
       <c r="B36" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C36" s="126" t="s">
+      <c r="C36" s="142" t="s">
         <v>139</v>
       </c>
-      <c r="D36" s="126"/>
+      <c r="D36" s="142"/>
       <c r="F36" s="76" t="s">
         <v>101</v>
       </c>
@@ -17196,10 +17196,10 @@
       <c r="B37" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C37" s="126" t="s">
+      <c r="C37" s="142" t="s">
         <v>140</v>
       </c>
-      <c r="D37" s="126"/>
+      <c r="D37" s="142"/>
       <c r="F37" s="75" t="s">
         <v>101</v>
       </c>
@@ -17316,10 +17316,10 @@
       <c r="B38" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C38" s="126" t="s">
+      <c r="C38" s="142" t="s">
         <v>141</v>
       </c>
-      <c r="D38" s="126"/>
+      <c r="D38" s="142"/>
       <c r="F38" s="75" t="s">
         <v>102</v>
       </c>
@@ -17436,10 +17436,10 @@
       <c r="B39" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C39" s="126" t="s">
+      <c r="C39" s="142" t="s">
         <v>142</v>
       </c>
-      <c r="D39" s="126"/>
+      <c r="D39" s="142"/>
       <c r="F39" s="75" t="s">
         <v>116</v>
       </c>
@@ -17556,10 +17556,10 @@
       <c r="B40" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C40" s="126" t="s">
+      <c r="C40" s="142" t="s">
         <v>143</v>
       </c>
-      <c r="D40" s="126"/>
+      <c r="D40" s="142"/>
       <c r="F40" s="75" t="s">
         <v>116</v>
       </c>
@@ -17676,10 +17676,10 @@
       <c r="B41" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C41" s="126" t="s">
+      <c r="C41" s="142" t="s">
         <v>144</v>
       </c>
-      <c r="D41" s="126"/>
+      <c r="D41" s="142"/>
       <c r="F41" s="75" t="s">
         <v>96</v>
       </c>
@@ -17796,10 +17796,10 @@
       <c r="B42" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C42" s="126" t="s">
+      <c r="C42" s="142" t="s">
         <v>145</v>
       </c>
-      <c r="D42" s="126"/>
+      <c r="D42" s="142"/>
       <c r="F42" s="75" t="s">
         <v>96</v>
       </c>
@@ -17916,10 +17916,10 @@
       <c r="B43" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C43" s="126" t="s">
+      <c r="C43" s="142" t="s">
         <v>146</v>
       </c>
-      <c r="D43" s="126"/>
+      <c r="D43" s="142"/>
       <c r="F43" s="76" t="s">
         <v>101</v>
       </c>
@@ -18036,10 +18036,10 @@
       <c r="B44" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C44" s="126" t="s">
+      <c r="C44" s="142" t="s">
         <v>147</v>
       </c>
-      <c r="D44" s="126"/>
+      <c r="D44" s="142"/>
       <c r="F44" s="75" t="s">
         <v>102</v>
       </c>
@@ -18156,10 +18156,10 @@
       <c r="B45" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C45" s="126" t="s">
+      <c r="C45" s="142" t="s">
         <v>148</v>
       </c>
-      <c r="D45" s="126"/>
+      <c r="D45" s="142"/>
       <c r="F45" s="75" t="s">
         <v>102</v>
       </c>
@@ -18276,10 +18276,10 @@
       <c r="B46" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C46" s="126" t="s">
+      <c r="C46" s="142" t="s">
         <v>149</v>
       </c>
-      <c r="D46" s="126"/>
+      <c r="D46" s="142"/>
       <c r="F46" s="75" t="s">
         <v>116</v>
       </c>
@@ -18396,10 +18396,10 @@
       <c r="B47" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C47" s="126" t="s">
+      <c r="C47" s="142" t="s">
         <v>150</v>
       </c>
-      <c r="D47" s="126"/>
+      <c r="D47" s="142"/>
       <c r="F47" s="75" t="s">
         <v>116</v>
       </c>
@@ -18516,10 +18516,10 @@
       <c r="B48" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C48" s="126" t="s">
+      <c r="C48" s="142" t="s">
         <v>151</v>
       </c>
-      <c r="D48" s="126"/>
+      <c r="D48" s="142"/>
       <c r="F48" s="75" t="s">
         <v>96</v>
       </c>
@@ -18636,10 +18636,10 @@
       <c r="B49" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C49" s="126" t="s">
+      <c r="C49" s="142" t="s">
         <v>152</v>
       </c>
-      <c r="D49" s="126"/>
+      <c r="D49" s="142"/>
       <c r="F49" s="75" t="s">
         <v>96</v>
       </c>
@@ -18756,10 +18756,10 @@
       <c r="B50" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C50" s="126" t="s">
+      <c r="C50" s="142" t="s">
         <v>153</v>
       </c>
-      <c r="D50" s="126"/>
+      <c r="D50" s="142"/>
       <c r="F50" s="76" t="s">
         <v>95</v>
       </c>
@@ -18876,10 +18876,10 @@
       <c r="B51" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C51" s="126" t="s">
+      <c r="C51" s="142" t="s">
         <v>154</v>
       </c>
-      <c r="D51" s="126"/>
+      <c r="D51" s="142"/>
       <c r="F51" s="75" t="s">
         <v>101</v>
       </c>
@@ -18996,10 +18996,10 @@
       <c r="B52" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C52" s="126" t="s">
+      <c r="C52" s="142" t="s">
         <v>155</v>
       </c>
-      <c r="D52" s="126"/>
+      <c r="D52" s="142"/>
       <c r="F52" s="75" t="s">
         <v>102</v>
       </c>
@@ -19116,10 +19116,10 @@
       <c r="B53" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C53" s="126" t="s">
+      <c r="C53" s="142" t="s">
         <v>156</v>
       </c>
-      <c r="D53" s="126"/>
+      <c r="D53" s="142"/>
       <c r="F53" s="75" t="s">
         <v>116</v>
       </c>
@@ -19236,10 +19236,10 @@
       <c r="B54" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C54" s="126" t="s">
+      <c r="C54" s="142" t="s">
         <v>157</v>
       </c>
-      <c r="D54" s="126"/>
+      <c r="D54" s="142"/>
       <c r="F54" s="75" t="s">
         <v>116</v>
       </c>
@@ -19356,10 +19356,10 @@
       <c r="B55" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C55" s="96" t="s">
+      <c r="C55" s="112" t="s">
         <v>158</v>
       </c>
-      <c r="D55" s="97"/>
+      <c r="D55" s="113"/>
       <c r="F55" s="75" t="s">
         <v>96</v>
       </c>
@@ -19476,10 +19476,10 @@
       <c r="B56" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C56" s="96" t="s">
+      <c r="C56" s="112" t="s">
         <v>159</v>
       </c>
-      <c r="D56" s="97"/>
+      <c r="D56" s="113"/>
       <c r="F56" s="75" t="s">
         <v>96</v>
       </c>
@@ -19596,10 +19596,10 @@
       <c r="B57" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C57" s="96" t="s">
+      <c r="C57" s="112" t="s">
         <v>160</v>
       </c>
-      <c r="D57" s="97"/>
+      <c r="D57" s="113"/>
       <c r="F57" s="76" t="s">
         <v>101</v>
       </c>
@@ -19716,10 +19716,10 @@
       <c r="B58" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C58" s="96" t="s">
+      <c r="C58" s="112" t="s">
         <v>161</v>
       </c>
-      <c r="D58" s="97"/>
+      <c r="D58" s="113"/>
       <c r="F58" s="75" t="s">
         <v>95</v>
       </c>
@@ -19836,10 +19836,10 @@
       <c r="B59" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C59" s="104" t="s">
+      <c r="C59" s="149" t="s">
         <v>162</v>
       </c>
-      <c r="D59" s="104"/>
+      <c r="D59" s="149"/>
       <c r="F59" s="75" t="s">
         <v>101</v>
       </c>
@@ -19956,10 +19956,10 @@
       <c r="B60" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C60" s="104" t="s">
+      <c r="C60" s="149" t="s">
         <v>163</v>
       </c>
-      <c r="D60" s="104"/>
+      <c r="D60" s="149"/>
       <c r="F60" s="75" t="s">
         <v>96</v>
       </c>
@@ -20076,10 +20076,10 @@
       <c r="B61" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C61" s="124" t="s">
+      <c r="C61" s="150" t="s">
         <v>164</v>
       </c>
-      <c r="D61" s="125"/>
+      <c r="D61" s="151"/>
       <c r="F61" s="75" t="s">
         <v>95</v>
       </c>
@@ -20196,10 +20196,10 @@
       <c r="B62" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C62" s="104" t="s">
+      <c r="C62" s="149" t="s">
         <v>165</v>
       </c>
-      <c r="D62" s="104"/>
+      <c r="D62" s="149"/>
       <c r="F62" s="88" t="s">
         <v>166</v>
       </c>
@@ -20316,10 +20316,10 @@
       <c r="B63" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C63" s="102" t="s">
+      <c r="C63" s="120" t="s">
         <v>168</v>
       </c>
-      <c r="D63" s="103"/>
+      <c r="D63" s="121"/>
       <c r="F63" s="83" t="s">
         <v>102</v>
       </c>
@@ -20436,10 +20436,10 @@
       <c r="B64" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C64" s="96" t="s">
+      <c r="C64" s="112" t="s">
         <v>169</v>
       </c>
-      <c r="D64" s="97"/>
+      <c r="D64" s="113"/>
       <c r="F64" s="83" t="s">
         <v>102</v>
       </c>
@@ -20556,10 +20556,10 @@
       <c r="B65" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C65" s="96" t="s">
+      <c r="C65" s="112" t="s">
         <v>170</v>
       </c>
-      <c r="D65" s="97"/>
+      <c r="D65" s="113"/>
       <c r="F65" s="84" t="s">
         <v>95</v>
       </c>
@@ -20676,10 +20676,10 @@
       <c r="B66" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C66" s="96" t="s">
+      <c r="C66" s="112" t="s">
         <v>171</v>
       </c>
-      <c r="D66" s="97"/>
+      <c r="D66" s="113"/>
       <c r="F66" s="84" t="s">
         <v>95</v>
       </c>
@@ -20796,10 +20796,10 @@
       <c r="B67" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C67" s="96" t="s">
+      <c r="C67" s="112" t="s">
         <v>172</v>
       </c>
-      <c r="D67" s="97"/>
+      <c r="D67" s="113"/>
       <c r="F67" s="84" t="s">
         <v>96</v>
       </c>
@@ -20916,10 +20916,10 @@
       <c r="B68" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C68" s="96" t="s">
+      <c r="C68" s="112" t="s">
         <v>173</v>
       </c>
-      <c r="D68" s="97"/>
+      <c r="D68" s="113"/>
       <c r="F68" s="84" t="s">
         <v>96</v>
       </c>
@@ -21036,10 +21036,10 @@
       <c r="B69" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C69" s="96" t="s">
+      <c r="C69" s="112" t="s">
         <v>174</v>
       </c>
-      <c r="D69" s="97"/>
+      <c r="D69" s="113"/>
       <c r="F69" s="84" t="s">
         <v>101</v>
       </c>
@@ -21156,10 +21156,10 @@
       <c r="B70" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C70" s="96" t="s">
+      <c r="C70" s="112" t="s">
         <v>175</v>
       </c>
-      <c r="D70" s="97"/>
+      <c r="D70" s="113"/>
       <c r="F70" s="83" t="s">
         <v>101</v>
       </c>
@@ -21276,10 +21276,10 @@
       <c r="B71" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C71" s="96" t="s">
+      <c r="C71" s="112" t="s">
         <v>176</v>
       </c>
-      <c r="D71" s="97"/>
+      <c r="D71" s="113"/>
       <c r="F71" s="83" t="s">
         <v>101</v>
       </c>
@@ -21396,10 +21396,10 @@
       <c r="B72" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C72" s="96" t="s">
+      <c r="C72" s="112" t="s">
         <v>177</v>
       </c>
-      <c r="D72" s="97"/>
+      <c r="D72" s="113"/>
       <c r="F72" s="84" t="s">
         <v>116</v>
       </c>
@@ -21516,10 +21516,10 @@
       <c r="B73" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C73" s="96" t="s">
+      <c r="C73" s="112" t="s">
         <v>178</v>
       </c>
-      <c r="D73" s="97"/>
+      <c r="D73" s="113"/>
       <c r="F73" s="84" t="s">
         <v>116</v>
       </c>
@@ -21636,10 +21636,10 @@
       <c r="B74" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C74" s="96" t="s">
+      <c r="C74" s="112" t="s">
         <v>179</v>
       </c>
-      <c r="D74" s="97"/>
+      <c r="D74" s="113"/>
       <c r="F74" s="84" t="s">
         <v>96</v>
       </c>
@@ -21756,10 +21756,10 @@
       <c r="B75" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C75" s="96" t="s">
+      <c r="C75" s="112" t="s">
         <v>180</v>
       </c>
-      <c r="D75" s="97"/>
+      <c r="D75" s="113"/>
       <c r="F75" s="84" t="s">
         <v>96</v>
       </c>
@@ -21876,10 +21876,10 @@
       <c r="B76" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C76" s="96" t="s">
+      <c r="C76" s="112" t="s">
         <v>181</v>
       </c>
-      <c r="D76" s="97"/>
+      <c r="D76" s="113"/>
       <c r="F76" s="85" t="s">
         <v>101</v>
       </c>
@@ -21996,10 +21996,10 @@
       <c r="B77" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C77" s="96" t="s">
+      <c r="C77" s="112" t="s">
         <v>182</v>
       </c>
-      <c r="D77" s="97"/>
+      <c r="D77" s="113"/>
       <c r="F77" s="74" t="s">
         <v>116</v>
       </c>
@@ -22116,10 +22116,10 @@
       <c r="B78" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C78" s="96" t="s">
+      <c r="C78" s="112" t="s">
         <v>183</v>
       </c>
-      <c r="D78" s="97"/>
+      <c r="D78" s="113"/>
       <c r="F78" s="83" t="s">
         <v>96</v>
       </c>
@@ -22236,10 +22236,10 @@
       <c r="B79" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C79" s="96" t="s">
+      <c r="C79" s="112" t="s">
         <v>184</v>
       </c>
-      <c r="D79" s="97"/>
+      <c r="D79" s="113"/>
       <c r="F79" s="84" t="s">
         <v>102</v>
       </c>
@@ -22476,10 +22476,10 @@
       <c r="B81" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C81" s="98" t="s">
+      <c r="C81" s="126" t="s">
         <v>186</v>
       </c>
-      <c r="D81" s="99"/>
+      <c r="D81" s="127"/>
       <c r="F81" s="87" t="s">
         <v>101</v>
       </c>
@@ -22647,10 +22647,10 @@
       </c>
     </row>
     <row r="83" spans="2:42" ht="18.75">
-      <c r="C83" s="123" t="s">
+      <c r="C83" s="153" t="s">
         <v>188</v>
       </c>
-      <c r="D83" s="123"/>
+      <c r="D83" s="153"/>
       <c r="E83" s="34"/>
       <c r="F83" s="35">
         <f t="shared" ref="F83:AJ83" si="25">COUNTIF(F9:F81,"M*")</f>
@@ -22798,10 +22798,10 @@
       </c>
     </row>
     <row r="84" spans="2:42" ht="18.75">
-      <c r="C84" s="123" t="s">
+      <c r="C84" s="153" t="s">
         <v>189</v>
       </c>
-      <c r="D84" s="123"/>
+      <c r="D84" s="153"/>
       <c r="E84" s="34"/>
       <c r="F84" s="35">
         <f t="shared" ref="F84:AJ84" si="26">COUNTIF(F9:F81,"A*")</f>
@@ -22949,10 +22949,10 @@
       </c>
     </row>
     <row r="85" spans="2:42" ht="18.75">
-      <c r="C85" s="123" t="s">
+      <c r="C85" s="153" t="s">
         <v>77</v>
       </c>
-      <c r="D85" s="123"/>
+      <c r="D85" s="153"/>
       <c r="E85" s="34"/>
       <c r="F85" s="35">
         <f t="shared" ref="F85:AJ85" si="27">COUNTIF(F9:F81,"N*")</f>
@@ -23100,10 +23100,10 @@
       </c>
     </row>
     <row r="86" spans="2:42" ht="18.75">
-      <c r="C86" s="123" t="s">
+      <c r="C86" s="153" t="s">
         <v>78</v>
       </c>
-      <c r="D86" s="123"/>
+      <c r="D86" s="153"/>
       <c r="E86" s="34"/>
       <c r="F86" s="35">
         <f t="shared" ref="F86:AJ86" si="28">COUNTIF(F$30:F$81,"O*")</f>
@@ -23251,10 +23251,10 @@
       </c>
     </row>
     <row r="87" spans="2:42" ht="18.75">
-      <c r="C87" s="119" t="s">
+      <c r="C87" s="109" t="s">
         <v>190</v>
       </c>
-      <c r="D87" s="120"/>
+      <c r="D87" s="110"/>
       <c r="E87" s="34"/>
       <c r="F87" s="35">
         <f t="shared" ref="F87:AJ87" si="29">COUNTIF(F9:F81,"TR*")</f>
@@ -23402,10 +23402,10 @@
       </c>
     </row>
     <row r="88" spans="2:42" ht="18.75">
-      <c r="C88" s="119" t="s">
+      <c r="C88" s="109" t="s">
         <v>191</v>
       </c>
-      <c r="D88" s="120"/>
+      <c r="D88" s="110"/>
       <c r="E88" s="34"/>
       <c r="F88" s="35">
         <f>COUNTIF(F9:F81,"ST*")</f>
@@ -23553,10 +23553,10 @@
       </c>
     </row>
     <row r="89" spans="2:42" ht="18.75">
-      <c r="C89" s="121" t="s">
+      <c r="C89" s="152" t="s">
         <v>192</v>
       </c>
-      <c r="D89" s="121"/>
+      <c r="D89" s="152"/>
       <c r="E89" s="36"/>
       <c r="F89" s="37">
         <f>F91-F92</f>
@@ -23707,37 +23707,37 @@
       <c r="C90" s="38"/>
       <c r="D90" s="38"/>
       <c r="E90" s="34"/>
-      <c r="F90" s="122"/>
-      <c r="G90" s="122"/>
-      <c r="H90" s="122"/>
-      <c r="I90" s="122"/>
-      <c r="J90" s="122"/>
-      <c r="K90" s="122"/>
-      <c r="L90" s="122"/>
-      <c r="M90" s="122"/>
-      <c r="N90" s="122"/>
-      <c r="O90" s="122"/>
-      <c r="P90" s="122"/>
-      <c r="Q90" s="122"/>
-      <c r="R90" s="122"/>
-      <c r="S90" s="122"/>
-      <c r="T90" s="122"/>
-      <c r="U90" s="122"/>
-      <c r="V90" s="122"/>
-      <c r="W90" s="122"/>
-      <c r="X90" s="122"/>
-      <c r="Y90" s="122"/>
-      <c r="Z90" s="122"/>
-      <c r="AA90" s="122"/>
-      <c r="AB90" s="122"/>
-      <c r="AC90" s="122"/>
-      <c r="AD90" s="122"/>
-      <c r="AE90" s="122"/>
-      <c r="AF90" s="122"/>
-      <c r="AG90" s="122"/>
-      <c r="AH90" s="122"/>
-      <c r="AI90" s="122"/>
-      <c r="AJ90" s="122"/>
+      <c r="F90" s="108"/>
+      <c r="G90" s="108"/>
+      <c r="H90" s="108"/>
+      <c r="I90" s="108"/>
+      <c r="J90" s="108"/>
+      <c r="K90" s="108"/>
+      <c r="L90" s="108"/>
+      <c r="M90" s="108"/>
+      <c r="N90" s="108"/>
+      <c r="O90" s="108"/>
+      <c r="P90" s="108"/>
+      <c r="Q90" s="108"/>
+      <c r="R90" s="108"/>
+      <c r="S90" s="108"/>
+      <c r="T90" s="108"/>
+      <c r="U90" s="108"/>
+      <c r="V90" s="108"/>
+      <c r="W90" s="108"/>
+      <c r="X90" s="108"/>
+      <c r="Y90" s="108"/>
+      <c r="Z90" s="108"/>
+      <c r="AA90" s="108"/>
+      <c r="AB90" s="108"/>
+      <c r="AC90" s="108"/>
+      <c r="AD90" s="108"/>
+      <c r="AE90" s="108"/>
+      <c r="AF90" s="108"/>
+      <c r="AG90" s="108"/>
+      <c r="AH90" s="108"/>
+      <c r="AI90" s="108"/>
+      <c r="AJ90" s="108"/>
       <c r="AL90" s="20">
         <f t="shared" si="24"/>
         <v>0</v>
@@ -23760,10 +23760,10 @@
       </c>
     </row>
     <row r="91" spans="2:42" ht="18.75">
-      <c r="C91" s="123" t="s">
+      <c r="C91" s="153" t="s">
         <v>193</v>
       </c>
-      <c r="D91" s="123"/>
+      <c r="D91" s="153"/>
       <c r="E91" s="34"/>
       <c r="F91" s="39">
         <f>SUM(F83:F85)</f>
@@ -23910,10 +23910,10 @@
       </c>
     </row>
     <row r="92" spans="2:42" ht="18.75">
-      <c r="C92" s="123" t="s">
+      <c r="C92" s="153" t="s">
         <v>194</v>
       </c>
-      <c r="D92" s="123"/>
+      <c r="D92" s="153"/>
       <c r="E92" s="34"/>
       <c r="F92" s="35">
         <v>45</v>
@@ -24030,10 +24030,10 @@
       </c>
     </row>
     <row r="93" spans="2:42" ht="18.75">
-      <c r="C93" s="123" t="s">
+      <c r="C93" s="153" t="s">
         <v>195</v>
       </c>
-      <c r="D93" s="123"/>
+      <c r="D93" s="153"/>
       <c r="E93" s="34"/>
       <c r="F93" s="35">
         <f>SUM(F83,F84,F85,F86,F88)</f>
@@ -24202,14 +24202,14 @@
       </c>
     </row>
     <row r="95" spans="2:42" ht="16.5" thickBot="1">
-      <c r="F95" s="110" t="s">
+      <c r="F95" s="95" t="s">
         <v>196</v>
       </c>
-      <c r="G95" s="111"/>
-      <c r="H95" s="111"/>
-      <c r="I95" s="111"/>
-      <c r="J95" s="111"/>
-      <c r="K95" s="112"/>
+      <c r="G95" s="96"/>
+      <c r="H95" s="96"/>
+      <c r="I95" s="96"/>
+      <c r="J95" s="96"/>
+      <c r="K95" s="97"/>
       <c r="AL95" s="20">
         <f t="shared" si="24"/>
         <v>0</v>
@@ -24235,17 +24235,17 @@
       <c r="F96" s="80" t="s">
         <v>197</v>
       </c>
-      <c r="G96" s="113" t="s">
+      <c r="G96" s="106" t="s">
         <v>198</v>
       </c>
-      <c r="H96" s="113"/>
+      <c r="H96" s="106"/>
       <c r="I96" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="J96" s="94" t="s">
+      <c r="J96" s="98" t="s">
         <v>199</v>
       </c>
-      <c r="K96" s="95"/>
+      <c r="K96" s="99"/>
       <c r="AL96" s="20">
         <f t="shared" si="24"/>
         <v>0</v>
@@ -24271,17 +24271,17 @@
       <c r="F97" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="G97" s="114" t="s">
+      <c r="G97" s="107" t="s">
         <v>200</v>
       </c>
-      <c r="H97" s="114"/>
+      <c r="H97" s="107"/>
       <c r="I97" s="77" t="s">
         <v>201</v>
       </c>
-      <c r="J97" s="115" t="s">
+      <c r="J97" s="100" t="s">
         <v>202</v>
       </c>
-      <c r="K97" s="116"/>
+      <c r="K97" s="101"/>
       <c r="AL97" s="20">
         <f t="shared" si="24"/>
         <v>0</v>
@@ -24307,17 +24307,17 @@
       <c r="F98" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="G98" s="100" t="s">
+      <c r="G98" s="102" t="s">
         <v>203</v>
       </c>
-      <c r="H98" s="100"/>
+      <c r="H98" s="102"/>
       <c r="I98" s="78" t="s">
         <v>108</v>
       </c>
-      <c r="J98" s="100" t="s">
+      <c r="J98" s="102" t="s">
         <v>204</v>
       </c>
-      <c r="K98" s="101"/>
+      <c r="K98" s="103"/>
       <c r="AL98" s="20"/>
       <c r="AM98" s="20"/>
       <c r="AN98" s="20"/>
@@ -24328,17 +24328,17 @@
       <c r="F99" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="G99" s="105" t="s">
+      <c r="G99" s="111" t="s">
         <v>205</v>
       </c>
-      <c r="H99" s="105"/>
+      <c r="H99" s="111"/>
       <c r="I99" s="79" t="s">
         <v>206</v>
       </c>
-      <c r="J99" s="117" t="s">
+      <c r="J99" s="104" t="s">
         <v>207</v>
       </c>
-      <c r="K99" s="118"/>
+      <c r="K99" s="105"/>
       <c r="AL99" s="20">
         <f>COUNTIF($F81:$AJ81,"ST*")</f>
         <v>0</v>
@@ -24364,88 +24364,139 @@
       <c r="F100" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="G100" s="105" t="s">
+      <c r="G100" s="111" t="s">
         <v>208</v>
       </c>
-      <c r="H100" s="105"/>
+      <c r="H100" s="111"/>
       <c r="I100" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="J100" s="106" t="s">
+      <c r="J100" s="93" t="s">
         <v>209</v>
       </c>
-      <c r="K100" s="107"/>
+      <c r="K100" s="94"/>
     </row>
     <row r="101" spans="6:42">
       <c r="F101" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="G101" s="108" t="s">
+      <c r="G101" s="92" t="s">
         <v>210</v>
       </c>
-      <c r="H101" s="108"/>
+      <c r="H101" s="92"/>
       <c r="I101" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="J101" s="106" t="s">
+      <c r="J101" s="93" t="s">
         <v>211</v>
       </c>
-      <c r="K101" s="107"/>
+      <c r="K101" s="94"/>
     </row>
     <row r="102" spans="6:42">
       <c r="F102" s="82" t="s">
         <v>212</v>
       </c>
-      <c r="G102" s="109" t="s">
+      <c r="G102" s="123" t="s">
         <v>213</v>
       </c>
-      <c r="H102" s="109"/>
+      <c r="H102" s="123"/>
       <c r="I102" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="J102" s="106" t="s">
+      <c r="J102" s="93" t="s">
         <v>214</v>
       </c>
-      <c r="K102" s="107"/>
+      <c r="K102" s="94"/>
     </row>
     <row r="103" spans="6:42" ht="16.5" thickBot="1">
       <c r="F103" s="55" t="s">
         <v>215</v>
       </c>
-      <c r="G103" s="92" t="s">
+      <c r="G103" s="124" t="s">
         <v>216</v>
       </c>
-      <c r="H103" s="92"/>
+      <c r="H103" s="124"/>
       <c r="I103" s="56" t="s">
         <v>167</v>
       </c>
-      <c r="J103" s="92" t="s">
+      <c r="J103" s="124" t="s">
         <v>217</v>
       </c>
-      <c r="K103" s="93"/>
+      <c r="K103" s="125"/>
     </row>
     <row r="108" spans="6:42" ht="9.75" customHeight="1"/>
   </sheetData>
   <autoFilter ref="F4:AJ89" xr:uid="{10A87D31-A428-49C7-B3CE-66B468A7BADA}"/>
   <mergeCells count="111">
-    <mergeCell ref="F2:AJ2"/>
-    <mergeCell ref="AL2:AL4"/>
-    <mergeCell ref="AM2:AM4"/>
-    <mergeCell ref="AN2:AN4"/>
-    <mergeCell ref="AO2:AO4"/>
-    <mergeCell ref="AP2:AP4"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="G103:H103"/>
+    <mergeCell ref="J103:K103"/>
+    <mergeCell ref="J96:K96"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="G98:H98"/>
+    <mergeCell ref="J98:K98"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="G100:H100"/>
+    <mergeCell ref="J100:K100"/>
+    <mergeCell ref="G101:H101"/>
+    <mergeCell ref="J101:K101"/>
+    <mergeCell ref="G102:H102"/>
+    <mergeCell ref="J102:K102"/>
+    <mergeCell ref="F95:K95"/>
+    <mergeCell ref="G96:H96"/>
+    <mergeCell ref="G97:H97"/>
+    <mergeCell ref="J97:K97"/>
+    <mergeCell ref="G99:H99"/>
+    <mergeCell ref="J99:K99"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="F90:AJ90"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C45:D45"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="C39:D39"/>
@@ -24470,75 +24521,24 @@
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="G100:H100"/>
-    <mergeCell ref="J100:K100"/>
-    <mergeCell ref="G101:H101"/>
-    <mergeCell ref="J101:K101"/>
-    <mergeCell ref="G102:H102"/>
-    <mergeCell ref="J102:K102"/>
-    <mergeCell ref="F95:K95"/>
-    <mergeCell ref="G96:H96"/>
-    <mergeCell ref="G97:H97"/>
-    <mergeCell ref="J97:K97"/>
-    <mergeCell ref="G99:H99"/>
-    <mergeCell ref="J99:K99"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="F90:AJ90"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="G103:H103"/>
-    <mergeCell ref="J103:K103"/>
-    <mergeCell ref="J96:K96"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="G98:H98"/>
-    <mergeCell ref="J98:K98"/>
+    <mergeCell ref="F2:AJ2"/>
+    <mergeCell ref="AL2:AL4"/>
+    <mergeCell ref="AM2:AM4"/>
+    <mergeCell ref="AN2:AN4"/>
+    <mergeCell ref="AO2:AO4"/>
+    <mergeCell ref="AP2:AP4"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F63:AI81">
@@ -24688,61 +24688,61 @@
   <sheetData>
     <row r="1" spans="2:42" ht="16.5" thickBot="1"/>
     <row r="2" spans="2:42" ht="39" customHeight="1" thickBot="1">
-      <c r="F2" s="134" t="s">
+      <c r="F2" s="139" t="s">
         <v>79</v>
       </c>
-      <c r="G2" s="135"/>
-      <c r="H2" s="135"/>
-      <c r="I2" s="135"/>
-      <c r="J2" s="135"/>
-      <c r="K2" s="135"/>
-      <c r="L2" s="135"/>
-      <c r="M2" s="135"/>
-      <c r="N2" s="135"/>
-      <c r="O2" s="135"/>
-      <c r="P2" s="135"/>
-      <c r="Q2" s="135"/>
-      <c r="R2" s="135"/>
-      <c r="S2" s="135"/>
-      <c r="T2" s="135"/>
-      <c r="U2" s="135"/>
-      <c r="V2" s="135"/>
-      <c r="W2" s="135"/>
-      <c r="X2" s="135"/>
-      <c r="Y2" s="135"/>
-      <c r="Z2" s="135"/>
-      <c r="AA2" s="135"/>
-      <c r="AB2" s="135"/>
-      <c r="AC2" s="135"/>
-      <c r="AD2" s="135"/>
-      <c r="AE2" s="135"/>
-      <c r="AF2" s="135"/>
-      <c r="AG2" s="135"/>
-      <c r="AH2" s="135"/>
-      <c r="AI2" s="135"/>
-      <c r="AJ2" s="136"/>
-      <c r="AL2" s="137" t="s">
+      <c r="G2" s="140"/>
+      <c r="H2" s="140"/>
+      <c r="I2" s="140"/>
+      <c r="J2" s="140"/>
+      <c r="K2" s="140"/>
+      <c r="L2" s="140"/>
+      <c r="M2" s="140"/>
+      <c r="N2" s="140"/>
+      <c r="O2" s="140"/>
+      <c r="P2" s="140"/>
+      <c r="Q2" s="140"/>
+      <c r="R2" s="140"/>
+      <c r="S2" s="140"/>
+      <c r="T2" s="140"/>
+      <c r="U2" s="140"/>
+      <c r="V2" s="140"/>
+      <c r="W2" s="140"/>
+      <c r="X2" s="140"/>
+      <c r="Y2" s="140"/>
+      <c r="Z2" s="140"/>
+      <c r="AA2" s="140"/>
+      <c r="AB2" s="140"/>
+      <c r="AC2" s="140"/>
+      <c r="AD2" s="140"/>
+      <c r="AE2" s="140"/>
+      <c r="AF2" s="140"/>
+      <c r="AG2" s="140"/>
+      <c r="AH2" s="140"/>
+      <c r="AI2" s="140"/>
+      <c r="AJ2" s="141"/>
+      <c r="AL2" s="114" t="s">
         <v>80</v>
       </c>
-      <c r="AM2" s="137" t="s">
+      <c r="AM2" s="114" t="s">
         <v>81</v>
       </c>
-      <c r="AN2" s="137" t="s">
+      <c r="AN2" s="114" t="s">
         <v>82</v>
       </c>
-      <c r="AO2" s="137" t="s">
+      <c r="AO2" s="114" t="s">
         <v>83</v>
       </c>
-      <c r="AP2" s="137" t="s">
+      <c r="AP2" s="114" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="3" spans="2:42" ht="39.75" thickBot="1">
-      <c r="B3" s="127" t="s">
+      <c r="B3" s="122" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="127"/>
-      <c r="D3" s="127"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="122"/>
       <c r="F3" s="43" t="s">
         <v>86</v>
       </c>
@@ -24836,16 +24836,16 @@
       <c r="AJ3" s="43" t="s">
         <v>187</v>
       </c>
-      <c r="AL3" s="138"/>
-      <c r="AM3" s="138"/>
-      <c r="AN3" s="138"/>
-      <c r="AO3" s="138"/>
-      <c r="AP3" s="138"/>
+      <c r="AL3" s="115"/>
+      <c r="AM3" s="115"/>
+      <c r="AN3" s="115"/>
+      <c r="AO3" s="115"/>
+      <c r="AP3" s="115"/>
     </row>
     <row r="4" spans="2:42" ht="19.5" customHeight="1" thickBot="1">
-      <c r="B4" s="127"/>
-      <c r="C4" s="127"/>
-      <c r="D4" s="127"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
       <c r="F4" s="40">
         <v>1</v>
       </c>
@@ -24939,20 +24939,20 @@
       <c r="AJ4" s="58" t="s">
         <v>187</v>
       </c>
-      <c r="AL4" s="139"/>
-      <c r="AM4" s="139"/>
-      <c r="AN4" s="139"/>
-      <c r="AO4" s="139"/>
-      <c r="AP4" s="139"/>
+      <c r="AL4" s="116"/>
+      <c r="AM4" s="116"/>
+      <c r="AN4" s="116"/>
+      <c r="AO4" s="116"/>
+      <c r="AP4" s="116"/>
     </row>
     <row r="5" spans="2:42" ht="18.75">
       <c r="B5" s="35">
         <v>1</v>
       </c>
-      <c r="C5" s="126" t="s">
+      <c r="C5" s="142" t="s">
         <v>94</v>
       </c>
-      <c r="D5" s="126"/>
+      <c r="D5" s="142"/>
       <c r="F5" s="84" t="s">
         <v>95</v>
       </c>
@@ -25069,10 +25069,10 @@
       <c r="B6" s="35">
         <v>2</v>
       </c>
-      <c r="C6" s="126" t="s">
+      <c r="C6" s="142" t="s">
         <v>99</v>
       </c>
-      <c r="D6" s="126"/>
+      <c r="D6" s="142"/>
       <c r="F6" s="75" t="s">
         <v>97</v>
       </c>
@@ -25189,10 +25189,10 @@
       <c r="B7" s="35">
         <v>3</v>
       </c>
-      <c r="C7" s="126" t="s">
+      <c r="C7" s="142" t="s">
         <v>100</v>
       </c>
-      <c r="D7" s="126"/>
+      <c r="D7" s="142"/>
       <c r="F7" s="75" t="s">
         <v>101</v>
       </c>
@@ -25309,10 +25309,10 @@
       <c r="B8" s="35">
         <v>4</v>
       </c>
-      <c r="C8" s="126" t="s">
+      <c r="C8" s="142" t="s">
         <v>103</v>
       </c>
-      <c r="D8" s="126"/>
+      <c r="D8" s="142"/>
       <c r="F8" s="75" t="s">
         <v>96</v>
       </c>
@@ -25460,10 +25460,10 @@
       <c r="AI9" s="18"/>
     </row>
     <row r="10" spans="2:42" ht="18.75">
-      <c r="C10" s="123" t="s">
+      <c r="C10" s="153" t="s">
         <v>188</v>
       </c>
-      <c r="D10" s="123"/>
+      <c r="D10" s="153"/>
       <c r="E10" s="34"/>
       <c r="F10" s="35">
         <f t="shared" ref="F10:AJ10" si="5">COUNTIF(F$5:F$8,"M*")</f>
@@ -25591,10 +25591,10 @@
       </c>
     </row>
     <row r="11" spans="2:42" ht="18.75">
-      <c r="C11" s="123" t="s">
+      <c r="C11" s="153" t="s">
         <v>189</v>
       </c>
-      <c r="D11" s="123"/>
+      <c r="D11" s="153"/>
       <c r="E11" s="34"/>
       <c r="F11" s="35">
         <f t="shared" ref="F11:AJ11" si="6">COUNTIF(F$5:F$8,"A*")</f>
@@ -25722,10 +25722,10 @@
       </c>
     </row>
     <row r="12" spans="2:42" ht="18.75">
-      <c r="C12" s="123" t="s">
+      <c r="C12" s="153" t="s">
         <v>77</v>
       </c>
-      <c r="D12" s="123"/>
+      <c r="D12" s="153"/>
       <c r="E12" s="34"/>
       <c r="F12" s="35">
         <f t="shared" ref="F12:AJ12" si="7">COUNTIF(F$5:F$8,"N*")</f>
@@ -25853,10 +25853,10 @@
       </c>
     </row>
     <row r="13" spans="2:42" ht="18.75">
-      <c r="C13" s="123" t="s">
+      <c r="C13" s="153" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="123"/>
+      <c r="D13" s="153"/>
       <c r="E13" s="34"/>
       <c r="F13" s="35">
         <f t="shared" ref="F13:AJ13" si="8">COUNTIF(F$5:F$8,"O*")</f>
@@ -25984,10 +25984,10 @@
       </c>
     </row>
     <row r="14" spans="2:42" ht="18.75">
-      <c r="C14" s="119" t="s">
+      <c r="C14" s="109" t="s">
         <v>190</v>
       </c>
-      <c r="D14" s="120"/>
+      <c r="D14" s="110"/>
       <c r="E14" s="34"/>
       <c r="F14" s="35">
         <f t="shared" ref="F14:AJ14" si="9">COUNTIF(F$5:F$8,"TR*")</f>
@@ -26115,10 +26115,10 @@
       </c>
     </row>
     <row r="15" spans="2:42" ht="18.75">
-      <c r="C15" s="119" t="s">
+      <c r="C15" s="109" t="s">
         <v>191</v>
       </c>
-      <c r="D15" s="120"/>
+      <c r="D15" s="110"/>
       <c r="E15" s="34"/>
       <c r="F15" s="35">
         <f t="shared" ref="F15:AJ15" si="10">COUNTIF(F$5:F$8,"ST*")</f>
@@ -26246,10 +26246,10 @@
       </c>
     </row>
     <row r="16" spans="2:42" ht="18.75">
-      <c r="C16" s="121" t="s">
+      <c r="C16" s="152" t="s">
         <v>192</v>
       </c>
-      <c r="D16" s="121"/>
+      <c r="D16" s="152"/>
       <c r="E16" s="36"/>
       <c r="F16" s="37">
         <f>F18-F19</f>
@@ -26380,43 +26380,43 @@
       <c r="C17" s="38"/>
       <c r="D17" s="38"/>
       <c r="E17" s="34"/>
-      <c r="F17" s="122"/>
-      <c r="G17" s="122"/>
-      <c r="H17" s="122"/>
-      <c r="I17" s="122"/>
-      <c r="J17" s="122"/>
-      <c r="K17" s="122"/>
-      <c r="L17" s="122"/>
-      <c r="M17" s="122"/>
-      <c r="N17" s="122"/>
-      <c r="O17" s="122"/>
-      <c r="P17" s="122"/>
-      <c r="Q17" s="122"/>
-      <c r="R17" s="122"/>
-      <c r="S17" s="122"/>
-      <c r="T17" s="122"/>
-      <c r="U17" s="122"/>
-      <c r="V17" s="122"/>
-      <c r="W17" s="122"/>
-      <c r="X17" s="122"/>
-      <c r="Y17" s="122"/>
-      <c r="Z17" s="122"/>
-      <c r="AA17" s="122"/>
-      <c r="AB17" s="122"/>
-      <c r="AC17" s="122"/>
-      <c r="AD17" s="122"/>
-      <c r="AE17" s="122"/>
-      <c r="AF17" s="122"/>
-      <c r="AG17" s="122"/>
-      <c r="AH17" s="122"/>
-      <c r="AI17" s="122"/>
-      <c r="AJ17" s="122"/>
+      <c r="F17" s="108"/>
+      <c r="G17" s="108"/>
+      <c r="H17" s="108"/>
+      <c r="I17" s="108"/>
+      <c r="J17" s="108"/>
+      <c r="K17" s="108"/>
+      <c r="L17" s="108"/>
+      <c r="M17" s="108"/>
+      <c r="N17" s="108"/>
+      <c r="O17" s="108"/>
+      <c r="P17" s="108"/>
+      <c r="Q17" s="108"/>
+      <c r="R17" s="108"/>
+      <c r="S17" s="108"/>
+      <c r="T17" s="108"/>
+      <c r="U17" s="108"/>
+      <c r="V17" s="108"/>
+      <c r="W17" s="108"/>
+      <c r="X17" s="108"/>
+      <c r="Y17" s="108"/>
+      <c r="Z17" s="108"/>
+      <c r="AA17" s="108"/>
+      <c r="AB17" s="108"/>
+      <c r="AC17" s="108"/>
+      <c r="AD17" s="108"/>
+      <c r="AE17" s="108"/>
+      <c r="AF17" s="108"/>
+      <c r="AG17" s="108"/>
+      <c r="AH17" s="108"/>
+      <c r="AI17" s="108"/>
+      <c r="AJ17" s="108"/>
     </row>
     <row r="18" spans="3:36" ht="18.75">
-      <c r="C18" s="123" t="s">
+      <c r="C18" s="153" t="s">
         <v>193</v>
       </c>
-      <c r="D18" s="123"/>
+      <c r="D18" s="153"/>
       <c r="E18" s="34"/>
       <c r="F18" s="39">
         <f>SUM(F10:F12)</f>
@@ -26543,10 +26543,10 @@
       </c>
     </row>
     <row r="19" spans="3:36" ht="18.75">
-      <c r="C19" s="123" t="s">
+      <c r="C19" s="153" t="s">
         <v>194</v>
       </c>
-      <c r="D19" s="123"/>
+      <c r="D19" s="153"/>
       <c r="E19" s="34"/>
       <c r="F19" s="35">
         <v>2</v>
@@ -26643,10 +26643,10 @@
       </c>
     </row>
     <row r="20" spans="3:36" ht="18.75">
-      <c r="C20" s="123" t="s">
+      <c r="C20" s="153" t="s">
         <v>195</v>
       </c>
-      <c r="D20" s="123"/>
+      <c r="D20" s="153"/>
       <c r="E20" s="34"/>
       <c r="F20" s="35">
         <f>SUM(F10,F11,F12,F13,F15)</f>
@@ -26774,110 +26774,110 @@
     </row>
     <row r="22" spans="3:36" ht="16.5" thickBot="1"/>
     <row r="23" spans="3:36" ht="16.5" thickBot="1">
-      <c r="F23" s="110" t="s">
+      <c r="F23" s="95" t="s">
         <v>196</v>
       </c>
-      <c r="G23" s="111"/>
-      <c r="H23" s="111"/>
-      <c r="I23" s="111"/>
-      <c r="J23" s="111"/>
-      <c r="K23" s="112"/>
+      <c r="G23" s="96"/>
+      <c r="H23" s="96"/>
+      <c r="I23" s="96"/>
+      <c r="J23" s="96"/>
+      <c r="K23" s="97"/>
     </row>
     <row r="24" spans="3:36">
       <c r="F24" s="80" t="s">
         <v>197</v>
       </c>
-      <c r="G24" s="113" t="s">
+      <c r="G24" s="106" t="s">
         <v>198</v>
       </c>
-      <c r="H24" s="113"/>
+      <c r="H24" s="106"/>
       <c r="I24" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="J24" s="94" t="s">
+      <c r="J24" s="98" t="s">
         <v>199</v>
       </c>
-      <c r="K24" s="95"/>
+      <c r="K24" s="99"/>
     </row>
     <row r="25" spans="3:36">
       <c r="F25" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="G25" s="114" t="s">
+      <c r="G25" s="107" t="s">
         <v>200</v>
       </c>
-      <c r="H25" s="114"/>
+      <c r="H25" s="107"/>
       <c r="I25" s="77" t="s">
         <v>201</v>
       </c>
-      <c r="J25" s="115" t="s">
+      <c r="J25" s="100" t="s">
         <v>202</v>
       </c>
-      <c r="K25" s="116"/>
+      <c r="K25" s="101"/>
     </row>
     <row r="26" spans="3:36">
       <c r="F26" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="G26" s="100" t="s">
+      <c r="G26" s="102" t="s">
         <v>203</v>
       </c>
-      <c r="H26" s="100"/>
+      <c r="H26" s="102"/>
       <c r="I26" s="78" t="s">
         <v>108</v>
       </c>
-      <c r="J26" s="100" t="s">
+      <c r="J26" s="102" t="s">
         <v>204</v>
       </c>
-      <c r="K26" s="101"/>
+      <c r="K26" s="103"/>
     </row>
     <row r="27" spans="3:36">
       <c r="F27" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="G27" s="105" t="s">
+      <c r="G27" s="111" t="s">
         <v>205</v>
       </c>
-      <c r="H27" s="105"/>
+      <c r="H27" s="111"/>
       <c r="I27" s="79" t="s">
         <v>206</v>
       </c>
-      <c r="J27" s="117" t="s">
+      <c r="J27" s="104" t="s">
         <v>207</v>
       </c>
-      <c r="K27" s="118"/>
+      <c r="K27" s="105"/>
     </row>
     <row r="28" spans="3:36">
       <c r="F28" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="G28" s="105" t="s">
+      <c r="G28" s="111" t="s">
         <v>208</v>
       </c>
-      <c r="H28" s="105"/>
+      <c r="H28" s="111"/>
       <c r="I28" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="J28" s="106" t="s">
+      <c r="J28" s="93" t="s">
         <v>209</v>
       </c>
-      <c r="K28" s="107"/>
+      <c r="K28" s="94"/>
     </row>
     <row r="29" spans="3:36">
       <c r="F29" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="G29" s="108" t="s">
+      <c r="G29" s="92" t="s">
         <v>210</v>
       </c>
-      <c r="H29" s="108"/>
+      <c r="H29" s="92"/>
       <c r="I29" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="J29" s="106" t="s">
+      <c r="J29" s="93" t="s">
         <v>211</v>
       </c>
-      <c r="K29" s="107"/>
+      <c r="K29" s="94"/>
       <c r="R29" s="16" t="s">
         <v>187</v>
       </c>
@@ -26886,59 +26886,36 @@
       <c r="F30" s="82" t="s">
         <v>212</v>
       </c>
-      <c r="G30" s="109" t="s">
+      <c r="G30" s="123" t="s">
         <v>213</v>
       </c>
-      <c r="H30" s="109"/>
+      <c r="H30" s="123"/>
       <c r="I30" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="J30" s="106" t="s">
+      <c r="J30" s="93" t="s">
         <v>214</v>
       </c>
-      <c r="K30" s="107"/>
+      <c r="K30" s="94"/>
     </row>
     <row r="31" spans="3:36" ht="16.5" thickBot="1">
       <c r="F31" s="55" t="s">
         <v>215</v>
       </c>
-      <c r="G31" s="92" t="s">
+      <c r="G31" s="124" t="s">
         <v>216</v>
       </c>
-      <c r="H31" s="92"/>
+      <c r="H31" s="124"/>
       <c r="I31" s="56" t="s">
         <v>167</v>
       </c>
-      <c r="J31" s="92" t="s">
+      <c r="J31" s="124" t="s">
         <v>217</v>
       </c>
-      <c r="K31" s="93"/>
+      <c r="K31" s="125"/>
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="F23:K23"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="B3:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C6:D6"/>
     <mergeCell ref="J30:K30"/>
     <mergeCell ref="G31:H31"/>
     <mergeCell ref="J31:K31"/>
@@ -26955,6 +26932,29 @@
     <mergeCell ref="G30:H30"/>
     <mergeCell ref="G24:H24"/>
     <mergeCell ref="G25:H25"/>
+    <mergeCell ref="B3:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="F23:K23"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F5:AJ8">
@@ -27011,61 +27011,61 @@
   <sheetData>
     <row r="1" spans="2:42" ht="16.5" thickBot="1"/>
     <row r="2" spans="2:42" ht="39" customHeight="1" thickBot="1">
-      <c r="F2" s="134" t="s">
+      <c r="F2" s="139" t="s">
         <v>218</v>
       </c>
-      <c r="G2" s="135"/>
-      <c r="H2" s="135"/>
-      <c r="I2" s="135"/>
-      <c r="J2" s="135"/>
-      <c r="K2" s="135"/>
-      <c r="L2" s="135"/>
-      <c r="M2" s="135"/>
-      <c r="N2" s="135"/>
-      <c r="O2" s="135"/>
-      <c r="P2" s="135"/>
-      <c r="Q2" s="135"/>
-      <c r="R2" s="135"/>
-      <c r="S2" s="135"/>
-      <c r="T2" s="135"/>
-      <c r="U2" s="135"/>
-      <c r="V2" s="135"/>
-      <c r="W2" s="135"/>
-      <c r="X2" s="135"/>
-      <c r="Y2" s="135"/>
-      <c r="Z2" s="135"/>
-      <c r="AA2" s="135"/>
-      <c r="AB2" s="135"/>
-      <c r="AC2" s="135"/>
-      <c r="AD2" s="135"/>
-      <c r="AE2" s="135"/>
-      <c r="AF2" s="135"/>
-      <c r="AG2" s="135"/>
-      <c r="AH2" s="135"/>
-      <c r="AI2" s="135"/>
-      <c r="AJ2" s="136"/>
-      <c r="AL2" s="137" t="s">
+      <c r="G2" s="140"/>
+      <c r="H2" s="140"/>
+      <c r="I2" s="140"/>
+      <c r="J2" s="140"/>
+      <c r="K2" s="140"/>
+      <c r="L2" s="140"/>
+      <c r="M2" s="140"/>
+      <c r="N2" s="140"/>
+      <c r="O2" s="140"/>
+      <c r="P2" s="140"/>
+      <c r="Q2" s="140"/>
+      <c r="R2" s="140"/>
+      <c r="S2" s="140"/>
+      <c r="T2" s="140"/>
+      <c r="U2" s="140"/>
+      <c r="V2" s="140"/>
+      <c r="W2" s="140"/>
+      <c r="X2" s="140"/>
+      <c r="Y2" s="140"/>
+      <c r="Z2" s="140"/>
+      <c r="AA2" s="140"/>
+      <c r="AB2" s="140"/>
+      <c r="AC2" s="140"/>
+      <c r="AD2" s="140"/>
+      <c r="AE2" s="140"/>
+      <c r="AF2" s="140"/>
+      <c r="AG2" s="140"/>
+      <c r="AH2" s="140"/>
+      <c r="AI2" s="140"/>
+      <c r="AJ2" s="141"/>
+      <c r="AL2" s="114" t="s">
         <v>80</v>
       </c>
-      <c r="AM2" s="137" t="s">
+      <c r="AM2" s="114" t="s">
         <v>81</v>
       </c>
-      <c r="AN2" s="137" t="s">
+      <c r="AN2" s="114" t="s">
         <v>82</v>
       </c>
-      <c r="AO2" s="137" t="s">
+      <c r="AO2" s="114" t="s">
         <v>83</v>
       </c>
-      <c r="AP2" s="137" t="s">
+      <c r="AP2" s="114" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="3" spans="2:42" ht="39.75" thickBot="1">
-      <c r="B3" s="127" t="s">
+      <c r="B3" s="122" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="127"/>
-      <c r="D3" s="127"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="122"/>
       <c r="F3" s="43" t="s">
         <v>86</v>
       </c>
@@ -27157,16 +27157,16 @@
         <v>87</v>
       </c>
       <c r="AJ3" s="43"/>
-      <c r="AL3" s="138"/>
-      <c r="AM3" s="138"/>
-      <c r="AN3" s="138"/>
-      <c r="AO3" s="138"/>
-      <c r="AP3" s="138"/>
+      <c r="AL3" s="115"/>
+      <c r="AM3" s="115"/>
+      <c r="AN3" s="115"/>
+      <c r="AO3" s="115"/>
+      <c r="AP3" s="115"/>
     </row>
     <row r="4" spans="2:42" ht="19.5" customHeight="1" thickBot="1">
-      <c r="B4" s="127"/>
-      <c r="C4" s="127"/>
-      <c r="D4" s="127"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
       <c r="F4" s="40">
         <v>1</v>
       </c>
@@ -27260,20 +27260,20 @@
       <c r="AJ4" s="58" t="s">
         <v>187</v>
       </c>
-      <c r="AL4" s="139"/>
-      <c r="AM4" s="139"/>
-      <c r="AN4" s="139"/>
-      <c r="AO4" s="139"/>
-      <c r="AP4" s="139"/>
+      <c r="AL4" s="116"/>
+      <c r="AM4" s="116"/>
+      <c r="AN4" s="116"/>
+      <c r="AO4" s="116"/>
+      <c r="AP4" s="116"/>
     </row>
     <row r="5" spans="2:42" ht="18.75">
       <c r="B5" s="35">
         <v>1</v>
       </c>
-      <c r="C5" s="126" t="s">
+      <c r="C5" s="142" t="s">
         <v>105</v>
       </c>
-      <c r="D5" s="126"/>
+      <c r="D5" s="142"/>
       <c r="F5" s="90" t="s">
         <v>106</v>
       </c>
@@ -27390,10 +27390,10 @@
       <c r="B6" s="35">
         <v>2</v>
       </c>
-      <c r="C6" s="126" t="s">
+      <c r="C6" s="142" t="s">
         <v>109</v>
       </c>
-      <c r="D6" s="126"/>
+      <c r="D6" s="142"/>
       <c r="F6" s="75" t="s">
         <v>96</v>
       </c>
@@ -27510,10 +27510,10 @@
       <c r="B7" s="35">
         <v>3</v>
       </c>
-      <c r="C7" s="126" t="s">
+      <c r="C7" s="142" t="s">
         <v>110</v>
       </c>
-      <c r="D7" s="126"/>
+      <c r="D7" s="142"/>
       <c r="F7" s="75" t="s">
         <v>95</v>
       </c>
@@ -27630,10 +27630,10 @@
       <c r="B8" s="35">
         <v>4</v>
       </c>
-      <c r="C8" s="126" t="s">
+      <c r="C8" s="142" t="s">
         <v>111</v>
       </c>
-      <c r="D8" s="126"/>
+      <c r="D8" s="142"/>
       <c r="F8" s="75" t="s">
         <v>107</v>
       </c>
@@ -27750,10 +27750,10 @@
       <c r="B9" s="35">
         <v>5</v>
       </c>
-      <c r="C9" s="126" t="s">
+      <c r="C9" s="142" t="s">
         <v>112</v>
       </c>
-      <c r="D9" s="126"/>
+      <c r="D9" s="142"/>
       <c r="F9" s="75" t="s">
         <v>108</v>
       </c>
@@ -27871,10 +27871,10 @@
       <c r="B10" s="35">
         <v>6</v>
       </c>
-      <c r="C10" s="126" t="s">
+      <c r="C10" s="142" t="s">
         <v>113</v>
       </c>
-      <c r="D10" s="126"/>
+      <c r="D10" s="142"/>
       <c r="F10" s="88" t="s">
         <v>95</v>
       </c>
@@ -28022,10 +28022,10 @@
       <c r="AI11" s="18"/>
     </row>
     <row r="12" spans="2:42" ht="18.75">
-      <c r="C12" s="123" t="s">
+      <c r="C12" s="153" t="s">
         <v>188</v>
       </c>
-      <c r="D12" s="123"/>
+      <c r="D12" s="153"/>
       <c r="E12" s="34"/>
       <c r="F12" s="35">
         <f>COUNTIF(F$5:F$9,"M*")</f>
@@ -28153,10 +28153,10 @@
       </c>
     </row>
     <row r="13" spans="2:42" ht="18.75">
-      <c r="C13" s="123" t="s">
+      <c r="C13" s="153" t="s">
         <v>189</v>
       </c>
-      <c r="D13" s="123"/>
+      <c r="D13" s="153"/>
       <c r="E13" s="34"/>
       <c r="F13" s="35">
         <f>COUNTIF(F$5:F$9,"A*")</f>
@@ -28284,10 +28284,10 @@
       </c>
     </row>
     <row r="14" spans="2:42" ht="18.75">
-      <c r="C14" s="123" t="s">
+      <c r="C14" s="153" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="123"/>
+      <c r="D14" s="153"/>
       <c r="E14" s="34"/>
       <c r="F14" s="35">
         <f>COUNTIF(F$5:F$9,"N*")</f>
@@ -28415,10 +28415,10 @@
       </c>
     </row>
     <row r="15" spans="2:42" ht="18.75">
-      <c r="C15" s="123" t="s">
+      <c r="C15" s="153" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="123"/>
+      <c r="D15" s="153"/>
       <c r="E15" s="34"/>
       <c r="F15" s="35">
         <f t="shared" ref="F15:AJ15" si="8">COUNTIF(F$5:F$10,"O*")</f>
@@ -28546,10 +28546,10 @@
       </c>
     </row>
     <row r="16" spans="2:42" ht="18.75">
-      <c r="C16" s="119" t="s">
+      <c r="C16" s="109" t="s">
         <v>190</v>
       </c>
-      <c r="D16" s="120"/>
+      <c r="D16" s="110"/>
       <c r="E16" s="34"/>
       <c r="F16" s="35">
         <f t="shared" ref="F16:AJ16" si="9">COUNTIF(F$5:F$10,"TR*")</f>
@@ -28677,10 +28677,10 @@
       </c>
     </row>
     <row r="17" spans="3:36" ht="18.75">
-      <c r="C17" s="119" t="s">
+      <c r="C17" s="109" t="s">
         <v>191</v>
       </c>
-      <c r="D17" s="120"/>
+      <c r="D17" s="110"/>
       <c r="E17" s="34"/>
       <c r="F17" s="35">
         <f t="shared" ref="F17:AJ17" si="10">COUNTIF(F$5:F$10,"ST*")</f>
@@ -28808,10 +28808,10 @@
       </c>
     </row>
     <row r="18" spans="3:36" ht="18.75">
-      <c r="C18" s="121" t="s">
+      <c r="C18" s="152" t="s">
         <v>192</v>
       </c>
-      <c r="D18" s="121"/>
+      <c r="D18" s="152"/>
       <c r="E18" s="36"/>
       <c r="F18" s="37">
         <f>F20-F21</f>
@@ -28942,43 +28942,43 @@
       <c r="C19" s="38"/>
       <c r="D19" s="38"/>
       <c r="E19" s="34"/>
-      <c r="F19" s="122"/>
-      <c r="G19" s="122"/>
-      <c r="H19" s="122"/>
-      <c r="I19" s="122"/>
-      <c r="J19" s="122"/>
-      <c r="K19" s="122"/>
-      <c r="L19" s="122"/>
-      <c r="M19" s="122"/>
-      <c r="N19" s="122"/>
-      <c r="O19" s="122"/>
-      <c r="P19" s="122"/>
-      <c r="Q19" s="122"/>
-      <c r="R19" s="122"/>
-      <c r="S19" s="122"/>
-      <c r="T19" s="122"/>
-      <c r="U19" s="122"/>
-      <c r="V19" s="122"/>
-      <c r="W19" s="122"/>
-      <c r="X19" s="122"/>
-      <c r="Y19" s="122"/>
-      <c r="Z19" s="122"/>
-      <c r="AA19" s="122"/>
-      <c r="AB19" s="122"/>
-      <c r="AC19" s="122"/>
-      <c r="AD19" s="122"/>
-      <c r="AE19" s="122"/>
-      <c r="AF19" s="122"/>
-      <c r="AG19" s="122"/>
-      <c r="AH19" s="122"/>
-      <c r="AI19" s="122"/>
-      <c r="AJ19" s="122"/>
+      <c r="F19" s="108"/>
+      <c r="G19" s="108"/>
+      <c r="H19" s="108"/>
+      <c r="I19" s="108"/>
+      <c r="J19" s="108"/>
+      <c r="K19" s="108"/>
+      <c r="L19" s="108"/>
+      <c r="M19" s="108"/>
+      <c r="N19" s="108"/>
+      <c r="O19" s="108"/>
+      <c r="P19" s="108"/>
+      <c r="Q19" s="108"/>
+      <c r="R19" s="108"/>
+      <c r="S19" s="108"/>
+      <c r="T19" s="108"/>
+      <c r="U19" s="108"/>
+      <c r="V19" s="108"/>
+      <c r="W19" s="108"/>
+      <c r="X19" s="108"/>
+      <c r="Y19" s="108"/>
+      <c r="Z19" s="108"/>
+      <c r="AA19" s="108"/>
+      <c r="AB19" s="108"/>
+      <c r="AC19" s="108"/>
+      <c r="AD19" s="108"/>
+      <c r="AE19" s="108"/>
+      <c r="AF19" s="108"/>
+      <c r="AG19" s="108"/>
+      <c r="AH19" s="108"/>
+      <c r="AI19" s="108"/>
+      <c r="AJ19" s="108"/>
     </row>
     <row r="20" spans="3:36" ht="18.75">
-      <c r="C20" s="123" t="s">
+      <c r="C20" s="153" t="s">
         <v>193</v>
       </c>
-      <c r="D20" s="123"/>
+      <c r="D20" s="153"/>
       <c r="E20" s="34"/>
       <c r="F20" s="39">
         <f>SUM(F12:F14)</f>
@@ -29105,10 +29105,10 @@
       </c>
     </row>
     <row r="21" spans="3:36" ht="18.75">
-      <c r="C21" s="123" t="s">
+      <c r="C21" s="153" t="s">
         <v>194</v>
       </c>
-      <c r="D21" s="123"/>
+      <c r="D21" s="153"/>
       <c r="E21" s="34"/>
       <c r="F21" s="35">
         <v>3</v>
@@ -29205,10 +29205,10 @@
       </c>
     </row>
     <row r="22" spans="3:36" ht="18.75">
-      <c r="C22" s="123" t="s">
+      <c r="C22" s="153" t="s">
         <v>195</v>
       </c>
-      <c r="D22" s="123"/>
+      <c r="D22" s="153"/>
       <c r="E22" s="34"/>
       <c r="F22" s="35">
         <f>SUM(F12,F13,F14,F15,F17)</f>
@@ -29336,271 +29336,315 @@
     </row>
     <row r="24" spans="3:36" ht="16.5" thickBot="1">
       <c r="F24" s="48"/>
-      <c r="G24" s="150"/>
-      <c r="H24" s="150"/>
-      <c r="J24" s="149"/>
-      <c r="K24" s="149"/>
+      <c r="G24" s="155"/>
+      <c r="H24" s="155"/>
+      <c r="J24" s="154"/>
+      <c r="K24" s="154"/>
     </row>
     <row r="25" spans="3:36" ht="16.5" thickBot="1">
-      <c r="F25" s="110" t="s">
+      <c r="F25" s="95" t="s">
         <v>196</v>
       </c>
-      <c r="G25" s="111"/>
-      <c r="H25" s="111"/>
-      <c r="I25" s="111"/>
-      <c r="J25" s="111"/>
-      <c r="K25" s="112"/>
-      <c r="M25" s="110" t="s">
+      <c r="G25" s="96"/>
+      <c r="H25" s="96"/>
+      <c r="I25" s="96"/>
+      <c r="J25" s="96"/>
+      <c r="K25" s="97"/>
+      <c r="M25" s="95" t="s">
         <v>196</v>
       </c>
-      <c r="N25" s="111"/>
-      <c r="O25" s="111"/>
-      <c r="P25" s="111"/>
-      <c r="Q25" s="111"/>
-      <c r="R25" s="112"/>
+      <c r="N25" s="96"/>
+      <c r="O25" s="96"/>
+      <c r="P25" s="96"/>
+      <c r="Q25" s="96"/>
+      <c r="R25" s="97"/>
     </row>
     <row r="26" spans="3:36">
       <c r="F26" s="80" t="s">
         <v>197</v>
       </c>
-      <c r="G26" s="113" t="s">
+      <c r="G26" s="106" t="s">
         <v>198</v>
       </c>
-      <c r="H26" s="113"/>
+      <c r="H26" s="106"/>
       <c r="I26" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="J26" s="94" t="s">
+      <c r="J26" s="98" t="s">
         <v>199</v>
       </c>
-      <c r="K26" s="95"/>
+      <c r="K26" s="99"/>
       <c r="M26" s="80" t="s">
         <v>197</v>
       </c>
-      <c r="N26" s="113" t="s">
+      <c r="N26" s="106" t="s">
         <v>198</v>
       </c>
-      <c r="O26" s="113"/>
+      <c r="O26" s="106"/>
       <c r="P26" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="Q26" s="94" t="s">
+      <c r="Q26" s="98" t="s">
         <v>199</v>
       </c>
-      <c r="R26" s="95"/>
+      <c r="R26" s="99"/>
     </row>
     <row r="27" spans="3:36">
       <c r="F27" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="G27" s="114" t="s">
+      <c r="G27" s="107" t="s">
         <v>200</v>
       </c>
-      <c r="H27" s="114"/>
+      <c r="H27" s="107"/>
       <c r="I27" s="77" t="s">
         <v>201</v>
       </c>
-      <c r="J27" s="115" t="s">
+      <c r="J27" s="100" t="s">
         <v>202</v>
       </c>
-      <c r="K27" s="116"/>
+      <c r="K27" s="101"/>
       <c r="M27" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="N27" s="114" t="s">
+      <c r="N27" s="107" t="s">
         <v>200</v>
       </c>
-      <c r="O27" s="114"/>
+      <c r="O27" s="107"/>
       <c r="P27" s="77" t="s">
         <v>201</v>
       </c>
-      <c r="Q27" s="115" t="s">
+      <c r="Q27" s="100" t="s">
         <v>202</v>
       </c>
-      <c r="R27" s="116"/>
+      <c r="R27" s="101"/>
     </row>
     <row r="28" spans="3:36">
       <c r="F28" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="G28" s="100" t="s">
+      <c r="G28" s="102" t="s">
         <v>203</v>
       </c>
-      <c r="H28" s="100"/>
+      <c r="H28" s="102"/>
       <c r="I28" s="78" t="s">
         <v>108</v>
       </c>
-      <c r="J28" s="100" t="s">
+      <c r="J28" s="102" t="s">
         <v>204</v>
       </c>
-      <c r="K28" s="101"/>
+      <c r="K28" s="103"/>
       <c r="M28" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="N28" s="100" t="s">
+      <c r="N28" s="102" t="s">
         <v>203</v>
       </c>
-      <c r="O28" s="100"/>
+      <c r="O28" s="102"/>
       <c r="P28" s="78" t="s">
         <v>108</v>
       </c>
-      <c r="Q28" s="100" t="s">
+      <c r="Q28" s="102" t="s">
         <v>204</v>
       </c>
-      <c r="R28" s="101"/>
+      <c r="R28" s="103"/>
     </row>
     <row r="29" spans="3:36">
       <c r="F29" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="G29" s="105" t="s">
+      <c r="G29" s="111" t="s">
         <v>205</v>
       </c>
-      <c r="H29" s="105"/>
+      <c r="H29" s="111"/>
       <c r="I29" s="79" t="s">
         <v>206</v>
       </c>
-      <c r="J29" s="117" t="s">
+      <c r="J29" s="104" t="s">
         <v>207</v>
       </c>
-      <c r="K29" s="118"/>
+      <c r="K29" s="105"/>
       <c r="M29" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="N29" s="105" t="s">
+      <c r="N29" s="111" t="s">
         <v>205</v>
       </c>
-      <c r="O29" s="105"/>
+      <c r="O29" s="111"/>
       <c r="P29" s="79" t="s">
         <v>206</v>
       </c>
-      <c r="Q29" s="117" t="s">
+      <c r="Q29" s="104" t="s">
         <v>207</v>
       </c>
-      <c r="R29" s="118"/>
+      <c r="R29" s="105"/>
     </row>
     <row r="30" spans="3:36">
       <c r="F30" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="G30" s="105" t="s">
+      <c r="G30" s="111" t="s">
         <v>208</v>
       </c>
-      <c r="H30" s="105"/>
+      <c r="H30" s="111"/>
       <c r="I30" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="J30" s="106" t="s">
+      <c r="J30" s="93" t="s">
         <v>209</v>
       </c>
-      <c r="K30" s="107"/>
+      <c r="K30" s="94"/>
       <c r="M30" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="N30" s="105" t="s">
+      <c r="N30" s="111" t="s">
         <v>208</v>
       </c>
-      <c r="O30" s="105"/>
+      <c r="O30" s="111"/>
       <c r="P30" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="Q30" s="106" t="s">
+      <c r="Q30" s="93" t="s">
         <v>209</v>
       </c>
-      <c r="R30" s="107"/>
+      <c r="R30" s="94"/>
     </row>
     <row r="31" spans="3:36">
       <c r="F31" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="G31" s="108" t="s">
+      <c r="G31" s="92" t="s">
         <v>210</v>
       </c>
-      <c r="H31" s="108"/>
+      <c r="H31" s="92"/>
       <c r="I31" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="J31" s="106" t="s">
+      <c r="J31" s="93" t="s">
         <v>211</v>
       </c>
-      <c r="K31" s="107"/>
+      <c r="K31" s="94"/>
       <c r="M31" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="N31" s="108" t="s">
+      <c r="N31" s="92" t="s">
         <v>210</v>
       </c>
-      <c r="O31" s="108"/>
+      <c r="O31" s="92"/>
       <c r="P31" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="Q31" s="106" t="s">
+      <c r="Q31" s="93" t="s">
         <v>211</v>
       </c>
-      <c r="R31" s="107"/>
+      <c r="R31" s="94"/>
     </row>
     <row r="32" spans="3:36">
       <c r="F32" s="82" t="s">
         <v>212</v>
       </c>
-      <c r="G32" s="109" t="s">
+      <c r="G32" s="123" t="s">
         <v>213</v>
       </c>
-      <c r="H32" s="109"/>
+      <c r="H32" s="123"/>
       <c r="I32" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="J32" s="106" t="s">
+      <c r="J32" s="93" t="s">
         <v>214</v>
       </c>
-      <c r="K32" s="107"/>
+      <c r="K32" s="94"/>
       <c r="M32" s="82" t="s">
         <v>212</v>
       </c>
-      <c r="N32" s="109" t="s">
+      <c r="N32" s="123" t="s">
         <v>213</v>
       </c>
-      <c r="O32" s="109"/>
+      <c r="O32" s="123"/>
       <c r="P32" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="Q32" s="106" t="s">
+      <c r="Q32" s="93" t="s">
         <v>214</v>
       </c>
-      <c r="R32" s="107"/>
+      <c r="R32" s="94"/>
     </row>
     <row r="33" spans="6:18" ht="16.5" thickBot="1">
       <c r="F33" s="55" t="s">
         <v>215</v>
       </c>
-      <c r="G33" s="92" t="s">
+      <c r="G33" s="124" t="s">
         <v>216</v>
       </c>
-      <c r="H33" s="92"/>
+      <c r="H33" s="124"/>
       <c r="I33" s="56" t="s">
         <v>167</v>
       </c>
-      <c r="J33" s="92" t="s">
+      <c r="J33" s="124" t="s">
         <v>217</v>
       </c>
-      <c r="K33" s="93"/>
+      <c r="K33" s="125"/>
       <c r="M33" s="55" t="s">
         <v>215</v>
       </c>
-      <c r="N33" s="92" t="s">
+      <c r="N33" s="124" t="s">
         <v>216</v>
       </c>
-      <c r="O33" s="92"/>
+      <c r="O33" s="124"/>
       <c r="P33" s="56" t="s">
         <v>167</v>
       </c>
-      <c r="Q33" s="92" t="s">
+      <c r="Q33" s="124" t="s">
         <v>217</v>
       </c>
-      <c r="R33" s="93"/>
+      <c r="R33" s="125"/>
     </row>
   </sheetData>
   <mergeCells count="60">
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B3:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="AP2:AP4"/>
+    <mergeCell ref="F2:AJ2"/>
+    <mergeCell ref="AL2:AL4"/>
+    <mergeCell ref="AM2:AM4"/>
+    <mergeCell ref="AN2:AN4"/>
+    <mergeCell ref="AO2:AO4"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="F19:AJ19"/>
+    <mergeCell ref="F25:K25"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G24:H24"/>
     <mergeCell ref="N32:O32"/>
     <mergeCell ref="Q32:R32"/>
     <mergeCell ref="N33:O33"/>
@@ -29617,50 +29661,6 @@
     <mergeCell ref="N30:O30"/>
     <mergeCell ref="Q30:R30"/>
     <mergeCell ref="N31:O31"/>
-    <mergeCell ref="Q31:R31"/>
-    <mergeCell ref="F19:AJ19"/>
-    <mergeCell ref="F25:K25"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="AP2:AP4"/>
-    <mergeCell ref="F2:AJ2"/>
-    <mergeCell ref="AL2:AL4"/>
-    <mergeCell ref="AM2:AM4"/>
-    <mergeCell ref="AN2:AN4"/>
-    <mergeCell ref="AO2:AO4"/>
-    <mergeCell ref="B3:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="J31:K31"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F5:AJ10">
@@ -29708,61 +29708,61 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:42" ht="39" customHeight="1" thickBot="1">
-      <c r="F2" s="157" t="s">
+      <c r="F2" s="162" t="s">
         <v>219</v>
       </c>
-      <c r="G2" s="157"/>
-      <c r="H2" s="157"/>
-      <c r="I2" s="157"/>
-      <c r="J2" s="157"/>
-      <c r="K2" s="157"/>
-      <c r="L2" s="157"/>
-      <c r="M2" s="157"/>
-      <c r="N2" s="157"/>
-      <c r="O2" s="157"/>
-      <c r="P2" s="157"/>
-      <c r="Q2" s="157"/>
-      <c r="R2" s="157"/>
-      <c r="S2" s="157"/>
-      <c r="T2" s="157"/>
-      <c r="U2" s="157"/>
-      <c r="V2" s="157"/>
-      <c r="W2" s="157"/>
-      <c r="X2" s="157"/>
-      <c r="Y2" s="157"/>
-      <c r="Z2" s="157"/>
-      <c r="AA2" s="157"/>
-      <c r="AB2" s="157"/>
-      <c r="AC2" s="157"/>
-      <c r="AD2" s="157"/>
-      <c r="AE2" s="157"/>
-      <c r="AF2" s="157"/>
-      <c r="AG2" s="157"/>
-      <c r="AH2" s="157"/>
-      <c r="AI2" s="157"/>
-      <c r="AJ2" s="157"/>
-      <c r="AL2" s="137" t="s">
+      <c r="G2" s="162"/>
+      <c r="H2" s="162"/>
+      <c r="I2" s="162"/>
+      <c r="J2" s="162"/>
+      <c r="K2" s="162"/>
+      <c r="L2" s="162"/>
+      <c r="M2" s="162"/>
+      <c r="N2" s="162"/>
+      <c r="O2" s="162"/>
+      <c r="P2" s="162"/>
+      <c r="Q2" s="162"/>
+      <c r="R2" s="162"/>
+      <c r="S2" s="162"/>
+      <c r="T2" s="162"/>
+      <c r="U2" s="162"/>
+      <c r="V2" s="162"/>
+      <c r="W2" s="162"/>
+      <c r="X2" s="162"/>
+      <c r="Y2" s="162"/>
+      <c r="Z2" s="162"/>
+      <c r="AA2" s="162"/>
+      <c r="AB2" s="162"/>
+      <c r="AC2" s="162"/>
+      <c r="AD2" s="162"/>
+      <c r="AE2" s="162"/>
+      <c r="AF2" s="162"/>
+      <c r="AG2" s="162"/>
+      <c r="AH2" s="162"/>
+      <c r="AI2" s="162"/>
+      <c r="AJ2" s="162"/>
+      <c r="AL2" s="114" t="s">
         <v>80</v>
       </c>
-      <c r="AM2" s="137" t="s">
+      <c r="AM2" s="114" t="s">
         <v>81</v>
       </c>
-      <c r="AN2" s="137" t="s">
+      <c r="AN2" s="114" t="s">
         <v>82</v>
       </c>
-      <c r="AO2" s="137" t="s">
+      <c r="AO2" s="114" t="s">
         <v>83</v>
       </c>
-      <c r="AP2" s="137" t="s">
+      <c r="AP2" s="114" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="3" spans="2:42" ht="39.75" thickBot="1">
-      <c r="B3" s="151" t="s">
+      <c r="B3" s="156" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="152"/>
-      <c r="D3" s="153"/>
+      <c r="C3" s="157"/>
+      <c r="D3" s="158"/>
       <c r="F3" s="62" t="s">
         <v>86</v>
       </c>
@@ -29854,16 +29854,16 @@
         <v>87</v>
       </c>
       <c r="AJ3" s="62"/>
-      <c r="AL3" s="138"/>
-      <c r="AM3" s="138"/>
-      <c r="AN3" s="138"/>
-      <c r="AO3" s="138"/>
-      <c r="AP3" s="138"/>
+      <c r="AL3" s="115"/>
+      <c r="AM3" s="115"/>
+      <c r="AN3" s="115"/>
+      <c r="AO3" s="115"/>
+      <c r="AP3" s="115"/>
     </row>
     <row r="4" spans="2:42" ht="19.5" customHeight="1" thickBot="1">
-      <c r="B4" s="154"/>
-      <c r="C4" s="155"/>
-      <c r="D4" s="156"/>
+      <c r="B4" s="159"/>
+      <c r="C4" s="160"/>
+      <c r="D4" s="161"/>
       <c r="F4" s="59">
         <v>1</v>
       </c>
@@ -29955,20 +29955,20 @@
         <v>30</v>
       </c>
       <c r="AJ4" s="61"/>
-      <c r="AL4" s="139"/>
-      <c r="AM4" s="139"/>
-      <c r="AN4" s="139"/>
-      <c r="AO4" s="139"/>
-      <c r="AP4" s="139"/>
+      <c r="AL4" s="116"/>
+      <c r="AM4" s="116"/>
+      <c r="AN4" s="116"/>
+      <c r="AO4" s="116"/>
+      <c r="AP4" s="116"/>
     </row>
     <row r="5" spans="2:42" ht="18.75">
       <c r="B5" s="47">
         <v>1</v>
       </c>
-      <c r="C5" s="128" t="s">
+      <c r="C5" s="144" t="s">
         <v>115</v>
       </c>
-      <c r="D5" s="129"/>
+      <c r="D5" s="145"/>
       <c r="F5" s="72" t="s">
         <v>101</v>
       </c>
@@ -30085,10 +30085,10 @@
       <c r="B6" s="45">
         <v>2</v>
       </c>
-      <c r="C6" s="126" t="s">
+      <c r="C6" s="142" t="s">
         <v>117</v>
       </c>
-      <c r="D6" s="133"/>
+      <c r="D6" s="143"/>
       <c r="F6" s="74" t="s">
         <v>102</v>
       </c>
@@ -30205,10 +30205,10 @@
       <c r="B7" s="45">
         <v>3</v>
       </c>
-      <c r="C7" s="126" t="s">
+      <c r="C7" s="142" t="s">
         <v>118</v>
       </c>
-      <c r="D7" s="133"/>
+      <c r="D7" s="143"/>
       <c r="F7" s="75" t="s">
         <v>95</v>
       </c>
@@ -30325,10 +30325,10 @@
       <c r="B8" s="45">
         <v>4</v>
       </c>
-      <c r="C8" s="126" t="s">
+      <c r="C8" s="142" t="s">
         <v>119</v>
       </c>
-      <c r="D8" s="133"/>
+      <c r="D8" s="143"/>
       <c r="F8" s="75" t="s">
         <v>98</v>
       </c>
@@ -30445,10 +30445,10 @@
       <c r="B9" s="45">
         <v>5</v>
       </c>
-      <c r="C9" s="126" t="s">
+      <c r="C9" s="142" t="s">
         <v>120</v>
       </c>
-      <c r="D9" s="133"/>
+      <c r="D9" s="143"/>
       <c r="F9" s="75" t="s">
         <v>96</v>
       </c>
@@ -30565,10 +30565,10 @@
       <c r="B10" s="45">
         <v>6</v>
       </c>
-      <c r="C10" s="126" t="s">
+      <c r="C10" s="142" t="s">
         <v>121</v>
       </c>
-      <c r="D10" s="133"/>
+      <c r="D10" s="143"/>
       <c r="F10" s="75" t="s">
         <v>96</v>
       </c>
@@ -30685,10 +30685,10 @@
       <c r="B11" s="45">
         <v>7</v>
       </c>
-      <c r="C11" s="126" t="s">
+      <c r="C11" s="142" t="s">
         <v>122</v>
       </c>
-      <c r="D11" s="133"/>
+      <c r="D11" s="143"/>
       <c r="F11" s="75" t="s">
         <v>101</v>
       </c>
@@ -30805,10 +30805,10 @@
       <c r="B12" s="45">
         <v>8</v>
       </c>
-      <c r="C12" s="126" t="s">
+      <c r="C12" s="142" t="s">
         <v>123</v>
       </c>
-      <c r="D12" s="133"/>
+      <c r="D12" s="143"/>
       <c r="F12" s="75" t="s">
         <v>102</v>
       </c>
@@ -30925,10 +30925,10 @@
       <c r="B13" s="45">
         <v>9</v>
       </c>
-      <c r="C13" s="126" t="s">
+      <c r="C13" s="142" t="s">
         <v>124</v>
       </c>
-      <c r="D13" s="133"/>
+      <c r="D13" s="143"/>
       <c r="F13" s="74" t="s">
         <v>95</v>
       </c>
@@ -31045,10 +31045,10 @@
       <c r="B14" s="45">
         <v>10</v>
       </c>
-      <c r="C14" s="126" t="s">
+      <c r="C14" s="142" t="s">
         <v>125</v>
       </c>
-      <c r="D14" s="133"/>
+      <c r="D14" s="143"/>
       <c r="F14" s="75" t="s">
         <v>116</v>
       </c>
@@ -31165,10 +31165,10 @@
       <c r="B15" s="45">
         <v>11</v>
       </c>
-      <c r="C15" s="96" t="s">
+      <c r="C15" s="112" t="s">
         <v>126</v>
       </c>
-      <c r="D15" s="130"/>
+      <c r="D15" s="146"/>
       <c r="F15" s="75" t="s">
         <v>116</v>
       </c>
@@ -31285,10 +31285,10 @@
       <c r="B16" s="45">
         <v>12</v>
       </c>
-      <c r="C16" s="96" t="s">
+      <c r="C16" s="112" t="s">
         <v>127</v>
       </c>
-      <c r="D16" s="130"/>
+      <c r="D16" s="146"/>
       <c r="F16" s="75" t="s">
         <v>96</v>
       </c>
@@ -31405,10 +31405,10 @@
       <c r="B17" s="45">
         <v>13</v>
       </c>
-      <c r="C17" s="96" t="s">
+      <c r="C17" s="112" t="s">
         <v>128</v>
       </c>
-      <c r="D17" s="130"/>
+      <c r="D17" s="146"/>
       <c r="F17" s="75" t="s">
         <v>96</v>
       </c>
@@ -31525,10 +31525,10 @@
       <c r="B18" s="45">
         <v>14</v>
       </c>
-      <c r="C18" s="96" t="s">
+      <c r="C18" s="112" t="s">
         <v>129</v>
       </c>
-      <c r="D18" s="130"/>
+      <c r="D18" s="146"/>
       <c r="F18" s="75" t="s">
         <v>101</v>
       </c>
@@ -31645,10 +31645,10 @@
       <c r="B19" s="46">
         <v>15</v>
       </c>
-      <c r="C19" s="131" t="s">
+      <c r="C19" s="147" t="s">
         <v>130</v>
       </c>
-      <c r="D19" s="132"/>
+      <c r="D19" s="148"/>
       <c r="F19" s="74" t="s">
         <v>96</v>
       </c>
@@ -31796,10 +31796,10 @@
       <c r="AI20" s="18"/>
     </row>
     <row r="21" spans="2:42" ht="18.75">
-      <c r="C21" s="123" t="s">
+      <c r="C21" s="153" t="s">
         <v>188</v>
       </c>
-      <c r="D21" s="123"/>
+      <c r="D21" s="153"/>
       <c r="E21" s="34"/>
       <c r="F21" s="35">
         <f t="shared" ref="F21:AJ21" si="5">COUNTIF(F$5:F$19,"M*")</f>
@@ -31927,10 +31927,10 @@
       </c>
     </row>
     <row r="22" spans="2:42" ht="18.75">
-      <c r="C22" s="123" t="s">
+      <c r="C22" s="153" t="s">
         <v>189</v>
       </c>
-      <c r="D22" s="123"/>
+      <c r="D22" s="153"/>
       <c r="E22" s="34"/>
       <c r="F22" s="35">
         <f t="shared" ref="F22:AJ22" si="6">COUNTIF(F$5:F$19,"A*")</f>
@@ -32058,10 +32058,10 @@
       </c>
     </row>
     <row r="23" spans="2:42" ht="18.75">
-      <c r="C23" s="123" t="s">
+      <c r="C23" s="153" t="s">
         <v>77</v>
       </c>
-      <c r="D23" s="123"/>
+      <c r="D23" s="153"/>
       <c r="E23" s="34"/>
       <c r="F23" s="35">
         <f t="shared" ref="F23:AJ23" si="7">COUNTIF(F$5:F$19,"N*")</f>
@@ -32189,10 +32189,10 @@
       </c>
     </row>
     <row r="24" spans="2:42" ht="18.75">
-      <c r="C24" s="123" t="s">
+      <c r="C24" s="153" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="123"/>
+      <c r="D24" s="153"/>
       <c r="E24" s="34"/>
       <c r="F24" s="35">
         <f t="shared" ref="F24:AJ24" si="8">COUNTIF(F$5:F$19,"O*")</f>
@@ -32320,10 +32320,10 @@
       </c>
     </row>
     <row r="25" spans="2:42" ht="18.75">
-      <c r="C25" s="119" t="s">
+      <c r="C25" s="109" t="s">
         <v>191</v>
       </c>
-      <c r="D25" s="120"/>
+      <c r="D25" s="110"/>
       <c r="E25" s="34"/>
       <c r="F25" s="35">
         <f t="shared" ref="F25:AJ25" si="9">COUNTIF(F$5:F$19,"ST*")</f>
@@ -32451,10 +32451,10 @@
       </c>
     </row>
     <row r="26" spans="2:42" ht="18.75">
-      <c r="C26" s="121" t="s">
+      <c r="C26" s="152" t="s">
         <v>192</v>
       </c>
-      <c r="D26" s="121"/>
+      <c r="D26" s="152"/>
       <c r="E26" s="36"/>
       <c r="F26" s="37">
         <f>F28-F29</f>
@@ -32582,43 +32582,43 @@
       <c r="C27" s="38"/>
       <c r="D27" s="38"/>
       <c r="E27" s="34"/>
-      <c r="F27" s="122"/>
-      <c r="G27" s="122"/>
-      <c r="H27" s="122"/>
-      <c r="I27" s="122"/>
-      <c r="J27" s="122"/>
-      <c r="K27" s="122"/>
-      <c r="L27" s="122"/>
-      <c r="M27" s="122"/>
-      <c r="N27" s="122"/>
-      <c r="O27" s="122"/>
-      <c r="P27" s="122"/>
-      <c r="Q27" s="122"/>
-      <c r="R27" s="122"/>
-      <c r="S27" s="122"/>
-      <c r="T27" s="122"/>
-      <c r="U27" s="122"/>
-      <c r="V27" s="122"/>
-      <c r="W27" s="122"/>
-      <c r="X27" s="122"/>
-      <c r="Y27" s="122"/>
-      <c r="Z27" s="122"/>
-      <c r="AA27" s="122"/>
-      <c r="AB27" s="122"/>
-      <c r="AC27" s="122"/>
-      <c r="AD27" s="122"/>
-      <c r="AE27" s="122"/>
-      <c r="AF27" s="122"/>
-      <c r="AG27" s="122"/>
-      <c r="AH27" s="122"/>
-      <c r="AI27" s="122"/>
-      <c r="AJ27" s="122"/>
+      <c r="F27" s="108"/>
+      <c r="G27" s="108"/>
+      <c r="H27" s="108"/>
+      <c r="I27" s="108"/>
+      <c r="J27" s="108"/>
+      <c r="K27" s="108"/>
+      <c r="L27" s="108"/>
+      <c r="M27" s="108"/>
+      <c r="N27" s="108"/>
+      <c r="O27" s="108"/>
+      <c r="P27" s="108"/>
+      <c r="Q27" s="108"/>
+      <c r="R27" s="108"/>
+      <c r="S27" s="108"/>
+      <c r="T27" s="108"/>
+      <c r="U27" s="108"/>
+      <c r="V27" s="108"/>
+      <c r="W27" s="108"/>
+      <c r="X27" s="108"/>
+      <c r="Y27" s="108"/>
+      <c r="Z27" s="108"/>
+      <c r="AA27" s="108"/>
+      <c r="AB27" s="108"/>
+      <c r="AC27" s="108"/>
+      <c r="AD27" s="108"/>
+      <c r="AE27" s="108"/>
+      <c r="AF27" s="108"/>
+      <c r="AG27" s="108"/>
+      <c r="AH27" s="108"/>
+      <c r="AI27" s="108"/>
+      <c r="AJ27" s="108"/>
     </row>
     <row r="28" spans="2:42" ht="18.75">
-      <c r="C28" s="123" t="s">
+      <c r="C28" s="153" t="s">
         <v>193</v>
       </c>
-      <c r="D28" s="123"/>
+      <c r="D28" s="153"/>
       <c r="E28" s="34"/>
       <c r="F28" s="39">
         <f>SUM(F21:F23)</f>
@@ -32745,10 +32745,10 @@
       </c>
     </row>
     <row r="29" spans="2:42" ht="18.75">
-      <c r="C29" s="123" t="s">
+      <c r="C29" s="153" t="s">
         <v>194</v>
       </c>
-      <c r="D29" s="123"/>
+      <c r="D29" s="153"/>
       <c r="E29" s="34"/>
       <c r="F29" s="35">
         <v>6</v>
@@ -32845,10 +32845,10 @@
       </c>
     </row>
     <row r="30" spans="2:42" ht="18.75">
-      <c r="C30" s="123" t="s">
+      <c r="C30" s="153" t="s">
         <v>195</v>
       </c>
-      <c r="D30" s="123"/>
+      <c r="D30" s="153"/>
       <c r="E30" s="34"/>
       <c r="F30" s="35">
         <f>SUM(F21,F22,F23,F24,F25)</f>
@@ -32976,178 +32976,145 @@
     </row>
     <row r="32" spans="2:42" ht="9.75" customHeight="1" thickBot="1"/>
     <row r="33" spans="6:11" ht="16.5" thickBot="1">
-      <c r="F33" s="110" t="s">
+      <c r="F33" s="95" t="s">
         <v>196</v>
       </c>
-      <c r="G33" s="111"/>
-      <c r="H33" s="111"/>
-      <c r="I33" s="111"/>
-      <c r="J33" s="111"/>
-      <c r="K33" s="112"/>
+      <c r="G33" s="96"/>
+      <c r="H33" s="96"/>
+      <c r="I33" s="96"/>
+      <c r="J33" s="96"/>
+      <c r="K33" s="97"/>
     </row>
     <row r="34" spans="6:11">
       <c r="F34" s="80" t="s">
         <v>197</v>
       </c>
-      <c r="G34" s="113" t="s">
+      <c r="G34" s="106" t="s">
         <v>198</v>
       </c>
-      <c r="H34" s="113"/>
+      <c r="H34" s="106"/>
       <c r="I34" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="J34" s="94" t="s">
+      <c r="J34" s="98" t="s">
         <v>199</v>
       </c>
-      <c r="K34" s="95"/>
+      <c r="K34" s="99"/>
     </row>
     <row r="35" spans="6:11">
       <c r="F35" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="G35" s="114" t="s">
+      <c r="G35" s="107" t="s">
         <v>200</v>
       </c>
-      <c r="H35" s="114"/>
+      <c r="H35" s="107"/>
       <c r="I35" s="77" t="s">
         <v>201</v>
       </c>
-      <c r="J35" s="115" t="s">
+      <c r="J35" s="100" t="s">
         <v>202</v>
       </c>
-      <c r="K35" s="116"/>
+      <c r="K35" s="101"/>
     </row>
     <row r="36" spans="6:11">
       <c r="F36" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="G36" s="100" t="s">
+      <c r="G36" s="102" t="s">
         <v>203</v>
       </c>
-      <c r="H36" s="100"/>
+      <c r="H36" s="102"/>
       <c r="I36" s="78" t="s">
         <v>108</v>
       </c>
-      <c r="J36" s="100" t="s">
+      <c r="J36" s="102" t="s">
         <v>204</v>
       </c>
-      <c r="K36" s="101"/>
+      <c r="K36" s="103"/>
     </row>
     <row r="37" spans="6:11">
       <c r="F37" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="G37" s="105" t="s">
+      <c r="G37" s="111" t="s">
         <v>205</v>
       </c>
-      <c r="H37" s="105"/>
+      <c r="H37" s="111"/>
       <c r="I37" s="79" t="s">
         <v>206</v>
       </c>
-      <c r="J37" s="117" t="s">
+      <c r="J37" s="104" t="s">
         <v>207</v>
       </c>
-      <c r="K37" s="118"/>
+      <c r="K37" s="105"/>
     </row>
     <row r="38" spans="6:11">
       <c r="F38" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="G38" s="105" t="s">
+      <c r="G38" s="111" t="s">
         <v>208</v>
       </c>
-      <c r="H38" s="105"/>
+      <c r="H38" s="111"/>
       <c r="I38" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="J38" s="106" t="s">
+      <c r="J38" s="93" t="s">
         <v>209</v>
       </c>
-      <c r="K38" s="107"/>
+      <c r="K38" s="94"/>
     </row>
     <row r="39" spans="6:11">
       <c r="F39" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="G39" s="108" t="s">
+      <c r="G39" s="92" t="s">
         <v>210</v>
       </c>
-      <c r="H39" s="108"/>
+      <c r="H39" s="92"/>
       <c r="I39" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="J39" s="106" t="s">
+      <c r="J39" s="93" t="s">
         <v>211</v>
       </c>
-      <c r="K39" s="107"/>
+      <c r="K39" s="94"/>
     </row>
     <row r="40" spans="6:11">
       <c r="F40" s="82" t="s">
         <v>212</v>
       </c>
-      <c r="G40" s="109" t="s">
+      <c r="G40" s="123" t="s">
         <v>213</v>
       </c>
-      <c r="H40" s="109"/>
+      <c r="H40" s="123"/>
       <c r="I40" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="J40" s="106" t="s">
+      <c r="J40" s="93" t="s">
         <v>214</v>
       </c>
-      <c r="K40" s="107"/>
+      <c r="K40" s="94"/>
     </row>
     <row r="41" spans="6:11" ht="16.5" thickBot="1">
       <c r="F41" s="55" t="s">
         <v>215</v>
       </c>
-      <c r="G41" s="92" t="s">
+      <c r="G41" s="124" t="s">
         <v>216</v>
       </c>
-      <c r="H41" s="92"/>
+      <c r="H41" s="124"/>
       <c r="I41" s="56" t="s">
         <v>167</v>
       </c>
-      <c r="J41" s="92" t="s">
+      <c r="J41" s="124" t="s">
         <v>217</v>
       </c>
-      <c r="K41" s="93"/>
+      <c r="K41" s="125"/>
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="F33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="F27:AJ27"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C25:D25"/>
     <mergeCell ref="G41:H41"/>
     <mergeCell ref="J41:K41"/>
     <mergeCell ref="B3:D4"/>
@@ -33164,6 +33131,39 @@
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F27:AJ27"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="F33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="G37:H37"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F5:AJ19">
@@ -33211,61 +33211,61 @@
   <sheetData>
     <row r="1" spans="2:42" ht="16.5" thickBot="1"/>
     <row r="2" spans="2:42" ht="39" customHeight="1" thickBot="1">
-      <c r="F2" s="134" t="s">
+      <c r="F2" s="139" t="s">
         <v>218</v>
       </c>
-      <c r="G2" s="135"/>
-      <c r="H2" s="135"/>
-      <c r="I2" s="135"/>
-      <c r="J2" s="135"/>
-      <c r="K2" s="135"/>
-      <c r="L2" s="135"/>
-      <c r="M2" s="135"/>
-      <c r="N2" s="135"/>
-      <c r="O2" s="135"/>
-      <c r="P2" s="135"/>
-      <c r="Q2" s="135"/>
-      <c r="R2" s="135"/>
-      <c r="S2" s="135"/>
-      <c r="T2" s="135"/>
-      <c r="U2" s="135"/>
-      <c r="V2" s="135"/>
-      <c r="W2" s="135"/>
-      <c r="X2" s="135"/>
-      <c r="Y2" s="135"/>
-      <c r="Z2" s="135"/>
-      <c r="AA2" s="135"/>
-      <c r="AB2" s="135"/>
-      <c r="AC2" s="135"/>
-      <c r="AD2" s="135"/>
-      <c r="AE2" s="135"/>
-      <c r="AF2" s="135"/>
-      <c r="AG2" s="135"/>
-      <c r="AH2" s="135"/>
-      <c r="AI2" s="135"/>
-      <c r="AJ2" s="136"/>
-      <c r="AL2" s="137" t="s">
+      <c r="G2" s="140"/>
+      <c r="H2" s="140"/>
+      <c r="I2" s="140"/>
+      <c r="J2" s="140"/>
+      <c r="K2" s="140"/>
+      <c r="L2" s="140"/>
+      <c r="M2" s="140"/>
+      <c r="N2" s="140"/>
+      <c r="O2" s="140"/>
+      <c r="P2" s="140"/>
+      <c r="Q2" s="140"/>
+      <c r="R2" s="140"/>
+      <c r="S2" s="140"/>
+      <c r="T2" s="140"/>
+      <c r="U2" s="140"/>
+      <c r="V2" s="140"/>
+      <c r="W2" s="140"/>
+      <c r="X2" s="140"/>
+      <c r="Y2" s="140"/>
+      <c r="Z2" s="140"/>
+      <c r="AA2" s="140"/>
+      <c r="AB2" s="140"/>
+      <c r="AC2" s="140"/>
+      <c r="AD2" s="140"/>
+      <c r="AE2" s="140"/>
+      <c r="AF2" s="140"/>
+      <c r="AG2" s="140"/>
+      <c r="AH2" s="140"/>
+      <c r="AI2" s="140"/>
+      <c r="AJ2" s="141"/>
+      <c r="AL2" s="114" t="s">
         <v>80</v>
       </c>
-      <c r="AM2" s="137" t="s">
+      <c r="AM2" s="114" t="s">
         <v>81</v>
       </c>
-      <c r="AN2" s="137" t="s">
+      <c r="AN2" s="114" t="s">
         <v>82</v>
       </c>
-      <c r="AO2" s="137" t="s">
+      <c r="AO2" s="114" t="s">
         <v>83</v>
       </c>
-      <c r="AP2" s="137" t="s">
+      <c r="AP2" s="114" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="3" spans="2:42" ht="39.75" thickBot="1">
-      <c r="B3" s="127" t="s">
+      <c r="B3" s="122" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="127"/>
-      <c r="D3" s="127"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="122"/>
       <c r="F3" s="43" t="s">
         <v>86</v>
       </c>
@@ -33359,16 +33359,16 @@
       <c r="AJ3" s="43" t="s">
         <v>187</v>
       </c>
-      <c r="AL3" s="138"/>
-      <c r="AM3" s="138"/>
-      <c r="AN3" s="138"/>
-      <c r="AO3" s="138"/>
-      <c r="AP3" s="138"/>
+      <c r="AL3" s="115"/>
+      <c r="AM3" s="115"/>
+      <c r="AN3" s="115"/>
+      <c r="AO3" s="115"/>
+      <c r="AP3" s="115"/>
     </row>
     <row r="4" spans="2:42" ht="19.5" customHeight="1" thickBot="1">
-      <c r="B4" s="127"/>
-      <c r="C4" s="127"/>
-      <c r="D4" s="127"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
       <c r="F4" s="40">
         <v>1</v>
       </c>
@@ -33462,20 +33462,20 @@
       <c r="AJ4" s="58" t="s">
         <v>187</v>
       </c>
-      <c r="AL4" s="139"/>
-      <c r="AM4" s="139"/>
-      <c r="AN4" s="139"/>
-      <c r="AO4" s="139"/>
-      <c r="AP4" s="139"/>
+      <c r="AL4" s="116"/>
+      <c r="AM4" s="116"/>
+      <c r="AN4" s="116"/>
+      <c r="AO4" s="116"/>
+      <c r="AP4" s="116"/>
     </row>
     <row r="5" spans="2:42" ht="18.75">
       <c r="B5" s="35">
         <v>1</v>
       </c>
-      <c r="C5" s="126" t="s">
+      <c r="C5" s="142" t="s">
         <v>132</v>
       </c>
-      <c r="D5" s="126"/>
+      <c r="D5" s="142"/>
       <c r="F5" s="73" t="s">
         <v>102</v>
       </c>
@@ -33592,10 +33592,10 @@
       <c r="B6" s="35">
         <v>2</v>
       </c>
-      <c r="C6" s="126" t="s">
+      <c r="C6" s="142" t="s">
         <v>133</v>
       </c>
-      <c r="D6" s="126"/>
+      <c r="D6" s="142"/>
       <c r="F6" s="75" t="s">
         <v>102</v>
       </c>
@@ -33712,10 +33712,10 @@
       <c r="B7" s="35">
         <v>3</v>
       </c>
-      <c r="C7" s="126" t="s">
+      <c r="C7" s="142" t="s">
         <v>134</v>
       </c>
-      <c r="D7" s="126"/>
+      <c r="D7" s="142"/>
       <c r="F7" s="75" t="s">
         <v>98</v>
       </c>
@@ -33832,10 +33832,10 @@
       <c r="B8" s="35">
         <v>4</v>
       </c>
-      <c r="C8" s="126" t="s">
+      <c r="C8" s="142" t="s">
         <v>136</v>
       </c>
-      <c r="D8" s="126"/>
+      <c r="D8" s="142"/>
       <c r="F8" s="75" t="s">
         <v>95</v>
       </c>
@@ -33952,10 +33952,10 @@
       <c r="B9" s="35">
         <v>5</v>
       </c>
-      <c r="C9" s="126" t="s">
+      <c r="C9" s="142" t="s">
         <v>137</v>
       </c>
-      <c r="D9" s="126"/>
+      <c r="D9" s="142"/>
       <c r="F9" s="75" t="s">
         <v>96</v>
       </c>
@@ -34072,10 +34072,10 @@
       <c r="B10" s="35">
         <v>6</v>
       </c>
-      <c r="C10" s="126" t="s">
+      <c r="C10" s="142" t="s">
         <v>138</v>
       </c>
-      <c r="D10" s="126"/>
+      <c r="D10" s="142"/>
       <c r="F10" s="75" t="s">
         <v>96</v>
       </c>
@@ -34192,10 +34192,10 @@
       <c r="B11" s="35">
         <v>7</v>
       </c>
-      <c r="C11" s="126" t="s">
+      <c r="C11" s="142" t="s">
         <v>139</v>
       </c>
-      <c r="D11" s="126"/>
+      <c r="D11" s="142"/>
       <c r="F11" s="76" t="s">
         <v>101</v>
       </c>
@@ -34312,10 +34312,10 @@
       <c r="B12" s="35">
         <v>8</v>
       </c>
-      <c r="C12" s="126" t="s">
+      <c r="C12" s="142" t="s">
         <v>140</v>
       </c>
-      <c r="D12" s="126"/>
+      <c r="D12" s="142"/>
       <c r="F12" s="75" t="s">
         <v>101</v>
       </c>
@@ -34432,10 +34432,10 @@
       <c r="B13" s="35">
         <v>9</v>
       </c>
-      <c r="C13" s="126" t="s">
+      <c r="C13" s="142" t="s">
         <v>220</v>
       </c>
-      <c r="D13" s="126"/>
+      <c r="D13" s="142"/>
       <c r="F13" s="75" t="s">
         <v>102</v>
       </c>
@@ -34552,10 +34552,10 @@
       <c r="B14" s="35">
         <v>10</v>
       </c>
-      <c r="C14" s="126" t="s">
+      <c r="C14" s="142" t="s">
         <v>142</v>
       </c>
-      <c r="D14" s="126"/>
+      <c r="D14" s="142"/>
       <c r="F14" s="75" t="s">
         <v>116</v>
       </c>
@@ -34672,10 +34672,10 @@
       <c r="B15" s="35">
         <v>11</v>
       </c>
-      <c r="C15" s="126" t="s">
+      <c r="C15" s="142" t="s">
         <v>143</v>
       </c>
-      <c r="D15" s="126"/>
+      <c r="D15" s="142"/>
       <c r="F15" s="75" t="s">
         <v>116</v>
       </c>
@@ -34792,10 +34792,10 @@
       <c r="B16" s="35">
         <v>12</v>
       </c>
-      <c r="C16" s="126" t="s">
+      <c r="C16" s="142" t="s">
         <v>144</v>
       </c>
-      <c r="D16" s="126"/>
+      <c r="D16" s="142"/>
       <c r="F16" s="75" t="s">
         <v>96</v>
       </c>
@@ -34912,10 +34912,10 @@
       <c r="B17" s="35">
         <v>13</v>
       </c>
-      <c r="C17" s="126" t="s">
+      <c r="C17" s="142" t="s">
         <v>145</v>
       </c>
-      <c r="D17" s="126"/>
+      <c r="D17" s="142"/>
       <c r="F17" s="75" t="s">
         <v>96</v>
       </c>
@@ -35032,10 +35032,10 @@
       <c r="B18" s="35">
         <v>14</v>
       </c>
-      <c r="C18" s="126" t="s">
+      <c r="C18" s="142" t="s">
         <v>146</v>
       </c>
-      <c r="D18" s="126"/>
+      <c r="D18" s="142"/>
       <c r="F18" s="76" t="s">
         <v>101</v>
       </c>
@@ -35152,10 +35152,10 @@
       <c r="B19" s="35">
         <v>15</v>
       </c>
-      <c r="C19" s="126" t="s">
+      <c r="C19" s="142" t="s">
         <v>147</v>
       </c>
-      <c r="D19" s="126"/>
+      <c r="D19" s="142"/>
       <c r="F19" s="75" t="s">
         <v>102</v>
       </c>
@@ -35272,10 +35272,10 @@
       <c r="B20" s="35">
         <v>16</v>
       </c>
-      <c r="C20" s="126" t="s">
+      <c r="C20" s="142" t="s">
         <v>148</v>
       </c>
-      <c r="D20" s="126"/>
+      <c r="D20" s="142"/>
       <c r="F20" s="75" t="s">
         <v>102</v>
       </c>
@@ -35392,10 +35392,10 @@
       <c r="B21" s="35">
         <v>17</v>
       </c>
-      <c r="C21" s="126" t="s">
+      <c r="C21" s="142" t="s">
         <v>149</v>
       </c>
-      <c r="D21" s="126"/>
+      <c r="D21" s="142"/>
       <c r="F21" s="75" t="s">
         <v>116</v>
       </c>
@@ -35512,10 +35512,10 @@
       <c r="B22" s="35">
         <v>18</v>
       </c>
-      <c r="C22" s="126" t="s">
+      <c r="C22" s="142" t="s">
         <v>150</v>
       </c>
-      <c r="D22" s="126"/>
+      <c r="D22" s="142"/>
       <c r="F22" s="75" t="s">
         <v>116</v>
       </c>
@@ -35632,10 +35632,10 @@
       <c r="B23" s="35">
         <v>19</v>
       </c>
-      <c r="C23" s="126" t="s">
+      <c r="C23" s="142" t="s">
         <v>151</v>
       </c>
-      <c r="D23" s="126"/>
+      <c r="D23" s="142"/>
       <c r="F23" s="75" t="s">
         <v>96</v>
       </c>
@@ -35752,10 +35752,10 @@
       <c r="B24" s="35">
         <v>20</v>
       </c>
-      <c r="C24" s="126" t="s">
+      <c r="C24" s="142" t="s">
         <v>152</v>
       </c>
-      <c r="D24" s="126"/>
+      <c r="D24" s="142"/>
       <c r="F24" s="75" t="s">
         <v>96</v>
       </c>
@@ -35872,10 +35872,10 @@
       <c r="B25" s="35">
         <v>21</v>
       </c>
-      <c r="C25" s="126" t="s">
+      <c r="C25" s="142" t="s">
         <v>153</v>
       </c>
-      <c r="D25" s="126"/>
+      <c r="D25" s="142"/>
       <c r="F25" s="76" t="s">
         <v>95</v>
       </c>
@@ -35992,10 +35992,10 @@
       <c r="B26" s="35">
         <v>22</v>
       </c>
-      <c r="C26" s="126" t="s">
+      <c r="C26" s="142" t="s">
         <v>154</v>
       </c>
-      <c r="D26" s="126"/>
+      <c r="D26" s="142"/>
       <c r="F26" s="75" t="s">
         <v>101</v>
       </c>
@@ -36112,10 +36112,10 @@
       <c r="B27" s="35">
         <v>23</v>
       </c>
-      <c r="C27" s="126" t="s">
+      <c r="C27" s="142" t="s">
         <v>155</v>
       </c>
-      <c r="D27" s="126"/>
+      <c r="D27" s="142"/>
       <c r="F27" s="75" t="s">
         <v>102</v>
       </c>
@@ -36232,10 +36232,10 @@
       <c r="B28" s="35">
         <v>24</v>
       </c>
-      <c r="C28" s="126" t="s">
+      <c r="C28" s="142" t="s">
         <v>156</v>
       </c>
-      <c r="D28" s="126"/>
+      <c r="D28" s="142"/>
       <c r="F28" s="75" t="s">
         <v>116</v>
       </c>
@@ -36352,10 +36352,10 @@
       <c r="B29" s="35">
         <v>25</v>
       </c>
-      <c r="C29" s="126" t="s">
+      <c r="C29" s="142" t="s">
         <v>157</v>
       </c>
-      <c r="D29" s="126"/>
+      <c r="D29" s="142"/>
       <c r="F29" s="75" t="s">
         <v>116</v>
       </c>
@@ -36472,10 +36472,10 @@
       <c r="B30" s="35">
         <v>26</v>
       </c>
-      <c r="C30" s="96" t="s">
+      <c r="C30" s="112" t="s">
         <v>158</v>
       </c>
-      <c r="D30" s="97"/>
+      <c r="D30" s="113"/>
       <c r="F30" s="75" t="s">
         <v>96</v>
       </c>
@@ -36592,10 +36592,10 @@
       <c r="B31" s="35">
         <v>27</v>
       </c>
-      <c r="C31" s="96" t="s">
+      <c r="C31" s="112" t="s">
         <v>159</v>
       </c>
-      <c r="D31" s="97"/>
+      <c r="D31" s="113"/>
       <c r="F31" s="75" t="s">
         <v>96</v>
       </c>
@@ -36712,10 +36712,10 @@
       <c r="B32" s="35">
         <v>28</v>
       </c>
-      <c r="C32" s="96" t="s">
+      <c r="C32" s="112" t="s">
         <v>160</v>
       </c>
-      <c r="D32" s="97"/>
+      <c r="D32" s="113"/>
       <c r="F32" s="76" t="s">
         <v>101</v>
       </c>
@@ -36832,10 +36832,10 @@
       <c r="B33" s="35">
         <v>29</v>
       </c>
-      <c r="C33" s="96" t="s">
+      <c r="C33" s="112" t="s">
         <v>161</v>
       </c>
-      <c r="D33" s="97"/>
+      <c r="D33" s="113"/>
       <c r="F33" s="75" t="s">
         <v>95</v>
       </c>
@@ -36952,10 +36952,10 @@
       <c r="B34" s="35">
         <v>30</v>
       </c>
-      <c r="C34" s="104" t="s">
+      <c r="C34" s="149" t="s">
         <v>162</v>
       </c>
-      <c r="D34" s="104"/>
+      <c r="D34" s="149"/>
       <c r="F34" s="75" t="s">
         <v>101</v>
       </c>
@@ -37072,10 +37072,10 @@
       <c r="B35" s="35">
         <v>31</v>
       </c>
-      <c r="C35" s="104" t="s">
+      <c r="C35" s="149" t="s">
         <v>163</v>
       </c>
-      <c r="D35" s="104"/>
+      <c r="D35" s="149"/>
       <c r="F35" s="75" t="s">
         <v>96</v>
       </c>
@@ -37192,10 +37192,10 @@
       <c r="B36" s="35">
         <v>32</v>
       </c>
-      <c r="C36" s="124" t="s">
+      <c r="C36" s="150" t="s">
         <v>164</v>
       </c>
-      <c r="D36" s="125"/>
+      <c r="D36" s="151"/>
       <c r="F36" s="75" t="s">
         <v>95</v>
       </c>
@@ -37312,10 +37312,10 @@
       <c r="B37" s="35">
         <v>33</v>
       </c>
-      <c r="C37" s="104" t="s">
+      <c r="C37" s="149" t="s">
         <v>165</v>
       </c>
-      <c r="D37" s="104"/>
+      <c r="D37" s="149"/>
       <c r="F37" s="88" t="s">
         <v>166</v>
       </c>
@@ -37463,10 +37463,10 @@
       <c r="AI38" s="18"/>
     </row>
     <row r="39" spans="2:42" ht="18.75">
-      <c r="C39" s="123" t="s">
+      <c r="C39" s="153" t="s">
         <v>188</v>
       </c>
-      <c r="D39" s="123"/>
+      <c r="D39" s="153"/>
       <c r="E39" s="34"/>
       <c r="F39" s="35">
         <f t="shared" ref="F39:AJ39" si="5">COUNTIF(F$5:F$36,"M*")</f>
@@ -37594,10 +37594,10 @@
       </c>
     </row>
     <row r="40" spans="2:42" ht="18.75">
-      <c r="C40" s="123" t="s">
+      <c r="C40" s="153" t="s">
         <v>189</v>
       </c>
-      <c r="D40" s="123"/>
+      <c r="D40" s="153"/>
       <c r="E40" s="34"/>
       <c r="F40" s="35">
         <f t="shared" ref="F40:AJ40" si="6">COUNTIF(F$5:F$36,"A*")</f>
@@ -37725,10 +37725,10 @@
       </c>
     </row>
     <row r="41" spans="2:42" ht="18.75">
-      <c r="C41" s="123" t="s">
+      <c r="C41" s="153" t="s">
         <v>77</v>
       </c>
-      <c r="D41" s="123"/>
+      <c r="D41" s="153"/>
       <c r="E41" s="34"/>
       <c r="F41" s="35">
         <f t="shared" ref="F41:AJ41" si="7">COUNTIF(F$5:F$36,"N*")</f>
@@ -37856,10 +37856,10 @@
       </c>
     </row>
     <row r="42" spans="2:42" ht="18.75">
-      <c r="C42" s="123" t="s">
+      <c r="C42" s="153" t="s">
         <v>78</v>
       </c>
-      <c r="D42" s="123"/>
+      <c r="D42" s="153"/>
       <c r="E42" s="34"/>
       <c r="F42" s="35">
         <f t="shared" ref="F42:AJ42" si="8">COUNTIF(F$5:F$37,"O*")</f>
@@ -37987,10 +37987,10 @@
       </c>
     </row>
     <row r="43" spans="2:42" ht="18.75">
-      <c r="C43" s="119" t="s">
+      <c r="C43" s="109" t="s">
         <v>190</v>
       </c>
-      <c r="D43" s="120"/>
+      <c r="D43" s="110"/>
       <c r="E43" s="34"/>
       <c r="F43" s="35">
         <f t="shared" ref="F43:AJ43" si="9">COUNTIF(F$5:F$37,"TR*")</f>
@@ -38118,10 +38118,10 @@
       </c>
     </row>
     <row r="44" spans="2:42" ht="18.75">
-      <c r="C44" s="119" t="s">
+      <c r="C44" s="109" t="s">
         <v>191</v>
       </c>
-      <c r="D44" s="120"/>
+      <c r="D44" s="110"/>
       <c r="E44" s="34"/>
       <c r="F44" s="35">
         <f t="shared" ref="F44:AJ44" si="10">COUNTIF(F$5:F$36,"ST*")</f>
@@ -38249,10 +38249,10 @@
       </c>
     </row>
     <row r="45" spans="2:42" ht="18.75">
-      <c r="C45" s="121" t="s">
+      <c r="C45" s="152" t="s">
         <v>192</v>
       </c>
-      <c r="D45" s="121"/>
+      <c r="D45" s="152"/>
       <c r="E45" s="36"/>
       <c r="F45" s="37">
         <f>F47-F48</f>
@@ -38383,43 +38383,43 @@
       <c r="C46" s="38"/>
       <c r="D46" s="38"/>
       <c r="E46" s="34"/>
-      <c r="F46" s="122"/>
-      <c r="G46" s="122"/>
-      <c r="H46" s="122"/>
-      <c r="I46" s="122"/>
-      <c r="J46" s="122"/>
-      <c r="K46" s="122"/>
-      <c r="L46" s="122"/>
-      <c r="M46" s="122"/>
-      <c r="N46" s="122"/>
-      <c r="O46" s="122"/>
-      <c r="P46" s="122"/>
-      <c r="Q46" s="122"/>
-      <c r="R46" s="122"/>
-      <c r="S46" s="122"/>
-      <c r="T46" s="122"/>
-      <c r="U46" s="122"/>
-      <c r="V46" s="122"/>
-      <c r="W46" s="122"/>
-      <c r="X46" s="122"/>
-      <c r="Y46" s="122"/>
-      <c r="Z46" s="122"/>
-      <c r="AA46" s="122"/>
-      <c r="AB46" s="122"/>
-      <c r="AC46" s="122"/>
-      <c r="AD46" s="122"/>
-      <c r="AE46" s="122"/>
-      <c r="AF46" s="122"/>
-      <c r="AG46" s="122"/>
-      <c r="AH46" s="122"/>
-      <c r="AI46" s="122"/>
-      <c r="AJ46" s="122"/>
+      <c r="F46" s="108"/>
+      <c r="G46" s="108"/>
+      <c r="H46" s="108"/>
+      <c r="I46" s="108"/>
+      <c r="J46" s="108"/>
+      <c r="K46" s="108"/>
+      <c r="L46" s="108"/>
+      <c r="M46" s="108"/>
+      <c r="N46" s="108"/>
+      <c r="O46" s="108"/>
+      <c r="P46" s="108"/>
+      <c r="Q46" s="108"/>
+      <c r="R46" s="108"/>
+      <c r="S46" s="108"/>
+      <c r="T46" s="108"/>
+      <c r="U46" s="108"/>
+      <c r="V46" s="108"/>
+      <c r="W46" s="108"/>
+      <c r="X46" s="108"/>
+      <c r="Y46" s="108"/>
+      <c r="Z46" s="108"/>
+      <c r="AA46" s="108"/>
+      <c r="AB46" s="108"/>
+      <c r="AC46" s="108"/>
+      <c r="AD46" s="108"/>
+      <c r="AE46" s="108"/>
+      <c r="AF46" s="108"/>
+      <c r="AG46" s="108"/>
+      <c r="AH46" s="108"/>
+      <c r="AI46" s="108"/>
+      <c r="AJ46" s="108"/>
     </row>
     <row r="47" spans="2:42" ht="19.5" thickBot="1">
-      <c r="C47" s="123" t="s">
+      <c r="C47" s="153" t="s">
         <v>193</v>
       </c>
-      <c r="D47" s="123"/>
+      <c r="D47" s="153"/>
       <c r="E47" s="34"/>
       <c r="F47" s="39">
         <f>SUM(F39:F41)</f>
@@ -38546,10 +38546,10 @@
       </c>
     </row>
     <row r="48" spans="2:42" ht="18.75">
-      <c r="C48" s="123" t="s">
+      <c r="C48" s="153" t="s">
         <v>194</v>
       </c>
-      <c r="D48" s="123"/>
+      <c r="D48" s="153"/>
       <c r="E48" s="34"/>
       <c r="F48" s="35">
         <v>18</v>
@@ -38646,10 +38646,10 @@
       </c>
     </row>
     <row r="49" spans="3:36" ht="19.5" thickBot="1">
-      <c r="C49" s="123" t="s">
+      <c r="C49" s="153" t="s">
         <v>195</v>
       </c>
-      <c r="D49" s="123"/>
+      <c r="D49" s="153"/>
       <c r="E49" s="34"/>
       <c r="F49" s="35">
         <f>SUM(F39,F40,F41,F42,F44)</f>
@@ -38777,187 +38777,157 @@
     </row>
     <row r="51" spans="3:36" ht="16.5" thickBot="1"/>
     <row r="52" spans="3:36" ht="16.5" thickBot="1">
-      <c r="F52" s="110" t="s">
+      <c r="F52" s="95" t="s">
         <v>196</v>
       </c>
-      <c r="G52" s="111"/>
-      <c r="H52" s="111"/>
-      <c r="I52" s="111"/>
-      <c r="J52" s="111"/>
-      <c r="K52" s="112"/>
+      <c r="G52" s="96"/>
+      <c r="H52" s="96"/>
+      <c r="I52" s="96"/>
+      <c r="J52" s="96"/>
+      <c r="K52" s="97"/>
     </row>
     <row r="53" spans="3:36">
       <c r="F53" s="80" t="s">
         <v>197</v>
       </c>
-      <c r="G53" s="113" t="s">
+      <c r="G53" s="106" t="s">
         <v>198</v>
       </c>
-      <c r="H53" s="113"/>
+      <c r="H53" s="106"/>
       <c r="I53" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="J53" s="94" t="s">
+      <c r="J53" s="98" t="s">
         <v>199</v>
       </c>
-      <c r="K53" s="95"/>
+      <c r="K53" s="99"/>
     </row>
     <row r="54" spans="3:36">
       <c r="F54" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="G54" s="114" t="s">
+      <c r="G54" s="107" t="s">
         <v>200</v>
       </c>
-      <c r="H54" s="114"/>
+      <c r="H54" s="107"/>
       <c r="I54" s="77" t="s">
         <v>201</v>
       </c>
-      <c r="J54" s="115" t="s">
+      <c r="J54" s="100" t="s">
         <v>202</v>
       </c>
-      <c r="K54" s="116"/>
+      <c r="K54" s="101"/>
     </row>
     <row r="55" spans="3:36">
       <c r="F55" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="G55" s="100" t="s">
+      <c r="G55" s="102" t="s">
         <v>203</v>
       </c>
-      <c r="H55" s="100"/>
+      <c r="H55" s="102"/>
       <c r="I55" s="78" t="s">
         <v>108</v>
       </c>
-      <c r="J55" s="100" t="s">
+      <c r="J55" s="102" t="s">
         <v>204</v>
       </c>
-      <c r="K55" s="101"/>
+      <c r="K55" s="103"/>
     </row>
     <row r="56" spans="3:36">
       <c r="F56" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="G56" s="105" t="s">
+      <c r="G56" s="111" t="s">
         <v>205</v>
       </c>
-      <c r="H56" s="105"/>
+      <c r="H56" s="111"/>
       <c r="I56" s="79" t="s">
         <v>206</v>
       </c>
-      <c r="J56" s="117" t="s">
+      <c r="J56" s="104" t="s">
         <v>207</v>
       </c>
-      <c r="K56" s="118"/>
+      <c r="K56" s="105"/>
     </row>
     <row r="57" spans="3:36">
       <c r="F57" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="G57" s="105" t="s">
+      <c r="G57" s="111" t="s">
         <v>208</v>
       </c>
-      <c r="H57" s="105"/>
+      <c r="H57" s="111"/>
       <c r="I57" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="J57" s="106" t="s">
+      <c r="J57" s="93" t="s">
         <v>209</v>
       </c>
-      <c r="K57" s="107"/>
+      <c r="K57" s="94"/>
     </row>
     <row r="58" spans="3:36">
       <c r="F58" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="G58" s="108" t="s">
+      <c r="G58" s="92" t="s">
         <v>210</v>
       </c>
-      <c r="H58" s="108"/>
+      <c r="H58" s="92"/>
       <c r="I58" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="J58" s="106" t="s">
+      <c r="J58" s="93" t="s">
         <v>211</v>
       </c>
-      <c r="K58" s="107"/>
+      <c r="K58" s="94"/>
     </row>
     <row r="59" spans="3:36">
       <c r="F59" s="82" t="s">
         <v>212</v>
       </c>
-      <c r="G59" s="109" t="s">
+      <c r="G59" s="123" t="s">
         <v>213</v>
       </c>
-      <c r="H59" s="109"/>
+      <c r="H59" s="123"/>
       <c r="I59" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="J59" s="106" t="s">
+      <c r="J59" s="93" t="s">
         <v>214</v>
       </c>
-      <c r="K59" s="107"/>
+      <c r="K59" s="94"/>
     </row>
     <row r="60" spans="3:36" ht="16.5" thickBot="1">
       <c r="F60" s="55" t="s">
         <v>215</v>
       </c>
-      <c r="G60" s="92" t="s">
+      <c r="G60" s="124" t="s">
         <v>216</v>
       </c>
-      <c r="H60" s="92"/>
+      <c r="H60" s="124"/>
       <c r="I60" s="56" t="s">
         <v>167</v>
       </c>
-      <c r="J60" s="92" t="s">
+      <c r="J60" s="124" t="s">
         <v>217</v>
       </c>
-      <c r="K60" s="93"/>
+      <c r="K60" s="125"/>
     </row>
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="68">
-    <mergeCell ref="F52:K52"/>
-    <mergeCell ref="G56:H56"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="J53:K53"/>
-    <mergeCell ref="J54:K54"/>
-    <mergeCell ref="J55:K55"/>
-    <mergeCell ref="J56:K56"/>
-    <mergeCell ref="J57:K57"/>
-    <mergeCell ref="G53:H53"/>
-    <mergeCell ref="G54:H54"/>
-    <mergeCell ref="G55:H55"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="F46:AJ46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="G58:H58"/>
+    <mergeCell ref="J58:K58"/>
+    <mergeCell ref="G59:H59"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="G60:H60"/>
+    <mergeCell ref="J60:K60"/>
+    <mergeCell ref="AM2:AM4"/>
+    <mergeCell ref="AN2:AN4"/>
+    <mergeCell ref="AO2:AO4"/>
+    <mergeCell ref="AP2:AP4"/>
+    <mergeCell ref="B3:D4"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="F2:AJ2"/>
@@ -38974,17 +38944,47 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C17:D17"/>
-    <mergeCell ref="AM2:AM4"/>
-    <mergeCell ref="AN2:AN4"/>
-    <mergeCell ref="AO2:AO4"/>
-    <mergeCell ref="AP2:AP4"/>
-    <mergeCell ref="B3:D4"/>
-    <mergeCell ref="G58:H58"/>
-    <mergeCell ref="J58:K58"/>
-    <mergeCell ref="G59:H59"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="G60:H60"/>
-    <mergeCell ref="J60:K60"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="F46:AJ46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="F52:K52"/>
+    <mergeCell ref="G56:H56"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="J53:K53"/>
+    <mergeCell ref="J54:K54"/>
+    <mergeCell ref="J55:K55"/>
+    <mergeCell ref="J56:K56"/>
+    <mergeCell ref="J57:K57"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="G55:H55"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F5:AJ37">
@@ -39034,61 +39034,61 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:42" ht="39" customHeight="1" thickBot="1">
-      <c r="F2" s="160" t="s">
+      <c r="F2" s="117" t="s">
         <v>221</v>
       </c>
-      <c r="G2" s="161"/>
-      <c r="H2" s="161"/>
-      <c r="I2" s="161"/>
-      <c r="J2" s="161"/>
-      <c r="K2" s="161"/>
-      <c r="L2" s="161"/>
-      <c r="M2" s="161"/>
-      <c r="N2" s="161"/>
-      <c r="O2" s="161"/>
-      <c r="P2" s="161"/>
-      <c r="Q2" s="161"/>
-      <c r="R2" s="161"/>
-      <c r="S2" s="161"/>
-      <c r="T2" s="161"/>
-      <c r="U2" s="161"/>
-      <c r="V2" s="161"/>
-      <c r="W2" s="161"/>
-      <c r="X2" s="161"/>
-      <c r="Y2" s="161"/>
-      <c r="Z2" s="161"/>
-      <c r="AA2" s="161"/>
-      <c r="AB2" s="161"/>
-      <c r="AC2" s="161"/>
-      <c r="AD2" s="161"/>
-      <c r="AE2" s="161"/>
-      <c r="AF2" s="161"/>
-      <c r="AG2" s="161"/>
-      <c r="AH2" s="161"/>
-      <c r="AI2" s="161"/>
-      <c r="AJ2" s="162"/>
-      <c r="AL2" s="137" t="s">
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
+      <c r="N2" s="118"/>
+      <c r="O2" s="118"/>
+      <c r="P2" s="118"/>
+      <c r="Q2" s="118"/>
+      <c r="R2" s="118"/>
+      <c r="S2" s="118"/>
+      <c r="T2" s="118"/>
+      <c r="U2" s="118"/>
+      <c r="V2" s="118"/>
+      <c r="W2" s="118"/>
+      <c r="X2" s="118"/>
+      <c r="Y2" s="118"/>
+      <c r="Z2" s="118"/>
+      <c r="AA2" s="118"/>
+      <c r="AB2" s="118"/>
+      <c r="AC2" s="118"/>
+      <c r="AD2" s="118"/>
+      <c r="AE2" s="118"/>
+      <c r="AF2" s="118"/>
+      <c r="AG2" s="118"/>
+      <c r="AH2" s="118"/>
+      <c r="AI2" s="118"/>
+      <c r="AJ2" s="119"/>
+      <c r="AL2" s="114" t="s">
         <v>80</v>
       </c>
-      <c r="AM2" s="137" t="s">
+      <c r="AM2" s="114" t="s">
         <v>81</v>
       </c>
-      <c r="AN2" s="137" t="s">
+      <c r="AN2" s="114" t="s">
         <v>82</v>
       </c>
-      <c r="AO2" s="137" t="s">
+      <c r="AO2" s="114" t="s">
         <v>83</v>
       </c>
-      <c r="AP2" s="137" t="s">
+      <c r="AP2" s="114" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="3" spans="2:42" ht="39">
-      <c r="B3" s="127" t="s">
+      <c r="B3" s="122" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="127"/>
-      <c r="D3" s="127"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="122"/>
       <c r="F3" s="64" t="s">
         <v>86</v>
       </c>
@@ -39182,16 +39182,16 @@
       <c r="AJ3" s="64" t="s">
         <v>187</v>
       </c>
-      <c r="AL3" s="138"/>
-      <c r="AM3" s="138"/>
-      <c r="AN3" s="138"/>
-      <c r="AO3" s="138"/>
-      <c r="AP3" s="138"/>
+      <c r="AL3" s="115"/>
+      <c r="AM3" s="115"/>
+      <c r="AN3" s="115"/>
+      <c r="AO3" s="115"/>
+      <c r="AP3" s="115"/>
     </row>
     <row r="4" spans="2:42" ht="19.5" customHeight="1" thickBot="1">
-      <c r="B4" s="127"/>
-      <c r="C4" s="127"/>
-      <c r="D4" s="127"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
       <c r="F4" s="30">
         <v>1</v>
       </c>
@@ -39285,20 +39285,20 @@
       <c r="AJ4" s="67" t="s">
         <v>187</v>
       </c>
-      <c r="AL4" s="139"/>
-      <c r="AM4" s="139"/>
-      <c r="AN4" s="139"/>
-      <c r="AO4" s="139"/>
-      <c r="AP4" s="139"/>
+      <c r="AL4" s="116"/>
+      <c r="AM4" s="116"/>
+      <c r="AN4" s="116"/>
+      <c r="AO4" s="116"/>
+      <c r="AP4" s="116"/>
     </row>
     <row r="5" spans="2:42" ht="18.75">
       <c r="B5" s="35">
         <v>1</v>
       </c>
-      <c r="C5" s="102" t="s">
+      <c r="C5" s="120" t="s">
         <v>168</v>
       </c>
-      <c r="D5" s="103"/>
+      <c r="D5" s="121"/>
       <c r="F5" s="83" t="s">
         <v>102</v>
       </c>
@@ -39415,10 +39415,10 @@
       <c r="B6" s="35">
         <v>2</v>
       </c>
-      <c r="C6" s="96" t="s">
+      <c r="C6" s="112" t="s">
         <v>169</v>
       </c>
-      <c r="D6" s="97"/>
+      <c r="D6" s="113"/>
       <c r="F6" s="83" t="s">
         <v>102</v>
       </c>
@@ -39535,10 +39535,10 @@
       <c r="B7" s="35">
         <v>3</v>
       </c>
-      <c r="C7" s="96" t="s">
+      <c r="C7" s="112" t="s">
         <v>170</v>
       </c>
-      <c r="D7" s="97"/>
+      <c r="D7" s="113"/>
       <c r="F7" s="84" t="s">
         <v>95</v>
       </c>
@@ -39655,10 +39655,10 @@
       <c r="B8" s="35">
         <v>4</v>
       </c>
-      <c r="C8" s="96" t="s">
+      <c r="C8" s="112" t="s">
         <v>171</v>
       </c>
-      <c r="D8" s="97"/>
+      <c r="D8" s="113"/>
       <c r="F8" s="84" t="s">
         <v>95</v>
       </c>
@@ -39775,10 +39775,10 @@
       <c r="B9" s="35">
         <v>5</v>
       </c>
-      <c r="C9" s="96" t="s">
+      <c r="C9" s="112" t="s">
         <v>172</v>
       </c>
-      <c r="D9" s="97"/>
+      <c r="D9" s="113"/>
       <c r="F9" s="84" t="s">
         <v>96</v>
       </c>
@@ -39895,10 +39895,10 @@
       <c r="B10" s="35">
         <v>6</v>
       </c>
-      <c r="C10" s="96" t="s">
+      <c r="C10" s="112" t="s">
         <v>173</v>
       </c>
-      <c r="D10" s="97"/>
+      <c r="D10" s="113"/>
       <c r="F10" s="84" t="s">
         <v>96</v>
       </c>
@@ -40015,10 +40015,10 @@
       <c r="B11" s="35">
         <v>7</v>
       </c>
-      <c r="C11" s="96" t="s">
+      <c r="C11" s="112" t="s">
         <v>174</v>
       </c>
-      <c r="D11" s="97"/>
+      <c r="D11" s="113"/>
       <c r="F11" s="84" t="s">
         <v>101</v>
       </c>
@@ -40135,10 +40135,10 @@
       <c r="B12" s="35">
         <v>8</v>
       </c>
-      <c r="C12" s="96" t="s">
+      <c r="C12" s="112" t="s">
         <v>175</v>
       </c>
-      <c r="D12" s="97"/>
+      <c r="D12" s="113"/>
       <c r="F12" s="83" t="s">
         <v>101</v>
       </c>
@@ -40255,10 +40255,10 @@
       <c r="B13" s="35">
         <v>9</v>
       </c>
-      <c r="C13" s="96" t="s">
+      <c r="C13" s="112" t="s">
         <v>176</v>
       </c>
-      <c r="D13" s="97"/>
+      <c r="D13" s="113"/>
       <c r="F13" s="83" t="s">
         <v>101</v>
       </c>
@@ -40375,10 +40375,10 @@
       <c r="B14" s="35">
         <v>10</v>
       </c>
-      <c r="C14" s="96" t="s">
+      <c r="C14" s="112" t="s">
         <v>222</v>
       </c>
-      <c r="D14" s="97"/>
+      <c r="D14" s="113"/>
       <c r="F14" s="84" t="s">
         <v>116</v>
       </c>
@@ -40495,10 +40495,10 @@
       <c r="B15" s="35">
         <v>11</v>
       </c>
-      <c r="C15" s="96" t="s">
+      <c r="C15" s="112" t="s">
         <v>178</v>
       </c>
-      <c r="D15" s="97"/>
+      <c r="D15" s="113"/>
       <c r="F15" s="84" t="s">
         <v>116</v>
       </c>
@@ -40615,10 +40615,10 @@
       <c r="B16" s="35">
         <v>12</v>
       </c>
-      <c r="C16" s="96" t="s">
+      <c r="C16" s="112" t="s">
         <v>179</v>
       </c>
-      <c r="D16" s="97"/>
+      <c r="D16" s="113"/>
       <c r="F16" s="84" t="s">
         <v>96</v>
       </c>
@@ -40735,10 +40735,10 @@
       <c r="B17" s="35">
         <v>13</v>
       </c>
-      <c r="C17" s="96" t="s">
+      <c r="C17" s="112" t="s">
         <v>180</v>
       </c>
-      <c r="D17" s="97"/>
+      <c r="D17" s="113"/>
       <c r="F17" s="84" t="s">
         <v>96</v>
       </c>
@@ -40855,10 +40855,10 @@
       <c r="B18" s="35">
         <v>14</v>
       </c>
-      <c r="C18" s="96" t="s">
+      <c r="C18" s="112" t="s">
         <v>181</v>
       </c>
-      <c r="D18" s="97"/>
+      <c r="D18" s="113"/>
       <c r="F18" s="85" t="s">
         <v>101</v>
       </c>
@@ -40975,10 +40975,10 @@
       <c r="B19" s="35">
         <v>15</v>
       </c>
-      <c r="C19" s="96" t="s">
+      <c r="C19" s="112" t="s">
         <v>182</v>
       </c>
-      <c r="D19" s="97"/>
+      <c r="D19" s="113"/>
       <c r="F19" s="74" t="s">
         <v>116</v>
       </c>
@@ -41095,10 +41095,10 @@
       <c r="B20" s="35">
         <v>16</v>
       </c>
-      <c r="C20" s="96" t="s">
+      <c r="C20" s="112" t="s">
         <v>223</v>
       </c>
-      <c r="D20" s="97"/>
+      <c r="D20" s="113"/>
       <c r="F20" s="83" t="s">
         <v>96</v>
       </c>
@@ -41215,10 +41215,10 @@
       <c r="B21" s="35">
         <v>17</v>
       </c>
-      <c r="C21" s="96" t="s">
+      <c r="C21" s="112" t="s">
         <v>224</v>
       </c>
-      <c r="D21" s="97"/>
+      <c r="D21" s="113"/>
       <c r="F21" s="84" t="s">
         <v>102</v>
       </c>
@@ -41455,10 +41455,10 @@
       <c r="B23" s="35">
         <v>19</v>
       </c>
-      <c r="C23" s="98" t="s">
+      <c r="C23" s="126" t="s">
         <v>225</v>
       </c>
-      <c r="D23" s="99"/>
+      <c r="D23" s="127"/>
       <c r="F23" s="87" t="s">
         <v>101</v>
       </c>
@@ -41606,10 +41606,10 @@
       <c r="AI24" s="18"/>
     </row>
     <row r="25" spans="2:42" ht="18.75">
-      <c r="C25" s="119" t="s">
+      <c r="C25" s="109" t="s">
         <v>188</v>
       </c>
-      <c r="D25" s="120"/>
+      <c r="D25" s="110"/>
       <c r="E25" s="34"/>
       <c r="F25" s="35">
         <f>COUNTIF(F$5:F$21,"M*")</f>
@@ -41737,10 +41737,10 @@
       </c>
     </row>
     <row r="26" spans="2:42" ht="18.75">
-      <c r="C26" s="119" t="s">
+      <c r="C26" s="109" t="s">
         <v>189</v>
       </c>
-      <c r="D26" s="120"/>
+      <c r="D26" s="110"/>
       <c r="E26" s="34"/>
       <c r="F26" s="35">
         <f>COUNTIF(F$5:F$21,"A*")</f>
@@ -41868,10 +41868,10 @@
       </c>
     </row>
     <row r="27" spans="2:42" ht="18.75">
-      <c r="C27" s="119" t="s">
+      <c r="C27" s="109" t="s">
         <v>77</v>
       </c>
-      <c r="D27" s="120"/>
+      <c r="D27" s="110"/>
       <c r="E27" s="34"/>
       <c r="F27" s="35">
         <f>COUNTIF(F$5:F$21,"N*")</f>
@@ -41999,10 +41999,10 @@
       </c>
     </row>
     <row r="28" spans="2:42" ht="18.75">
-      <c r="C28" s="119" t="s">
+      <c r="C28" s="109" t="s">
         <v>78</v>
       </c>
-      <c r="D28" s="120"/>
+      <c r="D28" s="110"/>
       <c r="E28" s="34"/>
       <c r="F28" s="35">
         <f t="shared" ref="F28:AJ28" si="8">COUNTIF(F$5:F$23,"O*")</f>
@@ -42130,10 +42130,10 @@
       </c>
     </row>
     <row r="29" spans="2:42" ht="18.75">
-      <c r="C29" s="119" t="s">
+      <c r="C29" s="109" t="s">
         <v>190</v>
       </c>
-      <c r="D29" s="120"/>
+      <c r="D29" s="110"/>
       <c r="E29" s="34"/>
       <c r="F29" s="35">
         <f>COUNTIF(F$5:F$23,"TR*")</f>
@@ -42261,10 +42261,10 @@
       </c>
     </row>
     <row r="30" spans="2:42" ht="18.75">
-      <c r="C30" s="119" t="s">
+      <c r="C30" s="109" t="s">
         <v>191</v>
       </c>
-      <c r="D30" s="120"/>
+      <c r="D30" s="110"/>
       <c r="E30" s="34"/>
       <c r="F30" s="35">
         <f t="shared" ref="F30:AJ30" si="11">COUNTIF(F$5:F$23,"ST*")</f>
@@ -42392,10 +42392,10 @@
       </c>
     </row>
     <row r="31" spans="2:42" ht="18.75">
-      <c r="C31" s="158" t="s">
+      <c r="C31" s="128" t="s">
         <v>192</v>
       </c>
-      <c r="D31" s="159"/>
+      <c r="D31" s="129"/>
       <c r="E31" s="36"/>
       <c r="F31" s="37">
         <f>F33-F34</f>
@@ -42526,43 +42526,43 @@
       <c r="C32" s="38"/>
       <c r="D32" s="38"/>
       <c r="E32" s="34"/>
-      <c r="F32" s="122"/>
-      <c r="G32" s="122"/>
-      <c r="H32" s="122"/>
-      <c r="I32" s="122"/>
-      <c r="J32" s="122"/>
-      <c r="K32" s="122"/>
-      <c r="L32" s="122"/>
-      <c r="M32" s="122"/>
-      <c r="N32" s="122"/>
-      <c r="O32" s="122"/>
-      <c r="P32" s="122"/>
-      <c r="Q32" s="122"/>
-      <c r="R32" s="122"/>
-      <c r="S32" s="122"/>
-      <c r="T32" s="122"/>
-      <c r="U32" s="122"/>
-      <c r="V32" s="122"/>
-      <c r="W32" s="122"/>
-      <c r="X32" s="122"/>
-      <c r="Y32" s="122"/>
-      <c r="Z32" s="122"/>
-      <c r="AA32" s="122"/>
-      <c r="AB32" s="122"/>
-      <c r="AC32" s="122"/>
-      <c r="AD32" s="122"/>
-      <c r="AE32" s="122"/>
-      <c r="AF32" s="122"/>
-      <c r="AG32" s="122"/>
-      <c r="AH32" s="122"/>
-      <c r="AI32" s="122"/>
-      <c r="AJ32" s="122"/>
+      <c r="F32" s="108"/>
+      <c r="G32" s="108"/>
+      <c r="H32" s="108"/>
+      <c r="I32" s="108"/>
+      <c r="J32" s="108"/>
+      <c r="K32" s="108"/>
+      <c r="L32" s="108"/>
+      <c r="M32" s="108"/>
+      <c r="N32" s="108"/>
+      <c r="O32" s="108"/>
+      <c r="P32" s="108"/>
+      <c r="Q32" s="108"/>
+      <c r="R32" s="108"/>
+      <c r="S32" s="108"/>
+      <c r="T32" s="108"/>
+      <c r="U32" s="108"/>
+      <c r="V32" s="108"/>
+      <c r="W32" s="108"/>
+      <c r="X32" s="108"/>
+      <c r="Y32" s="108"/>
+      <c r="Z32" s="108"/>
+      <c r="AA32" s="108"/>
+      <c r="AB32" s="108"/>
+      <c r="AC32" s="108"/>
+      <c r="AD32" s="108"/>
+      <c r="AE32" s="108"/>
+      <c r="AF32" s="108"/>
+      <c r="AG32" s="108"/>
+      <c r="AH32" s="108"/>
+      <c r="AI32" s="108"/>
+      <c r="AJ32" s="108"/>
     </row>
     <row r="33" spans="3:36" ht="18.75">
-      <c r="C33" s="119" t="s">
+      <c r="C33" s="109" t="s">
         <v>193</v>
       </c>
-      <c r="D33" s="120"/>
+      <c r="D33" s="110"/>
       <c r="E33" s="34"/>
       <c r="F33" s="39">
         <f>SUM(F25:F27)</f>
@@ -42690,10 +42690,10 @@
       </c>
     </row>
     <row r="34" spans="3:36" ht="18.75">
-      <c r="C34" s="119" t="s">
+      <c r="C34" s="109" t="s">
         <v>194</v>
       </c>
-      <c r="D34" s="120"/>
+      <c r="D34" s="110"/>
       <c r="E34" s="34"/>
       <c r="F34" s="35">
         <v>9</v>
@@ -42790,10 +42790,10 @@
       </c>
     </row>
     <row r="35" spans="3:36" ht="18.75">
-      <c r="C35" s="119" t="s">
+      <c r="C35" s="109" t="s">
         <v>195</v>
       </c>
-      <c r="D35" s="120"/>
+      <c r="D35" s="110"/>
       <c r="E35" s="34"/>
       <c r="F35" s="35">
         <f>SUM(F25,F26,F27,F28,F30)</f>
@@ -42922,182 +42922,145 @@
     </row>
     <row r="37" spans="3:36" ht="16.5" thickBot="1"/>
     <row r="38" spans="3:36" ht="16.5" thickBot="1">
-      <c r="F38" s="110" t="s">
+      <c r="F38" s="95" t="s">
         <v>196</v>
       </c>
-      <c r="G38" s="111"/>
-      <c r="H38" s="111"/>
-      <c r="I38" s="111"/>
-      <c r="J38" s="111"/>
-      <c r="K38" s="112"/>
+      <c r="G38" s="96"/>
+      <c r="H38" s="96"/>
+      <c r="I38" s="96"/>
+      <c r="J38" s="96"/>
+      <c r="K38" s="97"/>
     </row>
     <row r="39" spans="3:36">
       <c r="F39" s="80" t="s">
         <v>197</v>
       </c>
-      <c r="G39" s="113" t="s">
+      <c r="G39" s="106" t="s">
         <v>198</v>
       </c>
-      <c r="H39" s="113"/>
+      <c r="H39" s="106"/>
       <c r="I39" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="J39" s="94" t="s">
+      <c r="J39" s="98" t="s">
         <v>199</v>
       </c>
-      <c r="K39" s="95"/>
+      <c r="K39" s="99"/>
     </row>
     <row r="40" spans="3:36">
       <c r="F40" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="G40" s="114" t="s">
+      <c r="G40" s="107" t="s">
         <v>200</v>
       </c>
-      <c r="H40" s="114"/>
+      <c r="H40" s="107"/>
       <c r="I40" s="77" t="s">
         <v>201</v>
       </c>
-      <c r="J40" s="115" t="s">
+      <c r="J40" s="100" t="s">
         <v>202</v>
       </c>
-      <c r="K40" s="116"/>
+      <c r="K40" s="101"/>
     </row>
     <row r="41" spans="3:36">
       <c r="F41" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="G41" s="100" t="s">
+      <c r="G41" s="102" t="s">
         <v>203</v>
       </c>
-      <c r="H41" s="100"/>
+      <c r="H41" s="102"/>
       <c r="I41" s="78" t="s">
         <v>108</v>
       </c>
-      <c r="J41" s="100" t="s">
+      <c r="J41" s="102" t="s">
         <v>204</v>
       </c>
-      <c r="K41" s="101"/>
+      <c r="K41" s="103"/>
     </row>
     <row r="42" spans="3:36">
       <c r="F42" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="G42" s="105" t="s">
+      <c r="G42" s="111" t="s">
         <v>205</v>
       </c>
-      <c r="H42" s="105"/>
+      <c r="H42" s="111"/>
       <c r="I42" s="79" t="s">
         <v>206</v>
       </c>
-      <c r="J42" s="117" t="s">
+      <c r="J42" s="104" t="s">
         <v>207</v>
       </c>
-      <c r="K42" s="118"/>
+      <c r="K42" s="105"/>
     </row>
     <row r="43" spans="3:36">
       <c r="F43" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="G43" s="105" t="s">
+      <c r="G43" s="111" t="s">
         <v>208</v>
       </c>
-      <c r="H43" s="105"/>
+      <c r="H43" s="111"/>
       <c r="I43" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="J43" s="106" t="s">
+      <c r="J43" s="93" t="s">
         <v>209</v>
       </c>
-      <c r="K43" s="107"/>
+      <c r="K43" s="94"/>
     </row>
     <row r="44" spans="3:36">
       <c r="F44" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="G44" s="108" t="s">
+      <c r="G44" s="92" t="s">
         <v>210</v>
       </c>
-      <c r="H44" s="108"/>
+      <c r="H44" s="92"/>
       <c r="I44" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="J44" s="106" t="s">
+      <c r="J44" s="93" t="s">
         <v>211</v>
       </c>
-      <c r="K44" s="107"/>
+      <c r="K44" s="94"/>
     </row>
     <row r="45" spans="3:36">
       <c r="F45" s="82" t="s">
         <v>212</v>
       </c>
-      <c r="G45" s="109" t="s">
+      <c r="G45" s="123" t="s">
         <v>213</v>
       </c>
-      <c r="H45" s="109"/>
+      <c r="H45" s="123"/>
       <c r="I45" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="J45" s="106" t="s">
+      <c r="J45" s="93" t="s">
         <v>214</v>
       </c>
-      <c r="K45" s="107"/>
+      <c r="K45" s="94"/>
     </row>
     <row r="46" spans="3:36" ht="16.5" thickBot="1">
       <c r="F46" s="55" t="s">
         <v>215</v>
       </c>
-      <c r="G46" s="92" t="s">
+      <c r="G46" s="124" t="s">
         <v>216</v>
       </c>
-      <c r="H46" s="92"/>
+      <c r="H46" s="124"/>
       <c r="I46" s="56" t="s">
         <v>167</v>
       </c>
-      <c r="J46" s="92" t="s">
+      <c r="J46" s="124" t="s">
         <v>217</v>
       </c>
-      <c r="K46" s="93"/>
+      <c r="K46" s="125"/>
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="G44:H44"/>
-    <mergeCell ref="J44:K44"/>
-    <mergeCell ref="F38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="J42:K42"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="F32:AJ32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="AO2:AO4"/>
-    <mergeCell ref="AP2:AP4"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F2:AJ2"/>
-    <mergeCell ref="AL2:AL4"/>
-    <mergeCell ref="AM2:AM4"/>
-    <mergeCell ref="AN2:AN4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="B3:D4"/>
     <mergeCell ref="G45:H45"/>
     <mergeCell ref="J45:K45"/>
     <mergeCell ref="G46:H46"/>
@@ -43114,6 +43077,43 @@
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="C31:D31"/>
+    <mergeCell ref="AO2:AO4"/>
+    <mergeCell ref="AP2:AP4"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F2:AJ2"/>
+    <mergeCell ref="AL2:AL4"/>
+    <mergeCell ref="AM2:AM4"/>
+    <mergeCell ref="AN2:AN4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="B3:D4"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F32:AJ32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="J44:K44"/>
+    <mergeCell ref="F38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="G40:H40"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F5:AI23">
@@ -43195,19 +43195,19 @@
       <c r="AG2" s="164"/>
       <c r="AH2" s="164"/>
       <c r="AI2" s="164"/>
-      <c r="AK2" s="137" t="s">
+      <c r="AK2" s="114" t="s">
         <v>80</v>
       </c>
-      <c r="AL2" s="137" t="s">
+      <c r="AL2" s="114" t="s">
         <v>81</v>
       </c>
-      <c r="AM2" s="137" t="s">
+      <c r="AM2" s="114" t="s">
         <v>82</v>
       </c>
-      <c r="AN2" s="137" t="s">
+      <c r="AN2" s="114" t="s">
         <v>83</v>
       </c>
-      <c r="AO2" s="137" t="s">
+      <c r="AO2" s="114" t="s">
         <v>84</v>
       </c>
     </row>
@@ -43307,11 +43307,11 @@
         <v>87</v>
       </c>
       <c r="AI3" s="29"/>
-      <c r="AK3" s="138"/>
-      <c r="AL3" s="138"/>
-      <c r="AM3" s="138"/>
-      <c r="AN3" s="138"/>
-      <c r="AO3" s="138"/>
+      <c r="AK3" s="115"/>
+      <c r="AL3" s="115"/>
+      <c r="AM3" s="115"/>
+      <c r="AN3" s="115"/>
+      <c r="AO3" s="115"/>
     </row>
     <row r="4" spans="2:41" ht="19.5" thickBot="1">
       <c r="B4" s="167"/>
@@ -43407,11 +43407,11 @@
         <v>30</v>
       </c>
       <c r="AI4" s="33"/>
-      <c r="AK4" s="139"/>
-      <c r="AL4" s="139"/>
-      <c r="AM4" s="139"/>
-      <c r="AN4" s="139"/>
-      <c r="AO4" s="139"/>
+      <c r="AK4" s="116"/>
+      <c r="AL4" s="116"/>
+      <c r="AM4" s="116"/>
+      <c r="AN4" s="116"/>
+      <c r="AO4" s="116"/>
     </row>
     <row r="5" spans="2:41" ht="18.75">
       <c r="B5" s="163" t="s">
@@ -44735,10 +44735,10 @@
       <c r="AH16" s="18"/>
     </row>
     <row r="17" spans="2:35" ht="18.75">
-      <c r="B17" s="123" t="s">
+      <c r="B17" s="153" t="s">
         <v>188</v>
       </c>
-      <c r="C17" s="123"/>
+      <c r="C17" s="153"/>
       <c r="D17" s="34"/>
       <c r="E17" s="35">
         <f t="shared" ref="E17:AH17" si="5">COUNTIF(E$5:E$15,"M*")</f>
@@ -44865,10 +44865,10 @@
       </c>
     </row>
     <row r="18" spans="2:35" ht="18.75">
-      <c r="B18" s="123" t="s">
+      <c r="B18" s="153" t="s">
         <v>189</v>
       </c>
-      <c r="C18" s="123"/>
+      <c r="C18" s="153"/>
       <c r="D18" s="34"/>
       <c r="E18" s="35">
         <f t="shared" ref="E18:AH18" si="6">COUNTIF(E$5:E$15,"A*")</f>
@@ -44995,10 +44995,10 @@
       </c>
     </row>
     <row r="19" spans="2:35" ht="18.75">
-      <c r="B19" s="123" t="s">
+      <c r="B19" s="153" t="s">
         <v>77</v>
       </c>
-      <c r="C19" s="123"/>
+      <c r="C19" s="153"/>
       <c r="D19" s="34"/>
       <c r="E19" s="35">
         <f t="shared" ref="E19:AH19" si="7">COUNTIF(E$5:E$15,"N*")</f>
@@ -45125,10 +45125,10 @@
       </c>
     </row>
     <row r="20" spans="2:35" ht="18.75">
-      <c r="B20" s="123" t="s">
+      <c r="B20" s="153" t="s">
         <v>78</v>
       </c>
-      <c r="C20" s="123"/>
+      <c r="C20" s="153"/>
       <c r="D20" s="34"/>
       <c r="E20" s="35">
         <f t="shared" ref="E20:AH20" si="8">COUNTIF(E$5:E$15,"O*")</f>
@@ -45255,10 +45255,10 @@
       </c>
     </row>
     <row r="21" spans="2:35" ht="18.75">
-      <c r="B21" s="119" t="s">
+      <c r="B21" s="109" t="s">
         <v>191</v>
       </c>
-      <c r="C21" s="120"/>
+      <c r="C21" s="110"/>
       <c r="D21" s="34"/>
       <c r="E21" s="35">
         <f t="shared" ref="E21:AH21" si="9">COUNTIF(E$5:E$15,"ST*")</f>
@@ -45385,10 +45385,10 @@
       </c>
     </row>
     <row r="22" spans="2:35" ht="18.75">
-      <c r="B22" s="121" t="s">
+      <c r="B22" s="152" t="s">
         <v>192</v>
       </c>
-      <c r="C22" s="121"/>
+      <c r="C22" s="152"/>
       <c r="D22" s="36"/>
       <c r="E22" s="37">
         <f>E24-E25</f>
@@ -45518,43 +45518,43 @@
       <c r="B23" s="38"/>
       <c r="C23" s="38"/>
       <c r="D23" s="34"/>
-      <c r="E23" s="122"/>
-      <c r="F23" s="122"/>
-      <c r="G23" s="122"/>
-      <c r="H23" s="122"/>
-      <c r="I23" s="122"/>
-      <c r="J23" s="122"/>
-      <c r="K23" s="122"/>
-      <c r="L23" s="122"/>
-      <c r="M23" s="122"/>
-      <c r="N23" s="122"/>
-      <c r="O23" s="122"/>
-      <c r="P23" s="122"/>
-      <c r="Q23" s="122"/>
-      <c r="R23" s="122"/>
-      <c r="S23" s="122"/>
-      <c r="T23" s="122"/>
-      <c r="U23" s="122"/>
-      <c r="V23" s="122"/>
-      <c r="W23" s="122"/>
-      <c r="X23" s="122"/>
-      <c r="Y23" s="122"/>
-      <c r="Z23" s="122"/>
-      <c r="AA23" s="122"/>
-      <c r="AB23" s="122"/>
-      <c r="AC23" s="122"/>
-      <c r="AD23" s="122"/>
-      <c r="AE23" s="122"/>
-      <c r="AF23" s="122"/>
-      <c r="AG23" s="122"/>
-      <c r="AH23" s="122"/>
-      <c r="AI23" s="122"/>
+      <c r="E23" s="108"/>
+      <c r="F23" s="108"/>
+      <c r="G23" s="108"/>
+      <c r="H23" s="108"/>
+      <c r="I23" s="108"/>
+      <c r="J23" s="108"/>
+      <c r="K23" s="108"/>
+      <c r="L23" s="108"/>
+      <c r="M23" s="108"/>
+      <c r="N23" s="108"/>
+      <c r="O23" s="108"/>
+      <c r="P23" s="108"/>
+      <c r="Q23" s="108"/>
+      <c r="R23" s="108"/>
+      <c r="S23" s="108"/>
+      <c r="T23" s="108"/>
+      <c r="U23" s="108"/>
+      <c r="V23" s="108"/>
+      <c r="W23" s="108"/>
+      <c r="X23" s="108"/>
+      <c r="Y23" s="108"/>
+      <c r="Z23" s="108"/>
+      <c r="AA23" s="108"/>
+      <c r="AB23" s="108"/>
+      <c r="AC23" s="108"/>
+      <c r="AD23" s="108"/>
+      <c r="AE23" s="108"/>
+      <c r="AF23" s="108"/>
+      <c r="AG23" s="108"/>
+      <c r="AH23" s="108"/>
+      <c r="AI23" s="108"/>
     </row>
     <row r="24" spans="2:35" ht="18.75">
-      <c r="B24" s="123" t="s">
+      <c r="B24" s="153" t="s">
         <v>193</v>
       </c>
-      <c r="C24" s="123"/>
+      <c r="C24" s="153"/>
       <c r="D24" s="34"/>
       <c r="E24" s="39">
         <f>SUM(E17:E19)</f>
@@ -45681,10 +45681,10 @@
       </c>
     </row>
     <row r="25" spans="2:35" ht="18.75">
-      <c r="B25" s="123" t="s">
+      <c r="B25" s="153" t="s">
         <v>194</v>
       </c>
-      <c r="C25" s="123"/>
+      <c r="C25" s="153"/>
       <c r="D25" s="34"/>
       <c r="E25" s="35">
         <v>7</v>
@@ -45781,10 +45781,10 @@
       </c>
     </row>
     <row r="26" spans="2:35" ht="18.75">
-      <c r="B26" s="123" t="s">
+      <c r="B26" s="153" t="s">
         <v>195</v>
       </c>
-      <c r="C26" s="123"/>
+      <c r="C26" s="153"/>
       <c r="D26" s="34"/>
       <c r="E26" s="35">
         <v>11</v>
@@ -45882,22 +45882,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="E23:AI23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
     <mergeCell ref="AN2:AN4"/>
     <mergeCell ref="AO2:AO4"/>
     <mergeCell ref="B9:C9"/>
@@ -45910,6 +45894,22 @@
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
+    <mergeCell ref="E23:AI23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
   </mergeCells>
   <conditionalFormatting sqref="E5:AH10">
     <cfRule type="containsText" dxfId="34" priority="23" operator="containsText" text="STN">
@@ -46062,6 +46062,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_activity xmlns="0ecd8b7c-869e-4f04-a6a3-066c3c63b311" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="مستند" ma:contentTypeID="0x01010053585A714B17B949862FA1B71BD97610" ma:contentTypeVersion="20" ma:contentTypeDescription="إنشاء مستند جديد." ma:contentTypeScope="" ma:versionID="dd8bd6d392f178541f6ccf1c351709a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns3="f1e9c892-1499-41bb-8a64-60ef909d8682" xmlns:ns4="0ecd8b7c-869e-4f04-a6a3-066c3c63b311" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9f246d41c9a2b9a4922388dcb99eeb28" ns1:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -46331,27 +46350,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_activity xmlns="0ecd8b7c-869e-4f04-a6a3-066c3c63b311" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57D06F05-5672-4668-89C3-4F6754D4BC82}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04335F04-3ECE-4043-846B-35335B1D83ED}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -46359,7 +46359,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04335F04-3ECE-4043-846B-35335B1D83ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57D06F05-5672-4668-89C3-4F6754D4BC82}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/rosters/.versions/2026-06/previous.xlsx
+++ b/rosters/.versions/2026-06/previous.xlsx
@@ -5853,7 +5853,7 @@
     <xf numFmtId="0" fontId="18" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5862,47 +5862,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -5910,14 +5886,11 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5946,38 +5919,71 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5988,25 +5994,22 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6024,20 +6027,17 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -7523,91 +7523,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:40" ht="9" customHeight="1">
-      <c r="E1" s="137"/>
-      <c r="F1" s="137"/>
-      <c r="G1" s="137"/>
-      <c r="H1" s="137"/>
-      <c r="I1" s="137"/>
-      <c r="J1" s="137"/>
-      <c r="K1" s="137"/>
-      <c r="L1" s="137"/>
-      <c r="M1" s="137"/>
-      <c r="N1" s="137"/>
-      <c r="O1" s="137"/>
-      <c r="P1" s="137"/>
-      <c r="Q1" s="137"/>
-      <c r="R1" s="137"/>
-      <c r="S1" s="137"/>
-      <c r="T1" s="137"/>
-      <c r="U1" s="137"/>
-      <c r="V1" s="137"/>
-      <c r="W1" s="137"/>
-      <c r="X1" s="137"/>
-      <c r="Y1" s="137"/>
-      <c r="Z1" s="137"/>
-      <c r="AA1" s="137"/>
-      <c r="AB1" s="137"/>
-      <c r="AC1" s="137"/>
-      <c r="AD1" s="137"/>
-      <c r="AE1" s="137"/>
-      <c r="AF1" s="137"/>
-      <c r="AG1" s="137"/>
-      <c r="AH1" s="137"/>
-      <c r="AI1" s="137"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
+      <c r="J1" s="130"/>
+      <c r="K1" s="130"/>
+      <c r="L1" s="130"/>
+      <c r="M1" s="130"/>
+      <c r="N1" s="130"/>
+      <c r="O1" s="130"/>
+      <c r="P1" s="130"/>
+      <c r="Q1" s="130"/>
+      <c r="R1" s="130"/>
+      <c r="S1" s="130"/>
+      <c r="T1" s="130"/>
+      <c r="U1" s="130"/>
+      <c r="V1" s="130"/>
+      <c r="W1" s="130"/>
+      <c r="X1" s="130"/>
+      <c r="Y1" s="130"/>
+      <c r="Z1" s="130"/>
+      <c r="AA1" s="130"/>
+      <c r="AB1" s="130"/>
+      <c r="AC1" s="130"/>
+      <c r="AD1" s="130"/>
+      <c r="AE1" s="130"/>
+      <c r="AF1" s="130"/>
+      <c r="AG1" s="130"/>
+      <c r="AH1" s="130"/>
+      <c r="AI1" s="130"/>
     </row>
     <row r="2" spans="2:40" ht="28.5">
-      <c r="B2" s="135" t="s">
+      <c r="B2" s="137" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="135"/>
+      <c r="C2" s="137"/>
       <c r="D2" s="9"/>
-      <c r="E2" s="136" t="s">
+      <c r="E2" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="136"/>
-      <c r="G2" s="136"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="136"/>
-      <c r="J2" s="136"/>
-      <c r="K2" s="136"/>
-      <c r="L2" s="136"/>
-      <c r="M2" s="136"/>
-      <c r="N2" s="136"/>
-      <c r="O2" s="136"/>
-      <c r="P2" s="136"/>
-      <c r="Q2" s="136"/>
-      <c r="R2" s="136"/>
-      <c r="S2" s="136"/>
-      <c r="T2" s="136"/>
-      <c r="U2" s="136"/>
-      <c r="V2" s="136"/>
-      <c r="W2" s="136" t="s">
+      <c r="F2" s="138"/>
+      <c r="G2" s="138"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="138"/>
+      <c r="L2" s="138"/>
+      <c r="M2" s="138"/>
+      <c r="N2" s="138"/>
+      <c r="O2" s="138"/>
+      <c r="P2" s="138"/>
+      <c r="Q2" s="138"/>
+      <c r="R2" s="138"/>
+      <c r="S2" s="138"/>
+      <c r="T2" s="138"/>
+      <c r="U2" s="138"/>
+      <c r="V2" s="138"/>
+      <c r="W2" s="138" t="s">
         <v>28</v>
       </c>
-      <c r="X2" s="136"/>
-      <c r="Y2" s="136"/>
-      <c r="Z2" s="136"/>
-      <c r="AA2" s="136"/>
-      <c r="AB2" s="136"/>
-      <c r="AC2" s="136">
+      <c r="X2" s="138"/>
+      <c r="Y2" s="138"/>
+      <c r="Z2" s="138"/>
+      <c r="AA2" s="138"/>
+      <c r="AB2" s="138"/>
+      <c r="AC2" s="138">
         <v>2025</v>
       </c>
-      <c r="AD2" s="136"/>
-      <c r="AE2" s="136"/>
-      <c r="AF2" s="136"/>
+      <c r="AD2" s="138"/>
+      <c r="AE2" s="138"/>
+      <c r="AF2" s="138"/>
       <c r="AG2" s="5"/>
       <c r="AH2" s="5"/>
       <c r="AI2" s="5"/>
-      <c r="AK2" s="130" t="s">
+      <c r="AK2" s="134" t="s">
         <v>34</v>
       </c>
-      <c r="AL2" s="130"/>
-      <c r="AM2" s="130"/>
-      <c r="AN2" s="130"/>
+      <c r="AL2" s="134"/>
+      <c r="AM2" s="134"/>
+      <c r="AN2" s="134"/>
     </row>
     <row r="3" spans="2:40">
-      <c r="B3" s="135"/>
-      <c r="C3" s="135"/>
+      <c r="B3" s="137"/>
+      <c r="C3" s="137"/>
       <c r="D3" s="10"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -7640,14 +7640,14 @@
       <c r="AG3" s="3"/>
       <c r="AH3" s="3"/>
       <c r="AI3" s="3"/>
-      <c r="AK3" s="130"/>
-      <c r="AL3" s="130"/>
-      <c r="AM3" s="130"/>
-      <c r="AN3" s="130"/>
+      <c r="AK3" s="134"/>
+      <c r="AL3" s="134"/>
+      <c r="AM3" s="134"/>
+      <c r="AN3" s="134"/>
     </row>
     <row r="4" spans="2:40">
-      <c r="B4" s="135"/>
-      <c r="C4" s="135"/>
+      <c r="B4" s="137"/>
+      <c r="C4" s="137"/>
       <c r="D4" s="10"/>
       <c r="E4" s="131" t="s">
         <v>35</v>
@@ -7661,37 +7661,37 @@
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
-      <c r="M4" s="133" t="s">
+      <c r="M4" s="132" t="s">
         <v>36</v>
       </c>
-      <c r="N4" s="133"/>
-      <c r="O4" s="133"/>
-      <c r="P4" s="138">
+      <c r="N4" s="132"/>
+      <c r="O4" s="132"/>
+      <c r="P4" s="133">
         <f>IFERROR(DATEVALUE(J4&amp;W2&amp;AC2),"")</f>
         <v>45901</v>
       </c>
-      <c r="Q4" s="138"/>
-      <c r="R4" s="138"/>
+      <c r="Q4" s="133"/>
+      <c r="R4" s="133"/>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
-      <c r="U4" s="133" t="s">
+      <c r="U4" s="132" t="s">
         <v>37</v>
       </c>
-      <c r="V4" s="133"/>
-      <c r="W4" s="133"/>
-      <c r="X4" s="138">
+      <c r="V4" s="132"/>
+      <c r="W4" s="132"/>
+      <c r="X4" s="133">
         <f>IFERROR(EOMONTH(P4,0)+J4-1,"")</f>
         <v>45930</v>
       </c>
-      <c r="Y4" s="138"/>
-      <c r="Z4" s="138"/>
+      <c r="Y4" s="133"/>
+      <c r="Z4" s="133"/>
       <c r="AA4" s="3"/>
       <c r="AB4" s="3"/>
-      <c r="AC4" s="133" t="s">
+      <c r="AC4" s="132" t="s">
         <v>38</v>
       </c>
-      <c r="AD4" s="133"/>
-      <c r="AE4" s="133"/>
+      <c r="AD4" s="132"/>
+      <c r="AE4" s="132"/>
       <c r="AF4" s="3">
         <f>COUNTIF(E6:AI6,"*?")</f>
         <v>30</v>
@@ -7699,10 +7699,10 @@
       <c r="AG4" s="3"/>
       <c r="AH4" s="3"/>
       <c r="AI4" s="3"/>
-      <c r="AK4" s="130"/>
-      <c r="AL4" s="130"/>
-      <c r="AM4" s="130"/>
-      <c r="AN4" s="130"/>
+      <c r="AK4" s="134"/>
+      <c r="AL4" s="134"/>
+      <c r="AM4" s="134"/>
+      <c r="AN4" s="134"/>
     </row>
     <row r="5" spans="2:40" ht="6.75" customHeight="1">
       <c r="B5" s="6"/>
@@ -7741,10 +7741,10 @@
       <c r="AI5" s="3"/>
     </row>
     <row r="6" spans="2:40" ht="27.75">
-      <c r="B6" s="134" t="s">
+      <c r="B6" s="136" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="134" t="s">
+      <c r="C6" s="136" t="s">
         <v>40</v>
       </c>
       <c r="D6" s="12"/>
@@ -7873,22 +7873,22 @@
         <v/>
       </c>
       <c r="AJ6" s="14"/>
-      <c r="AK6" s="132" t="s">
+      <c r="AK6" s="135" t="s">
         <v>41</v>
       </c>
-      <c r="AL6" s="132" t="s">
+      <c r="AL6" s="135" t="s">
         <v>42</v>
       </c>
-      <c r="AM6" s="132" t="s">
+      <c r="AM6" s="135" t="s">
         <v>43</v>
       </c>
-      <c r="AN6" s="132" t="s">
+      <c r="AN6" s="135" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="7" spans="2:40">
-      <c r="B7" s="134"/>
-      <c r="C7" s="134"/>
+      <c r="B7" s="136"/>
+      <c r="C7" s="136"/>
       <c r="D7" s="12"/>
       <c r="E7" s="15">
         <f>P4</f>
@@ -8015,10 +8015,10 @@
         <v/>
       </c>
       <c r="AJ7" s="14"/>
-      <c r="AK7" s="132"/>
-      <c r="AL7" s="132"/>
-      <c r="AM7" s="132"/>
-      <c r="AN7" s="132"/>
+      <c r="AK7" s="135"/>
+      <c r="AL7" s="135"/>
+      <c r="AM7" s="135"/>
+      <c r="AN7" s="135"/>
     </row>
     <row r="8" spans="2:40">
       <c r="B8" s="3" t="s">
@@ -12998,12 +12998,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="E1:AI1"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="M4:O4"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="U4:W4"/>
-    <mergeCell ref="X4:Z4"/>
     <mergeCell ref="AK2:AN4"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="B42:C42"/>
@@ -13020,6 +13014,12 @@
     <mergeCell ref="E2:V2"/>
     <mergeCell ref="W2:AB2"/>
     <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="E1:AI1"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="U4:W4"/>
+    <mergeCell ref="X4:Z4"/>
   </mergeCells>
   <conditionalFormatting sqref="E8:AI37 AK8:AN37 E39:AI42">
     <cfRule type="expression" dxfId="112" priority="4">
@@ -13083,61 +13083,61 @@
   <sheetData>
     <row r="1" spans="2:42" ht="16.5" thickBot="1"/>
     <row r="2" spans="2:42" ht="39" customHeight="1" thickBot="1">
-      <c r="F2" s="139" t="s">
+      <c r="F2" s="151" t="s">
         <v>79</v>
       </c>
-      <c r="G2" s="140"/>
-      <c r="H2" s="140"/>
-      <c r="I2" s="140"/>
-      <c r="J2" s="140"/>
-      <c r="K2" s="140"/>
-      <c r="L2" s="140"/>
-      <c r="M2" s="140"/>
-      <c r="N2" s="140"/>
-      <c r="O2" s="140"/>
-      <c r="P2" s="140"/>
-      <c r="Q2" s="140"/>
-      <c r="R2" s="140"/>
-      <c r="S2" s="140"/>
-      <c r="T2" s="140"/>
-      <c r="U2" s="140"/>
-      <c r="V2" s="140"/>
-      <c r="W2" s="140"/>
-      <c r="X2" s="140"/>
-      <c r="Y2" s="140"/>
-      <c r="Z2" s="140"/>
-      <c r="AA2" s="140"/>
-      <c r="AB2" s="140"/>
-      <c r="AC2" s="140"/>
-      <c r="AD2" s="140"/>
-      <c r="AE2" s="140"/>
-      <c r="AF2" s="140"/>
-      <c r="AG2" s="140"/>
-      <c r="AH2" s="140"/>
-      <c r="AI2" s="140"/>
-      <c r="AJ2" s="141"/>
-      <c r="AL2" s="114" t="s">
+      <c r="G2" s="152"/>
+      <c r="H2" s="152"/>
+      <c r="I2" s="152"/>
+      <c r="J2" s="152"/>
+      <c r="K2" s="152"/>
+      <c r="L2" s="152"/>
+      <c r="M2" s="152"/>
+      <c r="N2" s="152"/>
+      <c r="O2" s="152"/>
+      <c r="P2" s="152"/>
+      <c r="Q2" s="152"/>
+      <c r="R2" s="152"/>
+      <c r="S2" s="152"/>
+      <c r="T2" s="152"/>
+      <c r="U2" s="152"/>
+      <c r="V2" s="152"/>
+      <c r="W2" s="152"/>
+      <c r="X2" s="152"/>
+      <c r="Y2" s="152"/>
+      <c r="Z2" s="152"/>
+      <c r="AA2" s="152"/>
+      <c r="AB2" s="152"/>
+      <c r="AC2" s="152"/>
+      <c r="AD2" s="152"/>
+      <c r="AE2" s="152"/>
+      <c r="AF2" s="152"/>
+      <c r="AG2" s="152"/>
+      <c r="AH2" s="152"/>
+      <c r="AI2" s="152"/>
+      <c r="AJ2" s="153"/>
+      <c r="AL2" s="105" t="s">
         <v>80</v>
       </c>
-      <c r="AM2" s="114" t="s">
+      <c r="AM2" s="105" t="s">
         <v>81</v>
       </c>
-      <c r="AN2" s="114" t="s">
+      <c r="AN2" s="105" t="s">
         <v>82</v>
       </c>
-      <c r="AO2" s="114" t="s">
+      <c r="AO2" s="105" t="s">
         <v>83</v>
       </c>
-      <c r="AP2" s="114" t="s">
+      <c r="AP2" s="105" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="3" spans="2:42" ht="39.75" thickBot="1">
-      <c r="B3" s="122" t="s">
+      <c r="B3" s="113" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="122"/>
-      <c r="D3" s="122"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="113"/>
       <c r="F3" s="43" t="s">
         <v>86</v>
       </c>
@@ -13229,16 +13229,16 @@
         <v>87</v>
       </c>
       <c r="AJ3" s="43"/>
-      <c r="AL3" s="115"/>
-      <c r="AM3" s="115"/>
-      <c r="AN3" s="115"/>
-      <c r="AO3" s="115"/>
-      <c r="AP3" s="115"/>
+      <c r="AL3" s="106"/>
+      <c r="AM3" s="106"/>
+      <c r="AN3" s="106"/>
+      <c r="AO3" s="106"/>
+      <c r="AP3" s="106"/>
     </row>
     <row r="4" spans="2:42" ht="19.5" customHeight="1" thickBot="1">
-      <c r="B4" s="122"/>
-      <c r="C4" s="122"/>
-      <c r="D4" s="122"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
       <c r="F4" s="40">
         <v>1</v>
       </c>
@@ -13330,20 +13330,20 @@
         <v>30</v>
       </c>
       <c r="AJ4" s="68"/>
-      <c r="AL4" s="116"/>
-      <c r="AM4" s="116"/>
-      <c r="AN4" s="116"/>
-      <c r="AO4" s="116"/>
-      <c r="AP4" s="116"/>
+      <c r="AL4" s="107"/>
+      <c r="AM4" s="107"/>
+      <c r="AN4" s="107"/>
+      <c r="AO4" s="107"/>
+      <c r="AP4" s="107"/>
     </row>
     <row r="5" spans="2:42" ht="19.5" customHeight="1">
       <c r="B5" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="C5" s="142" t="s">
+      <c r="C5" s="144" t="s">
         <v>94</v>
       </c>
-      <c r="D5" s="142"/>
+      <c r="D5" s="144"/>
       <c r="F5" s="84" t="s">
         <v>95</v>
       </c>
@@ -13460,10 +13460,10 @@
       <c r="B6" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="142" t="s">
+      <c r="C6" s="144" t="s">
         <v>99</v>
       </c>
-      <c r="D6" s="142"/>
+      <c r="D6" s="144"/>
       <c r="F6" s="75" t="s">
         <v>97</v>
       </c>
@@ -13580,10 +13580,10 @@
       <c r="B7" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="C7" s="142" t="s">
+      <c r="C7" s="144" t="s">
         <v>100</v>
       </c>
-      <c r="D7" s="142"/>
+      <c r="D7" s="144"/>
       <c r="F7" s="75" t="s">
         <v>101</v>
       </c>
@@ -13700,10 +13700,10 @@
       <c r="B8" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="C8" s="142" t="s">
+      <c r="C8" s="144" t="s">
         <v>103</v>
       </c>
-      <c r="D8" s="142"/>
+      <c r="D8" s="144"/>
       <c r="F8" s="75" t="s">
         <v>96</v>
       </c>
@@ -13820,10 +13820,10 @@
       <c r="B9" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="C9" s="142" t="s">
+      <c r="C9" s="144" t="s">
         <v>105</v>
       </c>
-      <c r="D9" s="142"/>
+      <c r="D9" s="144"/>
       <c r="F9" s="90" t="s">
         <v>106</v>
       </c>
@@ -13940,10 +13940,10 @@
       <c r="B10" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="C10" s="142" t="s">
+      <c r="C10" s="144" t="s">
         <v>109</v>
       </c>
-      <c r="D10" s="142"/>
+      <c r="D10" s="144"/>
       <c r="F10" s="75" t="s">
         <v>96</v>
       </c>
@@ -14060,10 +14060,10 @@
       <c r="B11" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="C11" s="142" t="s">
+      <c r="C11" s="144" t="s">
         <v>110</v>
       </c>
-      <c r="D11" s="142"/>
+      <c r="D11" s="144"/>
       <c r="F11" s="75" t="s">
         <v>95</v>
       </c>
@@ -14180,10 +14180,10 @@
       <c r="B12" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="142" t="s">
+      <c r="C12" s="144" t="s">
         <v>111</v>
       </c>
-      <c r="D12" s="142"/>
+      <c r="D12" s="144"/>
       <c r="F12" s="75" t="s">
         <v>107</v>
       </c>
@@ -14300,10 +14300,10 @@
       <c r="B13" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="C13" s="142" t="s">
+      <c r="C13" s="144" t="s">
         <v>112</v>
       </c>
-      <c r="D13" s="142"/>
+      <c r="D13" s="144"/>
       <c r="F13" s="75" t="s">
         <v>108</v>
       </c>
@@ -14421,10 +14421,10 @@
       <c r="B14" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="C14" s="142" t="s">
+      <c r="C14" s="144" t="s">
         <v>113</v>
       </c>
-      <c r="D14" s="142"/>
+      <c r="D14" s="144"/>
       <c r="F14" s="88" t="s">
         <v>95</v>
       </c>
@@ -14541,10 +14541,10 @@
       <c r="B15" s="35" t="s">
         <v>114</v>
       </c>
-      <c r="C15" s="144" t="s">
+      <c r="C15" s="145" t="s">
         <v>115</v>
       </c>
-      <c r="D15" s="145"/>
+      <c r="D15" s="146"/>
       <c r="E15" s="53"/>
       <c r="F15" s="72" t="s">
         <v>101</v>
@@ -14662,10 +14662,10 @@
       <c r="B16" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C16" s="142" t="s">
+      <c r="C16" s="144" t="s">
         <v>117</v>
       </c>
-      <c r="D16" s="143"/>
+      <c r="D16" s="150"/>
       <c r="E16" s="53"/>
       <c r="F16" s="74" t="s">
         <v>102</v>
@@ -14783,10 +14783,10 @@
       <c r="B17" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C17" s="142" t="s">
+      <c r="C17" s="144" t="s">
         <v>118</v>
       </c>
-      <c r="D17" s="143"/>
+      <c r="D17" s="150"/>
       <c r="E17" s="53"/>
       <c r="F17" s="75" t="s">
         <v>95</v>
@@ -14904,10 +14904,10 @@
       <c r="B18" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C18" s="142" t="s">
+      <c r="C18" s="144" t="s">
         <v>119</v>
       </c>
-      <c r="D18" s="143"/>
+      <c r="D18" s="150"/>
       <c r="E18" s="53"/>
       <c r="F18" s="75" t="s">
         <v>98</v>
@@ -15025,10 +15025,10 @@
       <c r="B19" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C19" s="142" t="s">
+      <c r="C19" s="144" t="s">
         <v>120</v>
       </c>
-      <c r="D19" s="143"/>
+      <c r="D19" s="150"/>
       <c r="E19" s="53"/>
       <c r="F19" s="75" t="s">
         <v>96</v>
@@ -15146,10 +15146,10 @@
       <c r="B20" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C20" s="142" t="s">
+      <c r="C20" s="144" t="s">
         <v>121</v>
       </c>
-      <c r="D20" s="143"/>
+      <c r="D20" s="150"/>
       <c r="E20" s="53"/>
       <c r="F20" s="75" t="s">
         <v>96</v>
@@ -15267,10 +15267,10 @@
       <c r="B21" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C21" s="142" t="s">
+      <c r="C21" s="144" t="s">
         <v>122</v>
       </c>
-      <c r="D21" s="143"/>
+      <c r="D21" s="150"/>
       <c r="E21" s="53"/>
       <c r="F21" s="75" t="s">
         <v>101</v>
@@ -15388,10 +15388,10 @@
       <c r="B22" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C22" s="142" t="s">
+      <c r="C22" s="144" t="s">
         <v>123</v>
       </c>
-      <c r="D22" s="143"/>
+      <c r="D22" s="150"/>
       <c r="E22" s="53"/>
       <c r="F22" s="75" t="s">
         <v>102</v>
@@ -15509,10 +15509,10 @@
       <c r="B23" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C23" s="142" t="s">
+      <c r="C23" s="144" t="s">
         <v>124</v>
       </c>
-      <c r="D23" s="143"/>
+      <c r="D23" s="150"/>
       <c r="E23" s="53"/>
       <c r="F23" s="74" t="s">
         <v>95</v>
@@ -15630,10 +15630,10 @@
       <c r="B24" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C24" s="142" t="s">
+      <c r="C24" s="144" t="s">
         <v>125</v>
       </c>
-      <c r="D24" s="143"/>
+      <c r="D24" s="150"/>
       <c r="E24" s="53"/>
       <c r="F24" s="75" t="s">
         <v>116</v>
@@ -15751,10 +15751,10 @@
       <c r="B25" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C25" s="112" t="s">
+      <c r="C25" s="97" t="s">
         <v>126</v>
       </c>
-      <c r="D25" s="146"/>
+      <c r="D25" s="147"/>
       <c r="E25" s="53"/>
       <c r="F25" s="75" t="s">
         <v>116</v>
@@ -15872,10 +15872,10 @@
       <c r="B26" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C26" s="112" t="s">
+      <c r="C26" s="97" t="s">
         <v>127</v>
       </c>
-      <c r="D26" s="146"/>
+      <c r="D26" s="147"/>
       <c r="E26" s="53"/>
       <c r="F26" s="75" t="s">
         <v>96</v>
@@ -15993,10 +15993,10 @@
       <c r="B27" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C27" s="112" t="s">
+      <c r="C27" s="97" t="s">
         <v>128</v>
       </c>
-      <c r="D27" s="146"/>
+      <c r="D27" s="147"/>
       <c r="E27" s="53"/>
       <c r="F27" s="75" t="s">
         <v>96</v>
@@ -16114,10 +16114,10 @@
       <c r="B28" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C28" s="112" t="s">
+      <c r="C28" s="97" t="s">
         <v>129</v>
       </c>
-      <c r="D28" s="146"/>
+      <c r="D28" s="147"/>
       <c r="E28" s="53"/>
       <c r="F28" s="75" t="s">
         <v>101</v>
@@ -16235,10 +16235,10 @@
       <c r="B29" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C29" s="147" t="s">
+      <c r="C29" s="148" t="s">
         <v>130</v>
       </c>
-      <c r="D29" s="148"/>
+      <c r="D29" s="149"/>
       <c r="E29" s="53"/>
       <c r="F29" s="74" t="s">
         <v>96</v>
@@ -16356,10 +16356,10 @@
       <c r="B30" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C30" s="142" t="s">
+      <c r="C30" s="144" t="s">
         <v>132</v>
       </c>
-      <c r="D30" s="142"/>
+      <c r="D30" s="144"/>
       <c r="F30" s="73" t="s">
         <v>102</v>
       </c>
@@ -16476,10 +16476,10 @@
       <c r="B31" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C31" s="142" t="s">
+      <c r="C31" s="144" t="s">
         <v>133</v>
       </c>
-      <c r="D31" s="142"/>
+      <c r="D31" s="144"/>
       <c r="F31" s="75" t="s">
         <v>102</v>
       </c>
@@ -16596,10 +16596,10 @@
       <c r="B32" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C32" s="142" t="s">
+      <c r="C32" s="144" t="s">
         <v>134</v>
       </c>
-      <c r="D32" s="142"/>
+      <c r="D32" s="144"/>
       <c r="F32" s="75" t="s">
         <v>98</v>
       </c>
@@ -16716,10 +16716,10 @@
       <c r="B33" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C33" s="142" t="s">
+      <c r="C33" s="144" t="s">
         <v>136</v>
       </c>
-      <c r="D33" s="142"/>
+      <c r="D33" s="144"/>
       <c r="F33" s="75" t="s">
         <v>95</v>
       </c>
@@ -16836,10 +16836,10 @@
       <c r="B34" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C34" s="142" t="s">
+      <c r="C34" s="144" t="s">
         <v>137</v>
       </c>
-      <c r="D34" s="142"/>
+      <c r="D34" s="144"/>
       <c r="F34" s="75" t="s">
         <v>96</v>
       </c>
@@ -16956,10 +16956,10 @@
       <c r="B35" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C35" s="142" t="s">
+      <c r="C35" s="144" t="s">
         <v>138</v>
       </c>
-      <c r="D35" s="142"/>
+      <c r="D35" s="144"/>
       <c r="F35" s="75" t="s">
         <v>96</v>
       </c>
@@ -17076,10 +17076,10 @@
       <c r="B36" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C36" s="142" t="s">
+      <c r="C36" s="144" t="s">
         <v>139</v>
       </c>
-      <c r="D36" s="142"/>
+      <c r="D36" s="144"/>
       <c r="F36" s="76" t="s">
         <v>101</v>
       </c>
@@ -17196,10 +17196,10 @@
       <c r="B37" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C37" s="142" t="s">
+      <c r="C37" s="144" t="s">
         <v>140</v>
       </c>
-      <c r="D37" s="142"/>
+      <c r="D37" s="144"/>
       <c r="F37" s="75" t="s">
         <v>101</v>
       </c>
@@ -17316,10 +17316,10 @@
       <c r="B38" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C38" s="142" t="s">
+      <c r="C38" s="144" t="s">
         <v>141</v>
       </c>
-      <c r="D38" s="142"/>
+      <c r="D38" s="144"/>
       <c r="F38" s="75" t="s">
         <v>102</v>
       </c>
@@ -17436,10 +17436,10 @@
       <c r="B39" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C39" s="142" t="s">
+      <c r="C39" s="144" t="s">
         <v>142</v>
       </c>
-      <c r="D39" s="142"/>
+      <c r="D39" s="144"/>
       <c r="F39" s="75" t="s">
         <v>116</v>
       </c>
@@ -17556,10 +17556,10 @@
       <c r="B40" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C40" s="142" t="s">
+      <c r="C40" s="144" t="s">
         <v>143</v>
       </c>
-      <c r="D40" s="142"/>
+      <c r="D40" s="144"/>
       <c r="F40" s="75" t="s">
         <v>116</v>
       </c>
@@ -17676,10 +17676,10 @@
       <c r="B41" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C41" s="142" t="s">
+      <c r="C41" s="144" t="s">
         <v>144</v>
       </c>
-      <c r="D41" s="142"/>
+      <c r="D41" s="144"/>
       <c r="F41" s="75" t="s">
         <v>96</v>
       </c>
@@ -17796,10 +17796,10 @@
       <c r="B42" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C42" s="142" t="s">
+      <c r="C42" s="144" t="s">
         <v>145</v>
       </c>
-      <c r="D42" s="142"/>
+      <c r="D42" s="144"/>
       <c r="F42" s="75" t="s">
         <v>96</v>
       </c>
@@ -17916,10 +17916,10 @@
       <c r="B43" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C43" s="142" t="s">
+      <c r="C43" s="144" t="s">
         <v>146</v>
       </c>
-      <c r="D43" s="142"/>
+      <c r="D43" s="144"/>
       <c r="F43" s="76" t="s">
         <v>101</v>
       </c>
@@ -18036,10 +18036,10 @@
       <c r="B44" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C44" s="142" t="s">
+      <c r="C44" s="144" t="s">
         <v>147</v>
       </c>
-      <c r="D44" s="142"/>
+      <c r="D44" s="144"/>
       <c r="F44" s="75" t="s">
         <v>102</v>
       </c>
@@ -18156,10 +18156,10 @@
       <c r="B45" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C45" s="142" t="s">
+      <c r="C45" s="144" t="s">
         <v>148</v>
       </c>
-      <c r="D45" s="142"/>
+      <c r="D45" s="144"/>
       <c r="F45" s="75" t="s">
         <v>102</v>
       </c>
@@ -18276,10 +18276,10 @@
       <c r="B46" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C46" s="142" t="s">
+      <c r="C46" s="144" t="s">
         <v>149</v>
       </c>
-      <c r="D46" s="142"/>
+      <c r="D46" s="144"/>
       <c r="F46" s="75" t="s">
         <v>116</v>
       </c>
@@ -18396,10 +18396,10 @@
       <c r="B47" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C47" s="142" t="s">
+      <c r="C47" s="144" t="s">
         <v>150</v>
       </c>
-      <c r="D47" s="142"/>
+      <c r="D47" s="144"/>
       <c r="F47" s="75" t="s">
         <v>116</v>
       </c>
@@ -18516,10 +18516,10 @@
       <c r="B48" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C48" s="142" t="s">
+      <c r="C48" s="144" t="s">
         <v>151</v>
       </c>
-      <c r="D48" s="142"/>
+      <c r="D48" s="144"/>
       <c r="F48" s="75" t="s">
         <v>96</v>
       </c>
@@ -18636,10 +18636,10 @@
       <c r="B49" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C49" s="142" t="s">
+      <c r="C49" s="144" t="s">
         <v>152</v>
       </c>
-      <c r="D49" s="142"/>
+      <c r="D49" s="144"/>
       <c r="F49" s="75" t="s">
         <v>96</v>
       </c>
@@ -18756,10 +18756,10 @@
       <c r="B50" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C50" s="142" t="s">
+      <c r="C50" s="144" t="s">
         <v>153</v>
       </c>
-      <c r="D50" s="142"/>
+      <c r="D50" s="144"/>
       <c r="F50" s="76" t="s">
         <v>95</v>
       </c>
@@ -18876,10 +18876,10 @@
       <c r="B51" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C51" s="142" t="s">
+      <c r="C51" s="144" t="s">
         <v>154</v>
       </c>
-      <c r="D51" s="142"/>
+      <c r="D51" s="144"/>
       <c r="F51" s="75" t="s">
         <v>101</v>
       </c>
@@ -18996,10 +18996,10 @@
       <c r="B52" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C52" s="142" t="s">
+      <c r="C52" s="144" t="s">
         <v>155</v>
       </c>
-      <c r="D52" s="142"/>
+      <c r="D52" s="144"/>
       <c r="F52" s="75" t="s">
         <v>102</v>
       </c>
@@ -19116,10 +19116,10 @@
       <c r="B53" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C53" s="142" t="s">
+      <c r="C53" s="144" t="s">
         <v>156</v>
       </c>
-      <c r="D53" s="142"/>
+      <c r="D53" s="144"/>
       <c r="F53" s="75" t="s">
         <v>116</v>
       </c>
@@ -19236,10 +19236,10 @@
       <c r="B54" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C54" s="142" t="s">
+      <c r="C54" s="144" t="s">
         <v>157</v>
       </c>
-      <c r="D54" s="142"/>
+      <c r="D54" s="144"/>
       <c r="F54" s="75" t="s">
         <v>116</v>
       </c>
@@ -19356,10 +19356,10 @@
       <c r="B55" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C55" s="112" t="s">
+      <c r="C55" s="97" t="s">
         <v>158</v>
       </c>
-      <c r="D55" s="113"/>
+      <c r="D55" s="98"/>
       <c r="F55" s="75" t="s">
         <v>96</v>
       </c>
@@ -19476,10 +19476,10 @@
       <c r="B56" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C56" s="112" t="s">
+      <c r="C56" s="97" t="s">
         <v>159</v>
       </c>
-      <c r="D56" s="113"/>
+      <c r="D56" s="98"/>
       <c r="F56" s="75" t="s">
         <v>96</v>
       </c>
@@ -19596,10 +19596,10 @@
       <c r="B57" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C57" s="112" t="s">
+      <c r="C57" s="97" t="s">
         <v>160</v>
       </c>
-      <c r="D57" s="113"/>
+      <c r="D57" s="98"/>
       <c r="F57" s="76" t="s">
         <v>101</v>
       </c>
@@ -19716,10 +19716,10 @@
       <c r="B58" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C58" s="112" t="s">
+      <c r="C58" s="97" t="s">
         <v>161</v>
       </c>
-      <c r="D58" s="113"/>
+      <c r="D58" s="98"/>
       <c r="F58" s="75" t="s">
         <v>95</v>
       </c>
@@ -19836,10 +19836,10 @@
       <c r="B59" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C59" s="149" t="s">
+      <c r="C59" s="139" t="s">
         <v>162</v>
       </c>
-      <c r="D59" s="149"/>
+      <c r="D59" s="139"/>
       <c r="F59" s="75" t="s">
         <v>101</v>
       </c>
@@ -19956,10 +19956,10 @@
       <c r="B60" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C60" s="149" t="s">
+      <c r="C60" s="139" t="s">
         <v>163</v>
       </c>
-      <c r="D60" s="149"/>
+      <c r="D60" s="139"/>
       <c r="F60" s="75" t="s">
         <v>96</v>
       </c>
@@ -20076,10 +20076,10 @@
       <c r="B61" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C61" s="150" t="s">
+      <c r="C61" s="142" t="s">
         <v>164</v>
       </c>
-      <c r="D61" s="151"/>
+      <c r="D61" s="143"/>
       <c r="F61" s="75" t="s">
         <v>95</v>
       </c>
@@ -20196,10 +20196,10 @@
       <c r="B62" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C62" s="149" t="s">
+      <c r="C62" s="139" t="s">
         <v>165</v>
       </c>
-      <c r="D62" s="149"/>
+      <c r="D62" s="139"/>
       <c r="F62" s="88" t="s">
         <v>166</v>
       </c>
@@ -20316,10 +20316,10 @@
       <c r="B63" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C63" s="120" t="s">
+      <c r="C63" s="111" t="s">
         <v>168</v>
       </c>
-      <c r="D63" s="121"/>
+      <c r="D63" s="112"/>
       <c r="F63" s="83" t="s">
         <v>102</v>
       </c>
@@ -20436,10 +20436,10 @@
       <c r="B64" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C64" s="112" t="s">
+      <c r="C64" s="97" t="s">
         <v>169</v>
       </c>
-      <c r="D64" s="113"/>
+      <c r="D64" s="98"/>
       <c r="F64" s="83" t="s">
         <v>102</v>
       </c>
@@ -20556,10 +20556,10 @@
       <c r="B65" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C65" s="112" t="s">
+      <c r="C65" s="97" t="s">
         <v>170</v>
       </c>
-      <c r="D65" s="113"/>
+      <c r="D65" s="98"/>
       <c r="F65" s="84" t="s">
         <v>95</v>
       </c>
@@ -20676,10 +20676,10 @@
       <c r="B66" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C66" s="112" t="s">
+      <c r="C66" s="97" t="s">
         <v>171</v>
       </c>
-      <c r="D66" s="113"/>
+      <c r="D66" s="98"/>
       <c r="F66" s="84" t="s">
         <v>95</v>
       </c>
@@ -20796,10 +20796,10 @@
       <c r="B67" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C67" s="112" t="s">
+      <c r="C67" s="97" t="s">
         <v>172</v>
       </c>
-      <c r="D67" s="113"/>
+      <c r="D67" s="98"/>
       <c r="F67" s="84" t="s">
         <v>96</v>
       </c>
@@ -20916,10 +20916,10 @@
       <c r="B68" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C68" s="112" t="s">
+      <c r="C68" s="97" t="s">
         <v>173</v>
       </c>
-      <c r="D68" s="113"/>
+      <c r="D68" s="98"/>
       <c r="F68" s="84" t="s">
         <v>96</v>
       </c>
@@ -21036,10 +21036,10 @@
       <c r="B69" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C69" s="112" t="s">
+      <c r="C69" s="97" t="s">
         <v>174</v>
       </c>
-      <c r="D69" s="113"/>
+      <c r="D69" s="98"/>
       <c r="F69" s="84" t="s">
         <v>101</v>
       </c>
@@ -21156,10 +21156,10 @@
       <c r="B70" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C70" s="112" t="s">
+      <c r="C70" s="97" t="s">
         <v>175</v>
       </c>
-      <c r="D70" s="113"/>
+      <c r="D70" s="98"/>
       <c r="F70" s="83" t="s">
         <v>101</v>
       </c>
@@ -21276,10 +21276,10 @@
       <c r="B71" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C71" s="112" t="s">
+      <c r="C71" s="97" t="s">
         <v>176</v>
       </c>
-      <c r="D71" s="113"/>
+      <c r="D71" s="98"/>
       <c r="F71" s="83" t="s">
         <v>101</v>
       </c>
@@ -21396,10 +21396,10 @@
       <c r="B72" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C72" s="112" t="s">
+      <c r="C72" s="97" t="s">
         <v>177</v>
       </c>
-      <c r="D72" s="113"/>
+      <c r="D72" s="98"/>
       <c r="F72" s="84" t="s">
         <v>116</v>
       </c>
@@ -21516,10 +21516,10 @@
       <c r="B73" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C73" s="112" t="s">
+      <c r="C73" s="97" t="s">
         <v>178</v>
       </c>
-      <c r="D73" s="113"/>
+      <c r="D73" s="98"/>
       <c r="F73" s="84" t="s">
         <v>116</v>
       </c>
@@ -21636,10 +21636,10 @@
       <c r="B74" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C74" s="112" t="s">
+      <c r="C74" s="97" t="s">
         <v>179</v>
       </c>
-      <c r="D74" s="113"/>
+      <c r="D74" s="98"/>
       <c r="F74" s="84" t="s">
         <v>96</v>
       </c>
@@ -21756,10 +21756,10 @@
       <c r="B75" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C75" s="112" t="s">
+      <c r="C75" s="97" t="s">
         <v>180</v>
       </c>
-      <c r="D75" s="113"/>
+      <c r="D75" s="98"/>
       <c r="F75" s="84" t="s">
         <v>96</v>
       </c>
@@ -21876,10 +21876,10 @@
       <c r="B76" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C76" s="112" t="s">
+      <c r="C76" s="97" t="s">
         <v>181</v>
       </c>
-      <c r="D76" s="113"/>
+      <c r="D76" s="98"/>
       <c r="F76" s="85" t="s">
         <v>101</v>
       </c>
@@ -21996,10 +21996,10 @@
       <c r="B77" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C77" s="112" t="s">
+      <c r="C77" s="97" t="s">
         <v>182</v>
       </c>
-      <c r="D77" s="113"/>
+      <c r="D77" s="98"/>
       <c r="F77" s="74" t="s">
         <v>116</v>
       </c>
@@ -22116,10 +22116,10 @@
       <c r="B78" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C78" s="112" t="s">
+      <c r="C78" s="97" t="s">
         <v>183</v>
       </c>
-      <c r="D78" s="113"/>
+      <c r="D78" s="98"/>
       <c r="F78" s="83" t="s">
         <v>96</v>
       </c>
@@ -22236,10 +22236,10 @@
       <c r="B79" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C79" s="112" t="s">
+      <c r="C79" s="97" t="s">
         <v>184</v>
       </c>
-      <c r="D79" s="113"/>
+      <c r="D79" s="98"/>
       <c r="F79" s="84" t="s">
         <v>102</v>
       </c>
@@ -22476,10 +22476,10 @@
       <c r="B81" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C81" s="126" t="s">
+      <c r="C81" s="99" t="s">
         <v>186</v>
       </c>
-      <c r="D81" s="127"/>
+      <c r="D81" s="100"/>
       <c r="F81" s="87" t="s">
         <v>101</v>
       </c>
@@ -22647,10 +22647,10 @@
       </c>
     </row>
     <row r="83" spans="2:42" ht="18.75">
-      <c r="C83" s="153" t="s">
+      <c r="C83" s="141" t="s">
         <v>188</v>
       </c>
-      <c r="D83" s="153"/>
+      <c r="D83" s="141"/>
       <c r="E83" s="34"/>
       <c r="F83" s="35">
         <f t="shared" ref="F83:AJ83" si="25">COUNTIF(F9:F81,"M*")</f>
@@ -22798,10 +22798,10 @@
       </c>
     </row>
     <row r="84" spans="2:42" ht="18.75">
-      <c r="C84" s="153" t="s">
+      <c r="C84" s="141" t="s">
         <v>189</v>
       </c>
-      <c r="D84" s="153"/>
+      <c r="D84" s="141"/>
       <c r="E84" s="34"/>
       <c r="F84" s="35">
         <f t="shared" ref="F84:AJ84" si="26">COUNTIF(F9:F81,"A*")</f>
@@ -22949,10 +22949,10 @@
       </c>
     </row>
     <row r="85" spans="2:42" ht="18.75">
-      <c r="C85" s="153" t="s">
+      <c r="C85" s="141" t="s">
         <v>77</v>
       </c>
-      <c r="D85" s="153"/>
+      <c r="D85" s="141"/>
       <c r="E85" s="34"/>
       <c r="F85" s="35">
         <f t="shared" ref="F85:AJ85" si="27">COUNTIF(F9:F81,"N*")</f>
@@ -23100,10 +23100,10 @@
       </c>
     </row>
     <row r="86" spans="2:42" ht="18.75">
-      <c r="C86" s="153" t="s">
+      <c r="C86" s="141" t="s">
         <v>78</v>
       </c>
-      <c r="D86" s="153"/>
+      <c r="D86" s="141"/>
       <c r="E86" s="34"/>
       <c r="F86" s="35">
         <f t="shared" ref="F86:AJ86" si="28">COUNTIF(F$30:F$81,"O*")</f>
@@ -23251,10 +23251,10 @@
       </c>
     </row>
     <row r="87" spans="2:42" ht="18.75">
-      <c r="C87" s="109" t="s">
+      <c r="C87" s="101" t="s">
         <v>190</v>
       </c>
-      <c r="D87" s="110"/>
+      <c r="D87" s="102"/>
       <c r="E87" s="34"/>
       <c r="F87" s="35">
         <f t="shared" ref="F87:AJ87" si="29">COUNTIF(F9:F81,"TR*")</f>
@@ -23402,10 +23402,10 @@
       </c>
     </row>
     <row r="88" spans="2:42" ht="18.75">
-      <c r="C88" s="109" t="s">
+      <c r="C88" s="101" t="s">
         <v>191</v>
       </c>
-      <c r="D88" s="110"/>
+      <c r="D88" s="102"/>
       <c r="E88" s="34"/>
       <c r="F88" s="35">
         <f>COUNTIF(F9:F81,"ST*")</f>
@@ -23553,10 +23553,10 @@
       </c>
     </row>
     <row r="89" spans="2:42" ht="18.75">
-      <c r="C89" s="152" t="s">
+      <c r="C89" s="140" t="s">
         <v>192</v>
       </c>
-      <c r="D89" s="152"/>
+      <c r="D89" s="140"/>
       <c r="E89" s="36"/>
       <c r="F89" s="37">
         <f>F91-F92</f>
@@ -23707,37 +23707,37 @@
       <c r="C90" s="38"/>
       <c r="D90" s="38"/>
       <c r="E90" s="34"/>
-      <c r="F90" s="108"/>
-      <c r="G90" s="108"/>
-      <c r="H90" s="108"/>
-      <c r="I90" s="108"/>
-      <c r="J90" s="108"/>
-      <c r="K90" s="108"/>
-      <c r="L90" s="108"/>
-      <c r="M90" s="108"/>
-      <c r="N90" s="108"/>
-      <c r="O90" s="108"/>
-      <c r="P90" s="108"/>
-      <c r="Q90" s="108"/>
-      <c r="R90" s="108"/>
-      <c r="S90" s="108"/>
-      <c r="T90" s="108"/>
-      <c r="U90" s="108"/>
-      <c r="V90" s="108"/>
-      <c r="W90" s="108"/>
-      <c r="X90" s="108"/>
-      <c r="Y90" s="108"/>
-      <c r="Z90" s="108"/>
-      <c r="AA90" s="108"/>
-      <c r="AB90" s="108"/>
-      <c r="AC90" s="108"/>
-      <c r="AD90" s="108"/>
-      <c r="AE90" s="108"/>
-      <c r="AF90" s="108"/>
-      <c r="AG90" s="108"/>
-      <c r="AH90" s="108"/>
-      <c r="AI90" s="108"/>
-      <c r="AJ90" s="108"/>
+      <c r="F90" s="114"/>
+      <c r="G90" s="114"/>
+      <c r="H90" s="114"/>
+      <c r="I90" s="114"/>
+      <c r="J90" s="114"/>
+      <c r="K90" s="114"/>
+      <c r="L90" s="114"/>
+      <c r="M90" s="114"/>
+      <c r="N90" s="114"/>
+      <c r="O90" s="114"/>
+      <c r="P90" s="114"/>
+      <c r="Q90" s="114"/>
+      <c r="R90" s="114"/>
+      <c r="S90" s="114"/>
+      <c r="T90" s="114"/>
+      <c r="U90" s="114"/>
+      <c r="V90" s="114"/>
+      <c r="W90" s="114"/>
+      <c r="X90" s="114"/>
+      <c r="Y90" s="114"/>
+      <c r="Z90" s="114"/>
+      <c r="AA90" s="114"/>
+      <c r="AB90" s="114"/>
+      <c r="AC90" s="114"/>
+      <c r="AD90" s="114"/>
+      <c r="AE90" s="114"/>
+      <c r="AF90" s="114"/>
+      <c r="AG90" s="114"/>
+      <c r="AH90" s="114"/>
+      <c r="AI90" s="114"/>
+      <c r="AJ90" s="114"/>
       <c r="AL90" s="20">
         <f t="shared" si="24"/>
         <v>0</v>
@@ -23760,10 +23760,10 @@
       </c>
     </row>
     <row r="91" spans="2:42" ht="18.75">
-      <c r="C91" s="153" t="s">
+      <c r="C91" s="141" t="s">
         <v>193</v>
       </c>
-      <c r="D91" s="153"/>
+      <c r="D91" s="141"/>
       <c r="E91" s="34"/>
       <c r="F91" s="39">
         <f>SUM(F83:F85)</f>
@@ -23910,10 +23910,10 @@
       </c>
     </row>
     <row r="92" spans="2:42" ht="18.75">
-      <c r="C92" s="153" t="s">
+      <c r="C92" s="141" t="s">
         <v>194</v>
       </c>
-      <c r="D92" s="153"/>
+      <c r="D92" s="141"/>
       <c r="E92" s="34"/>
       <c r="F92" s="35">
         <v>45</v>
@@ -24030,10 +24030,10 @@
       </c>
     </row>
     <row r="93" spans="2:42" ht="18.75">
-      <c r="C93" s="153" t="s">
+      <c r="C93" s="141" t="s">
         <v>195</v>
       </c>
-      <c r="D93" s="153"/>
+      <c r="D93" s="141"/>
       <c r="E93" s="34"/>
       <c r="F93" s="35">
         <f>SUM(F83,F84,F85,F86,F88)</f>
@@ -24202,14 +24202,14 @@
       </c>
     </row>
     <row r="95" spans="2:42" ht="16.5" thickBot="1">
-      <c r="F95" s="95" t="s">
+      <c r="F95" s="118" t="s">
         <v>196</v>
       </c>
-      <c r="G95" s="96"/>
-      <c r="H95" s="96"/>
-      <c r="I95" s="96"/>
-      <c r="J95" s="96"/>
-      <c r="K95" s="97"/>
+      <c r="G95" s="119"/>
+      <c r="H95" s="119"/>
+      <c r="I95" s="119"/>
+      <c r="J95" s="119"/>
+      <c r="K95" s="120"/>
       <c r="AL95" s="20">
         <f t="shared" si="24"/>
         <v>0</v>
@@ -24235,17 +24235,17 @@
       <c r="F96" s="80" t="s">
         <v>197</v>
       </c>
-      <c r="G96" s="106" t="s">
+      <c r="G96" s="128" t="s">
         <v>198</v>
       </c>
-      <c r="H96" s="106"/>
+      <c r="H96" s="128"/>
       <c r="I96" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="J96" s="98" t="s">
+      <c r="J96" s="121" t="s">
         <v>199</v>
       </c>
-      <c r="K96" s="99"/>
+      <c r="K96" s="122"/>
       <c r="AL96" s="20">
         <f t="shared" si="24"/>
         <v>0</v>
@@ -24271,17 +24271,17 @@
       <c r="F97" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="G97" s="107" t="s">
+      <c r="G97" s="129" t="s">
         <v>200</v>
       </c>
-      <c r="H97" s="107"/>
+      <c r="H97" s="129"/>
       <c r="I97" s="77" t="s">
         <v>201</v>
       </c>
-      <c r="J97" s="100" t="s">
+      <c r="J97" s="123" t="s">
         <v>202</v>
       </c>
-      <c r="K97" s="101"/>
+      <c r="K97" s="124"/>
       <c r="AL97" s="20">
         <f t="shared" si="24"/>
         <v>0</v>
@@ -24307,17 +24307,17 @@
       <c r="F98" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="G98" s="102" t="s">
+      <c r="G98" s="115" t="s">
         <v>203</v>
       </c>
-      <c r="H98" s="102"/>
+      <c r="H98" s="115"/>
       <c r="I98" s="78" t="s">
         <v>108</v>
       </c>
-      <c r="J98" s="102" t="s">
+      <c r="J98" s="115" t="s">
         <v>204</v>
       </c>
-      <c r="K98" s="103"/>
+      <c r="K98" s="125"/>
       <c r="AL98" s="20"/>
       <c r="AM98" s="20"/>
       <c r="AN98" s="20"/>
@@ -24328,17 +24328,17 @@
       <c r="F99" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="G99" s="111" t="s">
+      <c r="G99" s="116" t="s">
         <v>205</v>
       </c>
-      <c r="H99" s="111"/>
+      <c r="H99" s="116"/>
       <c r="I99" s="79" t="s">
         <v>206</v>
       </c>
-      <c r="J99" s="104" t="s">
+      <c r="J99" s="126" t="s">
         <v>207</v>
       </c>
-      <c r="K99" s="105"/>
+      <c r="K99" s="127"/>
       <c r="AL99" s="20">
         <f>COUNTIF($F81:$AJ81,"ST*")</f>
         <v>0</v>
@@ -24364,10 +24364,10 @@
       <c r="F100" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="G100" s="111" t="s">
+      <c r="G100" s="116" t="s">
         <v>208</v>
       </c>
-      <c r="H100" s="111"/>
+      <c r="H100" s="116"/>
       <c r="I100" s="20" t="s">
         <v>104</v>
       </c>
@@ -24380,10 +24380,10 @@
       <c r="F101" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="G101" s="92" t="s">
+      <c r="G101" s="117" t="s">
         <v>210</v>
       </c>
-      <c r="H101" s="92"/>
+      <c r="H101" s="117"/>
       <c r="I101" s="20" t="s">
         <v>114</v>
       </c>
@@ -24396,10 +24396,10 @@
       <c r="F102" s="82" t="s">
         <v>212</v>
       </c>
-      <c r="G102" s="123" t="s">
+      <c r="G102" s="92" t="s">
         <v>213</v>
       </c>
-      <c r="H102" s="123"/>
+      <c r="H102" s="92"/>
       <c r="I102" s="20" t="s">
         <v>131</v>
       </c>
@@ -24412,45 +24412,86 @@
       <c r="F103" s="55" t="s">
         <v>215</v>
       </c>
-      <c r="G103" s="124" t="s">
+      <c r="G103" s="95" t="s">
         <v>216</v>
       </c>
-      <c r="H103" s="124"/>
+      <c r="H103" s="95"/>
       <c r="I103" s="56" t="s">
         <v>167</v>
       </c>
-      <c r="J103" s="124" t="s">
+      <c r="J103" s="95" t="s">
         <v>217</v>
       </c>
-      <c r="K103" s="125"/>
+      <c r="K103" s="96"/>
     </row>
     <row r="108" spans="6:42" ht="9.75" customHeight="1"/>
   </sheetData>
   <autoFilter ref="F4:AJ89" xr:uid="{10A87D31-A428-49C7-B3CE-66B468A7BADA}"/>
   <mergeCells count="111">
-    <mergeCell ref="G103:H103"/>
-    <mergeCell ref="J103:K103"/>
-    <mergeCell ref="J96:K96"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="G98:H98"/>
-    <mergeCell ref="J98:K98"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="F2:AJ2"/>
+    <mergeCell ref="AL2:AL4"/>
+    <mergeCell ref="AM2:AM4"/>
+    <mergeCell ref="AN2:AN4"/>
+    <mergeCell ref="AO2:AO4"/>
+    <mergeCell ref="AP2:AP4"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="B3:D4"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="C57:D57"/>
     <mergeCell ref="C62:D62"/>
     <mergeCell ref="G100:H100"/>
     <mergeCell ref="J100:K100"/>
@@ -24475,70 +24516,29 @@
     <mergeCell ref="C85:D85"/>
     <mergeCell ref="C86:D86"/>
     <mergeCell ref="C87:D87"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="B3:D4"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F2:AJ2"/>
-    <mergeCell ref="AL2:AL4"/>
-    <mergeCell ref="AM2:AM4"/>
-    <mergeCell ref="AN2:AN4"/>
-    <mergeCell ref="AO2:AO4"/>
-    <mergeCell ref="AP2:AP4"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="G103:H103"/>
+    <mergeCell ref="J103:K103"/>
+    <mergeCell ref="J96:K96"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="G98:H98"/>
+    <mergeCell ref="J98:K98"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F63:AI81">
@@ -24688,61 +24688,61 @@
   <sheetData>
     <row r="1" spans="2:42" ht="16.5" thickBot="1"/>
     <row r="2" spans="2:42" ht="39" customHeight="1" thickBot="1">
-      <c r="F2" s="139" t="s">
+      <c r="F2" s="151" t="s">
         <v>79</v>
       </c>
-      <c r="G2" s="140"/>
-      <c r="H2" s="140"/>
-      <c r="I2" s="140"/>
-      <c r="J2" s="140"/>
-      <c r="K2" s="140"/>
-      <c r="L2" s="140"/>
-      <c r="M2" s="140"/>
-      <c r="N2" s="140"/>
-      <c r="O2" s="140"/>
-      <c r="P2" s="140"/>
-      <c r="Q2" s="140"/>
-      <c r="R2" s="140"/>
-      <c r="S2" s="140"/>
-      <c r="T2" s="140"/>
-      <c r="U2" s="140"/>
-      <c r="V2" s="140"/>
-      <c r="W2" s="140"/>
-      <c r="X2" s="140"/>
-      <c r="Y2" s="140"/>
-      <c r="Z2" s="140"/>
-      <c r="AA2" s="140"/>
-      <c r="AB2" s="140"/>
-      <c r="AC2" s="140"/>
-      <c r="AD2" s="140"/>
-      <c r="AE2" s="140"/>
-      <c r="AF2" s="140"/>
-      <c r="AG2" s="140"/>
-      <c r="AH2" s="140"/>
-      <c r="AI2" s="140"/>
-      <c r="AJ2" s="141"/>
-      <c r="AL2" s="114" t="s">
+      <c r="G2" s="152"/>
+      <c r="H2" s="152"/>
+      <c r="I2" s="152"/>
+      <c r="J2" s="152"/>
+      <c r="K2" s="152"/>
+      <c r="L2" s="152"/>
+      <c r="M2" s="152"/>
+      <c r="N2" s="152"/>
+      <c r="O2" s="152"/>
+      <c r="P2" s="152"/>
+      <c r="Q2" s="152"/>
+      <c r="R2" s="152"/>
+      <c r="S2" s="152"/>
+      <c r="T2" s="152"/>
+      <c r="U2" s="152"/>
+      <c r="V2" s="152"/>
+      <c r="W2" s="152"/>
+      <c r="X2" s="152"/>
+      <c r="Y2" s="152"/>
+      <c r="Z2" s="152"/>
+      <c r="AA2" s="152"/>
+      <c r="AB2" s="152"/>
+      <c r="AC2" s="152"/>
+      <c r="AD2" s="152"/>
+      <c r="AE2" s="152"/>
+      <c r="AF2" s="152"/>
+      <c r="AG2" s="152"/>
+      <c r="AH2" s="152"/>
+      <c r="AI2" s="152"/>
+      <c r="AJ2" s="153"/>
+      <c r="AL2" s="105" t="s">
         <v>80</v>
       </c>
-      <c r="AM2" s="114" t="s">
+      <c r="AM2" s="105" t="s">
         <v>81</v>
       </c>
-      <c r="AN2" s="114" t="s">
+      <c r="AN2" s="105" t="s">
         <v>82</v>
       </c>
-      <c r="AO2" s="114" t="s">
+      <c r="AO2" s="105" t="s">
         <v>83</v>
       </c>
-      <c r="AP2" s="114" t="s">
+      <c r="AP2" s="105" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="3" spans="2:42" ht="39.75" thickBot="1">
-      <c r="B3" s="122" t="s">
+      <c r="B3" s="113" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="122"/>
-      <c r="D3" s="122"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="113"/>
       <c r="F3" s="43" t="s">
         <v>86</v>
       </c>
@@ -24836,16 +24836,16 @@
       <c r="AJ3" s="43" t="s">
         <v>187</v>
       </c>
-      <c r="AL3" s="115"/>
-      <c r="AM3" s="115"/>
-      <c r="AN3" s="115"/>
-      <c r="AO3" s="115"/>
-      <c r="AP3" s="115"/>
+      <c r="AL3" s="106"/>
+      <c r="AM3" s="106"/>
+      <c r="AN3" s="106"/>
+      <c r="AO3" s="106"/>
+      <c r="AP3" s="106"/>
     </row>
     <row r="4" spans="2:42" ht="19.5" customHeight="1" thickBot="1">
-      <c r="B4" s="122"/>
-      <c r="C4" s="122"/>
-      <c r="D4" s="122"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
       <c r="F4" s="40">
         <v>1</v>
       </c>
@@ -24939,20 +24939,20 @@
       <c r="AJ4" s="58" t="s">
         <v>187</v>
       </c>
-      <c r="AL4" s="116"/>
-      <c r="AM4" s="116"/>
-      <c r="AN4" s="116"/>
-      <c r="AO4" s="116"/>
-      <c r="AP4" s="116"/>
+      <c r="AL4" s="107"/>
+      <c r="AM4" s="107"/>
+      <c r="AN4" s="107"/>
+      <c r="AO4" s="107"/>
+      <c r="AP4" s="107"/>
     </row>
     <row r="5" spans="2:42" ht="18.75">
       <c r="B5" s="35">
         <v>1</v>
       </c>
-      <c r="C5" s="142" t="s">
+      <c r="C5" s="144" t="s">
         <v>94</v>
       </c>
-      <c r="D5" s="142"/>
+      <c r="D5" s="144"/>
       <c r="F5" s="84" t="s">
         <v>95</v>
       </c>
@@ -25069,10 +25069,10 @@
       <c r="B6" s="35">
         <v>2</v>
       </c>
-      <c r="C6" s="142" t="s">
+      <c r="C6" s="144" t="s">
         <v>99</v>
       </c>
-      <c r="D6" s="142"/>
+      <c r="D6" s="144"/>
       <c r="F6" s="75" t="s">
         <v>97</v>
       </c>
@@ -25189,10 +25189,10 @@
       <c r="B7" s="35">
         <v>3</v>
       </c>
-      <c r="C7" s="142" t="s">
+      <c r="C7" s="144" t="s">
         <v>100</v>
       </c>
-      <c r="D7" s="142"/>
+      <c r="D7" s="144"/>
       <c r="F7" s="75" t="s">
         <v>101</v>
       </c>
@@ -25309,10 +25309,10 @@
       <c r="B8" s="35">
         <v>4</v>
       </c>
-      <c r="C8" s="142" t="s">
+      <c r="C8" s="144" t="s">
         <v>103</v>
       </c>
-      <c r="D8" s="142"/>
+      <c r="D8" s="144"/>
       <c r="F8" s="75" t="s">
         <v>96</v>
       </c>
@@ -25460,10 +25460,10 @@
       <c r="AI9" s="18"/>
     </row>
     <row r="10" spans="2:42" ht="18.75">
-      <c r="C10" s="153" t="s">
+      <c r="C10" s="141" t="s">
         <v>188</v>
       </c>
-      <c r="D10" s="153"/>
+      <c r="D10" s="141"/>
       <c r="E10" s="34"/>
       <c r="F10" s="35">
         <f t="shared" ref="F10:AJ10" si="5">COUNTIF(F$5:F$8,"M*")</f>
@@ -25591,10 +25591,10 @@
       </c>
     </row>
     <row r="11" spans="2:42" ht="18.75">
-      <c r="C11" s="153" t="s">
+      <c r="C11" s="141" t="s">
         <v>189</v>
       </c>
-      <c r="D11" s="153"/>
+      <c r="D11" s="141"/>
       <c r="E11" s="34"/>
       <c r="F11" s="35">
         <f t="shared" ref="F11:AJ11" si="6">COUNTIF(F$5:F$8,"A*")</f>
@@ -25722,10 +25722,10 @@
       </c>
     </row>
     <row r="12" spans="2:42" ht="18.75">
-      <c r="C12" s="153" t="s">
+      <c r="C12" s="141" t="s">
         <v>77</v>
       </c>
-      <c r="D12" s="153"/>
+      <c r="D12" s="141"/>
       <c r="E12" s="34"/>
       <c r="F12" s="35">
         <f t="shared" ref="F12:AJ12" si="7">COUNTIF(F$5:F$8,"N*")</f>
@@ -25853,10 +25853,10 @@
       </c>
     </row>
     <row r="13" spans="2:42" ht="18.75">
-      <c r="C13" s="153" t="s">
+      <c r="C13" s="141" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="153"/>
+      <c r="D13" s="141"/>
       <c r="E13" s="34"/>
       <c r="F13" s="35">
         <f t="shared" ref="F13:AJ13" si="8">COUNTIF(F$5:F$8,"O*")</f>
@@ -25984,10 +25984,10 @@
       </c>
     </row>
     <row r="14" spans="2:42" ht="18.75">
-      <c r="C14" s="109" t="s">
+      <c r="C14" s="101" t="s">
         <v>190</v>
       </c>
-      <c r="D14" s="110"/>
+      <c r="D14" s="102"/>
       <c r="E14" s="34"/>
       <c r="F14" s="35">
         <f t="shared" ref="F14:AJ14" si="9">COUNTIF(F$5:F$8,"TR*")</f>
@@ -26115,10 +26115,10 @@
       </c>
     </row>
     <row r="15" spans="2:42" ht="18.75">
-      <c r="C15" s="109" t="s">
+      <c r="C15" s="101" t="s">
         <v>191</v>
       </c>
-      <c r="D15" s="110"/>
+      <c r="D15" s="102"/>
       <c r="E15" s="34"/>
       <c r="F15" s="35">
         <f t="shared" ref="F15:AJ15" si="10">COUNTIF(F$5:F$8,"ST*")</f>
@@ -26246,10 +26246,10 @@
       </c>
     </row>
     <row r="16" spans="2:42" ht="18.75">
-      <c r="C16" s="152" t="s">
+      <c r="C16" s="140" t="s">
         <v>192</v>
       </c>
-      <c r="D16" s="152"/>
+      <c r="D16" s="140"/>
       <c r="E16" s="36"/>
       <c r="F16" s="37">
         <f>F18-F19</f>
@@ -26380,43 +26380,43 @@
       <c r="C17" s="38"/>
       <c r="D17" s="38"/>
       <c r="E17" s="34"/>
-      <c r="F17" s="108"/>
-      <c r="G17" s="108"/>
-      <c r="H17" s="108"/>
-      <c r="I17" s="108"/>
-      <c r="J17" s="108"/>
-      <c r="K17" s="108"/>
-      <c r="L17" s="108"/>
-      <c r="M17" s="108"/>
-      <c r="N17" s="108"/>
-      <c r="O17" s="108"/>
-      <c r="P17" s="108"/>
-      <c r="Q17" s="108"/>
-      <c r="R17" s="108"/>
-      <c r="S17" s="108"/>
-      <c r="T17" s="108"/>
-      <c r="U17" s="108"/>
-      <c r="V17" s="108"/>
-      <c r="W17" s="108"/>
-      <c r="X17" s="108"/>
-      <c r="Y17" s="108"/>
-      <c r="Z17" s="108"/>
-      <c r="AA17" s="108"/>
-      <c r="AB17" s="108"/>
-      <c r="AC17" s="108"/>
-      <c r="AD17" s="108"/>
-      <c r="AE17" s="108"/>
-      <c r="AF17" s="108"/>
-      <c r="AG17" s="108"/>
-      <c r="AH17" s="108"/>
-      <c r="AI17" s="108"/>
-      <c r="AJ17" s="108"/>
+      <c r="F17" s="114"/>
+      <c r="G17" s="114"/>
+      <c r="H17" s="114"/>
+      <c r="I17" s="114"/>
+      <c r="J17" s="114"/>
+      <c r="K17" s="114"/>
+      <c r="L17" s="114"/>
+      <c r="M17" s="114"/>
+      <c r="N17" s="114"/>
+      <c r="O17" s="114"/>
+      <c r="P17" s="114"/>
+      <c r="Q17" s="114"/>
+      <c r="R17" s="114"/>
+      <c r="S17" s="114"/>
+      <c r="T17" s="114"/>
+      <c r="U17" s="114"/>
+      <c r="V17" s="114"/>
+      <c r="W17" s="114"/>
+      <c r="X17" s="114"/>
+      <c r="Y17" s="114"/>
+      <c r="Z17" s="114"/>
+      <c r="AA17" s="114"/>
+      <c r="AB17" s="114"/>
+      <c r="AC17" s="114"/>
+      <c r="AD17" s="114"/>
+      <c r="AE17" s="114"/>
+      <c r="AF17" s="114"/>
+      <c r="AG17" s="114"/>
+      <c r="AH17" s="114"/>
+      <c r="AI17" s="114"/>
+      <c r="AJ17" s="114"/>
     </row>
     <row r="18" spans="3:36" ht="18.75">
-      <c r="C18" s="153" t="s">
+      <c r="C18" s="141" t="s">
         <v>193</v>
       </c>
-      <c r="D18" s="153"/>
+      <c r="D18" s="141"/>
       <c r="E18" s="34"/>
       <c r="F18" s="39">
         <f>SUM(F10:F12)</f>
@@ -26543,10 +26543,10 @@
       </c>
     </row>
     <row r="19" spans="3:36" ht="18.75">
-      <c r="C19" s="153" t="s">
+      <c r="C19" s="141" t="s">
         <v>194</v>
       </c>
-      <c r="D19" s="153"/>
+      <c r="D19" s="141"/>
       <c r="E19" s="34"/>
       <c r="F19" s="35">
         <v>2</v>
@@ -26643,10 +26643,10 @@
       </c>
     </row>
     <row r="20" spans="3:36" ht="18.75">
-      <c r="C20" s="153" t="s">
+      <c r="C20" s="141" t="s">
         <v>195</v>
       </c>
-      <c r="D20" s="153"/>
+      <c r="D20" s="141"/>
       <c r="E20" s="34"/>
       <c r="F20" s="35">
         <f>SUM(F10,F11,F12,F13,F15)</f>
@@ -26774,87 +26774,87 @@
     </row>
     <row r="22" spans="3:36" ht="16.5" thickBot="1"/>
     <row r="23" spans="3:36" ht="16.5" thickBot="1">
-      <c r="F23" s="95" t="s">
+      <c r="F23" s="118" t="s">
         <v>196</v>
       </c>
-      <c r="G23" s="96"/>
-      <c r="H23" s="96"/>
-      <c r="I23" s="96"/>
-      <c r="J23" s="96"/>
-      <c r="K23" s="97"/>
+      <c r="G23" s="119"/>
+      <c r="H23" s="119"/>
+      <c r="I23" s="119"/>
+      <c r="J23" s="119"/>
+      <c r="K23" s="120"/>
     </row>
     <row r="24" spans="3:36">
       <c r="F24" s="80" t="s">
         <v>197</v>
       </c>
-      <c r="G24" s="106" t="s">
+      <c r="G24" s="128" t="s">
         <v>198</v>
       </c>
-      <c r="H24" s="106"/>
+      <c r="H24" s="128"/>
       <c r="I24" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="J24" s="98" t="s">
+      <c r="J24" s="121" t="s">
         <v>199</v>
       </c>
-      <c r="K24" s="99"/>
+      <c r="K24" s="122"/>
     </row>
     <row r="25" spans="3:36">
       <c r="F25" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="G25" s="107" t="s">
+      <c r="G25" s="129" t="s">
         <v>200</v>
       </c>
-      <c r="H25" s="107"/>
+      <c r="H25" s="129"/>
       <c r="I25" s="77" t="s">
         <v>201</v>
       </c>
-      <c r="J25" s="100" t="s">
+      <c r="J25" s="123" t="s">
         <v>202</v>
       </c>
-      <c r="K25" s="101"/>
+      <c r="K25" s="124"/>
     </row>
     <row r="26" spans="3:36">
       <c r="F26" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="G26" s="102" t="s">
+      <c r="G26" s="115" t="s">
         <v>203</v>
       </c>
-      <c r="H26" s="102"/>
+      <c r="H26" s="115"/>
       <c r="I26" s="78" t="s">
         <v>108</v>
       </c>
-      <c r="J26" s="102" t="s">
+      <c r="J26" s="115" t="s">
         <v>204</v>
       </c>
-      <c r="K26" s="103"/>
+      <c r="K26" s="125"/>
     </row>
     <row r="27" spans="3:36">
       <c r="F27" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="G27" s="111" t="s">
+      <c r="G27" s="116" t="s">
         <v>205</v>
       </c>
-      <c r="H27" s="111"/>
+      <c r="H27" s="116"/>
       <c r="I27" s="79" t="s">
         <v>206</v>
       </c>
-      <c r="J27" s="104" t="s">
+      <c r="J27" s="126" t="s">
         <v>207</v>
       </c>
-      <c r="K27" s="105"/>
+      <c r="K27" s="127"/>
     </row>
     <row r="28" spans="3:36">
       <c r="F28" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="G28" s="111" t="s">
+      <c r="G28" s="116" t="s">
         <v>208</v>
       </c>
-      <c r="H28" s="111"/>
+      <c r="H28" s="116"/>
       <c r="I28" s="20" t="s">
         <v>104</v>
       </c>
@@ -26867,10 +26867,10 @@
       <c r="F29" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="G29" s="92" t="s">
+      <c r="G29" s="117" t="s">
         <v>210</v>
       </c>
-      <c r="H29" s="92"/>
+      <c r="H29" s="117"/>
       <c r="I29" s="20" t="s">
         <v>114</v>
       </c>
@@ -26886,10 +26886,10 @@
       <c r="F30" s="82" t="s">
         <v>212</v>
       </c>
-      <c r="G30" s="123" t="s">
+      <c r="G30" s="92" t="s">
         <v>213</v>
       </c>
-      <c r="H30" s="123"/>
+      <c r="H30" s="92"/>
       <c r="I30" s="20" t="s">
         <v>131</v>
       </c>
@@ -26902,20 +26902,43 @@
       <c r="F31" s="55" t="s">
         <v>215</v>
       </c>
-      <c r="G31" s="124" t="s">
+      <c r="G31" s="95" t="s">
         <v>216</v>
       </c>
-      <c r="H31" s="124"/>
+      <c r="H31" s="95"/>
       <c r="I31" s="56" t="s">
         <v>167</v>
       </c>
-      <c r="J31" s="124" t="s">
+      <c r="J31" s="95" t="s">
         <v>217</v>
       </c>
-      <c r="K31" s="125"/>
+      <c r="K31" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="F23:K23"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="B3:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C6:D6"/>
     <mergeCell ref="J30:K30"/>
     <mergeCell ref="G31:H31"/>
     <mergeCell ref="J31:K31"/>
@@ -26932,29 +26955,6 @@
     <mergeCell ref="G30:H30"/>
     <mergeCell ref="G24:H24"/>
     <mergeCell ref="G25:H25"/>
-    <mergeCell ref="B3:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="F23:K23"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F5:AJ8">
@@ -27011,61 +27011,61 @@
   <sheetData>
     <row r="1" spans="2:42" ht="16.5" thickBot="1"/>
     <row r="2" spans="2:42" ht="39" customHeight="1" thickBot="1">
-      <c r="F2" s="139" t="s">
+      <c r="F2" s="151" t="s">
         <v>218</v>
       </c>
-      <c r="G2" s="140"/>
-      <c r="H2" s="140"/>
-      <c r="I2" s="140"/>
-      <c r="J2" s="140"/>
-      <c r="K2" s="140"/>
-      <c r="L2" s="140"/>
-      <c r="M2" s="140"/>
-      <c r="N2" s="140"/>
-      <c r="O2" s="140"/>
-      <c r="P2" s="140"/>
-      <c r="Q2" s="140"/>
-      <c r="R2" s="140"/>
-      <c r="S2" s="140"/>
-      <c r="T2" s="140"/>
-      <c r="U2" s="140"/>
-      <c r="V2" s="140"/>
-      <c r="W2" s="140"/>
-      <c r="X2" s="140"/>
-      <c r="Y2" s="140"/>
-      <c r="Z2" s="140"/>
-      <c r="AA2" s="140"/>
-      <c r="AB2" s="140"/>
-      <c r="AC2" s="140"/>
-      <c r="AD2" s="140"/>
-      <c r="AE2" s="140"/>
-      <c r="AF2" s="140"/>
-      <c r="AG2" s="140"/>
-      <c r="AH2" s="140"/>
-      <c r="AI2" s="140"/>
-      <c r="AJ2" s="141"/>
-      <c r="AL2" s="114" t="s">
+      <c r="G2" s="152"/>
+      <c r="H2" s="152"/>
+      <c r="I2" s="152"/>
+      <c r="J2" s="152"/>
+      <c r="K2" s="152"/>
+      <c r="L2" s="152"/>
+      <c r="M2" s="152"/>
+      <c r="N2" s="152"/>
+      <c r="O2" s="152"/>
+      <c r="P2" s="152"/>
+      <c r="Q2" s="152"/>
+      <c r="R2" s="152"/>
+      <c r="S2" s="152"/>
+      <c r="T2" s="152"/>
+      <c r="U2" s="152"/>
+      <c r="V2" s="152"/>
+      <c r="W2" s="152"/>
+      <c r="X2" s="152"/>
+      <c r="Y2" s="152"/>
+      <c r="Z2" s="152"/>
+      <c r="AA2" s="152"/>
+      <c r="AB2" s="152"/>
+      <c r="AC2" s="152"/>
+      <c r="AD2" s="152"/>
+      <c r="AE2" s="152"/>
+      <c r="AF2" s="152"/>
+      <c r="AG2" s="152"/>
+      <c r="AH2" s="152"/>
+      <c r="AI2" s="152"/>
+      <c r="AJ2" s="153"/>
+      <c r="AL2" s="105" t="s">
         <v>80</v>
       </c>
-      <c r="AM2" s="114" t="s">
+      <c r="AM2" s="105" t="s">
         <v>81</v>
       </c>
-      <c r="AN2" s="114" t="s">
+      <c r="AN2" s="105" t="s">
         <v>82</v>
       </c>
-      <c r="AO2" s="114" t="s">
+      <c r="AO2" s="105" t="s">
         <v>83</v>
       </c>
-      <c r="AP2" s="114" t="s">
+      <c r="AP2" s="105" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="3" spans="2:42" ht="39.75" thickBot="1">
-      <c r="B3" s="122" t="s">
+      <c r="B3" s="113" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="122"/>
-      <c r="D3" s="122"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="113"/>
       <c r="F3" s="43" t="s">
         <v>86</v>
       </c>
@@ -27157,16 +27157,16 @@
         <v>87</v>
       </c>
       <c r="AJ3" s="43"/>
-      <c r="AL3" s="115"/>
-      <c r="AM3" s="115"/>
-      <c r="AN3" s="115"/>
-      <c r="AO3" s="115"/>
-      <c r="AP3" s="115"/>
+      <c r="AL3" s="106"/>
+      <c r="AM3" s="106"/>
+      <c r="AN3" s="106"/>
+      <c r="AO3" s="106"/>
+      <c r="AP3" s="106"/>
     </row>
     <row r="4" spans="2:42" ht="19.5" customHeight="1" thickBot="1">
-      <c r="B4" s="122"/>
-      <c r="C4" s="122"/>
-      <c r="D4" s="122"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
       <c r="F4" s="40">
         <v>1</v>
       </c>
@@ -27260,20 +27260,20 @@
       <c r="AJ4" s="58" t="s">
         <v>187</v>
       </c>
-      <c r="AL4" s="116"/>
-      <c r="AM4" s="116"/>
-      <c r="AN4" s="116"/>
-      <c r="AO4" s="116"/>
-      <c r="AP4" s="116"/>
+      <c r="AL4" s="107"/>
+      <c r="AM4" s="107"/>
+      <c r="AN4" s="107"/>
+      <c r="AO4" s="107"/>
+      <c r="AP4" s="107"/>
     </row>
     <row r="5" spans="2:42" ht="18.75">
       <c r="B5" s="35">
         <v>1</v>
       </c>
-      <c r="C5" s="142" t="s">
+      <c r="C5" s="144" t="s">
         <v>105</v>
       </c>
-      <c r="D5" s="142"/>
+      <c r="D5" s="144"/>
       <c r="F5" s="90" t="s">
         <v>106</v>
       </c>
@@ -27390,10 +27390,10 @@
       <c r="B6" s="35">
         <v>2</v>
       </c>
-      <c r="C6" s="142" t="s">
+      <c r="C6" s="144" t="s">
         <v>109</v>
       </c>
-      <c r="D6" s="142"/>
+      <c r="D6" s="144"/>
       <c r="F6" s="75" t="s">
         <v>96</v>
       </c>
@@ -27510,10 +27510,10 @@
       <c r="B7" s="35">
         <v>3</v>
       </c>
-      <c r="C7" s="142" t="s">
+      <c r="C7" s="144" t="s">
         <v>110</v>
       </c>
-      <c r="D7" s="142"/>
+      <c r="D7" s="144"/>
       <c r="F7" s="75" t="s">
         <v>95</v>
       </c>
@@ -27630,10 +27630,10 @@
       <c r="B8" s="35">
         <v>4</v>
       </c>
-      <c r="C8" s="142" t="s">
+      <c r="C8" s="144" t="s">
         <v>111</v>
       </c>
-      <c r="D8" s="142"/>
+      <c r="D8" s="144"/>
       <c r="F8" s="75" t="s">
         <v>107</v>
       </c>
@@ -27750,10 +27750,10 @@
       <c r="B9" s="35">
         <v>5</v>
       </c>
-      <c r="C9" s="142" t="s">
+      <c r="C9" s="144" t="s">
         <v>112</v>
       </c>
-      <c r="D9" s="142"/>
+      <c r="D9" s="144"/>
       <c r="F9" s="75" t="s">
         <v>108</v>
       </c>
@@ -27871,10 +27871,10 @@
       <c r="B10" s="35">
         <v>6</v>
       </c>
-      <c r="C10" s="142" t="s">
+      <c r="C10" s="144" t="s">
         <v>113</v>
       </c>
-      <c r="D10" s="142"/>
+      <c r="D10" s="144"/>
       <c r="F10" s="88" t="s">
         <v>95</v>
       </c>
@@ -28022,10 +28022,10 @@
       <c r="AI11" s="18"/>
     </row>
     <row r="12" spans="2:42" ht="18.75">
-      <c r="C12" s="153" t="s">
+      <c r="C12" s="141" t="s">
         <v>188</v>
       </c>
-      <c r="D12" s="153"/>
+      <c r="D12" s="141"/>
       <c r="E12" s="34"/>
       <c r="F12" s="35">
         <f>COUNTIF(F$5:F$9,"M*")</f>
@@ -28153,10 +28153,10 @@
       </c>
     </row>
     <row r="13" spans="2:42" ht="18.75">
-      <c r="C13" s="153" t="s">
+      <c r="C13" s="141" t="s">
         <v>189</v>
       </c>
-      <c r="D13" s="153"/>
+      <c r="D13" s="141"/>
       <c r="E13" s="34"/>
       <c r="F13" s="35">
         <f>COUNTIF(F$5:F$9,"A*")</f>
@@ -28284,10 +28284,10 @@
       </c>
     </row>
     <row r="14" spans="2:42" ht="18.75">
-      <c r="C14" s="153" t="s">
+      <c r="C14" s="141" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="153"/>
+      <c r="D14" s="141"/>
       <c r="E14" s="34"/>
       <c r="F14" s="35">
         <f>COUNTIF(F$5:F$9,"N*")</f>
@@ -28415,10 +28415,10 @@
       </c>
     </row>
     <row r="15" spans="2:42" ht="18.75">
-      <c r="C15" s="153" t="s">
+      <c r="C15" s="141" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="153"/>
+      <c r="D15" s="141"/>
       <c r="E15" s="34"/>
       <c r="F15" s="35">
         <f t="shared" ref="F15:AJ15" si="8">COUNTIF(F$5:F$10,"O*")</f>
@@ -28546,10 +28546,10 @@
       </c>
     </row>
     <row r="16" spans="2:42" ht="18.75">
-      <c r="C16" s="109" t="s">
+      <c r="C16" s="101" t="s">
         <v>190</v>
       </c>
-      <c r="D16" s="110"/>
+      <c r="D16" s="102"/>
       <c r="E16" s="34"/>
       <c r="F16" s="35">
         <f t="shared" ref="F16:AJ16" si="9">COUNTIF(F$5:F$10,"TR*")</f>
@@ -28677,10 +28677,10 @@
       </c>
     </row>
     <row r="17" spans="3:36" ht="18.75">
-      <c r="C17" s="109" t="s">
+      <c r="C17" s="101" t="s">
         <v>191</v>
       </c>
-      <c r="D17" s="110"/>
+      <c r="D17" s="102"/>
       <c r="E17" s="34"/>
       <c r="F17" s="35">
         <f t="shared" ref="F17:AJ17" si="10">COUNTIF(F$5:F$10,"ST*")</f>
@@ -28808,10 +28808,10 @@
       </c>
     </row>
     <row r="18" spans="3:36" ht="18.75">
-      <c r="C18" s="152" t="s">
+      <c r="C18" s="140" t="s">
         <v>192</v>
       </c>
-      <c r="D18" s="152"/>
+      <c r="D18" s="140"/>
       <c r="E18" s="36"/>
       <c r="F18" s="37">
         <f>F20-F21</f>
@@ -28942,43 +28942,43 @@
       <c r="C19" s="38"/>
       <c r="D19" s="38"/>
       <c r="E19" s="34"/>
-      <c r="F19" s="108"/>
-      <c r="G19" s="108"/>
-      <c r="H19" s="108"/>
-      <c r="I19" s="108"/>
-      <c r="J19" s="108"/>
-      <c r="K19" s="108"/>
-      <c r="L19" s="108"/>
-      <c r="M19" s="108"/>
-      <c r="N19" s="108"/>
-      <c r="O19" s="108"/>
-      <c r="P19" s="108"/>
-      <c r="Q19" s="108"/>
-      <c r="R19" s="108"/>
-      <c r="S19" s="108"/>
-      <c r="T19" s="108"/>
-      <c r="U19" s="108"/>
-      <c r="V19" s="108"/>
-      <c r="W19" s="108"/>
-      <c r="X19" s="108"/>
-      <c r="Y19" s="108"/>
-      <c r="Z19" s="108"/>
-      <c r="AA19" s="108"/>
-      <c r="AB19" s="108"/>
-      <c r="AC19" s="108"/>
-      <c r="AD19" s="108"/>
-      <c r="AE19" s="108"/>
-      <c r="AF19" s="108"/>
-      <c r="AG19" s="108"/>
-      <c r="AH19" s="108"/>
-      <c r="AI19" s="108"/>
-      <c r="AJ19" s="108"/>
+      <c r="F19" s="114"/>
+      <c r="G19" s="114"/>
+      <c r="H19" s="114"/>
+      <c r="I19" s="114"/>
+      <c r="J19" s="114"/>
+      <c r="K19" s="114"/>
+      <c r="L19" s="114"/>
+      <c r="M19" s="114"/>
+      <c r="N19" s="114"/>
+      <c r="O19" s="114"/>
+      <c r="P19" s="114"/>
+      <c r="Q19" s="114"/>
+      <c r="R19" s="114"/>
+      <c r="S19" s="114"/>
+      <c r="T19" s="114"/>
+      <c r="U19" s="114"/>
+      <c r="V19" s="114"/>
+      <c r="W19" s="114"/>
+      <c r="X19" s="114"/>
+      <c r="Y19" s="114"/>
+      <c r="Z19" s="114"/>
+      <c r="AA19" s="114"/>
+      <c r="AB19" s="114"/>
+      <c r="AC19" s="114"/>
+      <c r="AD19" s="114"/>
+      <c r="AE19" s="114"/>
+      <c r="AF19" s="114"/>
+      <c r="AG19" s="114"/>
+      <c r="AH19" s="114"/>
+      <c r="AI19" s="114"/>
+      <c r="AJ19" s="114"/>
     </row>
     <row r="20" spans="3:36" ht="18.75">
-      <c r="C20" s="153" t="s">
+      <c r="C20" s="141" t="s">
         <v>193</v>
       </c>
-      <c r="D20" s="153"/>
+      <c r="D20" s="141"/>
       <c r="E20" s="34"/>
       <c r="F20" s="39">
         <f>SUM(F12:F14)</f>
@@ -29105,10 +29105,10 @@
       </c>
     </row>
     <row r="21" spans="3:36" ht="18.75">
-      <c r="C21" s="153" t="s">
+      <c r="C21" s="141" t="s">
         <v>194</v>
       </c>
-      <c r="D21" s="153"/>
+      <c r="D21" s="141"/>
       <c r="E21" s="34"/>
       <c r="F21" s="35">
         <v>3</v>
@@ -29205,10 +29205,10 @@
       </c>
     </row>
     <row r="22" spans="3:36" ht="18.75">
-      <c r="C22" s="153" t="s">
+      <c r="C22" s="141" t="s">
         <v>195</v>
       </c>
-      <c r="D22" s="153"/>
+      <c r="D22" s="141"/>
       <c r="E22" s="34"/>
       <c r="F22" s="35">
         <f>SUM(F12,F13,F14,F15,F17)</f>
@@ -29342,151 +29342,151 @@
       <c r="K24" s="154"/>
     </row>
     <row r="25" spans="3:36" ht="16.5" thickBot="1">
-      <c r="F25" s="95" t="s">
+      <c r="F25" s="118" t="s">
         <v>196</v>
       </c>
-      <c r="G25" s="96"/>
-      <c r="H25" s="96"/>
-      <c r="I25" s="96"/>
-      <c r="J25" s="96"/>
-      <c r="K25" s="97"/>
-      <c r="M25" s="95" t="s">
+      <c r="G25" s="119"/>
+      <c r="H25" s="119"/>
+      <c r="I25" s="119"/>
+      <c r="J25" s="119"/>
+      <c r="K25" s="120"/>
+      <c r="M25" s="118" t="s">
         <v>196</v>
       </c>
-      <c r="N25" s="96"/>
-      <c r="O25" s="96"/>
-      <c r="P25" s="96"/>
-      <c r="Q25" s="96"/>
-      <c r="R25" s="97"/>
+      <c r="N25" s="119"/>
+      <c r="O25" s="119"/>
+      <c r="P25" s="119"/>
+      <c r="Q25" s="119"/>
+      <c r="R25" s="120"/>
     </row>
     <row r="26" spans="3:36">
       <c r="F26" s="80" t="s">
         <v>197</v>
       </c>
-      <c r="G26" s="106" t="s">
+      <c r="G26" s="128" t="s">
         <v>198</v>
       </c>
-      <c r="H26" s="106"/>
+      <c r="H26" s="128"/>
       <c r="I26" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="J26" s="98" t="s">
+      <c r="J26" s="121" t="s">
         <v>199</v>
       </c>
-      <c r="K26" s="99"/>
+      <c r="K26" s="122"/>
       <c r="M26" s="80" t="s">
         <v>197</v>
       </c>
-      <c r="N26" s="106" t="s">
+      <c r="N26" s="128" t="s">
         <v>198</v>
       </c>
-      <c r="O26" s="106"/>
+      <c r="O26" s="128"/>
       <c r="P26" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="Q26" s="98" t="s">
+      <c r="Q26" s="121" t="s">
         <v>199</v>
       </c>
-      <c r="R26" s="99"/>
+      <c r="R26" s="122"/>
     </row>
     <row r="27" spans="3:36">
       <c r="F27" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="G27" s="107" t="s">
+      <c r="G27" s="129" t="s">
         <v>200</v>
       </c>
-      <c r="H27" s="107"/>
+      <c r="H27" s="129"/>
       <c r="I27" s="77" t="s">
         <v>201</v>
       </c>
-      <c r="J27" s="100" t="s">
+      <c r="J27" s="123" t="s">
         <v>202</v>
       </c>
-      <c r="K27" s="101"/>
+      <c r="K27" s="124"/>
       <c r="M27" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="N27" s="107" t="s">
+      <c r="N27" s="129" t="s">
         <v>200</v>
       </c>
-      <c r="O27" s="107"/>
+      <c r="O27" s="129"/>
       <c r="P27" s="77" t="s">
         <v>201</v>
       </c>
-      <c r="Q27" s="100" t="s">
+      <c r="Q27" s="123" t="s">
         <v>202</v>
       </c>
-      <c r="R27" s="101"/>
+      <c r="R27" s="124"/>
     </row>
     <row r="28" spans="3:36">
       <c r="F28" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="G28" s="102" t="s">
+      <c r="G28" s="115" t="s">
         <v>203</v>
       </c>
-      <c r="H28" s="102"/>
+      <c r="H28" s="115"/>
       <c r="I28" s="78" t="s">
         <v>108</v>
       </c>
-      <c r="J28" s="102" t="s">
+      <c r="J28" s="115" t="s">
         <v>204</v>
       </c>
-      <c r="K28" s="103"/>
+      <c r="K28" s="125"/>
       <c r="M28" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="N28" s="102" t="s">
+      <c r="N28" s="115" t="s">
         <v>203</v>
       </c>
-      <c r="O28" s="102"/>
+      <c r="O28" s="115"/>
       <c r="P28" s="78" t="s">
         <v>108</v>
       </c>
-      <c r="Q28" s="102" t="s">
+      <c r="Q28" s="115" t="s">
         <v>204</v>
       </c>
-      <c r="R28" s="103"/>
+      <c r="R28" s="125"/>
     </row>
     <row r="29" spans="3:36">
       <c r="F29" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="G29" s="111" t="s">
+      <c r="G29" s="116" t="s">
         <v>205</v>
       </c>
-      <c r="H29" s="111"/>
+      <c r="H29" s="116"/>
       <c r="I29" s="79" t="s">
         <v>206</v>
       </c>
-      <c r="J29" s="104" t="s">
+      <c r="J29" s="126" t="s">
         <v>207</v>
       </c>
-      <c r="K29" s="105"/>
+      <c r="K29" s="127"/>
       <c r="M29" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="N29" s="111" t="s">
+      <c r="N29" s="116" t="s">
         <v>205</v>
       </c>
-      <c r="O29" s="111"/>
+      <c r="O29" s="116"/>
       <c r="P29" s="79" t="s">
         <v>206</v>
       </c>
-      <c r="Q29" s="104" t="s">
+      <c r="Q29" s="126" t="s">
         <v>207</v>
       </c>
-      <c r="R29" s="105"/>
+      <c r="R29" s="127"/>
     </row>
     <row r="30" spans="3:36">
       <c r="F30" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="G30" s="111" t="s">
+      <c r="G30" s="116" t="s">
         <v>208</v>
       </c>
-      <c r="H30" s="111"/>
+      <c r="H30" s="116"/>
       <c r="I30" s="20" t="s">
         <v>104</v>
       </c>
@@ -29497,10 +29497,10 @@
       <c r="M30" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="N30" s="111" t="s">
+      <c r="N30" s="116" t="s">
         <v>208</v>
       </c>
-      <c r="O30" s="111"/>
+      <c r="O30" s="116"/>
       <c r="P30" s="20" t="s">
         <v>104</v>
       </c>
@@ -29513,10 +29513,10 @@
       <c r="F31" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="G31" s="92" t="s">
+      <c r="G31" s="117" t="s">
         <v>210</v>
       </c>
-      <c r="H31" s="92"/>
+      <c r="H31" s="117"/>
       <c r="I31" s="20" t="s">
         <v>114</v>
       </c>
@@ -29527,10 +29527,10 @@
       <c r="M31" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="N31" s="92" t="s">
+      <c r="N31" s="117" t="s">
         <v>210</v>
       </c>
-      <c r="O31" s="92"/>
+      <c r="O31" s="117"/>
       <c r="P31" s="20" t="s">
         <v>114</v>
       </c>
@@ -29543,10 +29543,10 @@
       <c r="F32" s="82" t="s">
         <v>212</v>
       </c>
-      <c r="G32" s="123" t="s">
+      <c r="G32" s="92" t="s">
         <v>213</v>
       </c>
-      <c r="H32" s="123"/>
+      <c r="H32" s="92"/>
       <c r="I32" s="20" t="s">
         <v>131</v>
       </c>
@@ -29557,10 +29557,10 @@
       <c r="M32" s="82" t="s">
         <v>212</v>
       </c>
-      <c r="N32" s="123" t="s">
+      <c r="N32" s="92" t="s">
         <v>213</v>
       </c>
-      <c r="O32" s="123"/>
+      <c r="O32" s="92"/>
       <c r="P32" s="20" t="s">
         <v>131</v>
       </c>
@@ -29573,78 +29573,34 @@
       <c r="F33" s="55" t="s">
         <v>215</v>
       </c>
-      <c r="G33" s="124" t="s">
+      <c r="G33" s="95" t="s">
         <v>216</v>
       </c>
-      <c r="H33" s="124"/>
+      <c r="H33" s="95"/>
       <c r="I33" s="56" t="s">
         <v>167</v>
       </c>
-      <c r="J33" s="124" t="s">
+      <c r="J33" s="95" t="s">
         <v>217</v>
       </c>
-      <c r="K33" s="125"/>
+      <c r="K33" s="96"/>
       <c r="M33" s="55" t="s">
         <v>215</v>
       </c>
-      <c r="N33" s="124" t="s">
+      <c r="N33" s="95" t="s">
         <v>216</v>
       </c>
-      <c r="O33" s="124"/>
+      <c r="O33" s="95"/>
       <c r="P33" s="56" t="s">
         <v>167</v>
       </c>
-      <c r="Q33" s="124" t="s">
+      <c r="Q33" s="95" t="s">
         <v>217</v>
       </c>
-      <c r="R33" s="125"/>
+      <c r="R33" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="B3:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="AP2:AP4"/>
-    <mergeCell ref="F2:AJ2"/>
-    <mergeCell ref="AL2:AL4"/>
-    <mergeCell ref="AM2:AM4"/>
-    <mergeCell ref="AN2:AN4"/>
-    <mergeCell ref="AO2:AO4"/>
-    <mergeCell ref="Q31:R31"/>
-    <mergeCell ref="F19:AJ19"/>
-    <mergeCell ref="F25:K25"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G24:H24"/>
     <mergeCell ref="N32:O32"/>
     <mergeCell ref="Q32:R32"/>
     <mergeCell ref="N33:O33"/>
@@ -29661,6 +29617,50 @@
     <mergeCell ref="N30:O30"/>
     <mergeCell ref="Q30:R30"/>
     <mergeCell ref="N31:O31"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="F19:AJ19"/>
+    <mergeCell ref="F25:K25"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="AP2:AP4"/>
+    <mergeCell ref="F2:AJ2"/>
+    <mergeCell ref="AL2:AL4"/>
+    <mergeCell ref="AM2:AM4"/>
+    <mergeCell ref="AN2:AN4"/>
+    <mergeCell ref="AO2:AO4"/>
+    <mergeCell ref="B3:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="J31:K31"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F5:AJ10">
@@ -29741,19 +29741,19 @@
       <c r="AH2" s="162"/>
       <c r="AI2" s="162"/>
       <c r="AJ2" s="162"/>
-      <c r="AL2" s="114" t="s">
+      <c r="AL2" s="105" t="s">
         <v>80</v>
       </c>
-      <c r="AM2" s="114" t="s">
+      <c r="AM2" s="105" t="s">
         <v>81</v>
       </c>
-      <c r="AN2" s="114" t="s">
+      <c r="AN2" s="105" t="s">
         <v>82</v>
       </c>
-      <c r="AO2" s="114" t="s">
+      <c r="AO2" s="105" t="s">
         <v>83</v>
       </c>
-      <c r="AP2" s="114" t="s">
+      <c r="AP2" s="105" t="s">
         <v>84</v>
       </c>
     </row>
@@ -29854,11 +29854,11 @@
         <v>87</v>
       </c>
       <c r="AJ3" s="62"/>
-      <c r="AL3" s="115"/>
-      <c r="AM3" s="115"/>
-      <c r="AN3" s="115"/>
-      <c r="AO3" s="115"/>
-      <c r="AP3" s="115"/>
+      <c r="AL3" s="106"/>
+      <c r="AM3" s="106"/>
+      <c r="AN3" s="106"/>
+      <c r="AO3" s="106"/>
+      <c r="AP3" s="106"/>
     </row>
     <row r="4" spans="2:42" ht="19.5" customHeight="1" thickBot="1">
       <c r="B4" s="159"/>
@@ -29955,20 +29955,20 @@
         <v>30</v>
       </c>
       <c r="AJ4" s="61"/>
-      <c r="AL4" s="116"/>
-      <c r="AM4" s="116"/>
-      <c r="AN4" s="116"/>
-      <c r="AO4" s="116"/>
-      <c r="AP4" s="116"/>
+      <c r="AL4" s="107"/>
+      <c r="AM4" s="107"/>
+      <c r="AN4" s="107"/>
+      <c r="AO4" s="107"/>
+      <c r="AP4" s="107"/>
     </row>
     <row r="5" spans="2:42" ht="18.75">
       <c r="B5" s="47">
         <v>1</v>
       </c>
-      <c r="C5" s="144" t="s">
+      <c r="C5" s="145" t="s">
         <v>115</v>
       </c>
-      <c r="D5" s="145"/>
+      <c r="D5" s="146"/>
       <c r="F5" s="72" t="s">
         <v>101</v>
       </c>
@@ -30085,10 +30085,10 @@
       <c r="B6" s="45">
         <v>2</v>
       </c>
-      <c r="C6" s="142" t="s">
+      <c r="C6" s="144" t="s">
         <v>117</v>
       </c>
-      <c r="D6" s="143"/>
+      <c r="D6" s="150"/>
       <c r="F6" s="74" t="s">
         <v>102</v>
       </c>
@@ -30205,10 +30205,10 @@
       <c r="B7" s="45">
         <v>3</v>
       </c>
-      <c r="C7" s="142" t="s">
+      <c r="C7" s="144" t="s">
         <v>118</v>
       </c>
-      <c r="D7" s="143"/>
+      <c r="D7" s="150"/>
       <c r="F7" s="75" t="s">
         <v>95</v>
       </c>
@@ -30325,10 +30325,10 @@
       <c r="B8" s="45">
         <v>4</v>
       </c>
-      <c r="C8" s="142" t="s">
+      <c r="C8" s="144" t="s">
         <v>119</v>
       </c>
-      <c r="D8" s="143"/>
+      <c r="D8" s="150"/>
       <c r="F8" s="75" t="s">
         <v>98</v>
       </c>
@@ -30445,10 +30445,10 @@
       <c r="B9" s="45">
         <v>5</v>
       </c>
-      <c r="C9" s="142" t="s">
+      <c r="C9" s="144" t="s">
         <v>120</v>
       </c>
-      <c r="D9" s="143"/>
+      <c r="D9" s="150"/>
       <c r="F9" s="75" t="s">
         <v>96</v>
       </c>
@@ -30565,10 +30565,10 @@
       <c r="B10" s="45">
         <v>6</v>
       </c>
-      <c r="C10" s="142" t="s">
+      <c r="C10" s="144" t="s">
         <v>121</v>
       </c>
-      <c r="D10" s="143"/>
+      <c r="D10" s="150"/>
       <c r="F10" s="75" t="s">
         <v>96</v>
       </c>
@@ -30685,10 +30685,10 @@
       <c r="B11" s="45">
         <v>7</v>
       </c>
-      <c r="C11" s="142" t="s">
+      <c r="C11" s="144" t="s">
         <v>122</v>
       </c>
-      <c r="D11" s="143"/>
+      <c r="D11" s="150"/>
       <c r="F11" s="75" t="s">
         <v>101</v>
       </c>
@@ -30805,10 +30805,10 @@
       <c r="B12" s="45">
         <v>8</v>
       </c>
-      <c r="C12" s="142" t="s">
+      <c r="C12" s="144" t="s">
         <v>123</v>
       </c>
-      <c r="D12" s="143"/>
+      <c r="D12" s="150"/>
       <c r="F12" s="75" t="s">
         <v>102</v>
       </c>
@@ -30925,10 +30925,10 @@
       <c r="B13" s="45">
         <v>9</v>
       </c>
-      <c r="C13" s="142" t="s">
+      <c r="C13" s="144" t="s">
         <v>124</v>
       </c>
-      <c r="D13" s="143"/>
+      <c r="D13" s="150"/>
       <c r="F13" s="74" t="s">
         <v>95</v>
       </c>
@@ -31045,10 +31045,10 @@
       <c r="B14" s="45">
         <v>10</v>
       </c>
-      <c r="C14" s="142" t="s">
+      <c r="C14" s="144" t="s">
         <v>125</v>
       </c>
-      <c r="D14" s="143"/>
+      <c r="D14" s="150"/>
       <c r="F14" s="75" t="s">
         <v>116</v>
       </c>
@@ -31165,10 +31165,10 @@
       <c r="B15" s="45">
         <v>11</v>
       </c>
-      <c r="C15" s="112" t="s">
+      <c r="C15" s="97" t="s">
         <v>126</v>
       </c>
-      <c r="D15" s="146"/>
+      <c r="D15" s="147"/>
       <c r="F15" s="75" t="s">
         <v>116</v>
       </c>
@@ -31285,10 +31285,10 @@
       <c r="B16" s="45">
         <v>12</v>
       </c>
-      <c r="C16" s="112" t="s">
+      <c r="C16" s="97" t="s">
         <v>127</v>
       </c>
-      <c r="D16" s="146"/>
+      <c r="D16" s="147"/>
       <c r="F16" s="75" t="s">
         <v>96</v>
       </c>
@@ -31405,10 +31405,10 @@
       <c r="B17" s="45">
         <v>13</v>
       </c>
-      <c r="C17" s="112" t="s">
+      <c r="C17" s="97" t="s">
         <v>128</v>
       </c>
-      <c r="D17" s="146"/>
+      <c r="D17" s="147"/>
       <c r="F17" s="75" t="s">
         <v>96</v>
       </c>
@@ -31525,10 +31525,10 @@
       <c r="B18" s="45">
         <v>14</v>
       </c>
-      <c r="C18" s="112" t="s">
+      <c r="C18" s="97" t="s">
         <v>129</v>
       </c>
-      <c r="D18" s="146"/>
+      <c r="D18" s="147"/>
       <c r="F18" s="75" t="s">
         <v>101</v>
       </c>
@@ -31645,10 +31645,10 @@
       <c r="B19" s="46">
         <v>15</v>
       </c>
-      <c r="C19" s="147" t="s">
+      <c r="C19" s="148" t="s">
         <v>130</v>
       </c>
-      <c r="D19" s="148"/>
+      <c r="D19" s="149"/>
       <c r="F19" s="74" t="s">
         <v>96</v>
       </c>
@@ -31796,10 +31796,10 @@
       <c r="AI20" s="18"/>
     </row>
     <row r="21" spans="2:42" ht="18.75">
-      <c r="C21" s="153" t="s">
+      <c r="C21" s="141" t="s">
         <v>188</v>
       </c>
-      <c r="D21" s="153"/>
+      <c r="D21" s="141"/>
       <c r="E21" s="34"/>
       <c r="F21" s="35">
         <f t="shared" ref="F21:AJ21" si="5">COUNTIF(F$5:F$19,"M*")</f>
@@ -31927,10 +31927,10 @@
       </c>
     </row>
     <row r="22" spans="2:42" ht="18.75">
-      <c r="C22" s="153" t="s">
+      <c r="C22" s="141" t="s">
         <v>189</v>
       </c>
-      <c r="D22" s="153"/>
+      <c r="D22" s="141"/>
       <c r="E22" s="34"/>
       <c r="F22" s="35">
         <f t="shared" ref="F22:AJ22" si="6">COUNTIF(F$5:F$19,"A*")</f>
@@ -32058,10 +32058,10 @@
       </c>
     </row>
     <row r="23" spans="2:42" ht="18.75">
-      <c r="C23" s="153" t="s">
+      <c r="C23" s="141" t="s">
         <v>77</v>
       </c>
-      <c r="D23" s="153"/>
+      <c r="D23" s="141"/>
       <c r="E23" s="34"/>
       <c r="F23" s="35">
         <f t="shared" ref="F23:AJ23" si="7">COUNTIF(F$5:F$19,"N*")</f>
@@ -32189,10 +32189,10 @@
       </c>
     </row>
     <row r="24" spans="2:42" ht="18.75">
-      <c r="C24" s="153" t="s">
+      <c r="C24" s="141" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="153"/>
+      <c r="D24" s="141"/>
       <c r="E24" s="34"/>
       <c r="F24" s="35">
         <f t="shared" ref="F24:AJ24" si="8">COUNTIF(F$5:F$19,"O*")</f>
@@ -32320,10 +32320,10 @@
       </c>
     </row>
     <row r="25" spans="2:42" ht="18.75">
-      <c r="C25" s="109" t="s">
+      <c r="C25" s="101" t="s">
         <v>191</v>
       </c>
-      <c r="D25" s="110"/>
+      <c r="D25" s="102"/>
       <c r="E25" s="34"/>
       <c r="F25" s="35">
         <f t="shared" ref="F25:AJ25" si="9">COUNTIF(F$5:F$19,"ST*")</f>
@@ -32451,10 +32451,10 @@
       </c>
     </row>
     <row r="26" spans="2:42" ht="18.75">
-      <c r="C26" s="152" t="s">
+      <c r="C26" s="140" t="s">
         <v>192</v>
       </c>
-      <c r="D26" s="152"/>
+      <c r="D26" s="140"/>
       <c r="E26" s="36"/>
       <c r="F26" s="37">
         <f>F28-F29</f>
@@ -32582,43 +32582,43 @@
       <c r="C27" s="38"/>
       <c r="D27" s="38"/>
       <c r="E27" s="34"/>
-      <c r="F27" s="108"/>
-      <c r="G27" s="108"/>
-      <c r="H27" s="108"/>
-      <c r="I27" s="108"/>
-      <c r="J27" s="108"/>
-      <c r="K27" s="108"/>
-      <c r="L27" s="108"/>
-      <c r="M27" s="108"/>
-      <c r="N27" s="108"/>
-      <c r="O27" s="108"/>
-      <c r="P27" s="108"/>
-      <c r="Q27" s="108"/>
-      <c r="R27" s="108"/>
-      <c r="S27" s="108"/>
-      <c r="T27" s="108"/>
-      <c r="U27" s="108"/>
-      <c r="V27" s="108"/>
-      <c r="W27" s="108"/>
-      <c r="X27" s="108"/>
-      <c r="Y27" s="108"/>
-      <c r="Z27" s="108"/>
-      <c r="AA27" s="108"/>
-      <c r="AB27" s="108"/>
-      <c r="AC27" s="108"/>
-      <c r="AD27" s="108"/>
-      <c r="AE27" s="108"/>
-      <c r="AF27" s="108"/>
-      <c r="AG27" s="108"/>
-      <c r="AH27" s="108"/>
-      <c r="AI27" s="108"/>
-      <c r="AJ27" s="108"/>
+      <c r="F27" s="114"/>
+      <c r="G27" s="114"/>
+      <c r="H27" s="114"/>
+      <c r="I27" s="114"/>
+      <c r="J27" s="114"/>
+      <c r="K27" s="114"/>
+      <c r="L27" s="114"/>
+      <c r="M27" s="114"/>
+      <c r="N27" s="114"/>
+      <c r="O27" s="114"/>
+      <c r="P27" s="114"/>
+      <c r="Q27" s="114"/>
+      <c r="R27" s="114"/>
+      <c r="S27" s="114"/>
+      <c r="T27" s="114"/>
+      <c r="U27" s="114"/>
+      <c r="V27" s="114"/>
+      <c r="W27" s="114"/>
+      <c r="X27" s="114"/>
+      <c r="Y27" s="114"/>
+      <c r="Z27" s="114"/>
+      <c r="AA27" s="114"/>
+      <c r="AB27" s="114"/>
+      <c r="AC27" s="114"/>
+      <c r="AD27" s="114"/>
+      <c r="AE27" s="114"/>
+      <c r="AF27" s="114"/>
+      <c r="AG27" s="114"/>
+      <c r="AH27" s="114"/>
+      <c r="AI27" s="114"/>
+      <c r="AJ27" s="114"/>
     </row>
     <row r="28" spans="2:42" ht="18.75">
-      <c r="C28" s="153" t="s">
+      <c r="C28" s="141" t="s">
         <v>193</v>
       </c>
-      <c r="D28" s="153"/>
+      <c r="D28" s="141"/>
       <c r="E28" s="34"/>
       <c r="F28" s="39">
         <f>SUM(F21:F23)</f>
@@ -32745,10 +32745,10 @@
       </c>
     </row>
     <row r="29" spans="2:42" ht="18.75">
-      <c r="C29" s="153" t="s">
+      <c r="C29" s="141" t="s">
         <v>194</v>
       </c>
-      <c r="D29" s="153"/>
+      <c r="D29" s="141"/>
       <c r="E29" s="34"/>
       <c r="F29" s="35">
         <v>6</v>
@@ -32845,10 +32845,10 @@
       </c>
     </row>
     <row r="30" spans="2:42" ht="18.75">
-      <c r="C30" s="153" t="s">
+      <c r="C30" s="141" t="s">
         <v>195</v>
       </c>
-      <c r="D30" s="153"/>
+      <c r="D30" s="141"/>
       <c r="E30" s="34"/>
       <c r="F30" s="35">
         <f>SUM(F21,F22,F23,F24,F25)</f>
@@ -32976,87 +32976,87 @@
     </row>
     <row r="32" spans="2:42" ht="9.75" customHeight="1" thickBot="1"/>
     <row r="33" spans="6:11" ht="16.5" thickBot="1">
-      <c r="F33" s="95" t="s">
+      <c r="F33" s="118" t="s">
         <v>196</v>
       </c>
-      <c r="G33" s="96"/>
-      <c r="H33" s="96"/>
-      <c r="I33" s="96"/>
-      <c r="J33" s="96"/>
-      <c r="K33" s="97"/>
+      <c r="G33" s="119"/>
+      <c r="H33" s="119"/>
+      <c r="I33" s="119"/>
+      <c r="J33" s="119"/>
+      <c r="K33" s="120"/>
     </row>
     <row r="34" spans="6:11">
       <c r="F34" s="80" t="s">
         <v>197</v>
       </c>
-      <c r="G34" s="106" t="s">
+      <c r="G34" s="128" t="s">
         <v>198</v>
       </c>
-      <c r="H34" s="106"/>
+      <c r="H34" s="128"/>
       <c r="I34" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="J34" s="98" t="s">
+      <c r="J34" s="121" t="s">
         <v>199</v>
       </c>
-      <c r="K34" s="99"/>
+      <c r="K34" s="122"/>
     </row>
     <row r="35" spans="6:11">
       <c r="F35" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="G35" s="107" t="s">
+      <c r="G35" s="129" t="s">
         <v>200</v>
       </c>
-      <c r="H35" s="107"/>
+      <c r="H35" s="129"/>
       <c r="I35" s="77" t="s">
         <v>201</v>
       </c>
-      <c r="J35" s="100" t="s">
+      <c r="J35" s="123" t="s">
         <v>202</v>
       </c>
-      <c r="K35" s="101"/>
+      <c r="K35" s="124"/>
     </row>
     <row r="36" spans="6:11">
       <c r="F36" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="G36" s="102" t="s">
+      <c r="G36" s="115" t="s">
         <v>203</v>
       </c>
-      <c r="H36" s="102"/>
+      <c r="H36" s="115"/>
       <c r="I36" s="78" t="s">
         <v>108</v>
       </c>
-      <c r="J36" s="102" t="s">
+      <c r="J36" s="115" t="s">
         <v>204</v>
       </c>
-      <c r="K36" s="103"/>
+      <c r="K36" s="125"/>
     </row>
     <row r="37" spans="6:11">
       <c r="F37" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="G37" s="111" t="s">
+      <c r="G37" s="116" t="s">
         <v>205</v>
       </c>
-      <c r="H37" s="111"/>
+      <c r="H37" s="116"/>
       <c r="I37" s="79" t="s">
         <v>206</v>
       </c>
-      <c r="J37" s="104" t="s">
+      <c r="J37" s="126" t="s">
         <v>207</v>
       </c>
-      <c r="K37" s="105"/>
+      <c r="K37" s="127"/>
     </row>
     <row r="38" spans="6:11">
       <c r="F38" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="G38" s="111" t="s">
+      <c r="G38" s="116" t="s">
         <v>208</v>
       </c>
-      <c r="H38" s="111"/>
+      <c r="H38" s="116"/>
       <c r="I38" s="20" t="s">
         <v>104</v>
       </c>
@@ -33069,10 +33069,10 @@
       <c r="F39" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="G39" s="92" t="s">
+      <c r="G39" s="117" t="s">
         <v>210</v>
       </c>
-      <c r="H39" s="92"/>
+      <c r="H39" s="117"/>
       <c r="I39" s="20" t="s">
         <v>114</v>
       </c>
@@ -33085,10 +33085,10 @@
       <c r="F40" s="82" t="s">
         <v>212</v>
       </c>
-      <c r="G40" s="123" t="s">
+      <c r="G40" s="92" t="s">
         <v>213</v>
       </c>
-      <c r="H40" s="123"/>
+      <c r="H40" s="92"/>
       <c r="I40" s="20" t="s">
         <v>131</v>
       </c>
@@ -33101,20 +33101,53 @@
       <c r="F41" s="55" t="s">
         <v>215</v>
       </c>
-      <c r="G41" s="124" t="s">
+      <c r="G41" s="95" t="s">
         <v>216</v>
       </c>
-      <c r="H41" s="124"/>
+      <c r="H41" s="95"/>
       <c r="I41" s="56" t="s">
         <v>167</v>
       </c>
-      <c r="J41" s="124" t="s">
+      <c r="J41" s="95" t="s">
         <v>217</v>
       </c>
-      <c r="K41" s="125"/>
+      <c r="K41" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="49">
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="F33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="F27:AJ27"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C25:D25"/>
     <mergeCell ref="G41:H41"/>
     <mergeCell ref="J41:K41"/>
     <mergeCell ref="B3:D4"/>
@@ -33131,39 +33164,6 @@
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F27:AJ27"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="F33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="G37:H37"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F5:AJ19">
@@ -33211,61 +33211,61 @@
   <sheetData>
     <row r="1" spans="2:42" ht="16.5" thickBot="1"/>
     <row r="2" spans="2:42" ht="39" customHeight="1" thickBot="1">
-      <c r="F2" s="139" t="s">
+      <c r="F2" s="151" t="s">
         <v>218</v>
       </c>
-      <c r="G2" s="140"/>
-      <c r="H2" s="140"/>
-      <c r="I2" s="140"/>
-      <c r="J2" s="140"/>
-      <c r="K2" s="140"/>
-      <c r="L2" s="140"/>
-      <c r="M2" s="140"/>
-      <c r="N2" s="140"/>
-      <c r="O2" s="140"/>
-      <c r="P2" s="140"/>
-      <c r="Q2" s="140"/>
-      <c r="R2" s="140"/>
-      <c r="S2" s="140"/>
-      <c r="T2" s="140"/>
-      <c r="U2" s="140"/>
-      <c r="V2" s="140"/>
-      <c r="W2" s="140"/>
-      <c r="X2" s="140"/>
-      <c r="Y2" s="140"/>
-      <c r="Z2" s="140"/>
-      <c r="AA2" s="140"/>
-      <c r="AB2" s="140"/>
-      <c r="AC2" s="140"/>
-      <c r="AD2" s="140"/>
-      <c r="AE2" s="140"/>
-      <c r="AF2" s="140"/>
-      <c r="AG2" s="140"/>
-      <c r="AH2" s="140"/>
-      <c r="AI2" s="140"/>
-      <c r="AJ2" s="141"/>
-      <c r="AL2" s="114" t="s">
+      <c r="G2" s="152"/>
+      <c r="H2" s="152"/>
+      <c r="I2" s="152"/>
+      <c r="J2" s="152"/>
+      <c r="K2" s="152"/>
+      <c r="L2" s="152"/>
+      <c r="M2" s="152"/>
+      <c r="N2" s="152"/>
+      <c r="O2" s="152"/>
+      <c r="P2" s="152"/>
+      <c r="Q2" s="152"/>
+      <c r="R2" s="152"/>
+      <c r="S2" s="152"/>
+      <c r="T2" s="152"/>
+      <c r="U2" s="152"/>
+      <c r="V2" s="152"/>
+      <c r="W2" s="152"/>
+      <c r="X2" s="152"/>
+      <c r="Y2" s="152"/>
+      <c r="Z2" s="152"/>
+      <c r="AA2" s="152"/>
+      <c r="AB2" s="152"/>
+      <c r="AC2" s="152"/>
+      <c r="AD2" s="152"/>
+      <c r="AE2" s="152"/>
+      <c r="AF2" s="152"/>
+      <c r="AG2" s="152"/>
+      <c r="AH2" s="152"/>
+      <c r="AI2" s="152"/>
+      <c r="AJ2" s="153"/>
+      <c r="AL2" s="105" t="s">
         <v>80</v>
       </c>
-      <c r="AM2" s="114" t="s">
+      <c r="AM2" s="105" t="s">
         <v>81</v>
       </c>
-      <c r="AN2" s="114" t="s">
+      <c r="AN2" s="105" t="s">
         <v>82</v>
       </c>
-      <c r="AO2" s="114" t="s">
+      <c r="AO2" s="105" t="s">
         <v>83</v>
       </c>
-      <c r="AP2" s="114" t="s">
+      <c r="AP2" s="105" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="3" spans="2:42" ht="39.75" thickBot="1">
-      <c r="B3" s="122" t="s">
+      <c r="B3" s="113" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="122"/>
-      <c r="D3" s="122"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="113"/>
       <c r="F3" s="43" t="s">
         <v>86</v>
       </c>
@@ -33359,16 +33359,16 @@
       <c r="AJ3" s="43" t="s">
         <v>187</v>
       </c>
-      <c r="AL3" s="115"/>
-      <c r="AM3" s="115"/>
-      <c r="AN3" s="115"/>
-      <c r="AO3" s="115"/>
-      <c r="AP3" s="115"/>
+      <c r="AL3" s="106"/>
+      <c r="AM3" s="106"/>
+      <c r="AN3" s="106"/>
+      <c r="AO3" s="106"/>
+      <c r="AP3" s="106"/>
     </row>
     <row r="4" spans="2:42" ht="19.5" customHeight="1" thickBot="1">
-      <c r="B4" s="122"/>
-      <c r="C4" s="122"/>
-      <c r="D4" s="122"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
       <c r="F4" s="40">
         <v>1</v>
       </c>
@@ -33462,20 +33462,20 @@
       <c r="AJ4" s="58" t="s">
         <v>187</v>
       </c>
-      <c r="AL4" s="116"/>
-      <c r="AM4" s="116"/>
-      <c r="AN4" s="116"/>
-      <c r="AO4" s="116"/>
-      <c r="AP4" s="116"/>
+      <c r="AL4" s="107"/>
+      <c r="AM4" s="107"/>
+      <c r="AN4" s="107"/>
+      <c r="AO4" s="107"/>
+      <c r="AP4" s="107"/>
     </row>
     <row r="5" spans="2:42" ht="18.75">
       <c r="B5" s="35">
         <v>1</v>
       </c>
-      <c r="C5" s="142" t="s">
+      <c r="C5" s="144" t="s">
         <v>132</v>
       </c>
-      <c r="D5" s="142"/>
+      <c r="D5" s="144"/>
       <c r="F5" s="73" t="s">
         <v>102</v>
       </c>
@@ -33592,10 +33592,10 @@
       <c r="B6" s="35">
         <v>2</v>
       </c>
-      <c r="C6" s="142" t="s">
+      <c r="C6" s="144" t="s">
         <v>133</v>
       </c>
-      <c r="D6" s="142"/>
+      <c r="D6" s="144"/>
       <c r="F6" s="75" t="s">
         <v>102</v>
       </c>
@@ -33712,10 +33712,10 @@
       <c r="B7" s="35">
         <v>3</v>
       </c>
-      <c r="C7" s="142" t="s">
+      <c r="C7" s="144" t="s">
         <v>134</v>
       </c>
-      <c r="D7" s="142"/>
+      <c r="D7" s="144"/>
       <c r="F7" s="75" t="s">
         <v>98</v>
       </c>
@@ -33832,10 +33832,10 @@
       <c r="B8" s="35">
         <v>4</v>
       </c>
-      <c r="C8" s="142" t="s">
+      <c r="C8" s="144" t="s">
         <v>136</v>
       </c>
-      <c r="D8" s="142"/>
+      <c r="D8" s="144"/>
       <c r="F8" s="75" t="s">
         <v>95</v>
       </c>
@@ -33952,10 +33952,10 @@
       <c r="B9" s="35">
         <v>5</v>
       </c>
-      <c r="C9" s="142" t="s">
+      <c r="C9" s="144" t="s">
         <v>137</v>
       </c>
-      <c r="D9" s="142"/>
+      <c r="D9" s="144"/>
       <c r="F9" s="75" t="s">
         <v>96</v>
       </c>
@@ -34072,10 +34072,10 @@
       <c r="B10" s="35">
         <v>6</v>
       </c>
-      <c r="C10" s="142" t="s">
+      <c r="C10" s="144" t="s">
         <v>138</v>
       </c>
-      <c r="D10" s="142"/>
+      <c r="D10" s="144"/>
       <c r="F10" s="75" t="s">
         <v>96</v>
       </c>
@@ -34192,10 +34192,10 @@
       <c r="B11" s="35">
         <v>7</v>
       </c>
-      <c r="C11" s="142" t="s">
+      <c r="C11" s="144" t="s">
         <v>139</v>
       </c>
-      <c r="D11" s="142"/>
+      <c r="D11" s="144"/>
       <c r="F11" s="76" t="s">
         <v>101</v>
       </c>
@@ -34312,10 +34312,10 @@
       <c r="B12" s="35">
         <v>8</v>
       </c>
-      <c r="C12" s="142" t="s">
+      <c r="C12" s="144" t="s">
         <v>140</v>
       </c>
-      <c r="D12" s="142"/>
+      <c r="D12" s="144"/>
       <c r="F12" s="75" t="s">
         <v>101</v>
       </c>
@@ -34432,10 +34432,10 @@
       <c r="B13" s="35">
         <v>9</v>
       </c>
-      <c r="C13" s="142" t="s">
+      <c r="C13" s="144" t="s">
         <v>220</v>
       </c>
-      <c r="D13" s="142"/>
+      <c r="D13" s="144"/>
       <c r="F13" s="75" t="s">
         <v>102</v>
       </c>
@@ -34552,10 +34552,10 @@
       <c r="B14" s="35">
         <v>10</v>
       </c>
-      <c r="C14" s="142" t="s">
+      <c r="C14" s="144" t="s">
         <v>142</v>
       </c>
-      <c r="D14" s="142"/>
+      <c r="D14" s="144"/>
       <c r="F14" s="75" t="s">
         <v>116</v>
       </c>
@@ -34672,10 +34672,10 @@
       <c r="B15" s="35">
         <v>11</v>
       </c>
-      <c r="C15" s="142" t="s">
+      <c r="C15" s="144" t="s">
         <v>143</v>
       </c>
-      <c r="D15" s="142"/>
+      <c r="D15" s="144"/>
       <c r="F15" s="75" t="s">
         <v>116</v>
       </c>
@@ -34792,10 +34792,10 @@
       <c r="B16" s="35">
         <v>12</v>
       </c>
-      <c r="C16" s="142" t="s">
+      <c r="C16" s="144" t="s">
         <v>144</v>
       </c>
-      <c r="D16" s="142"/>
+      <c r="D16" s="144"/>
       <c r="F16" s="75" t="s">
         <v>96</v>
       </c>
@@ -34912,10 +34912,10 @@
       <c r="B17" s="35">
         <v>13</v>
       </c>
-      <c r="C17" s="142" t="s">
+      <c r="C17" s="144" t="s">
         <v>145</v>
       </c>
-      <c r="D17" s="142"/>
+      <c r="D17" s="144"/>
       <c r="F17" s="75" t="s">
         <v>96</v>
       </c>
@@ -35032,10 +35032,10 @@
       <c r="B18" s="35">
         <v>14</v>
       </c>
-      <c r="C18" s="142" t="s">
+      <c r="C18" s="144" t="s">
         <v>146</v>
       </c>
-      <c r="D18" s="142"/>
+      <c r="D18" s="144"/>
       <c r="F18" s="76" t="s">
         <v>101</v>
       </c>
@@ -35152,10 +35152,10 @@
       <c r="B19" s="35">
         <v>15</v>
       </c>
-      <c r="C19" s="142" t="s">
+      <c r="C19" s="144" t="s">
         <v>147</v>
       </c>
-      <c r="D19" s="142"/>
+      <c r="D19" s="144"/>
       <c r="F19" s="75" t="s">
         <v>102</v>
       </c>
@@ -35272,10 +35272,10 @@
       <c r="B20" s="35">
         <v>16</v>
       </c>
-      <c r="C20" s="142" t="s">
+      <c r="C20" s="144" t="s">
         <v>148</v>
       </c>
-      <c r="D20" s="142"/>
+      <c r="D20" s="144"/>
       <c r="F20" s="75" t="s">
         <v>102</v>
       </c>
@@ -35392,10 +35392,10 @@
       <c r="B21" s="35">
         <v>17</v>
       </c>
-      <c r="C21" s="142" t="s">
+      <c r="C21" s="144" t="s">
         <v>149</v>
       </c>
-      <c r="D21" s="142"/>
+      <c r="D21" s="144"/>
       <c r="F21" s="75" t="s">
         <v>116</v>
       </c>
@@ -35512,10 +35512,10 @@
       <c r="B22" s="35">
         <v>18</v>
       </c>
-      <c r="C22" s="142" t="s">
+      <c r="C22" s="144" t="s">
         <v>150</v>
       </c>
-      <c r="D22" s="142"/>
+      <c r="D22" s="144"/>
       <c r="F22" s="75" t="s">
         <v>116</v>
       </c>
@@ -35632,10 +35632,10 @@
       <c r="B23" s="35">
         <v>19</v>
       </c>
-      <c r="C23" s="142" t="s">
+      <c r="C23" s="144" t="s">
         <v>151</v>
       </c>
-      <c r="D23" s="142"/>
+      <c r="D23" s="144"/>
       <c r="F23" s="75" t="s">
         <v>96</v>
       </c>
@@ -35752,10 +35752,10 @@
       <c r="B24" s="35">
         <v>20</v>
       </c>
-      <c r="C24" s="142" t="s">
+      <c r="C24" s="144" t="s">
         <v>152</v>
       </c>
-      <c r="D24" s="142"/>
+      <c r="D24" s="144"/>
       <c r="F24" s="75" t="s">
         <v>96</v>
       </c>
@@ -35872,10 +35872,10 @@
       <c r="B25" s="35">
         <v>21</v>
       </c>
-      <c r="C25" s="142" t="s">
+      <c r="C25" s="144" t="s">
         <v>153</v>
       </c>
-      <c r="D25" s="142"/>
+      <c r="D25" s="144"/>
       <c r="F25" s="76" t="s">
         <v>95</v>
       </c>
@@ -35992,10 +35992,10 @@
       <c r="B26" s="35">
         <v>22</v>
       </c>
-      <c r="C26" s="142" t="s">
+      <c r="C26" s="144" t="s">
         <v>154</v>
       </c>
-      <c r="D26" s="142"/>
+      <c r="D26" s="144"/>
       <c r="F26" s="75" t="s">
         <v>101</v>
       </c>
@@ -36112,10 +36112,10 @@
       <c r="B27" s="35">
         <v>23</v>
       </c>
-      <c r="C27" s="142" t="s">
+      <c r="C27" s="144" t="s">
         <v>155</v>
       </c>
-      <c r="D27" s="142"/>
+      <c r="D27" s="144"/>
       <c r="F27" s="75" t="s">
         <v>102</v>
       </c>
@@ -36232,10 +36232,10 @@
       <c r="B28" s="35">
         <v>24</v>
       </c>
-      <c r="C28" s="142" t="s">
+      <c r="C28" s="144" t="s">
         <v>156</v>
       </c>
-      <c r="D28" s="142"/>
+      <c r="D28" s="144"/>
       <c r="F28" s="75" t="s">
         <v>116</v>
       </c>
@@ -36352,10 +36352,10 @@
       <c r="B29" s="35">
         <v>25</v>
       </c>
-      <c r="C29" s="142" t="s">
+      <c r="C29" s="144" t="s">
         <v>157</v>
       </c>
-      <c r="D29" s="142"/>
+      <c r="D29" s="144"/>
       <c r="F29" s="75" t="s">
         <v>116</v>
       </c>
@@ -36472,10 +36472,10 @@
       <c r="B30" s="35">
         <v>26</v>
       </c>
-      <c r="C30" s="112" t="s">
+      <c r="C30" s="97" t="s">
         <v>158</v>
       </c>
-      <c r="D30" s="113"/>
+      <c r="D30" s="98"/>
       <c r="F30" s="75" t="s">
         <v>96</v>
       </c>
@@ -36592,10 +36592,10 @@
       <c r="B31" s="35">
         <v>27</v>
       </c>
-      <c r="C31" s="112" t="s">
+      <c r="C31" s="97" t="s">
         <v>159</v>
       </c>
-      <c r="D31" s="113"/>
+      <c r="D31" s="98"/>
       <c r="F31" s="75" t="s">
         <v>96</v>
       </c>
@@ -36712,10 +36712,10 @@
       <c r="B32" s="35">
         <v>28</v>
       </c>
-      <c r="C32" s="112" t="s">
+      <c r="C32" s="97" t="s">
         <v>160</v>
       </c>
-      <c r="D32" s="113"/>
+      <c r="D32" s="98"/>
       <c r="F32" s="76" t="s">
         <v>101</v>
       </c>
@@ -36832,10 +36832,10 @@
       <c r="B33" s="35">
         <v>29</v>
       </c>
-      <c r="C33" s="112" t="s">
+      <c r="C33" s="97" t="s">
         <v>161</v>
       </c>
-      <c r="D33" s="113"/>
+      <c r="D33" s="98"/>
       <c r="F33" s="75" t="s">
         <v>95</v>
       </c>
@@ -36952,10 +36952,10 @@
       <c r="B34" s="35">
         <v>30</v>
       </c>
-      <c r="C34" s="149" t="s">
+      <c r="C34" s="139" t="s">
         <v>162</v>
       </c>
-      <c r="D34" s="149"/>
+      <c r="D34" s="139"/>
       <c r="F34" s="75" t="s">
         <v>101</v>
       </c>
@@ -37072,10 +37072,10 @@
       <c r="B35" s="35">
         <v>31</v>
       </c>
-      <c r="C35" s="149" t="s">
+      <c r="C35" s="139" t="s">
         <v>163</v>
       </c>
-      <c r="D35" s="149"/>
+      <c r="D35" s="139"/>
       <c r="F35" s="75" t="s">
         <v>96</v>
       </c>
@@ -37192,10 +37192,10 @@
       <c r="B36" s="35">
         <v>32</v>
       </c>
-      <c r="C36" s="150" t="s">
+      <c r="C36" s="142" t="s">
         <v>164</v>
       </c>
-      <c r="D36" s="151"/>
+      <c r="D36" s="143"/>
       <c r="F36" s="75" t="s">
         <v>95</v>
       </c>
@@ -37312,10 +37312,10 @@
       <c r="B37" s="35">
         <v>33</v>
       </c>
-      <c r="C37" s="149" t="s">
+      <c r="C37" s="139" t="s">
         <v>165</v>
       </c>
-      <c r="D37" s="149"/>
+      <c r="D37" s="139"/>
       <c r="F37" s="88" t="s">
         <v>166</v>
       </c>
@@ -37463,10 +37463,10 @@
       <c r="AI38" s="18"/>
     </row>
     <row r="39" spans="2:42" ht="18.75">
-      <c r="C39" s="153" t="s">
+      <c r="C39" s="141" t="s">
         <v>188</v>
       </c>
-      <c r="D39" s="153"/>
+      <c r="D39" s="141"/>
       <c r="E39" s="34"/>
       <c r="F39" s="35">
         <f t="shared" ref="F39:AJ39" si="5">COUNTIF(F$5:F$36,"M*")</f>
@@ -37594,10 +37594,10 @@
       </c>
     </row>
     <row r="40" spans="2:42" ht="18.75">
-      <c r="C40" s="153" t="s">
+      <c r="C40" s="141" t="s">
         <v>189</v>
       </c>
-      <c r="D40" s="153"/>
+      <c r="D40" s="141"/>
       <c r="E40" s="34"/>
       <c r="F40" s="35">
         <f t="shared" ref="F40:AJ40" si="6">COUNTIF(F$5:F$36,"A*")</f>
@@ -37725,10 +37725,10 @@
       </c>
     </row>
     <row r="41" spans="2:42" ht="18.75">
-      <c r="C41" s="153" t="s">
+      <c r="C41" s="141" t="s">
         <v>77</v>
       </c>
-      <c r="D41" s="153"/>
+      <c r="D41" s="141"/>
       <c r="E41" s="34"/>
       <c r="F41" s="35">
         <f t="shared" ref="F41:AJ41" si="7">COUNTIF(F$5:F$36,"N*")</f>
@@ -37856,10 +37856,10 @@
       </c>
     </row>
     <row r="42" spans="2:42" ht="18.75">
-      <c r="C42" s="153" t="s">
+      <c r="C42" s="141" t="s">
         <v>78</v>
       </c>
-      <c r="D42" s="153"/>
+      <c r="D42" s="141"/>
       <c r="E42" s="34"/>
       <c r="F42" s="35">
         <f t="shared" ref="F42:AJ42" si="8">COUNTIF(F$5:F$37,"O*")</f>
@@ -37987,10 +37987,10 @@
       </c>
     </row>
     <row r="43" spans="2:42" ht="18.75">
-      <c r="C43" s="109" t="s">
+      <c r="C43" s="101" t="s">
         <v>190</v>
       </c>
-      <c r="D43" s="110"/>
+      <c r="D43" s="102"/>
       <c r="E43" s="34"/>
       <c r="F43" s="35">
         <f t="shared" ref="F43:AJ43" si="9">COUNTIF(F$5:F$37,"TR*")</f>
@@ -38118,10 +38118,10 @@
       </c>
     </row>
     <row r="44" spans="2:42" ht="18.75">
-      <c r="C44" s="109" t="s">
+      <c r="C44" s="101" t="s">
         <v>191</v>
       </c>
-      <c r="D44" s="110"/>
+      <c r="D44" s="102"/>
       <c r="E44" s="34"/>
       <c r="F44" s="35">
         <f t="shared" ref="F44:AJ44" si="10">COUNTIF(F$5:F$36,"ST*")</f>
@@ -38249,10 +38249,10 @@
       </c>
     </row>
     <row r="45" spans="2:42" ht="18.75">
-      <c r="C45" s="152" t="s">
+      <c r="C45" s="140" t="s">
         <v>192</v>
       </c>
-      <c r="D45" s="152"/>
+      <c r="D45" s="140"/>
       <c r="E45" s="36"/>
       <c r="F45" s="37">
         <f>F47-F48</f>
@@ -38383,43 +38383,43 @@
       <c r="C46" s="38"/>
       <c r="D46" s="38"/>
       <c r="E46" s="34"/>
-      <c r="F46" s="108"/>
-      <c r="G46" s="108"/>
-      <c r="H46" s="108"/>
-      <c r="I46" s="108"/>
-      <c r="J46" s="108"/>
-      <c r="K46" s="108"/>
-      <c r="L46" s="108"/>
-      <c r="M46" s="108"/>
-      <c r="N46" s="108"/>
-      <c r="O46" s="108"/>
-      <c r="P46" s="108"/>
-      <c r="Q46" s="108"/>
-      <c r="R46" s="108"/>
-      <c r="S46" s="108"/>
-      <c r="T46" s="108"/>
-      <c r="U46" s="108"/>
-      <c r="V46" s="108"/>
-      <c r="W46" s="108"/>
-      <c r="X46" s="108"/>
-      <c r="Y46" s="108"/>
-      <c r="Z46" s="108"/>
-      <c r="AA46" s="108"/>
-      <c r="AB46" s="108"/>
-      <c r="AC46" s="108"/>
-      <c r="AD46" s="108"/>
-      <c r="AE46" s="108"/>
-      <c r="AF46" s="108"/>
-      <c r="AG46" s="108"/>
-      <c r="AH46" s="108"/>
-      <c r="AI46" s="108"/>
-      <c r="AJ46" s="108"/>
+      <c r="F46" s="114"/>
+      <c r="G46" s="114"/>
+      <c r="H46" s="114"/>
+      <c r="I46" s="114"/>
+      <c r="J46" s="114"/>
+      <c r="K46" s="114"/>
+      <c r="L46" s="114"/>
+      <c r="M46" s="114"/>
+      <c r="N46" s="114"/>
+      <c r="O46" s="114"/>
+      <c r="P46" s="114"/>
+      <c r="Q46" s="114"/>
+      <c r="R46" s="114"/>
+      <c r="S46" s="114"/>
+      <c r="T46" s="114"/>
+      <c r="U46" s="114"/>
+      <c r="V46" s="114"/>
+      <c r="W46" s="114"/>
+      <c r="X46" s="114"/>
+      <c r="Y46" s="114"/>
+      <c r="Z46" s="114"/>
+      <c r="AA46" s="114"/>
+      <c r="AB46" s="114"/>
+      <c r="AC46" s="114"/>
+      <c r="AD46" s="114"/>
+      <c r="AE46" s="114"/>
+      <c r="AF46" s="114"/>
+      <c r="AG46" s="114"/>
+      <c r="AH46" s="114"/>
+      <c r="AI46" s="114"/>
+      <c r="AJ46" s="114"/>
     </row>
     <row r="47" spans="2:42" ht="19.5" thickBot="1">
-      <c r="C47" s="153" t="s">
+      <c r="C47" s="141" t="s">
         <v>193</v>
       </c>
-      <c r="D47" s="153"/>
+      <c r="D47" s="141"/>
       <c r="E47" s="34"/>
       <c r="F47" s="39">
         <f>SUM(F39:F41)</f>
@@ -38546,10 +38546,10 @@
       </c>
     </row>
     <row r="48" spans="2:42" ht="18.75">
-      <c r="C48" s="153" t="s">
+      <c r="C48" s="141" t="s">
         <v>194</v>
       </c>
-      <c r="D48" s="153"/>
+      <c r="D48" s="141"/>
       <c r="E48" s="34"/>
       <c r="F48" s="35">
         <v>18</v>
@@ -38646,10 +38646,10 @@
       </c>
     </row>
     <row r="49" spans="3:36" ht="19.5" thickBot="1">
-      <c r="C49" s="153" t="s">
+      <c r="C49" s="141" t="s">
         <v>195</v>
       </c>
-      <c r="D49" s="153"/>
+      <c r="D49" s="141"/>
       <c r="E49" s="34"/>
       <c r="F49" s="35">
         <f>SUM(F39,F40,F41,F42,F44)</f>
@@ -38777,87 +38777,87 @@
     </row>
     <row r="51" spans="3:36" ht="16.5" thickBot="1"/>
     <row r="52" spans="3:36" ht="16.5" thickBot="1">
-      <c r="F52" s="95" t="s">
+      <c r="F52" s="118" t="s">
         <v>196</v>
       </c>
-      <c r="G52" s="96"/>
-      <c r="H52" s="96"/>
-      <c r="I52" s="96"/>
-      <c r="J52" s="96"/>
-      <c r="K52" s="97"/>
+      <c r="G52" s="119"/>
+      <c r="H52" s="119"/>
+      <c r="I52" s="119"/>
+      <c r="J52" s="119"/>
+      <c r="K52" s="120"/>
     </row>
     <row r="53" spans="3:36">
       <c r="F53" s="80" t="s">
         <v>197</v>
       </c>
-      <c r="G53" s="106" t="s">
+      <c r="G53" s="128" t="s">
         <v>198</v>
       </c>
-      <c r="H53" s="106"/>
+      <c r="H53" s="128"/>
       <c r="I53" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="J53" s="98" t="s">
+      <c r="J53" s="121" t="s">
         <v>199</v>
       </c>
-      <c r="K53" s="99"/>
+      <c r="K53" s="122"/>
     </row>
     <row r="54" spans="3:36">
       <c r="F54" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="G54" s="107" t="s">
+      <c r="G54" s="129" t="s">
         <v>200</v>
       </c>
-      <c r="H54" s="107"/>
+      <c r="H54" s="129"/>
       <c r="I54" s="77" t="s">
         <v>201</v>
       </c>
-      <c r="J54" s="100" t="s">
+      <c r="J54" s="123" t="s">
         <v>202</v>
       </c>
-      <c r="K54" s="101"/>
+      <c r="K54" s="124"/>
     </row>
     <row r="55" spans="3:36">
       <c r="F55" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="G55" s="102" t="s">
+      <c r="G55" s="115" t="s">
         <v>203</v>
       </c>
-      <c r="H55" s="102"/>
+      <c r="H55" s="115"/>
       <c r="I55" s="78" t="s">
         <v>108</v>
       </c>
-      <c r="J55" s="102" t="s">
+      <c r="J55" s="115" t="s">
         <v>204</v>
       </c>
-      <c r="K55" s="103"/>
+      <c r="K55" s="125"/>
     </row>
     <row r="56" spans="3:36">
       <c r="F56" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="G56" s="111" t="s">
+      <c r="G56" s="116" t="s">
         <v>205</v>
       </c>
-      <c r="H56" s="111"/>
+      <c r="H56" s="116"/>
       <c r="I56" s="79" t="s">
         <v>206</v>
       </c>
-      <c r="J56" s="104" t="s">
+      <c r="J56" s="126" t="s">
         <v>207</v>
       </c>
-      <c r="K56" s="105"/>
+      <c r="K56" s="127"/>
     </row>
     <row r="57" spans="3:36">
       <c r="F57" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="G57" s="111" t="s">
+      <c r="G57" s="116" t="s">
         <v>208</v>
       </c>
-      <c r="H57" s="111"/>
+      <c r="H57" s="116"/>
       <c r="I57" s="20" t="s">
         <v>104</v>
       </c>
@@ -38870,10 +38870,10 @@
       <c r="F58" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="G58" s="92" t="s">
+      <c r="G58" s="117" t="s">
         <v>210</v>
       </c>
-      <c r="H58" s="92"/>
+      <c r="H58" s="117"/>
       <c r="I58" s="20" t="s">
         <v>114</v>
       </c>
@@ -38886,10 +38886,10 @@
       <c r="F59" s="82" t="s">
         <v>212</v>
       </c>
-      <c r="G59" s="123" t="s">
+      <c r="G59" s="92" t="s">
         <v>213</v>
       </c>
-      <c r="H59" s="123"/>
+      <c r="H59" s="92"/>
       <c r="I59" s="20" t="s">
         <v>131</v>
       </c>
@@ -38902,32 +38902,62 @@
       <c r="F60" s="55" t="s">
         <v>215</v>
       </c>
-      <c r="G60" s="124" t="s">
+      <c r="G60" s="95" t="s">
         <v>216</v>
       </c>
-      <c r="H60" s="124"/>
+      <c r="H60" s="95"/>
       <c r="I60" s="56" t="s">
         <v>167</v>
       </c>
-      <c r="J60" s="124" t="s">
+      <c r="J60" s="95" t="s">
         <v>217</v>
       </c>
-      <c r="K60" s="125"/>
+      <c r="K60" s="96"/>
     </row>
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="68">
-    <mergeCell ref="G58:H58"/>
-    <mergeCell ref="J58:K58"/>
-    <mergeCell ref="G59:H59"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="G60:H60"/>
-    <mergeCell ref="J60:K60"/>
-    <mergeCell ref="AM2:AM4"/>
-    <mergeCell ref="AN2:AN4"/>
-    <mergeCell ref="AO2:AO4"/>
-    <mergeCell ref="AP2:AP4"/>
-    <mergeCell ref="B3:D4"/>
+    <mergeCell ref="F52:K52"/>
+    <mergeCell ref="G56:H56"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="J53:K53"/>
+    <mergeCell ref="J54:K54"/>
+    <mergeCell ref="J55:K55"/>
+    <mergeCell ref="J56:K56"/>
+    <mergeCell ref="J57:K57"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="F46:AJ46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="F2:AJ2"/>
@@ -38944,47 +38974,17 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="F46:AJ46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="F52:K52"/>
-    <mergeCell ref="G56:H56"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="J53:K53"/>
-    <mergeCell ref="J54:K54"/>
-    <mergeCell ref="J55:K55"/>
-    <mergeCell ref="J56:K56"/>
-    <mergeCell ref="J57:K57"/>
-    <mergeCell ref="G53:H53"/>
-    <mergeCell ref="G54:H54"/>
-    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="AM2:AM4"/>
+    <mergeCell ref="AN2:AN4"/>
+    <mergeCell ref="AO2:AO4"/>
+    <mergeCell ref="AP2:AP4"/>
+    <mergeCell ref="B3:D4"/>
+    <mergeCell ref="G58:H58"/>
+    <mergeCell ref="J58:K58"/>
+    <mergeCell ref="G59:H59"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="G60:H60"/>
+    <mergeCell ref="J60:K60"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F5:AJ37">
@@ -39034,61 +39034,61 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:42" ht="39" customHeight="1" thickBot="1">
-      <c r="F2" s="117" t="s">
+      <c r="F2" s="108" t="s">
         <v>221</v>
       </c>
-      <c r="G2" s="118"/>
-      <c r="H2" s="118"/>
-      <c r="I2" s="118"/>
-      <c r="J2" s="118"/>
-      <c r="K2" s="118"/>
-      <c r="L2" s="118"/>
-      <c r="M2" s="118"/>
-      <c r="N2" s="118"/>
-      <c r="O2" s="118"/>
-      <c r="P2" s="118"/>
-      <c r="Q2" s="118"/>
-      <c r="R2" s="118"/>
-      <c r="S2" s="118"/>
-      <c r="T2" s="118"/>
-      <c r="U2" s="118"/>
-      <c r="V2" s="118"/>
-      <c r="W2" s="118"/>
-      <c r="X2" s="118"/>
-      <c r="Y2" s="118"/>
-      <c r="Z2" s="118"/>
-      <c r="AA2" s="118"/>
-      <c r="AB2" s="118"/>
-      <c r="AC2" s="118"/>
-      <c r="AD2" s="118"/>
-      <c r="AE2" s="118"/>
-      <c r="AF2" s="118"/>
-      <c r="AG2" s="118"/>
-      <c r="AH2" s="118"/>
-      <c r="AI2" s="118"/>
-      <c r="AJ2" s="119"/>
-      <c r="AL2" s="114" t="s">
+      <c r="G2" s="109"/>
+      <c r="H2" s="109"/>
+      <c r="I2" s="109"/>
+      <c r="J2" s="109"/>
+      <c r="K2" s="109"/>
+      <c r="L2" s="109"/>
+      <c r="M2" s="109"/>
+      <c r="N2" s="109"/>
+      <c r="O2" s="109"/>
+      <c r="P2" s="109"/>
+      <c r="Q2" s="109"/>
+      <c r="R2" s="109"/>
+      <c r="S2" s="109"/>
+      <c r="T2" s="109"/>
+      <c r="U2" s="109"/>
+      <c r="V2" s="109"/>
+      <c r="W2" s="109"/>
+      <c r="X2" s="109"/>
+      <c r="Y2" s="109"/>
+      <c r="Z2" s="109"/>
+      <c r="AA2" s="109"/>
+      <c r="AB2" s="109"/>
+      <c r="AC2" s="109"/>
+      <c r="AD2" s="109"/>
+      <c r="AE2" s="109"/>
+      <c r="AF2" s="109"/>
+      <c r="AG2" s="109"/>
+      <c r="AH2" s="109"/>
+      <c r="AI2" s="109"/>
+      <c r="AJ2" s="110"/>
+      <c r="AL2" s="105" t="s">
         <v>80</v>
       </c>
-      <c r="AM2" s="114" t="s">
+      <c r="AM2" s="105" t="s">
         <v>81</v>
       </c>
-      <c r="AN2" s="114" t="s">
+      <c r="AN2" s="105" t="s">
         <v>82</v>
       </c>
-      <c r="AO2" s="114" t="s">
+      <c r="AO2" s="105" t="s">
         <v>83</v>
       </c>
-      <c r="AP2" s="114" t="s">
+      <c r="AP2" s="105" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="3" spans="2:42" ht="39">
-      <c r="B3" s="122" t="s">
+      <c r="B3" s="113" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="122"/>
-      <c r="D3" s="122"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="113"/>
       <c r="F3" s="64" t="s">
         <v>86</v>
       </c>
@@ -39182,16 +39182,16 @@
       <c r="AJ3" s="64" t="s">
         <v>187</v>
       </c>
-      <c r="AL3" s="115"/>
-      <c r="AM3" s="115"/>
-      <c r="AN3" s="115"/>
-      <c r="AO3" s="115"/>
-      <c r="AP3" s="115"/>
+      <c r="AL3" s="106"/>
+      <c r="AM3" s="106"/>
+      <c r="AN3" s="106"/>
+      <c r="AO3" s="106"/>
+      <c r="AP3" s="106"/>
     </row>
     <row r="4" spans="2:42" ht="19.5" customHeight="1" thickBot="1">
-      <c r="B4" s="122"/>
-      <c r="C4" s="122"/>
-      <c r="D4" s="122"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
       <c r="F4" s="30">
         <v>1</v>
       </c>
@@ -39285,20 +39285,20 @@
       <c r="AJ4" s="67" t="s">
         <v>187</v>
       </c>
-      <c r="AL4" s="116"/>
-      <c r="AM4" s="116"/>
-      <c r="AN4" s="116"/>
-      <c r="AO4" s="116"/>
-      <c r="AP4" s="116"/>
+      <c r="AL4" s="107"/>
+      <c r="AM4" s="107"/>
+      <c r="AN4" s="107"/>
+      <c r="AO4" s="107"/>
+      <c r="AP4" s="107"/>
     </row>
     <row r="5" spans="2:42" ht="18.75">
       <c r="B5" s="35">
         <v>1</v>
       </c>
-      <c r="C5" s="120" t="s">
+      <c r="C5" s="111" t="s">
         <v>168</v>
       </c>
-      <c r="D5" s="121"/>
+      <c r="D5" s="112"/>
       <c r="F5" s="83" t="s">
         <v>102</v>
       </c>
@@ -39415,10 +39415,10 @@
       <c r="B6" s="35">
         <v>2</v>
       </c>
-      <c r="C6" s="112" t="s">
+      <c r="C6" s="97" t="s">
         <v>169</v>
       </c>
-      <c r="D6" s="113"/>
+      <c r="D6" s="98"/>
       <c r="F6" s="83" t="s">
         <v>102</v>
       </c>
@@ -39535,10 +39535,10 @@
       <c r="B7" s="35">
         <v>3</v>
       </c>
-      <c r="C7" s="112" t="s">
+      <c r="C7" s="97" t="s">
         <v>170</v>
       </c>
-      <c r="D7" s="113"/>
+      <c r="D7" s="98"/>
       <c r="F7" s="84" t="s">
         <v>95</v>
       </c>
@@ -39655,10 +39655,10 @@
       <c r="B8" s="35">
         <v>4</v>
       </c>
-      <c r="C8" s="112" t="s">
+      <c r="C8" s="97" t="s">
         <v>171</v>
       </c>
-      <c r="D8" s="113"/>
+      <c r="D8" s="98"/>
       <c r="F8" s="84" t="s">
         <v>95</v>
       </c>
@@ -39775,10 +39775,10 @@
       <c r="B9" s="35">
         <v>5</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="97" t="s">
         <v>172</v>
       </c>
-      <c r="D9" s="113"/>
+      <c r="D9" s="98"/>
       <c r="F9" s="84" t="s">
         <v>96</v>
       </c>
@@ -39895,10 +39895,10 @@
       <c r="B10" s="35">
         <v>6</v>
       </c>
-      <c r="C10" s="112" t="s">
+      <c r="C10" s="97" t="s">
         <v>173</v>
       </c>
-      <c r="D10" s="113"/>
+      <c r="D10" s="98"/>
       <c r="F10" s="84" t="s">
         <v>96</v>
       </c>
@@ -40015,10 +40015,10 @@
       <c r="B11" s="35">
         <v>7</v>
       </c>
-      <c r="C11" s="112" t="s">
+      <c r="C11" s="97" t="s">
         <v>174</v>
       </c>
-      <c r="D11" s="113"/>
+      <c r="D11" s="98"/>
       <c r="F11" s="84" t="s">
         <v>101</v>
       </c>
@@ -40135,10 +40135,10 @@
       <c r="B12" s="35">
         <v>8</v>
       </c>
-      <c r="C12" s="112" t="s">
+      <c r="C12" s="97" t="s">
         <v>175</v>
       </c>
-      <c r="D12" s="113"/>
+      <c r="D12" s="98"/>
       <c r="F12" s="83" t="s">
         <v>101</v>
       </c>
@@ -40255,10 +40255,10 @@
       <c r="B13" s="35">
         <v>9</v>
       </c>
-      <c r="C13" s="112" t="s">
+      <c r="C13" s="97" t="s">
         <v>176</v>
       </c>
-      <c r="D13" s="113"/>
+      <c r="D13" s="98"/>
       <c r="F13" s="83" t="s">
         <v>101</v>
       </c>
@@ -40375,10 +40375,10 @@
       <c r="B14" s="35">
         <v>10</v>
       </c>
-      <c r="C14" s="112" t="s">
+      <c r="C14" s="97" t="s">
         <v>222</v>
       </c>
-      <c r="D14" s="113"/>
+      <c r="D14" s="98"/>
       <c r="F14" s="84" t="s">
         <v>116</v>
       </c>
@@ -40495,10 +40495,10 @@
       <c r="B15" s="35">
         <v>11</v>
       </c>
-      <c r="C15" s="112" t="s">
+      <c r="C15" s="97" t="s">
         <v>178</v>
       </c>
-      <c r="D15" s="113"/>
+      <c r="D15" s="98"/>
       <c r="F15" s="84" t="s">
         <v>116</v>
       </c>
@@ -40615,10 +40615,10 @@
       <c r="B16" s="35">
         <v>12</v>
       </c>
-      <c r="C16" s="112" t="s">
+      <c r="C16" s="97" t="s">
         <v>179</v>
       </c>
-      <c r="D16" s="113"/>
+      <c r="D16" s="98"/>
       <c r="F16" s="84" t="s">
         <v>96</v>
       </c>
@@ -40735,10 +40735,10 @@
       <c r="B17" s="35">
         <v>13</v>
       </c>
-      <c r="C17" s="112" t="s">
+      <c r="C17" s="97" t="s">
         <v>180</v>
       </c>
-      <c r="D17" s="113"/>
+      <c r="D17" s="98"/>
       <c r="F17" s="84" t="s">
         <v>96</v>
       </c>
@@ -40855,10 +40855,10 @@
       <c r="B18" s="35">
         <v>14</v>
       </c>
-      <c r="C18" s="112" t="s">
+      <c r="C18" s="97" t="s">
         <v>181</v>
       </c>
-      <c r="D18" s="113"/>
+      <c r="D18" s="98"/>
       <c r="F18" s="85" t="s">
         <v>101</v>
       </c>
@@ -40975,10 +40975,10 @@
       <c r="B19" s="35">
         <v>15</v>
       </c>
-      <c r="C19" s="112" t="s">
+      <c r="C19" s="97" t="s">
         <v>182</v>
       </c>
-      <c r="D19" s="113"/>
+      <c r="D19" s="98"/>
       <c r="F19" s="74" t="s">
         <v>116</v>
       </c>
@@ -41095,10 +41095,10 @@
       <c r="B20" s="35">
         <v>16</v>
       </c>
-      <c r="C20" s="112" t="s">
+      <c r="C20" s="97" t="s">
         <v>223</v>
       </c>
-      <c r="D20" s="113"/>
+      <c r="D20" s="98"/>
       <c r="F20" s="83" t="s">
         <v>96</v>
       </c>
@@ -41215,10 +41215,10 @@
       <c r="B21" s="35">
         <v>17</v>
       </c>
-      <c r="C21" s="112" t="s">
+      <c r="C21" s="97" t="s">
         <v>224</v>
       </c>
-      <c r="D21" s="113"/>
+      <c r="D21" s="98"/>
       <c r="F21" s="84" t="s">
         <v>102</v>
       </c>
@@ -41455,10 +41455,10 @@
       <c r="B23" s="35">
         <v>19</v>
       </c>
-      <c r="C23" s="126" t="s">
+      <c r="C23" s="99" t="s">
         <v>225</v>
       </c>
-      <c r="D23" s="127"/>
+      <c r="D23" s="100"/>
       <c r="F23" s="87" t="s">
         <v>101</v>
       </c>
@@ -41606,10 +41606,10 @@
       <c r="AI24" s="18"/>
     </row>
     <row r="25" spans="2:42" ht="18.75">
-      <c r="C25" s="109" t="s">
+      <c r="C25" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="D25" s="110"/>
+      <c r="D25" s="102"/>
       <c r="E25" s="34"/>
       <c r="F25" s="35">
         <f>COUNTIF(F$5:F$21,"M*")</f>
@@ -41737,10 +41737,10 @@
       </c>
     </row>
     <row r="26" spans="2:42" ht="18.75">
-      <c r="C26" s="109" t="s">
+      <c r="C26" s="101" t="s">
         <v>189</v>
       </c>
-      <c r="D26" s="110"/>
+      <c r="D26" s="102"/>
       <c r="E26" s="34"/>
       <c r="F26" s="35">
         <f>COUNTIF(F$5:F$21,"A*")</f>
@@ -41868,10 +41868,10 @@
       </c>
     </row>
     <row r="27" spans="2:42" ht="18.75">
-      <c r="C27" s="109" t="s">
+      <c r="C27" s="101" t="s">
         <v>77</v>
       </c>
-      <c r="D27" s="110"/>
+      <c r="D27" s="102"/>
       <c r="E27" s="34"/>
       <c r="F27" s="35">
         <f>COUNTIF(F$5:F$21,"N*")</f>
@@ -41999,10 +41999,10 @@
       </c>
     </row>
     <row r="28" spans="2:42" ht="18.75">
-      <c r="C28" s="109" t="s">
+      <c r="C28" s="101" t="s">
         <v>78</v>
       </c>
-      <c r="D28" s="110"/>
+      <c r="D28" s="102"/>
       <c r="E28" s="34"/>
       <c r="F28" s="35">
         <f t="shared" ref="F28:AJ28" si="8">COUNTIF(F$5:F$23,"O*")</f>
@@ -42130,10 +42130,10 @@
       </c>
     </row>
     <row r="29" spans="2:42" ht="18.75">
-      <c r="C29" s="109" t="s">
+      <c r="C29" s="101" t="s">
         <v>190</v>
       </c>
-      <c r="D29" s="110"/>
+      <c r="D29" s="102"/>
       <c r="E29" s="34"/>
       <c r="F29" s="35">
         <f>COUNTIF(F$5:F$23,"TR*")</f>
@@ -42261,10 +42261,10 @@
       </c>
     </row>
     <row r="30" spans="2:42" ht="18.75">
-      <c r="C30" s="109" t="s">
+      <c r="C30" s="101" t="s">
         <v>191</v>
       </c>
-      <c r="D30" s="110"/>
+      <c r="D30" s="102"/>
       <c r="E30" s="34"/>
       <c r="F30" s="35">
         <f t="shared" ref="F30:AJ30" si="11">COUNTIF(F$5:F$23,"ST*")</f>
@@ -42392,10 +42392,10 @@
       </c>
     </row>
     <row r="31" spans="2:42" ht="18.75">
-      <c r="C31" s="128" t="s">
+      <c r="C31" s="103" t="s">
         <v>192</v>
       </c>
-      <c r="D31" s="129"/>
+      <c r="D31" s="104"/>
       <c r="E31" s="36"/>
       <c r="F31" s="37">
         <f>F33-F34</f>
@@ -42526,43 +42526,43 @@
       <c r="C32" s="38"/>
       <c r="D32" s="38"/>
       <c r="E32" s="34"/>
-      <c r="F32" s="108"/>
-      <c r="G32" s="108"/>
-      <c r="H32" s="108"/>
-      <c r="I32" s="108"/>
-      <c r="J32" s="108"/>
-      <c r="K32" s="108"/>
-      <c r="L32" s="108"/>
-      <c r="M32" s="108"/>
-      <c r="N32" s="108"/>
-      <c r="O32" s="108"/>
-      <c r="P32" s="108"/>
-      <c r="Q32" s="108"/>
-      <c r="R32" s="108"/>
-      <c r="S32" s="108"/>
-      <c r="T32" s="108"/>
-      <c r="U32" s="108"/>
-      <c r="V32" s="108"/>
-      <c r="W32" s="108"/>
-      <c r="X32" s="108"/>
-      <c r="Y32" s="108"/>
-      <c r="Z32" s="108"/>
-      <c r="AA32" s="108"/>
-      <c r="AB32" s="108"/>
-      <c r="AC32" s="108"/>
-      <c r="AD32" s="108"/>
-      <c r="AE32" s="108"/>
-      <c r="AF32" s="108"/>
-      <c r="AG32" s="108"/>
-      <c r="AH32" s="108"/>
-      <c r="AI32" s="108"/>
-      <c r="AJ32" s="108"/>
+      <c r="F32" s="114"/>
+      <c r="G32" s="114"/>
+      <c r="H32" s="114"/>
+      <c r="I32" s="114"/>
+      <c r="J32" s="114"/>
+      <c r="K32" s="114"/>
+      <c r="L32" s="114"/>
+      <c r="M32" s="114"/>
+      <c r="N32" s="114"/>
+      <c r="O32" s="114"/>
+      <c r="P32" s="114"/>
+      <c r="Q32" s="114"/>
+      <c r="R32" s="114"/>
+      <c r="S32" s="114"/>
+      <c r="T32" s="114"/>
+      <c r="U32" s="114"/>
+      <c r="V32" s="114"/>
+      <c r="W32" s="114"/>
+      <c r="X32" s="114"/>
+      <c r="Y32" s="114"/>
+      <c r="Z32" s="114"/>
+      <c r="AA32" s="114"/>
+      <c r="AB32" s="114"/>
+      <c r="AC32" s="114"/>
+      <c r="AD32" s="114"/>
+      <c r="AE32" s="114"/>
+      <c r="AF32" s="114"/>
+      <c r="AG32" s="114"/>
+      <c r="AH32" s="114"/>
+      <c r="AI32" s="114"/>
+      <c r="AJ32" s="114"/>
     </row>
     <row r="33" spans="3:36" ht="18.75">
-      <c r="C33" s="109" t="s">
+      <c r="C33" s="101" t="s">
         <v>193</v>
       </c>
-      <c r="D33" s="110"/>
+      <c r="D33" s="102"/>
       <c r="E33" s="34"/>
       <c r="F33" s="39">
         <f>SUM(F25:F27)</f>
@@ -42690,10 +42690,10 @@
       </c>
     </row>
     <row r="34" spans="3:36" ht="18.75">
-      <c r="C34" s="109" t="s">
+      <c r="C34" s="101" t="s">
         <v>194</v>
       </c>
-      <c r="D34" s="110"/>
+      <c r="D34" s="102"/>
       <c r="E34" s="34"/>
       <c r="F34" s="35">
         <v>9</v>
@@ -42790,10 +42790,10 @@
       </c>
     </row>
     <row r="35" spans="3:36" ht="18.75">
-      <c r="C35" s="109" t="s">
+      <c r="C35" s="101" t="s">
         <v>195</v>
       </c>
-      <c r="D35" s="110"/>
+      <c r="D35" s="102"/>
       <c r="E35" s="34"/>
       <c r="F35" s="35">
         <f>SUM(F25,F26,F27,F28,F30)</f>
@@ -42922,87 +42922,87 @@
     </row>
     <row r="37" spans="3:36" ht="16.5" thickBot="1"/>
     <row r="38" spans="3:36" ht="16.5" thickBot="1">
-      <c r="F38" s="95" t="s">
+      <c r="F38" s="118" t="s">
         <v>196</v>
       </c>
-      <c r="G38" s="96"/>
-      <c r="H38" s="96"/>
-      <c r="I38" s="96"/>
-      <c r="J38" s="96"/>
-      <c r="K38" s="97"/>
+      <c r="G38" s="119"/>
+      <c r="H38" s="119"/>
+      <c r="I38" s="119"/>
+      <c r="J38" s="119"/>
+      <c r="K38" s="120"/>
     </row>
     <row r="39" spans="3:36">
       <c r="F39" s="80" t="s">
         <v>197</v>
       </c>
-      <c r="G39" s="106" t="s">
+      <c r="G39" s="128" t="s">
         <v>198</v>
       </c>
-      <c r="H39" s="106"/>
+      <c r="H39" s="128"/>
       <c r="I39" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="J39" s="98" t="s">
+      <c r="J39" s="121" t="s">
         <v>199</v>
       </c>
-      <c r="K39" s="99"/>
+      <c r="K39" s="122"/>
     </row>
     <row r="40" spans="3:36">
       <c r="F40" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="G40" s="107" t="s">
+      <c r="G40" s="129" t="s">
         <v>200</v>
       </c>
-      <c r="H40" s="107"/>
+      <c r="H40" s="129"/>
       <c r="I40" s="77" t="s">
         <v>201</v>
       </c>
-      <c r="J40" s="100" t="s">
+      <c r="J40" s="123" t="s">
         <v>202</v>
       </c>
-      <c r="K40" s="101"/>
+      <c r="K40" s="124"/>
     </row>
     <row r="41" spans="3:36">
       <c r="F41" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="G41" s="102" t="s">
+      <c r="G41" s="115" t="s">
         <v>203</v>
       </c>
-      <c r="H41" s="102"/>
+      <c r="H41" s="115"/>
       <c r="I41" s="78" t="s">
         <v>108</v>
       </c>
-      <c r="J41" s="102" t="s">
+      <c r="J41" s="115" t="s">
         <v>204</v>
       </c>
-      <c r="K41" s="103"/>
+      <c r="K41" s="125"/>
     </row>
     <row r="42" spans="3:36">
       <c r="F42" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="G42" s="111" t="s">
+      <c r="G42" s="116" t="s">
         <v>205</v>
       </c>
-      <c r="H42" s="111"/>
+      <c r="H42" s="116"/>
       <c r="I42" s="79" t="s">
         <v>206</v>
       </c>
-      <c r="J42" s="104" t="s">
+      <c r="J42" s="126" t="s">
         <v>207</v>
       </c>
-      <c r="K42" s="105"/>
+      <c r="K42" s="127"/>
     </row>
     <row r="43" spans="3:36">
       <c r="F43" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="G43" s="111" t="s">
+      <c r="G43" s="116" t="s">
         <v>208</v>
       </c>
-      <c r="H43" s="111"/>
+      <c r="H43" s="116"/>
       <c r="I43" s="20" t="s">
         <v>104</v>
       </c>
@@ -43015,10 +43015,10 @@
       <c r="F44" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="G44" s="92" t="s">
+      <c r="G44" s="117" t="s">
         <v>210</v>
       </c>
-      <c r="H44" s="92"/>
+      <c r="H44" s="117"/>
       <c r="I44" s="20" t="s">
         <v>114</v>
       </c>
@@ -43031,10 +43031,10 @@
       <c r="F45" s="82" t="s">
         <v>212</v>
       </c>
-      <c r="G45" s="123" t="s">
+      <c r="G45" s="92" t="s">
         <v>213</v>
       </c>
-      <c r="H45" s="123"/>
+      <c r="H45" s="92"/>
       <c r="I45" s="20" t="s">
         <v>131</v>
       </c>
@@ -43047,20 +43047,57 @@
       <c r="F46" s="55" t="s">
         <v>215</v>
       </c>
-      <c r="G46" s="124" t="s">
+      <c r="G46" s="95" t="s">
         <v>216</v>
       </c>
-      <c r="H46" s="124"/>
+      <c r="H46" s="95"/>
       <c r="I46" s="56" t="s">
         <v>167</v>
       </c>
-      <c r="J46" s="124" t="s">
+      <c r="J46" s="95" t="s">
         <v>217</v>
       </c>
-      <c r="K46" s="125"/>
+      <c r="K46" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="53">
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="J44:K44"/>
+    <mergeCell ref="F38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="F32:AJ32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="AO2:AO4"/>
+    <mergeCell ref="AP2:AP4"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F2:AJ2"/>
+    <mergeCell ref="AL2:AL4"/>
+    <mergeCell ref="AM2:AM4"/>
+    <mergeCell ref="AN2:AN4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="B3:D4"/>
     <mergeCell ref="G45:H45"/>
     <mergeCell ref="J45:K45"/>
     <mergeCell ref="G46:H46"/>
@@ -43077,43 +43114,6 @@
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="C31:D31"/>
-    <mergeCell ref="AO2:AO4"/>
-    <mergeCell ref="AP2:AP4"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F2:AJ2"/>
-    <mergeCell ref="AL2:AL4"/>
-    <mergeCell ref="AM2:AM4"/>
-    <mergeCell ref="AN2:AN4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="B3:D4"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F32:AJ32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="G44:H44"/>
-    <mergeCell ref="J44:K44"/>
-    <mergeCell ref="F38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="J42:K42"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="G40:H40"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F5:AI23">
@@ -43195,19 +43195,19 @@
       <c r="AG2" s="164"/>
       <c r="AH2" s="164"/>
       <c r="AI2" s="164"/>
-      <c r="AK2" s="114" t="s">
+      <c r="AK2" s="105" t="s">
         <v>80</v>
       </c>
-      <c r="AL2" s="114" t="s">
+      <c r="AL2" s="105" t="s">
         <v>81</v>
       </c>
-      <c r="AM2" s="114" t="s">
+      <c r="AM2" s="105" t="s">
         <v>82</v>
       </c>
-      <c r="AN2" s="114" t="s">
+      <c r="AN2" s="105" t="s">
         <v>83</v>
       </c>
-      <c r="AO2" s="114" t="s">
+      <c r="AO2" s="105" t="s">
         <v>84</v>
       </c>
     </row>
@@ -43307,11 +43307,11 @@
         <v>87</v>
       </c>
       <c r="AI3" s="29"/>
-      <c r="AK3" s="115"/>
-      <c r="AL3" s="115"/>
-      <c r="AM3" s="115"/>
-      <c r="AN3" s="115"/>
-      <c r="AO3" s="115"/>
+      <c r="AK3" s="106"/>
+      <c r="AL3" s="106"/>
+      <c r="AM3" s="106"/>
+      <c r="AN3" s="106"/>
+      <c r="AO3" s="106"/>
     </row>
     <row r="4" spans="2:41" ht="19.5" thickBot="1">
       <c r="B4" s="167"/>
@@ -43407,11 +43407,11 @@
         <v>30</v>
       </c>
       <c r="AI4" s="33"/>
-      <c r="AK4" s="116"/>
-      <c r="AL4" s="116"/>
-      <c r="AM4" s="116"/>
-      <c r="AN4" s="116"/>
-      <c r="AO4" s="116"/>
+      <c r="AK4" s="107"/>
+      <c r="AL4" s="107"/>
+      <c r="AM4" s="107"/>
+      <c r="AN4" s="107"/>
+      <c r="AO4" s="107"/>
     </row>
     <row r="5" spans="2:41" ht="18.75">
       <c r="B5" s="163" t="s">
@@ -44735,10 +44735,10 @@
       <c r="AH16" s="18"/>
     </row>
     <row r="17" spans="2:35" ht="18.75">
-      <c r="B17" s="153" t="s">
+      <c r="B17" s="141" t="s">
         <v>188</v>
       </c>
-      <c r="C17" s="153"/>
+      <c r="C17" s="141"/>
       <c r="D17" s="34"/>
       <c r="E17" s="35">
         <f t="shared" ref="E17:AH17" si="5">COUNTIF(E$5:E$15,"M*")</f>
@@ -44865,10 +44865,10 @@
       </c>
     </row>
     <row r="18" spans="2:35" ht="18.75">
-      <c r="B18" s="153" t="s">
+      <c r="B18" s="141" t="s">
         <v>189</v>
       </c>
-      <c r="C18" s="153"/>
+      <c r="C18" s="141"/>
       <c r="D18" s="34"/>
       <c r="E18" s="35">
         <f t="shared" ref="E18:AH18" si="6">COUNTIF(E$5:E$15,"A*")</f>
@@ -44995,10 +44995,10 @@
       </c>
     </row>
     <row r="19" spans="2:35" ht="18.75">
-      <c r="B19" s="153" t="s">
+      <c r="B19" s="141" t="s">
         <v>77</v>
       </c>
-      <c r="C19" s="153"/>
+      <c r="C19" s="141"/>
       <c r="D19" s="34"/>
       <c r="E19" s="35">
         <f t="shared" ref="E19:AH19" si="7">COUNTIF(E$5:E$15,"N*")</f>
@@ -45125,10 +45125,10 @@
       </c>
     </row>
     <row r="20" spans="2:35" ht="18.75">
-      <c r="B20" s="153" t="s">
+      <c r="B20" s="141" t="s">
         <v>78</v>
       </c>
-      <c r="C20" s="153"/>
+      <c r="C20" s="141"/>
       <c r="D20" s="34"/>
       <c r="E20" s="35">
         <f t="shared" ref="E20:AH20" si="8">COUNTIF(E$5:E$15,"O*")</f>
@@ -45255,10 +45255,10 @@
       </c>
     </row>
     <row r="21" spans="2:35" ht="18.75">
-      <c r="B21" s="109" t="s">
+      <c r="B21" s="101" t="s">
         <v>191</v>
       </c>
-      <c r="C21" s="110"/>
+      <c r="C21" s="102"/>
       <c r="D21" s="34"/>
       <c r="E21" s="35">
         <f t="shared" ref="E21:AH21" si="9">COUNTIF(E$5:E$15,"ST*")</f>
@@ -45385,10 +45385,10 @@
       </c>
     </row>
     <row r="22" spans="2:35" ht="18.75">
-      <c r="B22" s="152" t="s">
+      <c r="B22" s="140" t="s">
         <v>192</v>
       </c>
-      <c r="C22" s="152"/>
+      <c r="C22" s="140"/>
       <c r="D22" s="36"/>
       <c r="E22" s="37">
         <f>E24-E25</f>
@@ -45518,43 +45518,43 @@
       <c r="B23" s="38"/>
       <c r="C23" s="38"/>
       <c r="D23" s="34"/>
-      <c r="E23" s="108"/>
-      <c r="F23" s="108"/>
-      <c r="G23" s="108"/>
-      <c r="H23" s="108"/>
-      <c r="I23" s="108"/>
-      <c r="J23" s="108"/>
-      <c r="K23" s="108"/>
-      <c r="L23" s="108"/>
-      <c r="M23" s="108"/>
-      <c r="N23" s="108"/>
-      <c r="O23" s="108"/>
-      <c r="P23" s="108"/>
-      <c r="Q23" s="108"/>
-      <c r="R23" s="108"/>
-      <c r="S23" s="108"/>
-      <c r="T23" s="108"/>
-      <c r="U23" s="108"/>
-      <c r="V23" s="108"/>
-      <c r="W23" s="108"/>
-      <c r="X23" s="108"/>
-      <c r="Y23" s="108"/>
-      <c r="Z23" s="108"/>
-      <c r="AA23" s="108"/>
-      <c r="AB23" s="108"/>
-      <c r="AC23" s="108"/>
-      <c r="AD23" s="108"/>
-      <c r="AE23" s="108"/>
-      <c r="AF23" s="108"/>
-      <c r="AG23" s="108"/>
-      <c r="AH23" s="108"/>
-      <c r="AI23" s="108"/>
+      <c r="E23" s="114"/>
+      <c r="F23" s="114"/>
+      <c r="G23" s="114"/>
+      <c r="H23" s="114"/>
+      <c r="I23" s="114"/>
+      <c r="J23" s="114"/>
+      <c r="K23" s="114"/>
+      <c r="L23" s="114"/>
+      <c r="M23" s="114"/>
+      <c r="N23" s="114"/>
+      <c r="O23" s="114"/>
+      <c r="P23" s="114"/>
+      <c r="Q23" s="114"/>
+      <c r="R23" s="114"/>
+      <c r="S23" s="114"/>
+      <c r="T23" s="114"/>
+      <c r="U23" s="114"/>
+      <c r="V23" s="114"/>
+      <c r="W23" s="114"/>
+      <c r="X23" s="114"/>
+      <c r="Y23" s="114"/>
+      <c r="Z23" s="114"/>
+      <c r="AA23" s="114"/>
+      <c r="AB23" s="114"/>
+      <c r="AC23" s="114"/>
+      <c r="AD23" s="114"/>
+      <c r="AE23" s="114"/>
+      <c r="AF23" s="114"/>
+      <c r="AG23" s="114"/>
+      <c r="AH23" s="114"/>
+      <c r="AI23" s="114"/>
     </row>
     <row r="24" spans="2:35" ht="18.75">
-      <c r="B24" s="153" t="s">
+      <c r="B24" s="141" t="s">
         <v>193</v>
       </c>
-      <c r="C24" s="153"/>
+      <c r="C24" s="141"/>
       <c r="D24" s="34"/>
       <c r="E24" s="39">
         <f>SUM(E17:E19)</f>
@@ -45681,10 +45681,10 @@
       </c>
     </row>
     <row r="25" spans="2:35" ht="18.75">
-      <c r="B25" s="153" t="s">
+      <c r="B25" s="141" t="s">
         <v>194</v>
       </c>
-      <c r="C25" s="153"/>
+      <c r="C25" s="141"/>
       <c r="D25" s="34"/>
       <c r="E25" s="35">
         <v>7</v>
@@ -45781,10 +45781,10 @@
       </c>
     </row>
     <row r="26" spans="2:35" ht="18.75">
-      <c r="B26" s="153" t="s">
+      <c r="B26" s="141" t="s">
         <v>195</v>
       </c>
-      <c r="C26" s="153"/>
+      <c r="C26" s="141"/>
       <c r="D26" s="34"/>
       <c r="E26" s="35">
         <v>11</v>
@@ -45882,6 +45882,22 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="E23:AI23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
     <mergeCell ref="AN2:AN4"/>
     <mergeCell ref="AO2:AO4"/>
     <mergeCell ref="B9:C9"/>
@@ -45894,22 +45910,6 @@
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="E23:AI23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
   </mergeCells>
   <conditionalFormatting sqref="E5:AH10">
     <cfRule type="containsText" dxfId="34" priority="23" operator="containsText" text="STN">
@@ -46062,25 +46062,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_activity xmlns="0ecd8b7c-869e-4f04-a6a3-066c3c63b311" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="مستند" ma:contentTypeID="0x01010053585A714B17B949862FA1B71BD97610" ma:contentTypeVersion="20" ma:contentTypeDescription="إنشاء مستند جديد." ma:contentTypeScope="" ma:versionID="dd8bd6d392f178541f6ccf1c351709a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns3="f1e9c892-1499-41bb-8a64-60ef909d8682" xmlns:ns4="0ecd8b7c-869e-4f04-a6a3-066c3c63b311" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9f246d41c9a2b9a4922388dcb99eeb28" ns1:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -46350,8 +46331,27 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_activity xmlns="0ecd8b7c-869e-4f04-a6a3-066c3c63b311" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04335F04-3ECE-4043-846B-35335B1D83ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57D06F05-5672-4668-89C3-4F6754D4BC82}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -46359,7 +46359,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57D06F05-5672-4668-89C3-4F6754D4BC82}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04335F04-3ECE-4043-846B-35335B1D83ED}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/rosters/.versions/2026-06/previous.xlsx
+++ b/rosters/.versions/2026-06/previous.xlsx
@@ -5805,7 +5805,7 @@
     <xf numFmtId="0" fontId="18" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5814,10 +5814,55 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5825,24 +5870,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5871,71 +5898,38 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5946,22 +5940,25 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5979,17 +5976,20 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -7475,91 +7475,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:40" ht="9" customHeight="1">
-      <c r="E1" s="130"/>
-      <c r="F1" s="130"/>
-      <c r="G1" s="130"/>
-      <c r="H1" s="130"/>
-      <c r="I1" s="130"/>
-      <c r="J1" s="130"/>
-      <c r="K1" s="130"/>
-      <c r="L1" s="130"/>
-      <c r="M1" s="130"/>
-      <c r="N1" s="130"/>
-      <c r="O1" s="130"/>
-      <c r="P1" s="130"/>
-      <c r="Q1" s="130"/>
-      <c r="R1" s="130"/>
-      <c r="S1" s="130"/>
-      <c r="T1" s="130"/>
-      <c r="U1" s="130"/>
-      <c r="V1" s="130"/>
-      <c r="W1" s="130"/>
-      <c r="X1" s="130"/>
-      <c r="Y1" s="130"/>
-      <c r="Z1" s="130"/>
-      <c r="AA1" s="130"/>
-      <c r="AB1" s="130"/>
-      <c r="AC1" s="130"/>
-      <c r="AD1" s="130"/>
-      <c r="AE1" s="130"/>
-      <c r="AF1" s="130"/>
-      <c r="AG1" s="130"/>
-      <c r="AH1" s="130"/>
-      <c r="AI1" s="130"/>
+      <c r="E1" s="137"/>
+      <c r="F1" s="137"/>
+      <c r="G1" s="137"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="137"/>
+      <c r="M1" s="137"/>
+      <c r="N1" s="137"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="137"/>
+      <c r="Q1" s="137"/>
+      <c r="R1" s="137"/>
+      <c r="S1" s="137"/>
+      <c r="T1" s="137"/>
+      <c r="U1" s="137"/>
+      <c r="V1" s="137"/>
+      <c r="W1" s="137"/>
+      <c r="X1" s="137"/>
+      <c r="Y1" s="137"/>
+      <c r="Z1" s="137"/>
+      <c r="AA1" s="137"/>
+      <c r="AB1" s="137"/>
+      <c r="AC1" s="137"/>
+      <c r="AD1" s="137"/>
+      <c r="AE1" s="137"/>
+      <c r="AF1" s="137"/>
+      <c r="AG1" s="137"/>
+      <c r="AH1" s="137"/>
+      <c r="AI1" s="137"/>
     </row>
     <row r="2" spans="2:40" ht="28.5">
-      <c r="B2" s="137" t="s">
+      <c r="B2" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="137"/>
+      <c r="C2" s="135"/>
       <c r="D2" s="9"/>
-      <c r="E2" s="138" t="s">
+      <c r="E2" s="136" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="138"/>
-      <c r="G2" s="138"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="138"/>
-      <c r="M2" s="138"/>
-      <c r="N2" s="138"/>
-      <c r="O2" s="138"/>
-      <c r="P2" s="138"/>
-      <c r="Q2" s="138"/>
-      <c r="R2" s="138"/>
-      <c r="S2" s="138"/>
-      <c r="T2" s="138"/>
-      <c r="U2" s="138"/>
-      <c r="V2" s="138"/>
-      <c r="W2" s="138" t="s">
+      <c r="F2" s="136"/>
+      <c r="G2" s="136"/>
+      <c r="H2" s="136"/>
+      <c r="I2" s="136"/>
+      <c r="J2" s="136"/>
+      <c r="K2" s="136"/>
+      <c r="L2" s="136"/>
+      <c r="M2" s="136"/>
+      <c r="N2" s="136"/>
+      <c r="O2" s="136"/>
+      <c r="P2" s="136"/>
+      <c r="Q2" s="136"/>
+      <c r="R2" s="136"/>
+      <c r="S2" s="136"/>
+      <c r="T2" s="136"/>
+      <c r="U2" s="136"/>
+      <c r="V2" s="136"/>
+      <c r="W2" s="136" t="s">
         <v>28</v>
       </c>
-      <c r="X2" s="138"/>
-      <c r="Y2" s="138"/>
-      <c r="Z2" s="138"/>
-      <c r="AA2" s="138"/>
-      <c r="AB2" s="138"/>
-      <c r="AC2" s="138">
+      <c r="X2" s="136"/>
+      <c r="Y2" s="136"/>
+      <c r="Z2" s="136"/>
+      <c r="AA2" s="136"/>
+      <c r="AB2" s="136"/>
+      <c r="AC2" s="136">
         <v>2025</v>
       </c>
-      <c r="AD2" s="138"/>
-      <c r="AE2" s="138"/>
-      <c r="AF2" s="138"/>
+      <c r="AD2" s="136"/>
+      <c r="AE2" s="136"/>
+      <c r="AF2" s="136"/>
       <c r="AG2" s="5"/>
       <c r="AH2" s="5"/>
       <c r="AI2" s="5"/>
-      <c r="AK2" s="134" t="s">
+      <c r="AK2" s="130" t="s">
         <v>34</v>
       </c>
-      <c r="AL2" s="134"/>
-      <c r="AM2" s="134"/>
-      <c r="AN2" s="134"/>
+      <c r="AL2" s="130"/>
+      <c r="AM2" s="130"/>
+      <c r="AN2" s="130"/>
     </row>
     <row r="3" spans="2:40">
-      <c r="B3" s="137"/>
-      <c r="C3" s="137"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="135"/>
       <c r="D3" s="10"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -7592,14 +7592,14 @@
       <c r="AG3" s="3"/>
       <c r="AH3" s="3"/>
       <c r="AI3" s="3"/>
-      <c r="AK3" s="134"/>
-      <c r="AL3" s="134"/>
-      <c r="AM3" s="134"/>
-      <c r="AN3" s="134"/>
+      <c r="AK3" s="130"/>
+      <c r="AL3" s="130"/>
+      <c r="AM3" s="130"/>
+      <c r="AN3" s="130"/>
     </row>
     <row r="4" spans="2:40">
-      <c r="B4" s="137"/>
-      <c r="C4" s="137"/>
+      <c r="B4" s="135"/>
+      <c r="C4" s="135"/>
       <c r="D4" s="10"/>
       <c r="E4" s="131" t="s">
         <v>35</v>
@@ -7613,37 +7613,37 @@
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
-      <c r="M4" s="132" t="s">
+      <c r="M4" s="133" t="s">
         <v>36</v>
       </c>
-      <c r="N4" s="132"/>
-      <c r="O4" s="132"/>
-      <c r="P4" s="133">
+      <c r="N4" s="133"/>
+      <c r="O4" s="133"/>
+      <c r="P4" s="138">
         <f>IFERROR(DATEVALUE(J4&amp;W2&amp;AC2),"")</f>
         <v>45901</v>
       </c>
-      <c r="Q4" s="133"/>
-      <c r="R4" s="133"/>
+      <c r="Q4" s="138"/>
+      <c r="R4" s="138"/>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
-      <c r="U4" s="132" t="s">
+      <c r="U4" s="133" t="s">
         <v>37</v>
       </c>
-      <c r="V4" s="132"/>
-      <c r="W4" s="132"/>
-      <c r="X4" s="133">
+      <c r="V4" s="133"/>
+      <c r="W4" s="133"/>
+      <c r="X4" s="138">
         <f>IFERROR(EOMONTH(P4,0)+J4-1,"")</f>
         <v>45930</v>
       </c>
-      <c r="Y4" s="133"/>
-      <c r="Z4" s="133"/>
+      <c r="Y4" s="138"/>
+      <c r="Z4" s="138"/>
       <c r="AA4" s="3"/>
       <c r="AB4" s="3"/>
-      <c r="AC4" s="132" t="s">
+      <c r="AC4" s="133" t="s">
         <v>38</v>
       </c>
-      <c r="AD4" s="132"/>
-      <c r="AE4" s="132"/>
+      <c r="AD4" s="133"/>
+      <c r="AE4" s="133"/>
       <c r="AF4" s="3">
         <f>COUNTIF(E6:AI6,"*?")</f>
         <v>30</v>
@@ -7651,10 +7651,10 @@
       <c r="AG4" s="3"/>
       <c r="AH4" s="3"/>
       <c r="AI4" s="3"/>
-      <c r="AK4" s="134"/>
-      <c r="AL4" s="134"/>
-      <c r="AM4" s="134"/>
-      <c r="AN4" s="134"/>
+      <c r="AK4" s="130"/>
+      <c r="AL4" s="130"/>
+      <c r="AM4" s="130"/>
+      <c r="AN4" s="130"/>
     </row>
     <row r="5" spans="2:40" ht="6.75" customHeight="1">
       <c r="B5" s="6"/>
@@ -7693,10 +7693,10 @@
       <c r="AI5" s="3"/>
     </row>
     <row r="6" spans="2:40" ht="27.75">
-      <c r="B6" s="136" t="s">
+      <c r="B6" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="136" t="s">
+      <c r="C6" s="134" t="s">
         <v>40</v>
       </c>
       <c r="D6" s="12"/>
@@ -7825,22 +7825,22 @@
         <v/>
       </c>
       <c r="AJ6" s="14"/>
-      <c r="AK6" s="135" t="s">
+      <c r="AK6" s="132" t="s">
         <v>41</v>
       </c>
-      <c r="AL6" s="135" t="s">
+      <c r="AL6" s="132" t="s">
         <v>42</v>
       </c>
-      <c r="AM6" s="135" t="s">
+      <c r="AM6" s="132" t="s">
         <v>43</v>
       </c>
-      <c r="AN6" s="135" t="s">
+      <c r="AN6" s="132" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="7" spans="2:40">
-      <c r="B7" s="136"/>
-      <c r="C7" s="136"/>
+      <c r="B7" s="134"/>
+      <c r="C7" s="134"/>
       <c r="D7" s="12"/>
       <c r="E7" s="15">
         <f>P4</f>
@@ -7967,10 +7967,10 @@
         <v/>
       </c>
       <c r="AJ7" s="14"/>
-      <c r="AK7" s="135"/>
-      <c r="AL7" s="135"/>
-      <c r="AM7" s="135"/>
-      <c r="AN7" s="135"/>
+      <c r="AK7" s="132"/>
+      <c r="AL7" s="132"/>
+      <c r="AM7" s="132"/>
+      <c r="AN7" s="132"/>
     </row>
     <row r="8" spans="2:40">
       <c r="B8" s="3" t="s">
@@ -12950,6 +12950,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="E1:AI1"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="U4:W4"/>
+    <mergeCell ref="X4:Z4"/>
     <mergeCell ref="AK2:AN4"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="B42:C42"/>
@@ -12966,12 +12972,6 @@
     <mergeCell ref="E2:V2"/>
     <mergeCell ref="W2:AB2"/>
     <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="E1:AI1"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="M4:O4"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="U4:W4"/>
-    <mergeCell ref="X4:Z4"/>
   </mergeCells>
   <conditionalFormatting sqref="E8:AI37 AK8:AN37 E39:AI42">
     <cfRule type="expression" dxfId="112" priority="4">
@@ -13035,61 +13035,61 @@
   <sheetData>
     <row r="1" spans="2:42" ht="16.5" thickBot="1"/>
     <row r="2" spans="2:42" ht="39" customHeight="1" thickBot="1">
-      <c r="F2" s="151" t="s">
+      <c r="F2" s="139" t="s">
         <v>79</v>
       </c>
-      <c r="G2" s="152"/>
-      <c r="H2" s="152"/>
-      <c r="I2" s="152"/>
-      <c r="J2" s="152"/>
-      <c r="K2" s="152"/>
-      <c r="L2" s="152"/>
-      <c r="M2" s="152"/>
-      <c r="N2" s="152"/>
-      <c r="O2" s="152"/>
-      <c r="P2" s="152"/>
-      <c r="Q2" s="152"/>
-      <c r="R2" s="152"/>
-      <c r="S2" s="152"/>
-      <c r="T2" s="152"/>
-      <c r="U2" s="152"/>
-      <c r="V2" s="152"/>
-      <c r="W2" s="152"/>
-      <c r="X2" s="152"/>
-      <c r="Y2" s="152"/>
-      <c r="Z2" s="152"/>
-      <c r="AA2" s="152"/>
-      <c r="AB2" s="152"/>
-      <c r="AC2" s="152"/>
-      <c r="AD2" s="152"/>
-      <c r="AE2" s="152"/>
-      <c r="AF2" s="152"/>
-      <c r="AG2" s="152"/>
-      <c r="AH2" s="152"/>
-      <c r="AI2" s="152"/>
-      <c r="AJ2" s="153"/>
-      <c r="AL2" s="105" t="s">
+      <c r="G2" s="140"/>
+      <c r="H2" s="140"/>
+      <c r="I2" s="140"/>
+      <c r="J2" s="140"/>
+      <c r="K2" s="140"/>
+      <c r="L2" s="140"/>
+      <c r="M2" s="140"/>
+      <c r="N2" s="140"/>
+      <c r="O2" s="140"/>
+      <c r="P2" s="140"/>
+      <c r="Q2" s="140"/>
+      <c r="R2" s="140"/>
+      <c r="S2" s="140"/>
+      <c r="T2" s="140"/>
+      <c r="U2" s="140"/>
+      <c r="V2" s="140"/>
+      <c r="W2" s="140"/>
+      <c r="X2" s="140"/>
+      <c r="Y2" s="140"/>
+      <c r="Z2" s="140"/>
+      <c r="AA2" s="140"/>
+      <c r="AB2" s="140"/>
+      <c r="AC2" s="140"/>
+      <c r="AD2" s="140"/>
+      <c r="AE2" s="140"/>
+      <c r="AF2" s="140"/>
+      <c r="AG2" s="140"/>
+      <c r="AH2" s="140"/>
+      <c r="AI2" s="140"/>
+      <c r="AJ2" s="141"/>
+      <c r="AL2" s="114" t="s">
         <v>80</v>
       </c>
-      <c r="AM2" s="105" t="s">
+      <c r="AM2" s="114" t="s">
         <v>81</v>
       </c>
-      <c r="AN2" s="105" t="s">
+      <c r="AN2" s="114" t="s">
         <v>82</v>
       </c>
-      <c r="AO2" s="105" t="s">
+      <c r="AO2" s="114" t="s">
         <v>83</v>
       </c>
-      <c r="AP2" s="105" t="s">
+      <c r="AP2" s="114" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="3" spans="2:42" ht="39.75" thickBot="1">
-      <c r="B3" s="113" t="s">
+      <c r="B3" s="122" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="113"/>
-      <c r="D3" s="113"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="122"/>
       <c r="F3" s="43" t="s">
         <v>86</v>
       </c>
@@ -13181,16 +13181,16 @@
         <v>87</v>
       </c>
       <c r="AJ3" s="43"/>
-      <c r="AL3" s="106"/>
-      <c r="AM3" s="106"/>
-      <c r="AN3" s="106"/>
-      <c r="AO3" s="106"/>
-      <c r="AP3" s="106"/>
+      <c r="AL3" s="115"/>
+      <c r="AM3" s="115"/>
+      <c r="AN3" s="115"/>
+      <c r="AO3" s="115"/>
+      <c r="AP3" s="115"/>
     </row>
     <row r="4" spans="2:42" ht="19.5" customHeight="1" thickBot="1">
-      <c r="B4" s="113"/>
-      <c r="C4" s="113"/>
-      <c r="D4" s="113"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
       <c r="F4" s="40">
         <v>1</v>
       </c>
@@ -13282,20 +13282,20 @@
         <v>30</v>
       </c>
       <c r="AJ4" s="68"/>
-      <c r="AL4" s="107"/>
-      <c r="AM4" s="107"/>
-      <c r="AN4" s="107"/>
-      <c r="AO4" s="107"/>
-      <c r="AP4" s="107"/>
+      <c r="AL4" s="116"/>
+      <c r="AM4" s="116"/>
+      <c r="AN4" s="116"/>
+      <c r="AO4" s="116"/>
+      <c r="AP4" s="116"/>
     </row>
     <row r="5" spans="2:42" ht="19.5" customHeight="1">
       <c r="B5" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="C5" s="144" t="s">
+      <c r="C5" s="142" t="s">
         <v>94</v>
       </c>
-      <c r="D5" s="144"/>
+      <c r="D5" s="142"/>
       <c r="F5" s="84" t="s">
         <v>95</v>
       </c>
@@ -13412,10 +13412,10 @@
       <c r="B6" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="144" t="s">
+      <c r="C6" s="142" t="s">
         <v>99</v>
       </c>
-      <c r="D6" s="144"/>
+      <c r="D6" s="142"/>
       <c r="F6" s="75" t="s">
         <v>97</v>
       </c>
@@ -13532,10 +13532,10 @@
       <c r="B7" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="C7" s="144" t="s">
+      <c r="C7" s="142" t="s">
         <v>100</v>
       </c>
-      <c r="D7" s="144"/>
+      <c r="D7" s="142"/>
       <c r="F7" s="75" t="s">
         <v>101</v>
       </c>
@@ -13652,10 +13652,10 @@
       <c r="B8" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="C8" s="144" t="s">
+      <c r="C8" s="142" t="s">
         <v>103</v>
       </c>
-      <c r="D8" s="144"/>
+      <c r="D8" s="142"/>
       <c r="F8" s="75" t="s">
         <v>96</v>
       </c>
@@ -13772,10 +13772,10 @@
       <c r="B9" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="C9" s="144" t="s">
+      <c r="C9" s="142" t="s">
         <v>105</v>
       </c>
-      <c r="D9" s="144"/>
+      <c r="D9" s="142"/>
       <c r="F9" s="90" t="s">
         <v>106</v>
       </c>
@@ -13892,10 +13892,10 @@
       <c r="B10" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="C10" s="144" t="s">
+      <c r="C10" s="142" t="s">
         <v>109</v>
       </c>
-      <c r="D10" s="144"/>
+      <c r="D10" s="142"/>
       <c r="F10" s="75" t="s">
         <v>96</v>
       </c>
@@ -14012,10 +14012,10 @@
       <c r="B11" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="C11" s="144" t="s">
+      <c r="C11" s="142" t="s">
         <v>110</v>
       </c>
-      <c r="D11" s="144"/>
+      <c r="D11" s="142"/>
       <c r="F11" s="75" t="s">
         <v>95</v>
       </c>
@@ -14132,10 +14132,10 @@
       <c r="B12" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="144" t="s">
+      <c r="C12" s="142" t="s">
         <v>111</v>
       </c>
-      <c r="D12" s="144"/>
+      <c r="D12" s="142"/>
       <c r="F12" s="75" t="s">
         <v>107</v>
       </c>
@@ -14252,10 +14252,10 @@
       <c r="B13" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="C13" s="144" t="s">
+      <c r="C13" s="142" t="s">
         <v>112</v>
       </c>
-      <c r="D13" s="144"/>
+      <c r="D13" s="142"/>
       <c r="F13" s="75" t="s">
         <v>108</v>
       </c>
@@ -14373,10 +14373,10 @@
       <c r="B14" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="C14" s="144" t="s">
+      <c r="C14" s="142" t="s">
         <v>113</v>
       </c>
-      <c r="D14" s="144"/>
+      <c r="D14" s="142"/>
       <c r="F14" s="88" t="s">
         <v>95</v>
       </c>
@@ -14493,10 +14493,10 @@
       <c r="B15" s="35" t="s">
         <v>114</v>
       </c>
-      <c r="C15" s="145" t="s">
+      <c r="C15" s="144" t="s">
         <v>115</v>
       </c>
-      <c r="D15" s="146"/>
+      <c r="D15" s="145"/>
       <c r="E15" s="53"/>
       <c r="F15" s="72" t="s">
         <v>101</v>
@@ -14614,10 +14614,10 @@
       <c r="B16" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C16" s="144" t="s">
+      <c r="C16" s="142" t="s">
         <v>117</v>
       </c>
-      <c r="D16" s="150"/>
+      <c r="D16" s="143"/>
       <c r="E16" s="53"/>
       <c r="F16" s="74" t="s">
         <v>102</v>
@@ -14735,10 +14735,10 @@
       <c r="B17" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C17" s="144" t="s">
+      <c r="C17" s="142" t="s">
         <v>118</v>
       </c>
-      <c r="D17" s="150"/>
+      <c r="D17" s="143"/>
       <c r="E17" s="53"/>
       <c r="F17" s="75" t="s">
         <v>95</v>
@@ -14856,10 +14856,10 @@
       <c r="B18" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C18" s="144" t="s">
+      <c r="C18" s="142" t="s">
         <v>119</v>
       </c>
-      <c r="D18" s="150"/>
+      <c r="D18" s="143"/>
       <c r="E18" s="53"/>
       <c r="F18" s="75" t="s">
         <v>98</v>
@@ -14977,10 +14977,10 @@
       <c r="B19" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C19" s="144" t="s">
+      <c r="C19" s="142" t="s">
         <v>120</v>
       </c>
-      <c r="D19" s="150"/>
+      <c r="D19" s="143"/>
       <c r="E19" s="53"/>
       <c r="F19" s="75" t="s">
         <v>96</v>
@@ -15098,10 +15098,10 @@
       <c r="B20" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C20" s="144" t="s">
+      <c r="C20" s="142" t="s">
         <v>121</v>
       </c>
-      <c r="D20" s="150"/>
+      <c r="D20" s="143"/>
       <c r="E20" s="53"/>
       <c r="F20" s="75" t="s">
         <v>96</v>
@@ -15219,10 +15219,10 @@
       <c r="B21" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C21" s="144" t="s">
+      <c r="C21" s="142" t="s">
         <v>122</v>
       </c>
-      <c r="D21" s="150"/>
+      <c r="D21" s="143"/>
       <c r="E21" s="53"/>
       <c r="F21" s="75" t="s">
         <v>101</v>
@@ -15340,10 +15340,10 @@
       <c r="B22" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C22" s="144" t="s">
+      <c r="C22" s="142" t="s">
         <v>123</v>
       </c>
-      <c r="D22" s="150"/>
+      <c r="D22" s="143"/>
       <c r="E22" s="53"/>
       <c r="F22" s="75" t="s">
         <v>102</v>
@@ -15461,10 +15461,10 @@
       <c r="B23" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C23" s="144" t="s">
+      <c r="C23" s="142" t="s">
         <v>124</v>
       </c>
-      <c r="D23" s="150"/>
+      <c r="D23" s="143"/>
       <c r="E23" s="53"/>
       <c r="F23" s="74" t="s">
         <v>95</v>
@@ -15582,10 +15582,10 @@
       <c r="B24" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C24" s="144" t="s">
+      <c r="C24" s="142" t="s">
         <v>125</v>
       </c>
-      <c r="D24" s="150"/>
+      <c r="D24" s="143"/>
       <c r="E24" s="53"/>
       <c r="F24" s="75" t="s">
         <v>116</v>
@@ -15703,10 +15703,10 @@
       <c r="B25" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C25" s="97" t="s">
+      <c r="C25" s="112" t="s">
         <v>126</v>
       </c>
-      <c r="D25" s="147"/>
+      <c r="D25" s="146"/>
       <c r="E25" s="53"/>
       <c r="F25" s="75" t="s">
         <v>116</v>
@@ -15824,10 +15824,10 @@
       <c r="B26" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C26" s="97" t="s">
+      <c r="C26" s="112" t="s">
         <v>127</v>
       </c>
-      <c r="D26" s="147"/>
+      <c r="D26" s="146"/>
       <c r="E26" s="53"/>
       <c r="F26" s="75" t="s">
         <v>96</v>
@@ -15945,10 +15945,10 @@
       <c r="B27" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C27" s="97" t="s">
+      <c r="C27" s="112" t="s">
         <v>128</v>
       </c>
-      <c r="D27" s="147"/>
+      <c r="D27" s="146"/>
       <c r="E27" s="53"/>
       <c r="F27" s="75" t="s">
         <v>96</v>
@@ -16066,10 +16066,10 @@
       <c r="B28" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C28" s="97" t="s">
+      <c r="C28" s="112" t="s">
         <v>129</v>
       </c>
-      <c r="D28" s="147"/>
+      <c r="D28" s="146"/>
       <c r="E28" s="53"/>
       <c r="F28" s="75" t="s">
         <v>101</v>
@@ -16187,10 +16187,10 @@
       <c r="B29" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C29" s="148" t="s">
+      <c r="C29" s="147" t="s">
         <v>130</v>
       </c>
-      <c r="D29" s="149"/>
+      <c r="D29" s="148"/>
       <c r="E29" s="53"/>
       <c r="F29" s="74" t="s">
         <v>96</v>
@@ -16308,10 +16308,10 @@
       <c r="B30" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C30" s="144" t="s">
+      <c r="C30" s="142" t="s">
         <v>132</v>
       </c>
-      <c r="D30" s="144"/>
+      <c r="D30" s="142"/>
       <c r="F30" s="73" t="s">
         <v>102</v>
       </c>
@@ -16428,10 +16428,10 @@
       <c r="B31" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C31" s="144" t="s">
+      <c r="C31" s="142" t="s">
         <v>133</v>
       </c>
-      <c r="D31" s="144"/>
+      <c r="D31" s="142"/>
       <c r="F31" s="75" t="s">
         <v>102</v>
       </c>
@@ -16548,10 +16548,10 @@
       <c r="B32" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C32" s="144" t="s">
+      <c r="C32" s="142" t="s">
         <v>134</v>
       </c>
-      <c r="D32" s="144"/>
+      <c r="D32" s="142"/>
       <c r="F32" s="75" t="s">
         <v>98</v>
       </c>
@@ -16668,10 +16668,10 @@
       <c r="B33" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C33" s="144" t="s">
+      <c r="C33" s="142" t="s">
         <v>136</v>
       </c>
-      <c r="D33" s="144"/>
+      <c r="D33" s="142"/>
       <c r="F33" s="75" t="s">
         <v>95</v>
       </c>
@@ -16788,10 +16788,10 @@
       <c r="B34" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C34" s="144" t="s">
+      <c r="C34" s="142" t="s">
         <v>137</v>
       </c>
-      <c r="D34" s="144"/>
+      <c r="D34" s="142"/>
       <c r="F34" s="75" t="s">
         <v>96</v>
       </c>
@@ -16908,10 +16908,10 @@
       <c r="B35" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C35" s="144" t="s">
+      <c r="C35" s="142" t="s">
         <v>138</v>
       </c>
-      <c r="D35" s="144"/>
+      <c r="D35" s="142"/>
       <c r="F35" s="75" t="s">
         <v>96</v>
       </c>
@@ -17028,10 +17028,10 @@
       <c r="B36" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C36" s="144" t="s">
+      <c r="C36" s="142" t="s">
         <v>139</v>
       </c>
-      <c r="D36" s="144"/>
+      <c r="D36" s="142"/>
       <c r="F36" s="76" t="s">
         <v>95</v>
       </c>
@@ -17148,10 +17148,10 @@
       <c r="B37" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C37" s="144" t="s">
+      <c r="C37" s="142" t="s">
         <v>140</v>
       </c>
-      <c r="D37" s="144"/>
+      <c r="D37" s="142"/>
       <c r="F37" s="75" t="s">
         <v>101</v>
       </c>
@@ -17268,10 +17268,10 @@
       <c r="B38" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C38" s="144" t="s">
+      <c r="C38" s="142" t="s">
         <v>141</v>
       </c>
-      <c r="D38" s="144"/>
+      <c r="D38" s="142"/>
       <c r="F38" s="75" t="s">
         <v>102</v>
       </c>
@@ -17388,10 +17388,10 @@
       <c r="B39" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C39" s="144" t="s">
+      <c r="C39" s="142" t="s">
         <v>142</v>
       </c>
-      <c r="D39" s="144"/>
+      <c r="D39" s="142"/>
       <c r="F39" s="75" t="s">
         <v>95</v>
       </c>
@@ -17508,10 +17508,10 @@
       <c r="B40" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C40" s="144" t="s">
+      <c r="C40" s="142" t="s">
         <v>143</v>
       </c>
-      <c r="D40" s="144"/>
+      <c r="D40" s="142"/>
       <c r="F40" s="75" t="s">
         <v>116</v>
       </c>
@@ -17628,10 +17628,10 @@
       <c r="B41" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C41" s="144" t="s">
+      <c r="C41" s="142" t="s">
         <v>144</v>
       </c>
-      <c r="D41" s="144"/>
+      <c r="D41" s="142"/>
       <c r="F41" s="75" t="s">
         <v>96</v>
       </c>
@@ -17748,10 +17748,10 @@
       <c r="B42" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C42" s="144" t="s">
+      <c r="C42" s="142" t="s">
         <v>145</v>
       </c>
-      <c r="D42" s="144"/>
+      <c r="D42" s="142"/>
       <c r="F42" s="75" t="s">
         <v>96</v>
       </c>
@@ -17868,10 +17868,10 @@
       <c r="B43" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C43" s="144" t="s">
+      <c r="C43" s="142" t="s">
         <v>146</v>
       </c>
-      <c r="D43" s="144"/>
+      <c r="D43" s="142"/>
       <c r="F43" s="76" t="s">
         <v>101</v>
       </c>
@@ -17988,10 +17988,10 @@
       <c r="B44" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C44" s="144" t="s">
+      <c r="C44" s="142" t="s">
         <v>147</v>
       </c>
-      <c r="D44" s="144"/>
+      <c r="D44" s="142"/>
       <c r="F44" s="75" t="s">
         <v>102</v>
       </c>
@@ -18108,10 +18108,10 @@
       <c r="B45" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C45" s="144" t="s">
+      <c r="C45" s="142" t="s">
         <v>148</v>
       </c>
-      <c r="D45" s="144"/>
+      <c r="D45" s="142"/>
       <c r="F45" s="75" t="s">
         <v>102</v>
       </c>
@@ -18228,10 +18228,10 @@
       <c r="B46" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C46" s="144" t="s">
+      <c r="C46" s="142" t="s">
         <v>149</v>
       </c>
-      <c r="D46" s="144"/>
+      <c r="D46" s="142"/>
       <c r="F46" s="75" t="s">
         <v>116</v>
       </c>
@@ -18348,10 +18348,10 @@
       <c r="B47" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C47" s="144" t="s">
+      <c r="C47" s="142" t="s">
         <v>150</v>
       </c>
-      <c r="D47" s="144"/>
+      <c r="D47" s="142"/>
       <c r="F47" s="75" t="s">
         <v>116</v>
       </c>
@@ -18468,10 +18468,10 @@
       <c r="B48" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C48" s="144" t="s">
+      <c r="C48" s="142" t="s">
         <v>151</v>
       </c>
-      <c r="D48" s="144"/>
+      <c r="D48" s="142"/>
       <c r="F48" s="75" t="s">
         <v>96</v>
       </c>
@@ -18588,10 +18588,10 @@
       <c r="B49" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C49" s="144" t="s">
+      <c r="C49" s="142" t="s">
         <v>152</v>
       </c>
-      <c r="D49" s="144"/>
+      <c r="D49" s="142"/>
       <c r="F49" s="75" t="s">
         <v>96</v>
       </c>
@@ -18708,10 +18708,10 @@
       <c r="B50" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C50" s="144" t="s">
+      <c r="C50" s="142" t="s">
         <v>153</v>
       </c>
-      <c r="D50" s="144"/>
+      <c r="D50" s="142"/>
       <c r="F50" s="76" t="s">
         <v>95</v>
       </c>
@@ -18828,10 +18828,10 @@
       <c r="B51" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C51" s="144" t="s">
+      <c r="C51" s="142" t="s">
         <v>154</v>
       </c>
-      <c r="D51" s="144"/>
+      <c r="D51" s="142"/>
       <c r="F51" s="75" t="s">
         <v>101</v>
       </c>
@@ -18948,10 +18948,10 @@
       <c r="B52" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C52" s="144" t="s">
+      <c r="C52" s="142" t="s">
         <v>155</v>
       </c>
-      <c r="D52" s="144"/>
+      <c r="D52" s="142"/>
       <c r="F52" s="75" t="s">
         <v>102</v>
       </c>
@@ -19068,10 +19068,10 @@
       <c r="B53" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C53" s="144" t="s">
+      <c r="C53" s="142" t="s">
         <v>156</v>
       </c>
-      <c r="D53" s="144"/>
+      <c r="D53" s="142"/>
       <c r="F53" s="75" t="s">
         <v>116</v>
       </c>
@@ -19188,10 +19188,10 @@
       <c r="B54" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C54" s="144" t="s">
+      <c r="C54" s="142" t="s">
         <v>157</v>
       </c>
-      <c r="D54" s="144"/>
+      <c r="D54" s="142"/>
       <c r="F54" s="75" t="s">
         <v>116</v>
       </c>
@@ -19308,10 +19308,10 @@
       <c r="B55" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C55" s="97" t="s">
+      <c r="C55" s="112" t="s">
         <v>158</v>
       </c>
-      <c r="D55" s="98"/>
+      <c r="D55" s="113"/>
       <c r="F55" s="75" t="s">
         <v>96</v>
       </c>
@@ -19428,10 +19428,10 @@
       <c r="B56" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C56" s="97" t="s">
+      <c r="C56" s="112" t="s">
         <v>159</v>
       </c>
-      <c r="D56" s="98"/>
+      <c r="D56" s="113"/>
       <c r="F56" s="75" t="s">
         <v>96</v>
       </c>
@@ -19548,10 +19548,10 @@
       <c r="B57" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C57" s="97" t="s">
+      <c r="C57" s="112" t="s">
         <v>160</v>
       </c>
-      <c r="D57" s="98"/>
+      <c r="D57" s="113"/>
       <c r="F57" s="76" t="s">
         <v>101</v>
       </c>
@@ -19668,10 +19668,10 @@
       <c r="B58" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C58" s="97" t="s">
+      <c r="C58" s="112" t="s">
         <v>161</v>
       </c>
-      <c r="D58" s="98"/>
+      <c r="D58" s="113"/>
       <c r="F58" s="75" t="s">
         <v>95</v>
       </c>
@@ -19788,10 +19788,10 @@
       <c r="B59" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C59" s="139" t="s">
+      <c r="C59" s="149" t="s">
         <v>162</v>
       </c>
-      <c r="D59" s="139"/>
+      <c r="D59" s="149"/>
       <c r="F59" s="75" t="s">
         <v>101</v>
       </c>
@@ -19908,10 +19908,10 @@
       <c r="B60" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C60" s="139" t="s">
+      <c r="C60" s="149" t="s">
         <v>163</v>
       </c>
-      <c r="D60" s="139"/>
+      <c r="D60" s="149"/>
       <c r="F60" s="75" t="s">
         <v>96</v>
       </c>
@@ -20028,10 +20028,10 @@
       <c r="B61" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C61" s="142" t="s">
+      <c r="C61" s="150" t="s">
         <v>164</v>
       </c>
-      <c r="D61" s="143"/>
+      <c r="D61" s="151"/>
       <c r="F61" s="75" t="s">
         <v>95</v>
       </c>
@@ -20148,10 +20148,10 @@
       <c r="B62" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="C62" s="139" t="s">
+      <c r="C62" s="149" t="s">
         <v>165</v>
       </c>
-      <c r="D62" s="139"/>
+      <c r="D62" s="149"/>
       <c r="F62" s="88" t="s">
         <v>166</v>
       </c>
@@ -20268,10 +20268,10 @@
       <c r="B63" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C63" s="111" t="s">
+      <c r="C63" s="120" t="s">
         <v>168</v>
       </c>
-      <c r="D63" s="112"/>
+      <c r="D63" s="121"/>
       <c r="F63" s="83" t="s">
         <v>102</v>
       </c>
@@ -20388,10 +20388,10 @@
       <c r="B64" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C64" s="97" t="s">
+      <c r="C64" s="112" t="s">
         <v>169</v>
       </c>
-      <c r="D64" s="98"/>
+      <c r="D64" s="113"/>
       <c r="F64" s="83" t="s">
         <v>102</v>
       </c>
@@ -20508,10 +20508,10 @@
       <c r="B65" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C65" s="97" t="s">
+      <c r="C65" s="112" t="s">
         <v>170</v>
       </c>
-      <c r="D65" s="98"/>
+      <c r="D65" s="113"/>
       <c r="F65" s="84" t="s">
         <v>95</v>
       </c>
@@ -20628,10 +20628,10 @@
       <c r="B66" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C66" s="97" t="s">
+      <c r="C66" s="112" t="s">
         <v>171</v>
       </c>
-      <c r="D66" s="98"/>
+      <c r="D66" s="113"/>
       <c r="F66" s="84" t="s">
         <v>95</v>
       </c>
@@ -20748,10 +20748,10 @@
       <c r="B67" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C67" s="97" t="s">
+      <c r="C67" s="112" t="s">
         <v>172</v>
       </c>
-      <c r="D67" s="98"/>
+      <c r="D67" s="113"/>
       <c r="F67" s="84" t="s">
         <v>96</v>
       </c>
@@ -20868,10 +20868,10 @@
       <c r="B68" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C68" s="97" t="s">
+      <c r="C68" s="112" t="s">
         <v>173</v>
       </c>
-      <c r="D68" s="98"/>
+      <c r="D68" s="113"/>
       <c r="F68" s="84" t="s">
         <v>96</v>
       </c>
@@ -20988,10 +20988,10 @@
       <c r="B69" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C69" s="97" t="s">
+      <c r="C69" s="112" t="s">
         <v>174</v>
       </c>
-      <c r="D69" s="98"/>
+      <c r="D69" s="113"/>
       <c r="F69" s="84" t="s">
         <v>101</v>
       </c>
@@ -21108,10 +21108,10 @@
       <c r="B70" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C70" s="97" t="s">
+      <c r="C70" s="112" t="s">
         <v>175</v>
       </c>
-      <c r="D70" s="98"/>
+      <c r="D70" s="113"/>
       <c r="F70" s="83" t="s">
         <v>101</v>
       </c>
@@ -21228,10 +21228,10 @@
       <c r="B71" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C71" s="97" t="s">
+      <c r="C71" s="112" t="s">
         <v>176</v>
       </c>
-      <c r="D71" s="98"/>
+      <c r="D71" s="113"/>
       <c r="F71" s="83" t="s">
         <v>101</v>
       </c>
@@ -21348,10 +21348,10 @@
       <c r="B72" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C72" s="97" t="s">
+      <c r="C72" s="112" t="s">
         <v>177</v>
       </c>
-      <c r="D72" s="98"/>
+      <c r="D72" s="113"/>
       <c r="F72" s="84" t="s">
         <v>116</v>
       </c>
@@ -21468,10 +21468,10 @@
       <c r="B73" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C73" s="97" t="s">
+      <c r="C73" s="112" t="s">
         <v>178</v>
       </c>
-      <c r="D73" s="98"/>
+      <c r="D73" s="113"/>
       <c r="F73" s="84" t="s">
         <v>116</v>
       </c>
@@ -21588,10 +21588,10 @@
       <c r="B74" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C74" s="97" t="s">
+      <c r="C74" s="112" t="s">
         <v>179</v>
       </c>
-      <c r="D74" s="98"/>
+      <c r="D74" s="113"/>
       <c r="F74" s="84" t="s">
         <v>96</v>
       </c>
@@ -21708,10 +21708,10 @@
       <c r="B75" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C75" s="97" t="s">
+      <c r="C75" s="112" t="s">
         <v>180</v>
       </c>
-      <c r="D75" s="98"/>
+      <c r="D75" s="113"/>
       <c r="F75" s="84" t="s">
         <v>96</v>
       </c>
@@ -21828,10 +21828,10 @@
       <c r="B76" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C76" s="97" t="s">
+      <c r="C76" s="112" t="s">
         <v>181</v>
       </c>
-      <c r="D76" s="98"/>
+      <c r="D76" s="113"/>
       <c r="F76" s="85" t="s">
         <v>101</v>
       </c>
@@ -21948,10 +21948,10 @@
       <c r="B77" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C77" s="97" t="s">
+      <c r="C77" s="112" t="s">
         <v>182</v>
       </c>
-      <c r="D77" s="98"/>
+      <c r="D77" s="113"/>
       <c r="F77" s="74" t="s">
         <v>116</v>
       </c>
@@ -22068,10 +22068,10 @@
       <c r="B78" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C78" s="97" t="s">
+      <c r="C78" s="112" t="s">
         <v>183</v>
       </c>
-      <c r="D78" s="98"/>
+      <c r="D78" s="113"/>
       <c r="F78" s="83" t="s">
         <v>96</v>
       </c>
@@ -22188,10 +22188,10 @@
       <c r="B79" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C79" s="97" t="s">
+      <c r="C79" s="112" t="s">
         <v>184</v>
       </c>
-      <c r="D79" s="98"/>
+      <c r="D79" s="113"/>
       <c r="F79" s="84" t="s">
         <v>102</v>
       </c>
@@ -22428,10 +22428,10 @@
       <c r="B81" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C81" s="99" t="s">
+      <c r="C81" s="126" t="s">
         <v>186</v>
       </c>
-      <c r="D81" s="100"/>
+      <c r="D81" s="127"/>
       <c r="F81" s="87" t="s">
         <v>101</v>
       </c>
@@ -22599,10 +22599,10 @@
       </c>
     </row>
     <row r="83" spans="2:42" ht="18.75">
-      <c r="C83" s="141" t="s">
+      <c r="C83" s="153" t="s">
         <v>188</v>
       </c>
-      <c r="D83" s="141"/>
+      <c r="D83" s="153"/>
       <c r="E83" s="34"/>
       <c r="F83" s="35">
         <f t="shared" ref="F83:AJ83" si="25">COUNTIF(F9:F81,"M*")</f>
@@ -22750,10 +22750,10 @@
       </c>
     </row>
     <row r="84" spans="2:42" ht="18.75">
-      <c r="C84" s="141" t="s">
+      <c r="C84" s="153" t="s">
         <v>189</v>
       </c>
-      <c r="D84" s="141"/>
+      <c r="D84" s="153"/>
       <c r="E84" s="34"/>
       <c r="F84" s="35">
         <f t="shared" ref="F84:AJ84" si="26">COUNTIF(F9:F81,"A*")</f>
@@ -22901,10 +22901,10 @@
       </c>
     </row>
     <row r="85" spans="2:42" ht="18.75">
-      <c r="C85" s="141" t="s">
+      <c r="C85" s="153" t="s">
         <v>77</v>
       </c>
-      <c r="D85" s="141"/>
+      <c r="D85" s="153"/>
       <c r="E85" s="34"/>
       <c r="F85" s="35">
         <f t="shared" ref="F85:AJ85" si="27">COUNTIF(F9:F81,"N*")</f>
@@ -23052,10 +23052,10 @@
       </c>
     </row>
     <row r="86" spans="2:42" ht="18.75">
-      <c r="C86" s="141" t="s">
+      <c r="C86" s="153" t="s">
         <v>78</v>
       </c>
-      <c r="D86" s="141"/>
+      <c r="D86" s="153"/>
       <c r="E86" s="34"/>
       <c r="F86" s="35">
         <f t="shared" ref="F86:AJ86" si="28">COUNTIF(F$30:F$81,"O*")</f>
@@ -23203,10 +23203,10 @@
       </c>
     </row>
     <row r="87" spans="2:42" ht="18.75">
-      <c r="C87" s="101" t="s">
+      <c r="C87" s="109" t="s">
         <v>190</v>
       </c>
-      <c r="D87" s="102"/>
+      <c r="D87" s="110"/>
       <c r="E87" s="34"/>
       <c r="F87" s="35">
         <f t="shared" ref="F87:AJ87" si="29">COUNTIF(F9:F81,"TR*")</f>
@@ -23354,10 +23354,10 @@
       </c>
     </row>
     <row r="88" spans="2:42" ht="18.75">
-      <c r="C88" s="101" t="s">
+      <c r="C88" s="109" t="s">
         <v>191</v>
       </c>
-      <c r="D88" s="102"/>
+      <c r="D88" s="110"/>
       <c r="E88" s="34"/>
       <c r="F88" s="35">
         <f>COUNTIF(F9:F81,"ST*")</f>
@@ -23505,10 +23505,10 @@
       </c>
     </row>
     <row r="89" spans="2:42" ht="18.75">
-      <c r="C89" s="140" t="s">
+      <c r="C89" s="152" t="s">
         <v>192</v>
       </c>
-      <c r="D89" s="140"/>
+      <c r="D89" s="152"/>
       <c r="E89" s="36"/>
       <c r="F89" s="37">
         <f>F91-F92</f>
@@ -23659,37 +23659,37 @@
       <c r="C90" s="38"/>
       <c r="D90" s="38"/>
       <c r="E90" s="34"/>
-      <c r="F90" s="114"/>
-      <c r="G90" s="114"/>
-      <c r="H90" s="114"/>
-      <c r="I90" s="114"/>
-      <c r="J90" s="114"/>
-      <c r="K90" s="114"/>
-      <c r="L90" s="114"/>
-      <c r="M90" s="114"/>
-      <c r="N90" s="114"/>
-      <c r="O90" s="114"/>
-      <c r="P90" s="114"/>
-      <c r="Q90" s="114"/>
-      <c r="R90" s="114"/>
-      <c r="S90" s="114"/>
-      <c r="T90" s="114"/>
-      <c r="U90" s="114"/>
-      <c r="V90" s="114"/>
-      <c r="W90" s="114"/>
-      <c r="X90" s="114"/>
-      <c r="Y90" s="114"/>
-      <c r="Z90" s="114"/>
-      <c r="AA90" s="114"/>
-      <c r="AB90" s="114"/>
-      <c r="AC90" s="114"/>
-      <c r="AD90" s="114"/>
-      <c r="AE90" s="114"/>
-      <c r="AF90" s="114"/>
-      <c r="AG90" s="114"/>
-      <c r="AH90" s="114"/>
-      <c r="AI90" s="114"/>
-      <c r="AJ90" s="114"/>
+      <c r="F90" s="108"/>
+      <c r="G90" s="108"/>
+      <c r="H90" s="108"/>
+      <c r="I90" s="108"/>
+      <c r="J90" s="108"/>
+      <c r="K90" s="108"/>
+      <c r="L90" s="108"/>
+      <c r="M90" s="108"/>
+      <c r="N90" s="108"/>
+      <c r="O90" s="108"/>
+      <c r="P90" s="108"/>
+      <c r="Q90" s="108"/>
+      <c r="R90" s="108"/>
+      <c r="S90" s="108"/>
+      <c r="T90" s="108"/>
+      <c r="U90" s="108"/>
+      <c r="V90" s="108"/>
+      <c r="W90" s="108"/>
+      <c r="X90" s="108"/>
+      <c r="Y90" s="108"/>
+      <c r="Z90" s="108"/>
+      <c r="AA90" s="108"/>
+      <c r="AB90" s="108"/>
+      <c r="AC90" s="108"/>
+      <c r="AD90" s="108"/>
+      <c r="AE90" s="108"/>
+      <c r="AF90" s="108"/>
+      <c r="AG90" s="108"/>
+      <c r="AH90" s="108"/>
+      <c r="AI90" s="108"/>
+      <c r="AJ90" s="108"/>
       <c r="AL90" s="20">
         <f t="shared" si="24"/>
         <v>0</v>
@@ -23712,10 +23712,10 @@
       </c>
     </row>
     <row r="91" spans="2:42" ht="18.75">
-      <c r="C91" s="141" t="s">
+      <c r="C91" s="153" t="s">
         <v>193</v>
       </c>
-      <c r="D91" s="141"/>
+      <c r="D91" s="153"/>
       <c r="E91" s="34"/>
       <c r="F91" s="39">
         <f>SUM(F83:F85)</f>
@@ -23862,10 +23862,10 @@
       </c>
     </row>
     <row r="92" spans="2:42" ht="18.75">
-      <c r="C92" s="141" t="s">
+      <c r="C92" s="153" t="s">
         <v>194</v>
       </c>
-      <c r="D92" s="141"/>
+      <c r="D92" s="153"/>
       <c r="E92" s="34"/>
       <c r="F92" s="35">
         <v>45</v>
@@ -23982,10 +23982,10 @@
       </c>
     </row>
     <row r="93" spans="2:42" ht="18.75">
-      <c r="C93" s="141" t="s">
+      <c r="C93" s="153" t="s">
         <v>195</v>
       </c>
-      <c r="D93" s="141"/>
+      <c r="D93" s="153"/>
       <c r="E93" s="34"/>
       <c r="F93" s="35">
         <f>SUM(F83,F84,F85,F86,F88)</f>
@@ -24154,14 +24154,14 @@
       </c>
     </row>
     <row r="95" spans="2:42" ht="16.5" thickBot="1">
-      <c r="F95" s="118" t="s">
+      <c r="F95" s="95" t="s">
         <v>196</v>
       </c>
-      <c r="G95" s="119"/>
-      <c r="H95" s="119"/>
-      <c r="I95" s="119"/>
-      <c r="J95" s="119"/>
-      <c r="K95" s="120"/>
+      <c r="G95" s="96"/>
+      <c r="H95" s="96"/>
+      <c r="I95" s="96"/>
+      <c r="J95" s="96"/>
+      <c r="K95" s="97"/>
       <c r="AL95" s="20">
         <f t="shared" si="24"/>
         <v>0</v>
@@ -24187,17 +24187,17 @@
       <c r="F96" s="80" t="s">
         <v>197</v>
       </c>
-      <c r="G96" s="128" t="s">
+      <c r="G96" s="106" t="s">
         <v>198</v>
       </c>
-      <c r="H96" s="128"/>
+      <c r="H96" s="106"/>
       <c r="I96" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="J96" s="121" t="s">
+      <c r="J96" s="98" t="s">
         <v>199</v>
       </c>
-      <c r="K96" s="122"/>
+      <c r="K96" s="99"/>
       <c r="AL96" s="20">
         <f t="shared" si="24"/>
         <v>0</v>
@@ -24223,17 +24223,17 @@
       <c r="F97" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="G97" s="129" t="s">
+      <c r="G97" s="107" t="s">
         <v>200</v>
       </c>
-      <c r="H97" s="129"/>
+      <c r="H97" s="107"/>
       <c r="I97" s="77" t="s">
         <v>201</v>
       </c>
-      <c r="J97" s="123" t="s">
+      <c r="J97" s="100" t="s">
         <v>202</v>
       </c>
-      <c r="K97" s="124"/>
+      <c r="K97" s="101"/>
       <c r="AL97" s="20">
         <f t="shared" si="24"/>
         <v>0</v>
@@ -24259,17 +24259,17 @@
       <c r="F98" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="G98" s="115" t="s">
+      <c r="G98" s="102" t="s">
         <v>203</v>
       </c>
-      <c r="H98" s="115"/>
+      <c r="H98" s="102"/>
       <c r="I98" s="78" t="s">
         <v>108</v>
       </c>
-      <c r="J98" s="115" t="s">
+      <c r="J98" s="102" t="s">
         <v>204</v>
       </c>
-      <c r="K98" s="125"/>
+      <c r="K98" s="103"/>
       <c r="AL98" s="20"/>
       <c r="AM98" s="20"/>
       <c r="AN98" s="20"/>
@@ -24280,17 +24280,17 @@
       <c r="F99" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="G99" s="116" t="s">
+      <c r="G99" s="111" t="s">
         <v>205</v>
       </c>
-      <c r="H99" s="116"/>
+      <c r="H99" s="111"/>
       <c r="I99" s="79" t="s">
         <v>206</v>
       </c>
-      <c r="J99" s="126" t="s">
+      <c r="J99" s="104" t="s">
         <v>207</v>
       </c>
-      <c r="K99" s="127"/>
+      <c r="K99" s="105"/>
       <c r="AL99" s="20">
         <f>COUNTIF($F81:$AJ81,"ST*")</f>
         <v>0</v>
@@ -24316,10 +24316,10 @@
       <c r="F100" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="G100" s="116" t="s">
+      <c r="G100" s="111" t="s">
         <v>208</v>
       </c>
-      <c r="H100" s="116"/>
+      <c r="H100" s="111"/>
       <c r="I100" s="20" t="s">
         <v>104</v>
       </c>
@@ -24332,10 +24332,10 @@
       <c r="F101" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="G101" s="117" t="s">
+      <c r="G101" s="92" t="s">
         <v>210</v>
       </c>
-      <c r="H101" s="117"/>
+      <c r="H101" s="92"/>
       <c r="I101" s="20" t="s">
         <v>114</v>
       </c>
@@ -24348,10 +24348,10 @@
       <c r="F102" s="82" t="s">
         <v>212</v>
       </c>
-      <c r="G102" s="92" t="s">
+      <c r="G102" s="123" t="s">
         <v>213</v>
       </c>
-      <c r="H102" s="92"/>
+      <c r="H102" s="123"/>
       <c r="I102" s="20" t="s">
         <v>131</v>
       </c>
@@ -24364,40 +24364,91 @@
       <c r="F103" s="55" t="s">
         <v>215</v>
       </c>
-      <c r="G103" s="95" t="s">
+      <c r="G103" s="124" t="s">
         <v>216</v>
       </c>
-      <c r="H103" s="95"/>
+      <c r="H103" s="124"/>
       <c r="I103" s="56" t="s">
         <v>167</v>
       </c>
-      <c r="J103" s="95" t="s">
+      <c r="J103" s="124" t="s">
         <v>217</v>
       </c>
-      <c r="K103" s="96"/>
+      <c r="K103" s="125"/>
     </row>
     <row r="108" spans="6:42" ht="9.75" customHeight="1"/>
   </sheetData>
   <autoFilter ref="F4:AJ89" xr:uid="{10A87D31-A428-49C7-B3CE-66B468A7BADA}"/>
   <mergeCells count="111">
-    <mergeCell ref="F2:AJ2"/>
-    <mergeCell ref="AL2:AL4"/>
-    <mergeCell ref="AM2:AM4"/>
-    <mergeCell ref="AN2:AN4"/>
-    <mergeCell ref="AO2:AO4"/>
-    <mergeCell ref="AP2:AP4"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="G103:H103"/>
+    <mergeCell ref="J103:K103"/>
+    <mergeCell ref="J96:K96"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="G98:H98"/>
+    <mergeCell ref="J98:K98"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="G100:H100"/>
+    <mergeCell ref="J100:K100"/>
+    <mergeCell ref="G101:H101"/>
+    <mergeCell ref="J101:K101"/>
+    <mergeCell ref="G102:H102"/>
+    <mergeCell ref="J102:K102"/>
+    <mergeCell ref="F95:K95"/>
+    <mergeCell ref="G96:H96"/>
+    <mergeCell ref="G97:H97"/>
+    <mergeCell ref="J97:K97"/>
+    <mergeCell ref="G99:H99"/>
+    <mergeCell ref="J99:K99"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="F90:AJ90"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C45:D45"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="C39:D39"/>
@@ -24422,75 +24473,24 @@
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="G100:H100"/>
-    <mergeCell ref="J100:K100"/>
-    <mergeCell ref="G101:H101"/>
-    <mergeCell ref="J101:K101"/>
-    <mergeCell ref="G102:H102"/>
-    <mergeCell ref="J102:K102"/>
-    <mergeCell ref="F95:K95"/>
-    <mergeCell ref="G96:H96"/>
-    <mergeCell ref="G97:H97"/>
-    <mergeCell ref="J97:K97"/>
-    <mergeCell ref="G99:H99"/>
-    <mergeCell ref="J99:K99"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="F90:AJ90"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="G103:H103"/>
-    <mergeCell ref="J103:K103"/>
-    <mergeCell ref="J96:K96"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="G98:H98"/>
-    <mergeCell ref="J98:K98"/>
+    <mergeCell ref="F2:AJ2"/>
+    <mergeCell ref="AL2:AL4"/>
+    <mergeCell ref="AM2:AM4"/>
+    <mergeCell ref="AN2:AN4"/>
+    <mergeCell ref="AO2:AO4"/>
+    <mergeCell ref="AP2:AP4"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F63:AI81">
@@ -24640,61 +24640,61 @@
   <sheetData>
     <row r="1" spans="2:42" ht="16.5" thickBot="1"/>
     <row r="2" spans="2:42" ht="39" customHeight="1" thickBot="1">
-      <c r="F2" s="151" t="s">
+      <c r="F2" s="139" t="s">
         <v>79</v>
       </c>
-      <c r="G2" s="152"/>
-      <c r="H2" s="152"/>
-      <c r="I2" s="152"/>
-      <c r="J2" s="152"/>
-      <c r="K2" s="152"/>
-      <c r="L2" s="152"/>
-      <c r="M2" s="152"/>
-      <c r="N2" s="152"/>
-      <c r="O2" s="152"/>
-      <c r="P2" s="152"/>
-      <c r="Q2" s="152"/>
-      <c r="R2" s="152"/>
-      <c r="S2" s="152"/>
-      <c r="T2" s="152"/>
-      <c r="U2" s="152"/>
-      <c r="V2" s="152"/>
-      <c r="W2" s="152"/>
-      <c r="X2" s="152"/>
-      <c r="Y2" s="152"/>
-      <c r="Z2" s="152"/>
-      <c r="AA2" s="152"/>
-      <c r="AB2" s="152"/>
-      <c r="AC2" s="152"/>
-      <c r="AD2" s="152"/>
-      <c r="AE2" s="152"/>
-      <c r="AF2" s="152"/>
-      <c r="AG2" s="152"/>
-      <c r="AH2" s="152"/>
-      <c r="AI2" s="152"/>
-      <c r="AJ2" s="153"/>
-      <c r="AL2" s="105" t="s">
+      <c r="G2" s="140"/>
+      <c r="H2" s="140"/>
+      <c r="I2" s="140"/>
+      <c r="J2" s="140"/>
+      <c r="K2" s="140"/>
+      <c r="L2" s="140"/>
+      <c r="M2" s="140"/>
+      <c r="N2" s="140"/>
+      <c r="O2" s="140"/>
+      <c r="P2" s="140"/>
+      <c r="Q2" s="140"/>
+      <c r="R2" s="140"/>
+      <c r="S2" s="140"/>
+      <c r="T2" s="140"/>
+      <c r="U2" s="140"/>
+      <c r="V2" s="140"/>
+      <c r="W2" s="140"/>
+      <c r="X2" s="140"/>
+      <c r="Y2" s="140"/>
+      <c r="Z2" s="140"/>
+      <c r="AA2" s="140"/>
+      <c r="AB2" s="140"/>
+      <c r="AC2" s="140"/>
+      <c r="AD2" s="140"/>
+      <c r="AE2" s="140"/>
+      <c r="AF2" s="140"/>
+      <c r="AG2" s="140"/>
+      <c r="AH2" s="140"/>
+      <c r="AI2" s="140"/>
+      <c r="AJ2" s="141"/>
+      <c r="AL2" s="114" t="s">
         <v>80</v>
       </c>
-      <c r="AM2" s="105" t="s">
+      <c r="AM2" s="114" t="s">
         <v>81</v>
       </c>
-      <c r="AN2" s="105" t="s">
+      <c r="AN2" s="114" t="s">
         <v>82</v>
       </c>
-      <c r="AO2" s="105" t="s">
+      <c r="AO2" s="114" t="s">
         <v>83</v>
       </c>
-      <c r="AP2" s="105" t="s">
+      <c r="AP2" s="114" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="3" spans="2:42" ht="39.75" thickBot="1">
-      <c r="B3" s="113" t="s">
+      <c r="B3" s="122" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="113"/>
-      <c r="D3" s="113"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="122"/>
       <c r="F3" s="43" t="s">
         <v>86</v>
       </c>
@@ -24788,16 +24788,16 @@
       <c r="AJ3" s="43" t="s">
         <v>187</v>
       </c>
-      <c r="AL3" s="106"/>
-      <c r="AM3" s="106"/>
-      <c r="AN3" s="106"/>
-      <c r="AO3" s="106"/>
-      <c r="AP3" s="106"/>
+      <c r="AL3" s="115"/>
+      <c r="AM3" s="115"/>
+      <c r="AN3" s="115"/>
+      <c r="AO3" s="115"/>
+      <c r="AP3" s="115"/>
     </row>
     <row r="4" spans="2:42" ht="19.5" customHeight="1" thickBot="1">
-      <c r="B4" s="113"/>
-      <c r="C4" s="113"/>
-      <c r="D4" s="113"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
       <c r="F4" s="40">
         <v>1</v>
       </c>
@@ -24891,20 +24891,20 @@
       <c r="AJ4" s="58" t="s">
         <v>187</v>
       </c>
-      <c r="AL4" s="107"/>
-      <c r="AM4" s="107"/>
-      <c r="AN4" s="107"/>
-      <c r="AO4" s="107"/>
-      <c r="AP4" s="107"/>
+      <c r="AL4" s="116"/>
+      <c r="AM4" s="116"/>
+      <c r="AN4" s="116"/>
+      <c r="AO4" s="116"/>
+      <c r="AP4" s="116"/>
     </row>
     <row r="5" spans="2:42" ht="18.75">
       <c r="B5" s="35">
         <v>1</v>
       </c>
-      <c r="C5" s="144" t="s">
+      <c r="C5" s="142" t="s">
         <v>94</v>
       </c>
-      <c r="D5" s="144"/>
+      <c r="D5" s="142"/>
       <c r="F5" s="84" t="s">
         <v>95</v>
       </c>
@@ -25021,10 +25021,10 @@
       <c r="B6" s="35">
         <v>2</v>
       </c>
-      <c r="C6" s="144" t="s">
+      <c r="C6" s="142" t="s">
         <v>99</v>
       </c>
-      <c r="D6" s="144"/>
+      <c r="D6" s="142"/>
       <c r="F6" s="75" t="s">
         <v>97</v>
       </c>
@@ -25141,10 +25141,10 @@
       <c r="B7" s="35">
         <v>3</v>
       </c>
-      <c r="C7" s="144" t="s">
+      <c r="C7" s="142" t="s">
         <v>100</v>
       </c>
-      <c r="D7" s="144"/>
+      <c r="D7" s="142"/>
       <c r="F7" s="75" t="s">
         <v>101</v>
       </c>
@@ -25261,10 +25261,10 @@
       <c r="B8" s="35">
         <v>4</v>
       </c>
-      <c r="C8" s="144" t="s">
+      <c r="C8" s="142" t="s">
         <v>103</v>
       </c>
-      <c r="D8" s="144"/>
+      <c r="D8" s="142"/>
       <c r="F8" s="75" t="s">
         <v>96</v>
       </c>
@@ -25412,10 +25412,10 @@
       <c r="AI9" s="18"/>
     </row>
     <row r="10" spans="2:42" ht="18.75">
-      <c r="C10" s="141" t="s">
+      <c r="C10" s="153" t="s">
         <v>188</v>
       </c>
-      <c r="D10" s="141"/>
+      <c r="D10" s="153"/>
       <c r="E10" s="34"/>
       <c r="F10" s="35">
         <f t="shared" ref="F10:AJ10" si="5">COUNTIF(F$5:F$8,"M*")</f>
@@ -25543,10 +25543,10 @@
       </c>
     </row>
     <row r="11" spans="2:42" ht="18.75">
-      <c r="C11" s="141" t="s">
+      <c r="C11" s="153" t="s">
         <v>189</v>
       </c>
-      <c r="D11" s="141"/>
+      <c r="D11" s="153"/>
       <c r="E11" s="34"/>
       <c r="F11" s="35">
         <f t="shared" ref="F11:AJ11" si="6">COUNTIF(F$5:F$8,"A*")</f>
@@ -25674,10 +25674,10 @@
       </c>
     </row>
     <row r="12" spans="2:42" ht="18.75">
-      <c r="C12" s="141" t="s">
+      <c r="C12" s="153" t="s">
         <v>77</v>
       </c>
-      <c r="D12" s="141"/>
+      <c r="D12" s="153"/>
       <c r="E12" s="34"/>
       <c r="F12" s="35">
         <f t="shared" ref="F12:AJ12" si="7">COUNTIF(F$5:F$8,"N*")</f>
@@ -25805,10 +25805,10 @@
       </c>
     </row>
     <row r="13" spans="2:42" ht="18.75">
-      <c r="C13" s="141" t="s">
+      <c r="C13" s="153" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="141"/>
+      <c r="D13" s="153"/>
       <c r="E13" s="34"/>
       <c r="F13" s="35">
         <f t="shared" ref="F13:AJ13" si="8">COUNTIF(F$5:F$8,"O*")</f>
@@ -25936,10 +25936,10 @@
       </c>
     </row>
     <row r="14" spans="2:42" ht="18.75">
-      <c r="C14" s="101" t="s">
+      <c r="C14" s="109" t="s">
         <v>190</v>
       </c>
-      <c r="D14" s="102"/>
+      <c r="D14" s="110"/>
       <c r="E14" s="34"/>
       <c r="F14" s="35">
         <f t="shared" ref="F14:AJ14" si="9">COUNTIF(F$5:F$8,"TR*")</f>
@@ -26067,10 +26067,10 @@
       </c>
     </row>
     <row r="15" spans="2:42" ht="18.75">
-      <c r="C15" s="101" t="s">
+      <c r="C15" s="109" t="s">
         <v>191</v>
       </c>
-      <c r="D15" s="102"/>
+      <c r="D15" s="110"/>
       <c r="E15" s="34"/>
       <c r="F15" s="35">
         <f t="shared" ref="F15:AJ15" si="10">COUNTIF(F$5:F$8,"ST*")</f>
@@ -26198,10 +26198,10 @@
       </c>
     </row>
     <row r="16" spans="2:42" ht="18.75">
-      <c r="C16" s="140" t="s">
+      <c r="C16" s="152" t="s">
         <v>192</v>
       </c>
-      <c r="D16" s="140"/>
+      <c r="D16" s="152"/>
       <c r="E16" s="36"/>
       <c r="F16" s="37">
         <f>F18-F19</f>
@@ -26332,43 +26332,43 @@
       <c r="C17" s="38"/>
       <c r="D17" s="38"/>
       <c r="E17" s="34"/>
-      <c r="F17" s="114"/>
-      <c r="G17" s="114"/>
-      <c r="H17" s="114"/>
-      <c r="I17" s="114"/>
-      <c r="J17" s="114"/>
-      <c r="K17" s="114"/>
-      <c r="L17" s="114"/>
-      <c r="M17" s="114"/>
-      <c r="N17" s="114"/>
-      <c r="O17" s="114"/>
-      <c r="P17" s="114"/>
-      <c r="Q17" s="114"/>
-      <c r="R17" s="114"/>
-      <c r="S17" s="114"/>
-      <c r="T17" s="114"/>
-      <c r="U17" s="114"/>
-      <c r="V17" s="114"/>
-      <c r="W17" s="114"/>
-      <c r="X17" s="114"/>
-      <c r="Y17" s="114"/>
-      <c r="Z17" s="114"/>
-      <c r="AA17" s="114"/>
-      <c r="AB17" s="114"/>
-      <c r="AC17" s="114"/>
-      <c r="AD17" s="114"/>
-      <c r="AE17" s="114"/>
-      <c r="AF17" s="114"/>
-      <c r="AG17" s="114"/>
-      <c r="AH17" s="114"/>
-      <c r="AI17" s="114"/>
-      <c r="AJ17" s="114"/>
+      <c r="F17" s="108"/>
+      <c r="G17" s="108"/>
+      <c r="H17" s="108"/>
+      <c r="I17" s="108"/>
+      <c r="J17" s="108"/>
+      <c r="K17" s="108"/>
+      <c r="L17" s="108"/>
+      <c r="M17" s="108"/>
+      <c r="N17" s="108"/>
+      <c r="O17" s="108"/>
+      <c r="P17" s="108"/>
+      <c r="Q17" s="108"/>
+      <c r="R17" s="108"/>
+      <c r="S17" s="108"/>
+      <c r="T17" s="108"/>
+      <c r="U17" s="108"/>
+      <c r="V17" s="108"/>
+      <c r="W17" s="108"/>
+      <c r="X17" s="108"/>
+      <c r="Y17" s="108"/>
+      <c r="Z17" s="108"/>
+      <c r="AA17" s="108"/>
+      <c r="AB17" s="108"/>
+      <c r="AC17" s="108"/>
+      <c r="AD17" s="108"/>
+      <c r="AE17" s="108"/>
+      <c r="AF17" s="108"/>
+      <c r="AG17" s="108"/>
+      <c r="AH17" s="108"/>
+      <c r="AI17" s="108"/>
+      <c r="AJ17" s="108"/>
     </row>
     <row r="18" spans="3:36" ht="18.75">
-      <c r="C18" s="141" t="s">
+      <c r="C18" s="153" t="s">
         <v>193</v>
       </c>
-      <c r="D18" s="141"/>
+      <c r="D18" s="153"/>
       <c r="E18" s="34"/>
       <c r="F18" s="39">
         <f>SUM(F10:F12)</f>
@@ -26495,10 +26495,10 @@
       </c>
     </row>
     <row r="19" spans="3:36" ht="18.75">
-      <c r="C19" s="141" t="s">
+      <c r="C19" s="153" t="s">
         <v>194</v>
       </c>
-      <c r="D19" s="141"/>
+      <c r="D19" s="153"/>
       <c r="E19" s="34"/>
       <c r="F19" s="35">
         <v>2</v>
@@ -26595,10 +26595,10 @@
       </c>
     </row>
     <row r="20" spans="3:36" ht="18.75">
-      <c r="C20" s="141" t="s">
+      <c r="C20" s="153" t="s">
         <v>195</v>
       </c>
-      <c r="D20" s="141"/>
+      <c r="D20" s="153"/>
       <c r="E20" s="34"/>
       <c r="F20" s="35">
         <f>SUM(F10,F11,F12,F13,F15)</f>
@@ -26726,87 +26726,87 @@
     </row>
     <row r="22" spans="3:36" ht="16.5" thickBot="1"/>
     <row r="23" spans="3:36" ht="16.5" thickBot="1">
-      <c r="F23" s="118" t="s">
+      <c r="F23" s="95" t="s">
         <v>196</v>
       </c>
-      <c r="G23" s="119"/>
-      <c r="H23" s="119"/>
-      <c r="I23" s="119"/>
-      <c r="J23" s="119"/>
-      <c r="K23" s="120"/>
+      <c r="G23" s="96"/>
+      <c r="H23" s="96"/>
+      <c r="I23" s="96"/>
+      <c r="J23" s="96"/>
+      <c r="K23" s="97"/>
     </row>
     <row r="24" spans="3:36">
       <c r="F24" s="80" t="s">
         <v>197</v>
       </c>
-      <c r="G24" s="128" t="s">
+      <c r="G24" s="106" t="s">
         <v>198</v>
       </c>
-      <c r="H24" s="128"/>
+      <c r="H24" s="106"/>
       <c r="I24" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="J24" s="121" t="s">
+      <c r="J24" s="98" t="s">
         <v>199</v>
       </c>
-      <c r="K24" s="122"/>
+      <c r="K24" s="99"/>
     </row>
     <row r="25" spans="3:36">
       <c r="F25" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="G25" s="129" t="s">
+      <c r="G25" s="107" t="s">
         <v>200</v>
       </c>
-      <c r="H25" s="129"/>
+      <c r="H25" s="107"/>
       <c r="I25" s="77" t="s">
         <v>201</v>
       </c>
-      <c r="J25" s="123" t="s">
+      <c r="J25" s="100" t="s">
         <v>202</v>
       </c>
-      <c r="K25" s="124"/>
+      <c r="K25" s="101"/>
     </row>
     <row r="26" spans="3:36">
       <c r="F26" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="G26" s="115" t="s">
+      <c r="G26" s="102" t="s">
         <v>203</v>
       </c>
-      <c r="H26" s="115"/>
+      <c r="H26" s="102"/>
       <c r="I26" s="78" t="s">
         <v>108</v>
       </c>
-      <c r="J26" s="115" t="s">
+      <c r="J26" s="102" t="s">
         <v>204</v>
       </c>
-      <c r="K26" s="125"/>
+      <c r="K26" s="103"/>
     </row>
     <row r="27" spans="3:36">
       <c r="F27" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="G27" s="116" t="s">
+      <c r="G27" s="111" t="s">
         <v>205</v>
       </c>
-      <c r="H27" s="116"/>
+      <c r="H27" s="111"/>
       <c r="I27" s="79" t="s">
         <v>206</v>
       </c>
-      <c r="J27" s="126" t="s">
+      <c r="J27" s="104" t="s">
         <v>207</v>
       </c>
-      <c r="K27" s="127"/>
+      <c r="K27" s="105"/>
     </row>
     <row r="28" spans="3:36">
       <c r="F28" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="G28" s="116" t="s">
+      <c r="G28" s="111" t="s">
         <v>208</v>
       </c>
-      <c r="H28" s="116"/>
+      <c r="H28" s="111"/>
       <c r="I28" s="20" t="s">
         <v>104</v>
       </c>
@@ -26819,10 +26819,10 @@
       <c r="F29" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="G29" s="117" t="s">
+      <c r="G29" s="92" t="s">
         <v>210</v>
       </c>
-      <c r="H29" s="117"/>
+      <c r="H29" s="92"/>
       <c r="I29" s="20" t="s">
         <v>114</v>
       </c>
@@ -26838,10 +26838,10 @@
       <c r="F30" s="82" t="s">
         <v>212</v>
       </c>
-      <c r="G30" s="92" t="s">
+      <c r="G30" s="123" t="s">
         <v>213</v>
       </c>
-      <c r="H30" s="92"/>
+      <c r="H30" s="123"/>
       <c r="I30" s="20" t="s">
         <v>131</v>
       </c>
@@ -26854,43 +26854,20 @@
       <c r="F31" s="55" t="s">
         <v>215</v>
       </c>
-      <c r="G31" s="95" t="s">
+      <c r="G31" s="124" t="s">
         <v>216</v>
       </c>
-      <c r="H31" s="95"/>
+      <c r="H31" s="124"/>
       <c r="I31" s="56" t="s">
         <v>167</v>
       </c>
-      <c r="J31" s="95" t="s">
+      <c r="J31" s="124" t="s">
         <v>217</v>
       </c>
-      <c r="K31" s="96"/>
+      <c r="K31" s="125"/>
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="F23:K23"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="B3:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C6:D6"/>
     <mergeCell ref="J30:K30"/>
     <mergeCell ref="G31:H31"/>
     <mergeCell ref="J31:K31"/>
@@ -26907,6 +26884,29 @@
     <mergeCell ref="G30:H30"/>
     <mergeCell ref="G24:H24"/>
     <mergeCell ref="G25:H25"/>
+    <mergeCell ref="B3:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="F23:K23"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F5:AJ8">
@@ -26963,61 +26963,61 @@
   <sheetData>
     <row r="1" spans="2:42" ht="16.5" thickBot="1"/>
     <row r="2" spans="2:42" ht="39" customHeight="1" thickBot="1">
-      <c r="F2" s="151" t="s">
+      <c r="F2" s="139" t="s">
         <v>218</v>
       </c>
-      <c r="G2" s="152"/>
-      <c r="H2" s="152"/>
-      <c r="I2" s="152"/>
-      <c r="J2" s="152"/>
-      <c r="K2" s="152"/>
-      <c r="L2" s="152"/>
-      <c r="M2" s="152"/>
-      <c r="N2" s="152"/>
-      <c r="O2" s="152"/>
-      <c r="P2" s="152"/>
-      <c r="Q2" s="152"/>
-      <c r="R2" s="152"/>
-      <c r="S2" s="152"/>
-      <c r="T2" s="152"/>
-      <c r="U2" s="152"/>
-      <c r="V2" s="152"/>
-      <c r="W2" s="152"/>
-      <c r="X2" s="152"/>
-      <c r="Y2" s="152"/>
-      <c r="Z2" s="152"/>
-      <c r="AA2" s="152"/>
-      <c r="AB2" s="152"/>
-      <c r="AC2" s="152"/>
-      <c r="AD2" s="152"/>
-      <c r="AE2" s="152"/>
-      <c r="AF2" s="152"/>
-      <c r="AG2" s="152"/>
-      <c r="AH2" s="152"/>
-      <c r="AI2" s="152"/>
-      <c r="AJ2" s="153"/>
-      <c r="AL2" s="105" t="s">
+      <c r="G2" s="140"/>
+      <c r="H2" s="140"/>
+      <c r="I2" s="140"/>
+      <c r="J2" s="140"/>
+      <c r="K2" s="140"/>
+      <c r="L2" s="140"/>
+      <c r="M2" s="140"/>
+      <c r="N2" s="140"/>
+      <c r="O2" s="140"/>
+      <c r="P2" s="140"/>
+      <c r="Q2" s="140"/>
+      <c r="R2" s="140"/>
+      <c r="S2" s="140"/>
+      <c r="T2" s="140"/>
+      <c r="U2" s="140"/>
+      <c r="V2" s="140"/>
+      <c r="W2" s="140"/>
+      <c r="X2" s="140"/>
+      <c r="Y2" s="140"/>
+      <c r="Z2" s="140"/>
+      <c r="AA2" s="140"/>
+      <c r="AB2" s="140"/>
+      <c r="AC2" s="140"/>
+      <c r="AD2" s="140"/>
+      <c r="AE2" s="140"/>
+      <c r="AF2" s="140"/>
+      <c r="AG2" s="140"/>
+      <c r="AH2" s="140"/>
+      <c r="AI2" s="140"/>
+      <c r="AJ2" s="141"/>
+      <c r="AL2" s="114" t="s">
         <v>80</v>
       </c>
-      <c r="AM2" s="105" t="s">
+      <c r="AM2" s="114" t="s">
         <v>81</v>
       </c>
-      <c r="AN2" s="105" t="s">
+      <c r="AN2" s="114" t="s">
         <v>82</v>
       </c>
-      <c r="AO2" s="105" t="s">
+      <c r="AO2" s="114" t="s">
         <v>83</v>
       </c>
-      <c r="AP2" s="105" t="s">
+      <c r="AP2" s="114" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="3" spans="2:42" ht="39.75" thickBot="1">
-      <c r="B3" s="113" t="s">
+      <c r="B3" s="122" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="113"/>
-      <c r="D3" s="113"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="122"/>
       <c r="F3" s="43" t="s">
         <v>86</v>
       </c>
@@ -27109,16 +27109,16 @@
         <v>87</v>
       </c>
       <c r="AJ3" s="43"/>
-      <c r="AL3" s="106"/>
-      <c r="AM3" s="106"/>
-      <c r="AN3" s="106"/>
-      <c r="AO3" s="106"/>
-      <c r="AP3" s="106"/>
+      <c r="AL3" s="115"/>
+      <c r="AM3" s="115"/>
+      <c r="AN3" s="115"/>
+      <c r="AO3" s="115"/>
+      <c r="AP3" s="115"/>
     </row>
     <row r="4" spans="2:42" ht="19.5" customHeight="1" thickBot="1">
-      <c r="B4" s="113"/>
-      <c r="C4" s="113"/>
-      <c r="D4" s="113"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
       <c r="F4" s="40">
         <v>1</v>
       </c>
@@ -27212,20 +27212,20 @@
       <c r="AJ4" s="58" t="s">
         <v>187</v>
       </c>
-      <c r="AL4" s="107"/>
-      <c r="AM4" s="107"/>
-      <c r="AN4" s="107"/>
-      <c r="AO4" s="107"/>
-      <c r="AP4" s="107"/>
+      <c r="AL4" s="116"/>
+      <c r="AM4" s="116"/>
+      <c r="AN4" s="116"/>
+      <c r="AO4" s="116"/>
+      <c r="AP4" s="116"/>
     </row>
     <row r="5" spans="2:42" ht="18.75">
       <c r="B5" s="35">
         <v>1</v>
       </c>
-      <c r="C5" s="144" t="s">
+      <c r="C5" s="142" t="s">
         <v>105</v>
       </c>
-      <c r="D5" s="144"/>
+      <c r="D5" s="142"/>
       <c r="F5" s="90" t="s">
         <v>106</v>
       </c>
@@ -27342,10 +27342,10 @@
       <c r="B6" s="35">
         <v>2</v>
       </c>
-      <c r="C6" s="144" t="s">
+      <c r="C6" s="142" t="s">
         <v>109</v>
       </c>
-      <c r="D6" s="144"/>
+      <c r="D6" s="142"/>
       <c r="F6" s="75" t="s">
         <v>96</v>
       </c>
@@ -27462,10 +27462,10 @@
       <c r="B7" s="35">
         <v>3</v>
       </c>
-      <c r="C7" s="144" t="s">
+      <c r="C7" s="142" t="s">
         <v>110</v>
       </c>
-      <c r="D7" s="144"/>
+      <c r="D7" s="142"/>
       <c r="F7" s="75" t="s">
         <v>95</v>
       </c>
@@ -27582,10 +27582,10 @@
       <c r="B8" s="35">
         <v>4</v>
       </c>
-      <c r="C8" s="144" t="s">
+      <c r="C8" s="142" t="s">
         <v>111</v>
       </c>
-      <c r="D8" s="144"/>
+      <c r="D8" s="142"/>
       <c r="F8" s="75" t="s">
         <v>107</v>
       </c>
@@ -27702,10 +27702,10 @@
       <c r="B9" s="35">
         <v>5</v>
       </c>
-      <c r="C9" s="144" t="s">
+      <c r="C9" s="142" t="s">
         <v>112</v>
       </c>
-      <c r="D9" s="144"/>
+      <c r="D9" s="142"/>
       <c r="F9" s="75" t="s">
         <v>108</v>
       </c>
@@ -27823,10 +27823,10 @@
       <c r="B10" s="35">
         <v>6</v>
       </c>
-      <c r="C10" s="144" t="s">
+      <c r="C10" s="142" t="s">
         <v>113</v>
       </c>
-      <c r="D10" s="144"/>
+      <c r="D10" s="142"/>
       <c r="F10" s="88" t="s">
         <v>95</v>
       </c>
@@ -27974,10 +27974,10 @@
       <c r="AI11" s="18"/>
     </row>
     <row r="12" spans="2:42" ht="18.75">
-      <c r="C12" s="141" t="s">
+      <c r="C12" s="153" t="s">
         <v>188</v>
       </c>
-      <c r="D12" s="141"/>
+      <c r="D12" s="153"/>
       <c r="E12" s="34"/>
       <c r="F12" s="35">
         <f>COUNTIF(F$5:F$9,"M*")</f>
@@ -28105,10 +28105,10 @@
       </c>
     </row>
     <row r="13" spans="2:42" ht="18.75">
-      <c r="C13" s="141" t="s">
+      <c r="C13" s="153" t="s">
         <v>189</v>
       </c>
-      <c r="D13" s="141"/>
+      <c r="D13" s="153"/>
       <c r="E13" s="34"/>
       <c r="F13" s="35">
         <f>COUNTIF(F$5:F$9,"A*")</f>
@@ -28236,10 +28236,10 @@
       </c>
     </row>
     <row r="14" spans="2:42" ht="18.75">
-      <c r="C14" s="141" t="s">
+      <c r="C14" s="153" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="141"/>
+      <c r="D14" s="153"/>
       <c r="E14" s="34"/>
       <c r="F14" s="35">
         <f>COUNTIF(F$5:F$9,"N*")</f>
@@ -28367,10 +28367,10 @@
       </c>
     </row>
     <row r="15" spans="2:42" ht="18.75">
-      <c r="C15" s="141" t="s">
+      <c r="C15" s="153" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="141"/>
+      <c r="D15" s="153"/>
       <c r="E15" s="34"/>
       <c r="F15" s="35">
         <f t="shared" ref="F15:AJ15" si="8">COUNTIF(F$5:F$10,"O*")</f>
@@ -28498,10 +28498,10 @@
       </c>
     </row>
     <row r="16" spans="2:42" ht="18.75">
-      <c r="C16" s="101" t="s">
+      <c r="C16" s="109" t="s">
         <v>190</v>
       </c>
-      <c r="D16" s="102"/>
+      <c r="D16" s="110"/>
       <c r="E16" s="34"/>
       <c r="F16" s="35">
         <f t="shared" ref="F16:AJ16" si="9">COUNTIF(F$5:F$10,"TR*")</f>
@@ -28629,10 +28629,10 @@
       </c>
     </row>
     <row r="17" spans="3:36" ht="18.75">
-      <c r="C17" s="101" t="s">
+      <c r="C17" s="109" t="s">
         <v>191</v>
       </c>
-      <c r="D17" s="102"/>
+      <c r="D17" s="110"/>
       <c r="E17" s="34"/>
       <c r="F17" s="35">
         <f t="shared" ref="F17:AJ17" si="10">COUNTIF(F$5:F$10,"ST*")</f>
@@ -28760,10 +28760,10 @@
       </c>
     </row>
     <row r="18" spans="3:36" ht="18.75">
-      <c r="C18" s="140" t="s">
+      <c r="C18" s="152" t="s">
         <v>192</v>
       </c>
-      <c r="D18" s="140"/>
+      <c r="D18" s="152"/>
       <c r="E18" s="36"/>
       <c r="F18" s="37">
         <f>F20-F21</f>
@@ -28894,43 +28894,43 @@
       <c r="C19" s="38"/>
       <c r="D19" s="38"/>
       <c r="E19" s="34"/>
-      <c r="F19" s="114"/>
-      <c r="G19" s="114"/>
-      <c r="H19" s="114"/>
-      <c r="I19" s="114"/>
-      <c r="J19" s="114"/>
-      <c r="K19" s="114"/>
-      <c r="L19" s="114"/>
-      <c r="M19" s="114"/>
-      <c r="N19" s="114"/>
-      <c r="O19" s="114"/>
-      <c r="P19" s="114"/>
-      <c r="Q19" s="114"/>
-      <c r="R19" s="114"/>
-      <c r="S19" s="114"/>
-      <c r="T19" s="114"/>
-      <c r="U19" s="114"/>
-      <c r="V19" s="114"/>
-      <c r="W19" s="114"/>
-      <c r="X19" s="114"/>
-      <c r="Y19" s="114"/>
-      <c r="Z19" s="114"/>
-      <c r="AA19" s="114"/>
-      <c r="AB19" s="114"/>
-      <c r="AC19" s="114"/>
-      <c r="AD19" s="114"/>
-      <c r="AE19" s="114"/>
-      <c r="AF19" s="114"/>
-      <c r="AG19" s="114"/>
-      <c r="AH19" s="114"/>
-      <c r="AI19" s="114"/>
-      <c r="AJ19" s="114"/>
+      <c r="F19" s="108"/>
+      <c r="G19" s="108"/>
+      <c r="H19" s="108"/>
+      <c r="I19" s="108"/>
+      <c r="J19" s="108"/>
+      <c r="K19" s="108"/>
+      <c r="L19" s="108"/>
+      <c r="M19" s="108"/>
+      <c r="N19" s="108"/>
+      <c r="O19" s="108"/>
+      <c r="P19" s="108"/>
+      <c r="Q19" s="108"/>
+      <c r="R19" s="108"/>
+      <c r="S19" s="108"/>
+      <c r="T19" s="108"/>
+      <c r="U19" s="108"/>
+      <c r="V19" s="108"/>
+      <c r="W19" s="108"/>
+      <c r="X19" s="108"/>
+      <c r="Y19" s="108"/>
+      <c r="Z19" s="108"/>
+      <c r="AA19" s="108"/>
+      <c r="AB19" s="108"/>
+      <c r="AC19" s="108"/>
+      <c r="AD19" s="108"/>
+      <c r="AE19" s="108"/>
+      <c r="AF19" s="108"/>
+      <c r="AG19" s="108"/>
+      <c r="AH19" s="108"/>
+      <c r="AI19" s="108"/>
+      <c r="AJ19" s="108"/>
     </row>
     <row r="20" spans="3:36" ht="18.75">
-      <c r="C20" s="141" t="s">
+      <c r="C20" s="153" t="s">
         <v>193</v>
       </c>
-      <c r="D20" s="141"/>
+      <c r="D20" s="153"/>
       <c r="E20" s="34"/>
       <c r="F20" s="39">
         <f>SUM(F12:F14)</f>
@@ -29057,10 +29057,10 @@
       </c>
     </row>
     <row r="21" spans="3:36" ht="18.75">
-      <c r="C21" s="141" t="s">
+      <c r="C21" s="153" t="s">
         <v>194</v>
       </c>
-      <c r="D21" s="141"/>
+      <c r="D21" s="153"/>
       <c r="E21" s="34"/>
       <c r="F21" s="35">
         <v>3</v>
@@ -29157,10 +29157,10 @@
       </c>
     </row>
     <row r="22" spans="3:36" ht="18.75">
-      <c r="C22" s="141" t="s">
+      <c r="C22" s="153" t="s">
         <v>195</v>
       </c>
-      <c r="D22" s="141"/>
+      <c r="D22" s="153"/>
       <c r="E22" s="34"/>
       <c r="F22" s="35">
         <f>SUM(F12,F13,F14,F15,F17)</f>
@@ -29294,151 +29294,151 @@
       <c r="K24" s="154"/>
     </row>
     <row r="25" spans="3:36" ht="16.5" thickBot="1">
-      <c r="F25" s="118" t="s">
+      <c r="F25" s="95" t="s">
         <v>196</v>
       </c>
-      <c r="G25" s="119"/>
-      <c r="H25" s="119"/>
-      <c r="I25" s="119"/>
-      <c r="J25" s="119"/>
-      <c r="K25" s="120"/>
-      <c r="M25" s="118" t="s">
+      <c r="G25" s="96"/>
+      <c r="H25" s="96"/>
+      <c r="I25" s="96"/>
+      <c r="J25" s="96"/>
+      <c r="K25" s="97"/>
+      <c r="M25" s="95" t="s">
         <v>196</v>
       </c>
-      <c r="N25" s="119"/>
-      <c r="O25" s="119"/>
-      <c r="P25" s="119"/>
-      <c r="Q25" s="119"/>
-      <c r="R25" s="120"/>
+      <c r="N25" s="96"/>
+      <c r="O25" s="96"/>
+      <c r="P25" s="96"/>
+      <c r="Q25" s="96"/>
+      <c r="R25" s="97"/>
     </row>
     <row r="26" spans="3:36">
       <c r="F26" s="80" t="s">
         <v>197</v>
       </c>
-      <c r="G26" s="128" t="s">
+      <c r="G26" s="106" t="s">
         <v>198</v>
       </c>
-      <c r="H26" s="128"/>
+      <c r="H26" s="106"/>
       <c r="I26" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="J26" s="121" t="s">
+      <c r="J26" s="98" t="s">
         <v>199</v>
       </c>
-      <c r="K26" s="122"/>
+      <c r="K26" s="99"/>
       <c r="M26" s="80" t="s">
         <v>197</v>
       </c>
-      <c r="N26" s="128" t="s">
+      <c r="N26" s="106" t="s">
         <v>198</v>
       </c>
-      <c r="O26" s="128"/>
+      <c r="O26" s="106"/>
       <c r="P26" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="Q26" s="121" t="s">
+      <c r="Q26" s="98" t="s">
         <v>199</v>
       </c>
-      <c r="R26" s="122"/>
+      <c r="R26" s="99"/>
     </row>
     <row r="27" spans="3:36">
       <c r="F27" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="G27" s="129" t="s">
+      <c r="G27" s="107" t="s">
         <v>200</v>
       </c>
-      <c r="H27" s="129"/>
+      <c r="H27" s="107"/>
       <c r="I27" s="77" t="s">
         <v>201</v>
       </c>
-      <c r="J27" s="123" t="s">
+      <c r="J27" s="100" t="s">
         <v>202</v>
       </c>
-      <c r="K27" s="124"/>
+      <c r="K27" s="101"/>
       <c r="M27" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="N27" s="129" t="s">
+      <c r="N27" s="107" t="s">
         <v>200</v>
       </c>
-      <c r="O27" s="129"/>
+      <c r="O27" s="107"/>
       <c r="P27" s="77" t="s">
         <v>201</v>
       </c>
-      <c r="Q27" s="123" t="s">
+      <c r="Q27" s="100" t="s">
         <v>202</v>
       </c>
-      <c r="R27" s="124"/>
+      <c r="R27" s="101"/>
     </row>
     <row r="28" spans="3:36">
       <c r="F28" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="G28" s="115" t="s">
+      <c r="G28" s="102" t="s">
         <v>203</v>
       </c>
-      <c r="H28" s="115"/>
+      <c r="H28" s="102"/>
       <c r="I28" s="78" t="s">
         <v>108</v>
       </c>
-      <c r="J28" s="115" t="s">
+      <c r="J28" s="102" t="s">
         <v>204</v>
       </c>
-      <c r="K28" s="125"/>
+      <c r="K28" s="103"/>
       <c r="M28" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="N28" s="115" t="s">
+      <c r="N28" s="102" t="s">
         <v>203</v>
       </c>
-      <c r="O28" s="115"/>
+      <c r="O28" s="102"/>
       <c r="P28" s="78" t="s">
         <v>108</v>
       </c>
-      <c r="Q28" s="115" t="s">
+      <c r="Q28" s="102" t="s">
         <v>204</v>
       </c>
-      <c r="R28" s="125"/>
+      <c r="R28" s="103"/>
     </row>
     <row r="29" spans="3:36">
       <c r="F29" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="G29" s="116" t="s">
+      <c r="G29" s="111" t="s">
         <v>205</v>
       </c>
-      <c r="H29" s="116"/>
+      <c r="H29" s="111"/>
       <c r="I29" s="79" t="s">
         <v>206</v>
       </c>
-      <c r="J29" s="126" t="s">
+      <c r="J29" s="104" t="s">
         <v>207</v>
       </c>
-      <c r="K29" s="127"/>
+      <c r="K29" s="105"/>
       <c r="M29" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="N29" s="116" t="s">
+      <c r="N29" s="111" t="s">
         <v>205</v>
       </c>
-      <c r="O29" s="116"/>
+      <c r="O29" s="111"/>
       <c r="P29" s="79" t="s">
         <v>206</v>
       </c>
-      <c r="Q29" s="126" t="s">
+      <c r="Q29" s="104" t="s">
         <v>207</v>
       </c>
-      <c r="R29" s="127"/>
+      <c r="R29" s="105"/>
     </row>
     <row r="30" spans="3:36">
       <c r="F30" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="G30" s="116" t="s">
+      <c r="G30" s="111" t="s">
         <v>208</v>
       </c>
-      <c r="H30" s="116"/>
+      <c r="H30" s="111"/>
       <c r="I30" s="20" t="s">
         <v>104</v>
       </c>
@@ -29449,10 +29449,10 @@
       <c r="M30" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="N30" s="116" t="s">
+      <c r="N30" s="111" t="s">
         <v>208</v>
       </c>
-      <c r="O30" s="116"/>
+      <c r="O30" s="111"/>
       <c r="P30" s="20" t="s">
         <v>104</v>
       </c>
@@ -29465,10 +29465,10 @@
       <c r="F31" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="G31" s="117" t="s">
+      <c r="G31" s="92" t="s">
         <v>210</v>
       </c>
-      <c r="H31" s="117"/>
+      <c r="H31" s="92"/>
       <c r="I31" s="20" t="s">
         <v>114</v>
       </c>
@@ -29479,10 +29479,10 @@
       <c r="M31" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="N31" s="117" t="s">
+      <c r="N31" s="92" t="s">
         <v>210</v>
       </c>
-      <c r="O31" s="117"/>
+      <c r="O31" s="92"/>
       <c r="P31" s="20" t="s">
         <v>114</v>
       </c>
@@ -29495,10 +29495,10 @@
       <c r="F32" s="82" t="s">
         <v>212</v>
       </c>
-      <c r="G32" s="92" t="s">
+      <c r="G32" s="123" t="s">
         <v>213</v>
       </c>
-      <c r="H32" s="92"/>
+      <c r="H32" s="123"/>
       <c r="I32" s="20" t="s">
         <v>131</v>
       </c>
@@ -29509,10 +29509,10 @@
       <c r="M32" s="82" t="s">
         <v>212</v>
       </c>
-      <c r="N32" s="92" t="s">
+      <c r="N32" s="123" t="s">
         <v>213</v>
       </c>
-      <c r="O32" s="92"/>
+      <c r="O32" s="123"/>
       <c r="P32" s="20" t="s">
         <v>131</v>
       </c>
@@ -29525,34 +29525,78 @@
       <c r="F33" s="55" t="s">
         <v>215</v>
       </c>
-      <c r="G33" s="95" t="s">
+      <c r="G33" s="124" t="s">
         <v>216</v>
       </c>
-      <c r="H33" s="95"/>
+      <c r="H33" s="124"/>
       <c r="I33" s="56" t="s">
         <v>167</v>
       </c>
-      <c r="J33" s="95" t="s">
+      <c r="J33" s="124" t="s">
         <v>217</v>
       </c>
-      <c r="K33" s="96"/>
+      <c r="K33" s="125"/>
       <c r="M33" s="55" t="s">
         <v>215</v>
       </c>
-      <c r="N33" s="95" t="s">
+      <c r="N33" s="124" t="s">
         <v>216</v>
       </c>
-      <c r="O33" s="95"/>
+      <c r="O33" s="124"/>
       <c r="P33" s="56" t="s">
         <v>167</v>
       </c>
-      <c r="Q33" s="95" t="s">
+      <c r="Q33" s="124" t="s">
         <v>217</v>
       </c>
-      <c r="R33" s="96"/>
+      <c r="R33" s="125"/>
     </row>
   </sheetData>
   <mergeCells count="60">
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B3:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="AP2:AP4"/>
+    <mergeCell ref="F2:AJ2"/>
+    <mergeCell ref="AL2:AL4"/>
+    <mergeCell ref="AM2:AM4"/>
+    <mergeCell ref="AN2:AN4"/>
+    <mergeCell ref="AO2:AO4"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="F19:AJ19"/>
+    <mergeCell ref="F25:K25"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G24:H24"/>
     <mergeCell ref="N32:O32"/>
     <mergeCell ref="Q32:R32"/>
     <mergeCell ref="N33:O33"/>
@@ -29569,50 +29613,6 @@
     <mergeCell ref="N30:O30"/>
     <mergeCell ref="Q30:R30"/>
     <mergeCell ref="N31:O31"/>
-    <mergeCell ref="Q31:R31"/>
-    <mergeCell ref="F19:AJ19"/>
-    <mergeCell ref="F25:K25"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="AP2:AP4"/>
-    <mergeCell ref="F2:AJ2"/>
-    <mergeCell ref="AL2:AL4"/>
-    <mergeCell ref="AM2:AM4"/>
-    <mergeCell ref="AN2:AN4"/>
-    <mergeCell ref="AO2:AO4"/>
-    <mergeCell ref="B3:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="J31:K31"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F5:AJ10">
@@ -29693,19 +29693,19 @@
       <c r="AH2" s="162"/>
       <c r="AI2" s="162"/>
       <c r="AJ2" s="162"/>
-      <c r="AL2" s="105" t="s">
+      <c r="AL2" s="114" t="s">
         <v>80</v>
       </c>
-      <c r="AM2" s="105" t="s">
+      <c r="AM2" s="114" t="s">
         <v>81</v>
       </c>
-      <c r="AN2" s="105" t="s">
+      <c r="AN2" s="114" t="s">
         <v>82</v>
       </c>
-      <c r="AO2" s="105" t="s">
+      <c r="AO2" s="114" t="s">
         <v>83</v>
       </c>
-      <c r="AP2" s="105" t="s">
+      <c r="AP2" s="114" t="s">
         <v>84</v>
       </c>
     </row>
@@ -29806,11 +29806,11 @@
         <v>87</v>
       </c>
       <c r="AJ3" s="62"/>
-      <c r="AL3" s="106"/>
-      <c r="AM3" s="106"/>
-      <c r="AN3" s="106"/>
-      <c r="AO3" s="106"/>
-      <c r="AP3" s="106"/>
+      <c r="AL3" s="115"/>
+      <c r="AM3" s="115"/>
+      <c r="AN3" s="115"/>
+      <c r="AO3" s="115"/>
+      <c r="AP3" s="115"/>
     </row>
     <row r="4" spans="2:42" ht="19.5" customHeight="1" thickBot="1">
       <c r="B4" s="159"/>
@@ -29907,20 +29907,20 @@
         <v>30</v>
       </c>
       <c r="AJ4" s="61"/>
-      <c r="AL4" s="107"/>
-      <c r="AM4" s="107"/>
-      <c r="AN4" s="107"/>
-      <c r="AO4" s="107"/>
-      <c r="AP4" s="107"/>
+      <c r="AL4" s="116"/>
+      <c r="AM4" s="116"/>
+      <c r="AN4" s="116"/>
+      <c r="AO4" s="116"/>
+      <c r="AP4" s="116"/>
     </row>
     <row r="5" spans="2:42" ht="18.75">
       <c r="B5" s="47">
         <v>1</v>
       </c>
-      <c r="C5" s="145" t="s">
+      <c r="C5" s="144" t="s">
         <v>115</v>
       </c>
-      <c r="D5" s="146"/>
+      <c r="D5" s="145"/>
       <c r="F5" s="72" t="s">
         <v>101</v>
       </c>
@@ -30037,10 +30037,10 @@
       <c r="B6" s="45">
         <v>2</v>
       </c>
-      <c r="C6" s="144" t="s">
+      <c r="C6" s="142" t="s">
         <v>117</v>
       </c>
-      <c r="D6" s="150"/>
+      <c r="D6" s="143"/>
       <c r="F6" s="74" t="s">
         <v>102</v>
       </c>
@@ -30157,10 +30157,10 @@
       <c r="B7" s="45">
         <v>3</v>
       </c>
-      <c r="C7" s="144" t="s">
+      <c r="C7" s="142" t="s">
         <v>118</v>
       </c>
-      <c r="D7" s="150"/>
+      <c r="D7" s="143"/>
       <c r="F7" s="75" t="s">
         <v>95</v>
       </c>
@@ -30277,10 +30277,10 @@
       <c r="B8" s="45">
         <v>4</v>
       </c>
-      <c r="C8" s="144" t="s">
+      <c r="C8" s="142" t="s">
         <v>119</v>
       </c>
-      <c r="D8" s="150"/>
+      <c r="D8" s="143"/>
       <c r="F8" s="75" t="s">
         <v>98</v>
       </c>
@@ -30397,10 +30397,10 @@
       <c r="B9" s="45">
         <v>5</v>
       </c>
-      <c r="C9" s="144" t="s">
+      <c r="C9" s="142" t="s">
         <v>120</v>
       </c>
-      <c r="D9" s="150"/>
+      <c r="D9" s="143"/>
       <c r="F9" s="75" t="s">
         <v>96</v>
       </c>
@@ -30517,10 +30517,10 @@
       <c r="B10" s="45">
         <v>6</v>
       </c>
-      <c r="C10" s="144" t="s">
+      <c r="C10" s="142" t="s">
         <v>121</v>
       </c>
-      <c r="D10" s="150"/>
+      <c r="D10" s="143"/>
       <c r="F10" s="75" t="s">
         <v>96</v>
       </c>
@@ -30637,10 +30637,10 @@
       <c r="B11" s="45">
         <v>7</v>
       </c>
-      <c r="C11" s="144" t="s">
+      <c r="C11" s="142" t="s">
         <v>122</v>
       </c>
-      <c r="D11" s="150"/>
+      <c r="D11" s="143"/>
       <c r="F11" s="75" t="s">
         <v>101</v>
       </c>
@@ -30757,10 +30757,10 @@
       <c r="B12" s="45">
         <v>8</v>
       </c>
-      <c r="C12" s="144" t="s">
+      <c r="C12" s="142" t="s">
         <v>123</v>
       </c>
-      <c r="D12" s="150"/>
+      <c r="D12" s="143"/>
       <c r="F12" s="75" t="s">
         <v>102</v>
       </c>
@@ -30877,10 +30877,10 @@
       <c r="B13" s="45">
         <v>9</v>
       </c>
-      <c r="C13" s="144" t="s">
+      <c r="C13" s="142" t="s">
         <v>124</v>
       </c>
-      <c r="D13" s="150"/>
+      <c r="D13" s="143"/>
       <c r="F13" s="74" t="s">
         <v>95</v>
       </c>
@@ -30997,10 +30997,10 @@
       <c r="B14" s="45">
         <v>10</v>
       </c>
-      <c r="C14" s="144" t="s">
+      <c r="C14" s="142" t="s">
         <v>125</v>
       </c>
-      <c r="D14" s="150"/>
+      <c r="D14" s="143"/>
       <c r="F14" s="75" t="s">
         <v>116</v>
       </c>
@@ -31117,10 +31117,10 @@
       <c r="B15" s="45">
         <v>11</v>
       </c>
-      <c r="C15" s="97" t="s">
+      <c r="C15" s="112" t="s">
         <v>126</v>
       </c>
-      <c r="D15" s="147"/>
+      <c r="D15" s="146"/>
       <c r="F15" s="75" t="s">
         <v>116</v>
       </c>
@@ -31237,10 +31237,10 @@
       <c r="B16" s="45">
         <v>12</v>
       </c>
-      <c r="C16" s="97" t="s">
+      <c r="C16" s="112" t="s">
         <v>127</v>
       </c>
-      <c r="D16" s="147"/>
+      <c r="D16" s="146"/>
       <c r="F16" s="75" t="s">
         <v>96</v>
       </c>
@@ -31357,10 +31357,10 @@
       <c r="B17" s="45">
         <v>13</v>
       </c>
-      <c r="C17" s="97" t="s">
+      <c r="C17" s="112" t="s">
         <v>128</v>
       </c>
-      <c r="D17" s="147"/>
+      <c r="D17" s="146"/>
       <c r="F17" s="75" t="s">
         <v>96</v>
       </c>
@@ -31477,10 +31477,10 @@
       <c r="B18" s="45">
         <v>14</v>
       </c>
-      <c r="C18" s="97" t="s">
+      <c r="C18" s="112" t="s">
         <v>129</v>
       </c>
-      <c r="D18" s="147"/>
+      <c r="D18" s="146"/>
       <c r="F18" s="75" t="s">
         <v>101</v>
       </c>
@@ -31597,10 +31597,10 @@
       <c r="B19" s="46">
         <v>15</v>
       </c>
-      <c r="C19" s="148" t="s">
+      <c r="C19" s="147" t="s">
         <v>130</v>
       </c>
-      <c r="D19" s="149"/>
+      <c r="D19" s="148"/>
       <c r="F19" s="74" t="s">
         <v>96</v>
       </c>
@@ -31748,10 +31748,10 @@
       <c r="AI20" s="18"/>
     </row>
     <row r="21" spans="2:42" ht="18.75">
-      <c r="C21" s="141" t="s">
+      <c r="C21" s="153" t="s">
         <v>188</v>
       </c>
-      <c r="D21" s="141"/>
+      <c r="D21" s="153"/>
       <c r="E21" s="34"/>
       <c r="F21" s="35">
         <f t="shared" ref="F21:AJ21" si="5">COUNTIF(F$5:F$19,"M*")</f>
@@ -31879,10 +31879,10 @@
       </c>
     </row>
     <row r="22" spans="2:42" ht="18.75">
-      <c r="C22" s="141" t="s">
+      <c r="C22" s="153" t="s">
         <v>189</v>
       </c>
-      <c r="D22" s="141"/>
+      <c r="D22" s="153"/>
       <c r="E22" s="34"/>
       <c r="F22" s="35">
         <f t="shared" ref="F22:AJ22" si="6">COUNTIF(F$5:F$19,"A*")</f>
@@ -32010,10 +32010,10 @@
       </c>
     </row>
     <row r="23" spans="2:42" ht="18.75">
-      <c r="C23" s="141" t="s">
+      <c r="C23" s="153" t="s">
         <v>77</v>
       </c>
-      <c r="D23" s="141"/>
+      <c r="D23" s="153"/>
       <c r="E23" s="34"/>
       <c r="F23" s="35">
         <f t="shared" ref="F23:AJ23" si="7">COUNTIF(F$5:F$19,"N*")</f>
@@ -32141,10 +32141,10 @@
       </c>
     </row>
     <row r="24" spans="2:42" ht="18.75">
-      <c r="C24" s="141" t="s">
+      <c r="C24" s="153" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="141"/>
+      <c r="D24" s="153"/>
       <c r="E24" s="34"/>
       <c r="F24" s="35">
         <f t="shared" ref="F24:AJ24" si="8">COUNTIF(F$5:F$19,"O*")</f>
@@ -32272,10 +32272,10 @@
       </c>
     </row>
     <row r="25" spans="2:42" ht="18.75">
-      <c r="C25" s="101" t="s">
+      <c r="C25" s="109" t="s">
         <v>191</v>
       </c>
-      <c r="D25" s="102"/>
+      <c r="D25" s="110"/>
       <c r="E25" s="34"/>
       <c r="F25" s="35">
         <f t="shared" ref="F25:AJ25" si="9">COUNTIF(F$5:F$19,"ST*")</f>
@@ -32403,10 +32403,10 @@
       </c>
     </row>
     <row r="26" spans="2:42" ht="18.75">
-      <c r="C26" s="140" t="s">
+      <c r="C26" s="152" t="s">
         <v>192</v>
       </c>
-      <c r="D26" s="140"/>
+      <c r="D26" s="152"/>
       <c r="E26" s="36"/>
       <c r="F26" s="37">
         <f>F28-F29</f>
@@ -32534,43 +32534,43 @@
       <c r="C27" s="38"/>
       <c r="D27" s="38"/>
       <c r="E27" s="34"/>
-      <c r="F27" s="114"/>
-      <c r="G27" s="114"/>
-      <c r="H27" s="114"/>
-      <c r="I27" s="114"/>
-      <c r="J27" s="114"/>
-      <c r="K27" s="114"/>
-      <c r="L27" s="114"/>
-      <c r="M27" s="114"/>
-      <c r="N27" s="114"/>
-      <c r="O27" s="114"/>
-      <c r="P27" s="114"/>
-      <c r="Q27" s="114"/>
-      <c r="R27" s="114"/>
-      <c r="S27" s="114"/>
-      <c r="T27" s="114"/>
-      <c r="U27" s="114"/>
-      <c r="V27" s="114"/>
-      <c r="W27" s="114"/>
-      <c r="X27" s="114"/>
-      <c r="Y27" s="114"/>
-      <c r="Z27" s="114"/>
-      <c r="AA27" s="114"/>
-      <c r="AB27" s="114"/>
-      <c r="AC27" s="114"/>
-      <c r="AD27" s="114"/>
-      <c r="AE27" s="114"/>
-      <c r="AF27" s="114"/>
-      <c r="AG27" s="114"/>
-      <c r="AH27" s="114"/>
-      <c r="AI27" s="114"/>
-      <c r="AJ27" s="114"/>
+      <c r="F27" s="108"/>
+      <c r="G27" s="108"/>
+      <c r="H27" s="108"/>
+      <c r="I27" s="108"/>
+      <c r="J27" s="108"/>
+      <c r="K27" s="108"/>
+      <c r="L27" s="108"/>
+      <c r="M27" s="108"/>
+      <c r="N27" s="108"/>
+      <c r="O27" s="108"/>
+      <c r="P27" s="108"/>
+      <c r="Q27" s="108"/>
+      <c r="R27" s="108"/>
+      <c r="S27" s="108"/>
+      <c r="T27" s="108"/>
+      <c r="U27" s="108"/>
+      <c r="V27" s="108"/>
+      <c r="W27" s="108"/>
+      <c r="X27" s="108"/>
+      <c r="Y27" s="108"/>
+      <c r="Z27" s="108"/>
+      <c r="AA27" s="108"/>
+      <c r="AB27" s="108"/>
+      <c r="AC27" s="108"/>
+      <c r="AD27" s="108"/>
+      <c r="AE27" s="108"/>
+      <c r="AF27" s="108"/>
+      <c r="AG27" s="108"/>
+      <c r="AH27" s="108"/>
+      <c r="AI27" s="108"/>
+      <c r="AJ27" s="108"/>
     </row>
     <row r="28" spans="2:42" ht="18.75">
-      <c r="C28" s="141" t="s">
+      <c r="C28" s="153" t="s">
         <v>193</v>
       </c>
-      <c r="D28" s="141"/>
+      <c r="D28" s="153"/>
       <c r="E28" s="34"/>
       <c r="F28" s="39">
         <f>SUM(F21:F23)</f>
@@ -32697,10 +32697,10 @@
       </c>
     </row>
     <row r="29" spans="2:42" ht="18.75">
-      <c r="C29" s="141" t="s">
+      <c r="C29" s="153" t="s">
         <v>194</v>
       </c>
-      <c r="D29" s="141"/>
+      <c r="D29" s="153"/>
       <c r="E29" s="34"/>
       <c r="F29" s="35">
         <v>6</v>
@@ -32797,10 +32797,10 @@
       </c>
     </row>
     <row r="30" spans="2:42" ht="18.75">
-      <c r="C30" s="141" t="s">
+      <c r="C30" s="153" t="s">
         <v>195</v>
       </c>
-      <c r="D30" s="141"/>
+      <c r="D30" s="153"/>
       <c r="E30" s="34"/>
       <c r="F30" s="35">
         <f>SUM(F21,F22,F23,F24,F25)</f>
@@ -32928,87 +32928,87 @@
     </row>
     <row r="32" spans="2:42" ht="9.75" customHeight="1" thickBot="1"/>
     <row r="33" spans="6:11" ht="16.5" thickBot="1">
-      <c r="F33" s="118" t="s">
+      <c r="F33" s="95" t="s">
         <v>196</v>
       </c>
-      <c r="G33" s="119"/>
-      <c r="H33" s="119"/>
-      <c r="I33" s="119"/>
-      <c r="J33" s="119"/>
-      <c r="K33" s="120"/>
+      <c r="G33" s="96"/>
+      <c r="H33" s="96"/>
+      <c r="I33" s="96"/>
+      <c r="J33" s="96"/>
+      <c r="K33" s="97"/>
     </row>
     <row r="34" spans="6:11">
       <c r="F34" s="80" t="s">
         <v>197</v>
       </c>
-      <c r="G34" s="128" t="s">
+      <c r="G34" s="106" t="s">
         <v>198</v>
       </c>
-      <c r="H34" s="128"/>
+      <c r="H34" s="106"/>
       <c r="I34" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="J34" s="121" t="s">
+      <c r="J34" s="98" t="s">
         <v>199</v>
       </c>
-      <c r="K34" s="122"/>
+      <c r="K34" s="99"/>
     </row>
     <row r="35" spans="6:11">
       <c r="F35" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="G35" s="129" t="s">
+      <c r="G35" s="107" t="s">
         <v>200</v>
       </c>
-      <c r="H35" s="129"/>
+      <c r="H35" s="107"/>
       <c r="I35" s="77" t="s">
         <v>201</v>
       </c>
-      <c r="J35" s="123" t="s">
+      <c r="J35" s="100" t="s">
         <v>202</v>
       </c>
-      <c r="K35" s="124"/>
+      <c r="K35" s="101"/>
     </row>
     <row r="36" spans="6:11">
       <c r="F36" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="G36" s="115" t="s">
+      <c r="G36" s="102" t="s">
         <v>203</v>
       </c>
-      <c r="H36" s="115"/>
+      <c r="H36" s="102"/>
       <c r="I36" s="78" t="s">
         <v>108</v>
       </c>
-      <c r="J36" s="115" t="s">
+      <c r="J36" s="102" t="s">
         <v>204</v>
       </c>
-      <c r="K36" s="125"/>
+      <c r="K36" s="103"/>
     </row>
     <row r="37" spans="6:11">
       <c r="F37" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="G37" s="116" t="s">
+      <c r="G37" s="111" t="s">
         <v>205</v>
       </c>
-      <c r="H37" s="116"/>
+      <c r="H37" s="111"/>
       <c r="I37" s="79" t="s">
         <v>206</v>
       </c>
-      <c r="J37" s="126" t="s">
+      <c r="J37" s="104" t="s">
         <v>207</v>
       </c>
-      <c r="K37" s="127"/>
+      <c r="K37" s="105"/>
     </row>
     <row r="38" spans="6:11">
       <c r="F38" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="G38" s="116" t="s">
+      <c r="G38" s="111" t="s">
         <v>208</v>
       </c>
-      <c r="H38" s="116"/>
+      <c r="H38" s="111"/>
       <c r="I38" s="20" t="s">
         <v>104</v>
       </c>
@@ -33021,10 +33021,10 @@
       <c r="F39" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="G39" s="117" t="s">
+      <c r="G39" s="92" t="s">
         <v>210</v>
       </c>
-      <c r="H39" s="117"/>
+      <c r="H39" s="92"/>
       <c r="I39" s="20" t="s">
         <v>114</v>
       </c>
@@ -33037,10 +33037,10 @@
       <c r="F40" s="82" t="s">
         <v>212</v>
       </c>
-      <c r="G40" s="92" t="s">
+      <c r="G40" s="123" t="s">
         <v>213</v>
       </c>
-      <c r="H40" s="92"/>
+      <c r="H40" s="123"/>
       <c r="I40" s="20" t="s">
         <v>131</v>
       </c>
@@ -33053,53 +33053,20 @@
       <c r="F41" s="55" t="s">
         <v>215</v>
       </c>
-      <c r="G41" s="95" t="s">
+      <c r="G41" s="124" t="s">
         <v>216</v>
       </c>
-      <c r="H41" s="95"/>
+      <c r="H41" s="124"/>
       <c r="I41" s="56" t="s">
         <v>167</v>
       </c>
-      <c r="J41" s="95" t="s">
+      <c r="J41" s="124" t="s">
         <v>217</v>
       </c>
-      <c r="K41" s="96"/>
+      <c r="K41" s="125"/>
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="F33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="F27:AJ27"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C25:D25"/>
     <mergeCell ref="G41:H41"/>
     <mergeCell ref="J41:K41"/>
     <mergeCell ref="B3:D4"/>
@@ -33116,6 +33083,39 @@
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F27:AJ27"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="F33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="G37:H37"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F5:AJ19">
@@ -33163,61 +33163,61 @@
   <sheetData>
     <row r="1" spans="2:42" ht="16.5" thickBot="1"/>
     <row r="2" spans="2:42" ht="39" customHeight="1" thickBot="1">
-      <c r="F2" s="151" t="s">
+      <c r="F2" s="139" t="s">
         <v>218</v>
       </c>
-      <c r="G2" s="152"/>
-      <c r="H2" s="152"/>
-      <c r="I2" s="152"/>
-      <c r="J2" s="152"/>
-      <c r="K2" s="152"/>
-      <c r="L2" s="152"/>
-      <c r="M2" s="152"/>
-      <c r="N2" s="152"/>
-      <c r="O2" s="152"/>
-      <c r="P2" s="152"/>
-      <c r="Q2" s="152"/>
-      <c r="R2" s="152"/>
-      <c r="S2" s="152"/>
-      <c r="T2" s="152"/>
-      <c r="U2" s="152"/>
-      <c r="V2" s="152"/>
-      <c r="W2" s="152"/>
-      <c r="X2" s="152"/>
-      <c r="Y2" s="152"/>
-      <c r="Z2" s="152"/>
-      <c r="AA2" s="152"/>
-      <c r="AB2" s="152"/>
-      <c r="AC2" s="152"/>
-      <c r="AD2" s="152"/>
-      <c r="AE2" s="152"/>
-      <c r="AF2" s="152"/>
-      <c r="AG2" s="152"/>
-      <c r="AH2" s="152"/>
-      <c r="AI2" s="152"/>
-      <c r="AJ2" s="153"/>
-      <c r="AL2" s="105" t="s">
+      <c r="G2" s="140"/>
+      <c r="H2" s="140"/>
+      <c r="I2" s="140"/>
+      <c r="J2" s="140"/>
+      <c r="K2" s="140"/>
+      <c r="L2" s="140"/>
+      <c r="M2" s="140"/>
+      <c r="N2" s="140"/>
+      <c r="O2" s="140"/>
+      <c r="P2" s="140"/>
+      <c r="Q2" s="140"/>
+      <c r="R2" s="140"/>
+      <c r="S2" s="140"/>
+      <c r="T2" s="140"/>
+      <c r="U2" s="140"/>
+      <c r="V2" s="140"/>
+      <c r="W2" s="140"/>
+      <c r="X2" s="140"/>
+      <c r="Y2" s="140"/>
+      <c r="Z2" s="140"/>
+      <c r="AA2" s="140"/>
+      <c r="AB2" s="140"/>
+      <c r="AC2" s="140"/>
+      <c r="AD2" s="140"/>
+      <c r="AE2" s="140"/>
+      <c r="AF2" s="140"/>
+      <c r="AG2" s="140"/>
+      <c r="AH2" s="140"/>
+      <c r="AI2" s="140"/>
+      <c r="AJ2" s="141"/>
+      <c r="AL2" s="114" t="s">
         <v>80</v>
       </c>
-      <c r="AM2" s="105" t="s">
+      <c r="AM2" s="114" t="s">
         <v>81</v>
       </c>
-      <c r="AN2" s="105" t="s">
+      <c r="AN2" s="114" t="s">
         <v>82</v>
       </c>
-      <c r="AO2" s="105" t="s">
+      <c r="AO2" s="114" t="s">
         <v>83</v>
       </c>
-      <c r="AP2" s="105" t="s">
+      <c r="AP2" s="114" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="3" spans="2:42" ht="39.75" thickBot="1">
-      <c r="B3" s="113" t="s">
+      <c r="B3" s="122" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="113"/>
-      <c r="D3" s="113"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="122"/>
       <c r="F3" s="43" t="s">
         <v>86</v>
       </c>
@@ -33311,16 +33311,16 @@
       <c r="AJ3" s="43" t="s">
         <v>187</v>
       </c>
-      <c r="AL3" s="106"/>
-      <c r="AM3" s="106"/>
-      <c r="AN3" s="106"/>
-      <c r="AO3" s="106"/>
-      <c r="AP3" s="106"/>
+      <c r="AL3" s="115"/>
+      <c r="AM3" s="115"/>
+      <c r="AN3" s="115"/>
+      <c r="AO3" s="115"/>
+      <c r="AP3" s="115"/>
     </row>
     <row r="4" spans="2:42" ht="19.5" customHeight="1" thickBot="1">
-      <c r="B4" s="113"/>
-      <c r="C4" s="113"/>
-      <c r="D4" s="113"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
       <c r="F4" s="40">
         <v>1</v>
       </c>
@@ -33414,20 +33414,20 @@
       <c r="AJ4" s="58" t="s">
         <v>187</v>
       </c>
-      <c r="AL4" s="107"/>
-      <c r="AM4" s="107"/>
-      <c r="AN4" s="107"/>
-      <c r="AO4" s="107"/>
-      <c r="AP4" s="107"/>
+      <c r="AL4" s="116"/>
+      <c r="AM4" s="116"/>
+      <c r="AN4" s="116"/>
+      <c r="AO4" s="116"/>
+      <c r="AP4" s="116"/>
     </row>
     <row r="5" spans="2:42" ht="18.75">
       <c r="B5" s="35">
         <v>1</v>
       </c>
-      <c r="C5" s="144" t="s">
+      <c r="C5" s="142" t="s">
         <v>132</v>
       </c>
-      <c r="D5" s="144"/>
+      <c r="D5" s="142"/>
       <c r="F5" s="73" t="s">
         <v>102</v>
       </c>
@@ -33544,10 +33544,10 @@
       <c r="B6" s="35">
         <v>2</v>
       </c>
-      <c r="C6" s="144" t="s">
+      <c r="C6" s="142" t="s">
         <v>133</v>
       </c>
-      <c r="D6" s="144"/>
+      <c r="D6" s="142"/>
       <c r="F6" s="75" t="s">
         <v>102</v>
       </c>
@@ -33664,10 +33664,10 @@
       <c r="B7" s="35">
         <v>3</v>
       </c>
-      <c r="C7" s="144" t="s">
+      <c r="C7" s="142" t="s">
         <v>134</v>
       </c>
-      <c r="D7" s="144"/>
+      <c r="D7" s="142"/>
       <c r="F7" s="75" t="s">
         <v>98</v>
       </c>
@@ -33784,10 +33784,10 @@
       <c r="B8" s="35">
         <v>4</v>
       </c>
-      <c r="C8" s="144" t="s">
+      <c r="C8" s="142" t="s">
         <v>136</v>
       </c>
-      <c r="D8" s="144"/>
+      <c r="D8" s="142"/>
       <c r="F8" s="75" t="s">
         <v>95</v>
       </c>
@@ -33904,10 +33904,10 @@
       <c r="B9" s="35">
         <v>5</v>
       </c>
-      <c r="C9" s="144" t="s">
+      <c r="C9" s="142" t="s">
         <v>137</v>
       </c>
-      <c r="D9" s="144"/>
+      <c r="D9" s="142"/>
       <c r="F9" s="75" t="s">
         <v>96</v>
       </c>
@@ -34024,10 +34024,10 @@
       <c r="B10" s="35">
         <v>6</v>
       </c>
-      <c r="C10" s="144" t="s">
+      <c r="C10" s="142" t="s">
         <v>138</v>
       </c>
-      <c r="D10" s="144"/>
+      <c r="D10" s="142"/>
       <c r="F10" s="75" t="s">
         <v>96</v>
       </c>
@@ -34144,10 +34144,10 @@
       <c r="B11" s="35">
         <v>7</v>
       </c>
-      <c r="C11" s="144" t="s">
+      <c r="C11" s="142" t="s">
         <v>139</v>
       </c>
-      <c r="D11" s="144"/>
+      <c r="D11" s="142"/>
       <c r="F11" s="76" t="s">
         <v>95</v>
       </c>
@@ -34264,10 +34264,10 @@
       <c r="B12" s="35">
         <v>8</v>
       </c>
-      <c r="C12" s="144" t="s">
+      <c r="C12" s="142" t="s">
         <v>140</v>
       </c>
-      <c r="D12" s="144"/>
+      <c r="D12" s="142"/>
       <c r="F12" s="75" t="s">
         <v>101</v>
       </c>
@@ -34384,10 +34384,10 @@
       <c r="B13" s="35">
         <v>9</v>
       </c>
-      <c r="C13" s="144" t="s">
+      <c r="C13" s="142" t="s">
         <v>220</v>
       </c>
-      <c r="D13" s="144"/>
+      <c r="D13" s="142"/>
       <c r="F13" s="75" t="s">
         <v>102</v>
       </c>
@@ -34504,10 +34504,10 @@
       <c r="B14" s="35">
         <v>10</v>
       </c>
-      <c r="C14" s="144" t="s">
+      <c r="C14" s="142" t="s">
         <v>142</v>
       </c>
-      <c r="D14" s="144"/>
+      <c r="D14" s="142"/>
       <c r="F14" s="75" t="s">
         <v>95</v>
       </c>
@@ -34624,10 +34624,10 @@
       <c r="B15" s="35">
         <v>11</v>
       </c>
-      <c r="C15" s="144" t="s">
+      <c r="C15" s="142" t="s">
         <v>143</v>
       </c>
-      <c r="D15" s="144"/>
+      <c r="D15" s="142"/>
       <c r="F15" s="75" t="s">
         <v>116</v>
       </c>
@@ -34744,10 +34744,10 @@
       <c r="B16" s="35">
         <v>12</v>
       </c>
-      <c r="C16" s="144" t="s">
+      <c r="C16" s="142" t="s">
         <v>144</v>
       </c>
-      <c r="D16" s="144"/>
+      <c r="D16" s="142"/>
       <c r="F16" s="75" t="s">
         <v>96</v>
       </c>
@@ -34864,10 +34864,10 @@
       <c r="B17" s="35">
         <v>13</v>
       </c>
-      <c r="C17" s="144" t="s">
+      <c r="C17" s="142" t="s">
         <v>145</v>
       </c>
-      <c r="D17" s="144"/>
+      <c r="D17" s="142"/>
       <c r="F17" s="75" t="s">
         <v>96</v>
       </c>
@@ -34984,10 +34984,10 @@
       <c r="B18" s="35">
         <v>14</v>
       </c>
-      <c r="C18" s="144" t="s">
+      <c r="C18" s="142" t="s">
         <v>146</v>
       </c>
-      <c r="D18" s="144"/>
+      <c r="D18" s="142"/>
       <c r="F18" s="76" t="s">
         <v>101</v>
       </c>
@@ -35104,10 +35104,10 @@
       <c r="B19" s="35">
         <v>15</v>
       </c>
-      <c r="C19" s="144" t="s">
+      <c r="C19" s="142" t="s">
         <v>147</v>
       </c>
-      <c r="D19" s="144"/>
+      <c r="D19" s="142"/>
       <c r="F19" s="75" t="s">
         <v>102</v>
       </c>
@@ -35224,10 +35224,10 @@
       <c r="B20" s="35">
         <v>16</v>
       </c>
-      <c r="C20" s="144" t="s">
+      <c r="C20" s="142" t="s">
         <v>148</v>
       </c>
-      <c r="D20" s="144"/>
+      <c r="D20" s="142"/>
       <c r="F20" s="75" t="s">
         <v>102</v>
       </c>
@@ -35344,10 +35344,10 @@
       <c r="B21" s="35">
         <v>17</v>
       </c>
-      <c r="C21" s="144" t="s">
+      <c r="C21" s="142" t="s">
         <v>149</v>
       </c>
-      <c r="D21" s="144"/>
+      <c r="D21" s="142"/>
       <c r="F21" s="75" t="s">
         <v>116</v>
       </c>
@@ -35464,10 +35464,10 @@
       <c r="B22" s="35">
         <v>18</v>
       </c>
-      <c r="C22" s="144" t="s">
+      <c r="C22" s="142" t="s">
         <v>150</v>
       </c>
-      <c r="D22" s="144"/>
+      <c r="D22" s="142"/>
       <c r="F22" s="75" t="s">
         <v>116</v>
       </c>
@@ -35584,10 +35584,10 @@
       <c r="B23" s="35">
         <v>19</v>
       </c>
-      <c r="C23" s="144" t="s">
+      <c r="C23" s="142" t="s">
         <v>151</v>
       </c>
-      <c r="D23" s="144"/>
+      <c r="D23" s="142"/>
       <c r="F23" s="75" t="s">
         <v>96</v>
       </c>
@@ -35704,10 +35704,10 @@
       <c r="B24" s="35">
         <v>20</v>
       </c>
-      <c r="C24" s="144" t="s">
+      <c r="C24" s="142" t="s">
         <v>152</v>
       </c>
-      <c r="D24" s="144"/>
+      <c r="D24" s="142"/>
       <c r="F24" s="75" t="s">
         <v>96</v>
       </c>
@@ -35824,10 +35824,10 @@
       <c r="B25" s="35">
         <v>21</v>
       </c>
-      <c r="C25" s="144" t="s">
+      <c r="C25" s="142" t="s">
         <v>153</v>
       </c>
-      <c r="D25" s="144"/>
+      <c r="D25" s="142"/>
       <c r="F25" s="76" t="s">
         <v>95</v>
       </c>
@@ -35944,10 +35944,10 @@
       <c r="B26" s="35">
         <v>22</v>
       </c>
-      <c r="C26" s="144" t="s">
+      <c r="C26" s="142" t="s">
         <v>154</v>
       </c>
-      <c r="D26" s="144"/>
+      <c r="D26" s="142"/>
       <c r="F26" s="75" t="s">
         <v>101</v>
       </c>
@@ -36064,10 +36064,10 @@
       <c r="B27" s="35">
         <v>23</v>
       </c>
-      <c r="C27" s="144" t="s">
+      <c r="C27" s="142" t="s">
         <v>155</v>
       </c>
-      <c r="D27" s="144"/>
+      <c r="D27" s="142"/>
       <c r="F27" s="75" t="s">
         <v>102</v>
       </c>
@@ -36184,10 +36184,10 @@
       <c r="B28" s="35">
         <v>24</v>
       </c>
-      <c r="C28" s="144" t="s">
+      <c r="C28" s="142" t="s">
         <v>156</v>
       </c>
-      <c r="D28" s="144"/>
+      <c r="D28" s="142"/>
       <c r="F28" s="75" t="s">
         <v>116</v>
       </c>
@@ -36304,10 +36304,10 @@
       <c r="B29" s="35">
         <v>25</v>
       </c>
-      <c r="C29" s="144" t="s">
+      <c r="C29" s="142" t="s">
         <v>157</v>
       </c>
-      <c r="D29" s="144"/>
+      <c r="D29" s="142"/>
       <c r="F29" s="75" t="s">
         <v>116</v>
       </c>
@@ -36424,10 +36424,10 @@
       <c r="B30" s="35">
         <v>26</v>
       </c>
-      <c r="C30" s="97" t="s">
+      <c r="C30" s="112" t="s">
         <v>158</v>
       </c>
-      <c r="D30" s="98"/>
+      <c r="D30" s="113"/>
       <c r="F30" s="75" t="s">
         <v>96</v>
       </c>
@@ -36544,10 +36544,10 @@
       <c r="B31" s="35">
         <v>27</v>
       </c>
-      <c r="C31" s="97" t="s">
+      <c r="C31" s="112" t="s">
         <v>159</v>
       </c>
-      <c r="D31" s="98"/>
+      <c r="D31" s="113"/>
       <c r="F31" s="75" t="s">
         <v>96</v>
       </c>
@@ -36664,10 +36664,10 @@
       <c r="B32" s="35">
         <v>28</v>
       </c>
-      <c r="C32" s="97" t="s">
+      <c r="C32" s="112" t="s">
         <v>160</v>
       </c>
-      <c r="D32" s="98"/>
+      <c r="D32" s="113"/>
       <c r="F32" s="76" t="s">
         <v>101</v>
       </c>
@@ -36784,10 +36784,10 @@
       <c r="B33" s="35">
         <v>29</v>
       </c>
-      <c r="C33" s="97" t="s">
+      <c r="C33" s="112" t="s">
         <v>161</v>
       </c>
-      <c r="D33" s="98"/>
+      <c r="D33" s="113"/>
       <c r="F33" s="75" t="s">
         <v>95</v>
       </c>
@@ -36904,10 +36904,10 @@
       <c r="B34" s="35">
         <v>30</v>
       </c>
-      <c r="C34" s="139" t="s">
+      <c r="C34" s="149" t="s">
         <v>162</v>
       </c>
-      <c r="D34" s="139"/>
+      <c r="D34" s="149"/>
       <c r="F34" s="75" t="s">
         <v>101</v>
       </c>
@@ -37024,10 +37024,10 @@
       <c r="B35" s="35">
         <v>31</v>
       </c>
-      <c r="C35" s="139" t="s">
+      <c r="C35" s="149" t="s">
         <v>163</v>
       </c>
-      <c r="D35" s="139"/>
+      <c r="D35" s="149"/>
       <c r="F35" s="75" t="s">
         <v>96</v>
       </c>
@@ -37144,10 +37144,10 @@
       <c r="B36" s="35">
         <v>32</v>
       </c>
-      <c r="C36" s="142" t="s">
+      <c r="C36" s="150" t="s">
         <v>164</v>
       </c>
-      <c r="D36" s="143"/>
+      <c r="D36" s="151"/>
       <c r="F36" s="75" t="s">
         <v>95</v>
       </c>
@@ -37264,10 +37264,10 @@
       <c r="B37" s="35">
         <v>33</v>
       </c>
-      <c r="C37" s="139" t="s">
+      <c r="C37" s="149" t="s">
         <v>165</v>
       </c>
-      <c r="D37" s="139"/>
+      <c r="D37" s="149"/>
       <c r="F37" s="88" t="s">
         <v>166</v>
       </c>
@@ -37415,10 +37415,10 @@
       <c r="AI38" s="18"/>
     </row>
     <row r="39" spans="2:42" ht="18.75">
-      <c r="C39" s="141" t="s">
+      <c r="C39" s="153" t="s">
         <v>188</v>
       </c>
-      <c r="D39" s="141"/>
+      <c r="D39" s="153"/>
       <c r="E39" s="34"/>
       <c r="F39" s="35">
         <f t="shared" ref="F39:AJ39" si="5">COUNTIF(F$5:F$36,"M*")</f>
@@ -37546,10 +37546,10 @@
       </c>
     </row>
     <row r="40" spans="2:42" ht="18.75">
-      <c r="C40" s="141" t="s">
+      <c r="C40" s="153" t="s">
         <v>189</v>
       </c>
-      <c r="D40" s="141"/>
+      <c r="D40" s="153"/>
       <c r="E40" s="34"/>
       <c r="F40" s="35">
         <f t="shared" ref="F40:AJ40" si="6">COUNTIF(F$5:F$36,"A*")</f>
@@ -37677,10 +37677,10 @@
       </c>
     </row>
     <row r="41" spans="2:42" ht="18.75">
-      <c r="C41" s="141" t="s">
+      <c r="C41" s="153" t="s">
         <v>77</v>
       </c>
-      <c r="D41" s="141"/>
+      <c r="D41" s="153"/>
       <c r="E41" s="34"/>
       <c r="F41" s="35">
         <f t="shared" ref="F41:AJ41" si="7">COUNTIF(F$5:F$36,"N*")</f>
@@ -37808,10 +37808,10 @@
       </c>
     </row>
     <row r="42" spans="2:42" ht="18.75">
-      <c r="C42" s="141" t="s">
+      <c r="C42" s="153" t="s">
         <v>78</v>
       </c>
-      <c r="D42" s="141"/>
+      <c r="D42" s="153"/>
       <c r="E42" s="34"/>
       <c r="F42" s="35">
         <f t="shared" ref="F42:AJ42" si="8">COUNTIF(F$5:F$37,"O*")</f>
@@ -37939,10 +37939,10 @@
       </c>
     </row>
     <row r="43" spans="2:42" ht="18.75">
-      <c r="C43" s="101" t="s">
+      <c r="C43" s="109" t="s">
         <v>190</v>
       </c>
-      <c r="D43" s="102"/>
+      <c r="D43" s="110"/>
       <c r="E43" s="34"/>
       <c r="F43" s="35">
         <f t="shared" ref="F43:AJ43" si="9">COUNTIF(F$5:F$37,"TR*")</f>
@@ -38070,10 +38070,10 @@
       </c>
     </row>
     <row r="44" spans="2:42" ht="18.75">
-      <c r="C44" s="101" t="s">
+      <c r="C44" s="109" t="s">
         <v>191</v>
       </c>
-      <c r="D44" s="102"/>
+      <c r="D44" s="110"/>
       <c r="E44" s="34"/>
       <c r="F44" s="35">
         <f t="shared" ref="F44:AJ44" si="10">COUNTIF(F$5:F$36,"ST*")</f>
@@ -38201,10 +38201,10 @@
       </c>
     </row>
     <row r="45" spans="2:42" ht="18.75">
-      <c r="C45" s="140" t="s">
+      <c r="C45" s="152" t="s">
         <v>192</v>
       </c>
-      <c r="D45" s="140"/>
+      <c r="D45" s="152"/>
       <c r="E45" s="36"/>
       <c r="F45" s="37">
         <f>F47-F48</f>
@@ -38335,43 +38335,43 @@
       <c r="C46" s="38"/>
       <c r="D46" s="38"/>
       <c r="E46" s="34"/>
-      <c r="F46" s="114"/>
-      <c r="G46" s="114"/>
-      <c r="H46" s="114"/>
-      <c r="I46" s="114"/>
-      <c r="J46" s="114"/>
-      <c r="K46" s="114"/>
-      <c r="L46" s="114"/>
-      <c r="M46" s="114"/>
-      <c r="N46" s="114"/>
-      <c r="O46" s="114"/>
-      <c r="P46" s="114"/>
-      <c r="Q46" s="114"/>
-      <c r="R46" s="114"/>
-      <c r="S46" s="114"/>
-      <c r="T46" s="114"/>
-      <c r="U46" s="114"/>
-      <c r="V46" s="114"/>
-      <c r="W46" s="114"/>
-      <c r="X46" s="114"/>
-      <c r="Y46" s="114"/>
-      <c r="Z46" s="114"/>
-      <c r="AA46" s="114"/>
-      <c r="AB46" s="114"/>
-      <c r="AC46" s="114"/>
-      <c r="AD46" s="114"/>
-      <c r="AE46" s="114"/>
-      <c r="AF46" s="114"/>
-      <c r="AG46" s="114"/>
-      <c r="AH46" s="114"/>
-      <c r="AI46" s="114"/>
-      <c r="AJ46" s="114"/>
+      <c r="F46" s="108"/>
+      <c r="G46" s="108"/>
+      <c r="H46" s="108"/>
+      <c r="I46" s="108"/>
+      <c r="J46" s="108"/>
+      <c r="K46" s="108"/>
+      <c r="L46" s="108"/>
+      <c r="M46" s="108"/>
+      <c r="N46" s="108"/>
+      <c r="O46" s="108"/>
+      <c r="P46" s="108"/>
+      <c r="Q46" s="108"/>
+      <c r="R46" s="108"/>
+      <c r="S46" s="108"/>
+      <c r="T46" s="108"/>
+      <c r="U46" s="108"/>
+      <c r="V46" s="108"/>
+      <c r="W46" s="108"/>
+      <c r="X46" s="108"/>
+      <c r="Y46" s="108"/>
+      <c r="Z46" s="108"/>
+      <c r="AA46" s="108"/>
+      <c r="AB46" s="108"/>
+      <c r="AC46" s="108"/>
+      <c r="AD46" s="108"/>
+      <c r="AE46" s="108"/>
+      <c r="AF46" s="108"/>
+      <c r="AG46" s="108"/>
+      <c r="AH46" s="108"/>
+      <c r="AI46" s="108"/>
+      <c r="AJ46" s="108"/>
     </row>
     <row r="47" spans="2:42" ht="19.5" thickBot="1">
-      <c r="C47" s="141" t="s">
+      <c r="C47" s="153" t="s">
         <v>193</v>
       </c>
-      <c r="D47" s="141"/>
+      <c r="D47" s="153"/>
       <c r="E47" s="34"/>
       <c r="F47" s="39">
         <f>SUM(F39:F41)</f>
@@ -38498,10 +38498,10 @@
       </c>
     </row>
     <row r="48" spans="2:42" ht="18.75">
-      <c r="C48" s="141" t="s">
+      <c r="C48" s="153" t="s">
         <v>194</v>
       </c>
-      <c r="D48" s="141"/>
+      <c r="D48" s="153"/>
       <c r="E48" s="34"/>
       <c r="F48" s="35">
         <v>18</v>
@@ -38598,10 +38598,10 @@
       </c>
     </row>
     <row r="49" spans="3:36" ht="19.5" thickBot="1">
-      <c r="C49" s="141" t="s">
+      <c r="C49" s="153" t="s">
         <v>195</v>
       </c>
-      <c r="D49" s="141"/>
+      <c r="D49" s="153"/>
       <c r="E49" s="34"/>
       <c r="F49" s="35">
         <f>SUM(F39,F40,F41,F42,F44)</f>
@@ -38729,87 +38729,87 @@
     </row>
     <row r="51" spans="3:36" ht="16.5" thickBot="1"/>
     <row r="52" spans="3:36" ht="16.5" thickBot="1">
-      <c r="F52" s="118" t="s">
+      <c r="F52" s="95" t="s">
         <v>196</v>
       </c>
-      <c r="G52" s="119"/>
-      <c r="H52" s="119"/>
-      <c r="I52" s="119"/>
-      <c r="J52" s="119"/>
-      <c r="K52" s="120"/>
+      <c r="G52" s="96"/>
+      <c r="H52" s="96"/>
+      <c r="I52" s="96"/>
+      <c r="J52" s="96"/>
+      <c r="K52" s="97"/>
     </row>
     <row r="53" spans="3:36">
       <c r="F53" s="80" t="s">
         <v>197</v>
       </c>
-      <c r="G53" s="128" t="s">
+      <c r="G53" s="106" t="s">
         <v>198</v>
       </c>
-      <c r="H53" s="128"/>
+      <c r="H53" s="106"/>
       <c r="I53" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="J53" s="121" t="s">
+      <c r="J53" s="98" t="s">
         <v>199</v>
       </c>
-      <c r="K53" s="122"/>
+      <c r="K53" s="99"/>
     </row>
     <row r="54" spans="3:36">
       <c r="F54" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="G54" s="129" t="s">
+      <c r="G54" s="107" t="s">
         <v>200</v>
       </c>
-      <c r="H54" s="129"/>
+      <c r="H54" s="107"/>
       <c r="I54" s="77" t="s">
         <v>201</v>
       </c>
-      <c r="J54" s="123" t="s">
+      <c r="J54" s="100" t="s">
         <v>202</v>
       </c>
-      <c r="K54" s="124"/>
+      <c r="K54" s="101"/>
     </row>
     <row r="55" spans="3:36">
       <c r="F55" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="G55" s="115" t="s">
+      <c r="G55" s="102" t="s">
         <v>203</v>
       </c>
-      <c r="H55" s="115"/>
+      <c r="H55" s="102"/>
       <c r="I55" s="78" t="s">
         <v>108</v>
       </c>
-      <c r="J55" s="115" t="s">
+      <c r="J55" s="102" t="s">
         <v>204</v>
       </c>
-      <c r="K55" s="125"/>
+      <c r="K55" s="103"/>
     </row>
     <row r="56" spans="3:36">
       <c r="F56" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="G56" s="116" t="s">
+      <c r="G56" s="111" t="s">
         <v>205</v>
       </c>
-      <c r="H56" s="116"/>
+      <c r="H56" s="111"/>
       <c r="I56" s="79" t="s">
         <v>206</v>
       </c>
-      <c r="J56" s="126" t="s">
+      <c r="J56" s="104" t="s">
         <v>207</v>
       </c>
-      <c r="K56" s="127"/>
+      <c r="K56" s="105"/>
     </row>
     <row r="57" spans="3:36">
       <c r="F57" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="G57" s="116" t="s">
+      <c r="G57" s="111" t="s">
         <v>208</v>
       </c>
-      <c r="H57" s="116"/>
+      <c r="H57" s="111"/>
       <c r="I57" s="20" t="s">
         <v>104</v>
       </c>
@@ -38822,10 +38822,10 @@
       <c r="F58" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="G58" s="117" t="s">
+      <c r="G58" s="92" t="s">
         <v>210</v>
       </c>
-      <c r="H58" s="117"/>
+      <c r="H58" s="92"/>
       <c r="I58" s="20" t="s">
         <v>114</v>
       </c>
@@ -38838,10 +38838,10 @@
       <c r="F59" s="82" t="s">
         <v>212</v>
       </c>
-      <c r="G59" s="92" t="s">
+      <c r="G59" s="123" t="s">
         <v>213</v>
       </c>
-      <c r="H59" s="92"/>
+      <c r="H59" s="123"/>
       <c r="I59" s="20" t="s">
         <v>131</v>
       </c>
@@ -38854,62 +38854,32 @@
       <c r="F60" s="55" t="s">
         <v>215</v>
       </c>
-      <c r="G60" s="95" t="s">
+      <c r="G60" s="124" t="s">
         <v>216</v>
       </c>
-      <c r="H60" s="95"/>
+      <c r="H60" s="124"/>
       <c r="I60" s="56" t="s">
         <v>167</v>
       </c>
-      <c r="J60" s="95" t="s">
+      <c r="J60" s="124" t="s">
         <v>217</v>
       </c>
-      <c r="K60" s="96"/>
+      <c r="K60" s="125"/>
     </row>
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="68">
-    <mergeCell ref="F52:K52"/>
-    <mergeCell ref="G56:H56"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="J53:K53"/>
-    <mergeCell ref="J54:K54"/>
-    <mergeCell ref="J55:K55"/>
-    <mergeCell ref="J56:K56"/>
-    <mergeCell ref="J57:K57"/>
-    <mergeCell ref="G53:H53"/>
-    <mergeCell ref="G54:H54"/>
-    <mergeCell ref="G55:H55"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="F46:AJ46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="G58:H58"/>
+    <mergeCell ref="J58:K58"/>
+    <mergeCell ref="G59:H59"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="G60:H60"/>
+    <mergeCell ref="J60:K60"/>
+    <mergeCell ref="AM2:AM4"/>
+    <mergeCell ref="AN2:AN4"/>
+    <mergeCell ref="AO2:AO4"/>
+    <mergeCell ref="AP2:AP4"/>
+    <mergeCell ref="B3:D4"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="F2:AJ2"/>
@@ -38926,17 +38896,47 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C17:D17"/>
-    <mergeCell ref="AM2:AM4"/>
-    <mergeCell ref="AN2:AN4"/>
-    <mergeCell ref="AO2:AO4"/>
-    <mergeCell ref="AP2:AP4"/>
-    <mergeCell ref="B3:D4"/>
-    <mergeCell ref="G58:H58"/>
-    <mergeCell ref="J58:K58"/>
-    <mergeCell ref="G59:H59"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="G60:H60"/>
-    <mergeCell ref="J60:K60"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="F46:AJ46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="F52:K52"/>
+    <mergeCell ref="G56:H56"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="J53:K53"/>
+    <mergeCell ref="J54:K54"/>
+    <mergeCell ref="J55:K55"/>
+    <mergeCell ref="J56:K56"/>
+    <mergeCell ref="J57:K57"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="G55:H55"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F5:AJ37">
@@ -38986,61 +38986,61 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:42" ht="39" customHeight="1" thickBot="1">
-      <c r="F2" s="108" t="s">
+      <c r="F2" s="117" t="s">
         <v>221</v>
       </c>
-      <c r="G2" s="109"/>
-      <c r="H2" s="109"/>
-      <c r="I2" s="109"/>
-      <c r="J2" s="109"/>
-      <c r="K2" s="109"/>
-      <c r="L2" s="109"/>
-      <c r="M2" s="109"/>
-      <c r="N2" s="109"/>
-      <c r="O2" s="109"/>
-      <c r="P2" s="109"/>
-      <c r="Q2" s="109"/>
-      <c r="R2" s="109"/>
-      <c r="S2" s="109"/>
-      <c r="T2" s="109"/>
-      <c r="U2" s="109"/>
-      <c r="V2" s="109"/>
-      <c r="W2" s="109"/>
-      <c r="X2" s="109"/>
-      <c r="Y2" s="109"/>
-      <c r="Z2" s="109"/>
-      <c r="AA2" s="109"/>
-      <c r="AB2" s="109"/>
-      <c r="AC2" s="109"/>
-      <c r="AD2" s="109"/>
-      <c r="AE2" s="109"/>
-      <c r="AF2" s="109"/>
-      <c r="AG2" s="109"/>
-      <c r="AH2" s="109"/>
-      <c r="AI2" s="109"/>
-      <c r="AJ2" s="110"/>
-      <c r="AL2" s="105" t="s">
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
+      <c r="N2" s="118"/>
+      <c r="O2" s="118"/>
+      <c r="P2" s="118"/>
+      <c r="Q2" s="118"/>
+      <c r="R2" s="118"/>
+      <c r="S2" s="118"/>
+      <c r="T2" s="118"/>
+      <c r="U2" s="118"/>
+      <c r="V2" s="118"/>
+      <c r="W2" s="118"/>
+      <c r="X2" s="118"/>
+      <c r="Y2" s="118"/>
+      <c r="Z2" s="118"/>
+      <c r="AA2" s="118"/>
+      <c r="AB2" s="118"/>
+      <c r="AC2" s="118"/>
+      <c r="AD2" s="118"/>
+      <c r="AE2" s="118"/>
+      <c r="AF2" s="118"/>
+      <c r="AG2" s="118"/>
+      <c r="AH2" s="118"/>
+      <c r="AI2" s="118"/>
+      <c r="AJ2" s="119"/>
+      <c r="AL2" s="114" t="s">
         <v>80</v>
       </c>
-      <c r="AM2" s="105" t="s">
+      <c r="AM2" s="114" t="s">
         <v>81</v>
       </c>
-      <c r="AN2" s="105" t="s">
+      <c r="AN2" s="114" t="s">
         <v>82</v>
       </c>
-      <c r="AO2" s="105" t="s">
+      <c r="AO2" s="114" t="s">
         <v>83</v>
       </c>
-      <c r="AP2" s="105" t="s">
+      <c r="AP2" s="114" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="3" spans="2:42" ht="39">
-      <c r="B3" s="113" t="s">
+      <c r="B3" s="122" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="113"/>
-      <c r="D3" s="113"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="122"/>
       <c r="F3" s="64" t="s">
         <v>86</v>
       </c>
@@ -39134,16 +39134,16 @@
       <c r="AJ3" s="64" t="s">
         <v>187</v>
       </c>
-      <c r="AL3" s="106"/>
-      <c r="AM3" s="106"/>
-      <c r="AN3" s="106"/>
-      <c r="AO3" s="106"/>
-      <c r="AP3" s="106"/>
+      <c r="AL3" s="115"/>
+      <c r="AM3" s="115"/>
+      <c r="AN3" s="115"/>
+      <c r="AO3" s="115"/>
+      <c r="AP3" s="115"/>
     </row>
     <row r="4" spans="2:42" ht="19.5" customHeight="1" thickBot="1">
-      <c r="B4" s="113"/>
-      <c r="C4" s="113"/>
-      <c r="D4" s="113"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
       <c r="F4" s="30">
         <v>1</v>
       </c>
@@ -39237,20 +39237,20 @@
       <c r="AJ4" s="67" t="s">
         <v>187</v>
       </c>
-      <c r="AL4" s="107"/>
-      <c r="AM4" s="107"/>
-      <c r="AN4" s="107"/>
-      <c r="AO4" s="107"/>
-      <c r="AP4" s="107"/>
+      <c r="AL4" s="116"/>
+      <c r="AM4" s="116"/>
+      <c r="AN4" s="116"/>
+      <c r="AO4" s="116"/>
+      <c r="AP4" s="116"/>
     </row>
     <row r="5" spans="2:42" ht="18.75">
       <c r="B5" s="35">
         <v>1</v>
       </c>
-      <c r="C5" s="111" t="s">
+      <c r="C5" s="120" t="s">
         <v>168</v>
       </c>
-      <c r="D5" s="112"/>
+      <c r="D5" s="121"/>
       <c r="F5" s="83" t="s">
         <v>102</v>
       </c>
@@ -39367,10 +39367,10 @@
       <c r="B6" s="35">
         <v>2</v>
       </c>
-      <c r="C6" s="97" t="s">
+      <c r="C6" s="112" t="s">
         <v>169</v>
       </c>
-      <c r="D6" s="98"/>
+      <c r="D6" s="113"/>
       <c r="F6" s="83" t="s">
         <v>102</v>
       </c>
@@ -39487,10 +39487,10 @@
       <c r="B7" s="35">
         <v>3</v>
       </c>
-      <c r="C7" s="97" t="s">
+      <c r="C7" s="112" t="s">
         <v>170</v>
       </c>
-      <c r="D7" s="98"/>
+      <c r="D7" s="113"/>
       <c r="F7" s="84" t="s">
         <v>95</v>
       </c>
@@ -39607,10 +39607,10 @@
       <c r="B8" s="35">
         <v>4</v>
       </c>
-      <c r="C8" s="97" t="s">
+      <c r="C8" s="112" t="s">
         <v>171</v>
       </c>
-      <c r="D8" s="98"/>
+      <c r="D8" s="113"/>
       <c r="F8" s="84" t="s">
         <v>95</v>
       </c>
@@ -39727,10 +39727,10 @@
       <c r="B9" s="35">
         <v>5</v>
       </c>
-      <c r="C9" s="97" t="s">
+      <c r="C9" s="112" t="s">
         <v>172</v>
       </c>
-      <c r="D9" s="98"/>
+      <c r="D9" s="113"/>
       <c r="F9" s="84" t="s">
         <v>96</v>
       </c>
@@ -39847,10 +39847,10 @@
       <c r="B10" s="35">
         <v>6</v>
       </c>
-      <c r="C10" s="97" t="s">
+      <c r="C10" s="112" t="s">
         <v>173</v>
       </c>
-      <c r="D10" s="98"/>
+      <c r="D10" s="113"/>
       <c r="F10" s="84" t="s">
         <v>96</v>
       </c>
@@ -39967,10 +39967,10 @@
       <c r="B11" s="35">
         <v>7</v>
       </c>
-      <c r="C11" s="97" t="s">
+      <c r="C11" s="112" t="s">
         <v>174</v>
       </c>
-      <c r="D11" s="98"/>
+      <c r="D11" s="113"/>
       <c r="F11" s="84" t="s">
         <v>101</v>
       </c>
@@ -40087,10 +40087,10 @@
       <c r="B12" s="35">
         <v>8</v>
       </c>
-      <c r="C12" s="97" t="s">
+      <c r="C12" s="112" t="s">
         <v>175</v>
       </c>
-      <c r="D12" s="98"/>
+      <c r="D12" s="113"/>
       <c r="F12" s="83" t="s">
         <v>101</v>
       </c>
@@ -40207,10 +40207,10 @@
       <c r="B13" s="35">
         <v>9</v>
       </c>
-      <c r="C13" s="97" t="s">
+      <c r="C13" s="112" t="s">
         <v>176</v>
       </c>
-      <c r="D13" s="98"/>
+      <c r="D13" s="113"/>
       <c r="F13" s="83" t="s">
         <v>101</v>
       </c>
@@ -40327,10 +40327,10 @@
       <c r="B14" s="35">
         <v>10</v>
       </c>
-      <c r="C14" s="97" t="s">
+      <c r="C14" s="112" t="s">
         <v>222</v>
       </c>
-      <c r="D14" s="98"/>
+      <c r="D14" s="113"/>
       <c r="F14" s="84" t="s">
         <v>116</v>
       </c>
@@ -40447,10 +40447,10 @@
       <c r="B15" s="35">
         <v>11</v>
       </c>
-      <c r="C15" s="97" t="s">
+      <c r="C15" s="112" t="s">
         <v>178</v>
       </c>
-      <c r="D15" s="98"/>
+      <c r="D15" s="113"/>
       <c r="F15" s="84" t="s">
         <v>116</v>
       </c>
@@ -40567,10 +40567,10 @@
       <c r="B16" s="35">
         <v>12</v>
       </c>
-      <c r="C16" s="97" t="s">
+      <c r="C16" s="112" t="s">
         <v>179</v>
       </c>
-      <c r="D16" s="98"/>
+      <c r="D16" s="113"/>
       <c r="F16" s="84" t="s">
         <v>96</v>
       </c>
@@ -40687,10 +40687,10 @@
       <c r="B17" s="35">
         <v>13</v>
       </c>
-      <c r="C17" s="97" t="s">
+      <c r="C17" s="112" t="s">
         <v>180</v>
       </c>
-      <c r="D17" s="98"/>
+      <c r="D17" s="113"/>
       <c r="F17" s="84" t="s">
         <v>96</v>
       </c>
@@ -40807,10 +40807,10 @@
       <c r="B18" s="35">
         <v>14</v>
       </c>
-      <c r="C18" s="97" t="s">
+      <c r="C18" s="112" t="s">
         <v>181</v>
       </c>
-      <c r="D18" s="98"/>
+      <c r="D18" s="113"/>
       <c r="F18" s="85" t="s">
         <v>101</v>
       </c>
@@ -40927,10 +40927,10 @@
       <c r="B19" s="35">
         <v>15</v>
       </c>
-      <c r="C19" s="97" t="s">
+      <c r="C19" s="112" t="s">
         <v>182</v>
       </c>
-      <c r="D19" s="98"/>
+      <c r="D19" s="113"/>
       <c r="F19" s="74" t="s">
         <v>116</v>
       </c>
@@ -41047,10 +41047,10 @@
       <c r="B20" s="35">
         <v>16</v>
       </c>
-      <c r="C20" s="97" t="s">
+      <c r="C20" s="112" t="s">
         <v>223</v>
       </c>
-      <c r="D20" s="98"/>
+      <c r="D20" s="113"/>
       <c r="F20" s="83" t="s">
         <v>96</v>
       </c>
@@ -41167,10 +41167,10 @@
       <c r="B21" s="35">
         <v>17</v>
       </c>
-      <c r="C21" s="97" t="s">
+      <c r="C21" s="112" t="s">
         <v>224</v>
       </c>
-      <c r="D21" s="98"/>
+      <c r="D21" s="113"/>
       <c r="F21" s="84" t="s">
         <v>102</v>
       </c>
@@ -41407,10 +41407,10 @@
       <c r="B23" s="35">
         <v>19</v>
       </c>
-      <c r="C23" s="99" t="s">
+      <c r="C23" s="126" t="s">
         <v>225</v>
       </c>
-      <c r="D23" s="100"/>
+      <c r="D23" s="127"/>
       <c r="F23" s="87" t="s">
         <v>101</v>
       </c>
@@ -41558,10 +41558,10 @@
       <c r="AI24" s="18"/>
     </row>
     <row r="25" spans="2:42" ht="18.75">
-      <c r="C25" s="101" t="s">
+      <c r="C25" s="109" t="s">
         <v>188</v>
       </c>
-      <c r="D25" s="102"/>
+      <c r="D25" s="110"/>
       <c r="E25" s="34"/>
       <c r="F25" s="35">
         <f>COUNTIF(F$5:F$21,"M*")</f>
@@ -41689,10 +41689,10 @@
       </c>
     </row>
     <row r="26" spans="2:42" ht="18.75">
-      <c r="C26" s="101" t="s">
+      <c r="C26" s="109" t="s">
         <v>189</v>
       </c>
-      <c r="D26" s="102"/>
+      <c r="D26" s="110"/>
       <c r="E26" s="34"/>
       <c r="F26" s="35">
         <f>COUNTIF(F$5:F$21,"A*")</f>
@@ -41820,10 +41820,10 @@
       </c>
     </row>
     <row r="27" spans="2:42" ht="18.75">
-      <c r="C27" s="101" t="s">
+      <c r="C27" s="109" t="s">
         <v>77</v>
       </c>
-      <c r="D27" s="102"/>
+      <c r="D27" s="110"/>
       <c r="E27" s="34"/>
       <c r="F27" s="35">
         <f>COUNTIF(F$5:F$21,"N*")</f>
@@ -41951,10 +41951,10 @@
       </c>
     </row>
     <row r="28" spans="2:42" ht="18.75">
-      <c r="C28" s="101" t="s">
+      <c r="C28" s="109" t="s">
         <v>78</v>
       </c>
-      <c r="D28" s="102"/>
+      <c r="D28" s="110"/>
       <c r="E28" s="34"/>
       <c r="F28" s="35">
         <f t="shared" ref="F28:AJ28" si="8">COUNTIF(F$5:F$23,"O*")</f>
@@ -42082,10 +42082,10 @@
       </c>
     </row>
     <row r="29" spans="2:42" ht="18.75">
-      <c r="C29" s="101" t="s">
+      <c r="C29" s="109" t="s">
         <v>190</v>
       </c>
-      <c r="D29" s="102"/>
+      <c r="D29" s="110"/>
       <c r="E29" s="34"/>
       <c r="F29" s="35">
         <f>COUNTIF(F$5:F$23,"TR*")</f>
@@ -42213,10 +42213,10 @@
       </c>
     </row>
     <row r="30" spans="2:42" ht="18.75">
-      <c r="C30" s="101" t="s">
+      <c r="C30" s="109" t="s">
         <v>191</v>
       </c>
-      <c r="D30" s="102"/>
+      <c r="D30" s="110"/>
       <c r="E30" s="34"/>
       <c r="F30" s="35">
         <f t="shared" ref="F30:AJ30" si="11">COUNTIF(F$5:F$23,"ST*")</f>
@@ -42344,10 +42344,10 @@
       </c>
     </row>
     <row r="31" spans="2:42" ht="18.75">
-      <c r="C31" s="103" t="s">
+      <c r="C31" s="128" t="s">
         <v>192</v>
       </c>
-      <c r="D31" s="104"/>
+      <c r="D31" s="129"/>
       <c r="E31" s="36"/>
       <c r="F31" s="37">
         <f>F33-F34</f>
@@ -42478,43 +42478,43 @@
       <c r="C32" s="38"/>
       <c r="D32" s="38"/>
       <c r="E32" s="34"/>
-      <c r="F32" s="114"/>
-      <c r="G32" s="114"/>
-      <c r="H32" s="114"/>
-      <c r="I32" s="114"/>
-      <c r="J32" s="114"/>
-      <c r="K32" s="114"/>
-      <c r="L32" s="114"/>
-      <c r="M32" s="114"/>
-      <c r="N32" s="114"/>
-      <c r="O32" s="114"/>
-      <c r="P32" s="114"/>
-      <c r="Q32" s="114"/>
-      <c r="R32" s="114"/>
-      <c r="S32" s="114"/>
-      <c r="T32" s="114"/>
-      <c r="U32" s="114"/>
-      <c r="V32" s="114"/>
-      <c r="W32" s="114"/>
-      <c r="X32" s="114"/>
-      <c r="Y32" s="114"/>
-      <c r="Z32" s="114"/>
-      <c r="AA32" s="114"/>
-      <c r="AB32" s="114"/>
-      <c r="AC32" s="114"/>
-      <c r="AD32" s="114"/>
-      <c r="AE32" s="114"/>
-      <c r="AF32" s="114"/>
-      <c r="AG32" s="114"/>
-      <c r="AH32" s="114"/>
-      <c r="AI32" s="114"/>
-      <c r="AJ32" s="114"/>
+      <c r="F32" s="108"/>
+      <c r="G32" s="108"/>
+      <c r="H32" s="108"/>
+      <c r="I32" s="108"/>
+      <c r="J32" s="108"/>
+      <c r="K32" s="108"/>
+      <c r="L32" s="108"/>
+      <c r="M32" s="108"/>
+      <c r="N32" s="108"/>
+      <c r="O32" s="108"/>
+      <c r="P32" s="108"/>
+      <c r="Q32" s="108"/>
+      <c r="R32" s="108"/>
+      <c r="S32" s="108"/>
+      <c r="T32" s="108"/>
+      <c r="U32" s="108"/>
+      <c r="V32" s="108"/>
+      <c r="W32" s="108"/>
+      <c r="X32" s="108"/>
+      <c r="Y32" s="108"/>
+      <c r="Z32" s="108"/>
+      <c r="AA32" s="108"/>
+      <c r="AB32" s="108"/>
+      <c r="AC32" s="108"/>
+      <c r="AD32" s="108"/>
+      <c r="AE32" s="108"/>
+      <c r="AF32" s="108"/>
+      <c r="AG32" s="108"/>
+      <c r="AH32" s="108"/>
+      <c r="AI32" s="108"/>
+      <c r="AJ32" s="108"/>
     </row>
     <row r="33" spans="3:36" ht="18.75">
-      <c r="C33" s="101" t="s">
+      <c r="C33" s="109" t="s">
         <v>193</v>
       </c>
-      <c r="D33" s="102"/>
+      <c r="D33" s="110"/>
       <c r="E33" s="34"/>
       <c r="F33" s="39">
         <f>SUM(F25:F27)</f>
@@ -42642,10 +42642,10 @@
       </c>
     </row>
     <row r="34" spans="3:36" ht="18.75">
-      <c r="C34" s="101" t="s">
+      <c r="C34" s="109" t="s">
         <v>194</v>
       </c>
-      <c r="D34" s="102"/>
+      <c r="D34" s="110"/>
       <c r="E34" s="34"/>
       <c r="F34" s="35">
         <v>9</v>
@@ -42742,10 +42742,10 @@
       </c>
     </row>
     <row r="35" spans="3:36" ht="18.75">
-      <c r="C35" s="101" t="s">
+      <c r="C35" s="109" t="s">
         <v>195</v>
       </c>
-      <c r="D35" s="102"/>
+      <c r="D35" s="110"/>
       <c r="E35" s="34"/>
       <c r="F35" s="35">
         <f>SUM(F25,F26,F27,F28,F30)</f>
@@ -42874,87 +42874,87 @@
     </row>
     <row r="37" spans="3:36" ht="16.5" thickBot="1"/>
     <row r="38" spans="3:36" ht="16.5" thickBot="1">
-      <c r="F38" s="118" t="s">
+      <c r="F38" s="95" t="s">
         <v>196</v>
       </c>
-      <c r="G38" s="119"/>
-      <c r="H38" s="119"/>
-      <c r="I38" s="119"/>
-      <c r="J38" s="119"/>
-      <c r="K38" s="120"/>
+      <c r="G38" s="96"/>
+      <c r="H38" s="96"/>
+      <c r="I38" s="96"/>
+      <c r="J38" s="96"/>
+      <c r="K38" s="97"/>
     </row>
     <row r="39" spans="3:36">
       <c r="F39" s="80" t="s">
         <v>197</v>
       </c>
-      <c r="G39" s="128" t="s">
+      <c r="G39" s="106" t="s">
         <v>198</v>
       </c>
-      <c r="H39" s="128"/>
+      <c r="H39" s="106"/>
       <c r="I39" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="J39" s="121" t="s">
+      <c r="J39" s="98" t="s">
         <v>199</v>
       </c>
-      <c r="K39" s="122"/>
+      <c r="K39" s="99"/>
     </row>
     <row r="40" spans="3:36">
       <c r="F40" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="G40" s="129" t="s">
+      <c r="G40" s="107" t="s">
         <v>200</v>
       </c>
-      <c r="H40" s="129"/>
+      <c r="H40" s="107"/>
       <c r="I40" s="77" t="s">
         <v>201</v>
       </c>
-      <c r="J40" s="123" t="s">
+      <c r="J40" s="100" t="s">
         <v>202</v>
       </c>
-      <c r="K40" s="124"/>
+      <c r="K40" s="101"/>
     </row>
     <row r="41" spans="3:36">
       <c r="F41" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="G41" s="115" t="s">
+      <c r="G41" s="102" t="s">
         <v>203</v>
       </c>
-      <c r="H41" s="115"/>
+      <c r="H41" s="102"/>
       <c r="I41" s="78" t="s">
         <v>108</v>
       </c>
-      <c r="J41" s="115" t="s">
+      <c r="J41" s="102" t="s">
         <v>204</v>
       </c>
-      <c r="K41" s="125"/>
+      <c r="K41" s="103"/>
     </row>
     <row r="42" spans="3:36">
       <c r="F42" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="G42" s="116" t="s">
+      <c r="G42" s="111" t="s">
         <v>205</v>
       </c>
-      <c r="H42" s="116"/>
+      <c r="H42" s="111"/>
       <c r="I42" s="79" t="s">
         <v>206</v>
       </c>
-      <c r="J42" s="126" t="s">
+      <c r="J42" s="104" t="s">
         <v>207</v>
       </c>
-      <c r="K42" s="127"/>
+      <c r="K42" s="105"/>
     </row>
     <row r="43" spans="3:36">
       <c r="F43" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="G43" s="116" t="s">
+      <c r="G43" s="111" t="s">
         <v>208</v>
       </c>
-      <c r="H43" s="116"/>
+      <c r="H43" s="111"/>
       <c r="I43" s="20" t="s">
         <v>104</v>
       </c>
@@ -42967,10 +42967,10 @@
       <c r="F44" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="G44" s="117" t="s">
+      <c r="G44" s="92" t="s">
         <v>210</v>
       </c>
-      <c r="H44" s="117"/>
+      <c r="H44" s="92"/>
       <c r="I44" s="20" t="s">
         <v>114</v>
       </c>
@@ -42983,10 +42983,10 @@
       <c r="F45" s="82" t="s">
         <v>212</v>
       </c>
-      <c r="G45" s="92" t="s">
+      <c r="G45" s="123" t="s">
         <v>213</v>
       </c>
-      <c r="H45" s="92"/>
+      <c r="H45" s="123"/>
       <c r="I45" s="20" t="s">
         <v>131</v>
       </c>
@@ -42999,57 +42999,20 @@
       <c r="F46" s="55" t="s">
         <v>215</v>
       </c>
-      <c r="G46" s="95" t="s">
+      <c r="G46" s="124" t="s">
         <v>216</v>
       </c>
-      <c r="H46" s="95"/>
+      <c r="H46" s="124"/>
       <c r="I46" s="56" t="s">
         <v>167</v>
       </c>
-      <c r="J46" s="95" t="s">
+      <c r="J46" s="124" t="s">
         <v>217</v>
       </c>
-      <c r="K46" s="96"/>
+      <c r="K46" s="125"/>
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="G44:H44"/>
-    <mergeCell ref="J44:K44"/>
-    <mergeCell ref="F38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="J42:K42"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="F32:AJ32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="AO2:AO4"/>
-    <mergeCell ref="AP2:AP4"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F2:AJ2"/>
-    <mergeCell ref="AL2:AL4"/>
-    <mergeCell ref="AM2:AM4"/>
-    <mergeCell ref="AN2:AN4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="B3:D4"/>
     <mergeCell ref="G45:H45"/>
     <mergeCell ref="J45:K45"/>
     <mergeCell ref="G46:H46"/>
@@ -43066,6 +43029,43 @@
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="C31:D31"/>
+    <mergeCell ref="AO2:AO4"/>
+    <mergeCell ref="AP2:AP4"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F2:AJ2"/>
+    <mergeCell ref="AL2:AL4"/>
+    <mergeCell ref="AM2:AM4"/>
+    <mergeCell ref="AN2:AN4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="B3:D4"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F32:AJ32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="J44:K44"/>
+    <mergeCell ref="F38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="G40:H40"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F5:AI23">
@@ -43147,19 +43147,19 @@
       <c r="AG2" s="164"/>
       <c r="AH2" s="164"/>
       <c r="AI2" s="164"/>
-      <c r="AK2" s="105" t="s">
+      <c r="AK2" s="114" t="s">
         <v>80</v>
       </c>
-      <c r="AL2" s="105" t="s">
+      <c r="AL2" s="114" t="s">
         <v>81</v>
       </c>
-      <c r="AM2" s="105" t="s">
+      <c r="AM2" s="114" t="s">
         <v>82</v>
       </c>
-      <c r="AN2" s="105" t="s">
+      <c r="AN2" s="114" t="s">
         <v>83</v>
       </c>
-      <c r="AO2" s="105" t="s">
+      <c r="AO2" s="114" t="s">
         <v>84</v>
       </c>
     </row>
@@ -43259,11 +43259,11 @@
         <v>87</v>
       </c>
       <c r="AI3" s="29"/>
-      <c r="AK3" s="106"/>
-      <c r="AL3" s="106"/>
-      <c r="AM3" s="106"/>
-      <c r="AN3" s="106"/>
-      <c r="AO3" s="106"/>
+      <c r="AK3" s="115"/>
+      <c r="AL3" s="115"/>
+      <c r="AM3" s="115"/>
+      <c r="AN3" s="115"/>
+      <c r="AO3" s="115"/>
     </row>
     <row r="4" spans="2:41" ht="19.5" thickBot="1">
       <c r="B4" s="167"/>
@@ -43359,11 +43359,11 @@
         <v>30</v>
       </c>
       <c r="AI4" s="33"/>
-      <c r="AK4" s="107"/>
-      <c r="AL4" s="107"/>
-      <c r="AM4" s="107"/>
-      <c r="AN4" s="107"/>
-      <c r="AO4" s="107"/>
+      <c r="AK4" s="116"/>
+      <c r="AL4" s="116"/>
+      <c r="AM4" s="116"/>
+      <c r="AN4" s="116"/>
+      <c r="AO4" s="116"/>
     </row>
     <row r="5" spans="2:41" ht="18.75">
       <c r="B5" s="163" t="s">
@@ -44687,10 +44687,10 @@
       <c r="AH16" s="18"/>
     </row>
     <row r="17" spans="2:35" ht="18.75">
-      <c r="B17" s="141" t="s">
+      <c r="B17" s="153" t="s">
         <v>188</v>
       </c>
-      <c r="C17" s="141"/>
+      <c r="C17" s="153"/>
       <c r="D17" s="34"/>
       <c r="E17" s="35">
         <f t="shared" ref="E17:AH17" si="5">COUNTIF(E$5:E$15,"M*")</f>
@@ -44817,10 +44817,10 @@
       </c>
     </row>
     <row r="18" spans="2:35" ht="18.75">
-      <c r="B18" s="141" t="s">
+      <c r="B18" s="153" t="s">
         <v>189</v>
       </c>
-      <c r="C18" s="141"/>
+      <c r="C18" s="153"/>
       <c r="D18" s="34"/>
       <c r="E18" s="35">
         <f t="shared" ref="E18:AH18" si="6">COUNTIF(E$5:E$15,"A*")</f>
@@ -44947,10 +44947,10 @@
       </c>
     </row>
     <row r="19" spans="2:35" ht="18.75">
-      <c r="B19" s="141" t="s">
+      <c r="B19" s="153" t="s">
         <v>77</v>
       </c>
-      <c r="C19" s="141"/>
+      <c r="C19" s="153"/>
       <c r="D19" s="34"/>
       <c r="E19" s="35">
         <f t="shared" ref="E19:AH19" si="7">COUNTIF(E$5:E$15,"N*")</f>
@@ -45077,10 +45077,10 @@
       </c>
     </row>
     <row r="20" spans="2:35" ht="18.75">
-      <c r="B20" s="141" t="s">
+      <c r="B20" s="153" t="s">
         <v>78</v>
       </c>
-      <c r="C20" s="141"/>
+      <c r="C20" s="153"/>
       <c r="D20" s="34"/>
       <c r="E20" s="35">
         <f t="shared" ref="E20:AH20" si="8">COUNTIF(E$5:E$15,"O*")</f>
@@ -45207,10 +45207,10 @@
       </c>
     </row>
     <row r="21" spans="2:35" ht="18.75">
-      <c r="B21" s="101" t="s">
+      <c r="B21" s="109" t="s">
         <v>191</v>
       </c>
-      <c r="C21" s="102"/>
+      <c r="C21" s="110"/>
       <c r="D21" s="34"/>
       <c r="E21" s="35">
         <f t="shared" ref="E21:AH21" si="9">COUNTIF(E$5:E$15,"ST*")</f>
@@ -45337,10 +45337,10 @@
       </c>
     </row>
     <row r="22" spans="2:35" ht="18.75">
-      <c r="B22" s="140" t="s">
+      <c r="B22" s="152" t="s">
         <v>192</v>
       </c>
-      <c r="C22" s="140"/>
+      <c r="C22" s="152"/>
       <c r="D22" s="36"/>
       <c r="E22" s="37">
         <f>E24-E25</f>
@@ -45470,43 +45470,43 @@
       <c r="B23" s="38"/>
       <c r="C23" s="38"/>
       <c r="D23" s="34"/>
-      <c r="E23" s="114"/>
-      <c r="F23" s="114"/>
-      <c r="G23" s="114"/>
-      <c r="H23" s="114"/>
-      <c r="I23" s="114"/>
-      <c r="J23" s="114"/>
-      <c r="K23" s="114"/>
-      <c r="L23" s="114"/>
-      <c r="M23" s="114"/>
-      <c r="N23" s="114"/>
-      <c r="O23" s="114"/>
-      <c r="P23" s="114"/>
-      <c r="Q23" s="114"/>
-      <c r="R23" s="114"/>
-      <c r="S23" s="114"/>
-      <c r="T23" s="114"/>
-      <c r="U23" s="114"/>
-      <c r="V23" s="114"/>
-      <c r="W23" s="114"/>
-      <c r="X23" s="114"/>
-      <c r="Y23" s="114"/>
-      <c r="Z23" s="114"/>
-      <c r="AA23" s="114"/>
-      <c r="AB23" s="114"/>
-      <c r="AC23" s="114"/>
-      <c r="AD23" s="114"/>
-      <c r="AE23" s="114"/>
-      <c r="AF23" s="114"/>
-      <c r="AG23" s="114"/>
-      <c r="AH23" s="114"/>
-      <c r="AI23" s="114"/>
+      <c r="E23" s="108"/>
+      <c r="F23" s="108"/>
+      <c r="G23" s="108"/>
+      <c r="H23" s="108"/>
+      <c r="I23" s="108"/>
+      <c r="J23" s="108"/>
+      <c r="K23" s="108"/>
+      <c r="L23" s="108"/>
+      <c r="M23" s="108"/>
+      <c r="N23" s="108"/>
+      <c r="O23" s="108"/>
+      <c r="P23" s="108"/>
+      <c r="Q23" s="108"/>
+      <c r="R23" s="108"/>
+      <c r="S23" s="108"/>
+      <c r="T23" s="108"/>
+      <c r="U23" s="108"/>
+      <c r="V23" s="108"/>
+      <c r="W23" s="108"/>
+      <c r="X23" s="108"/>
+      <c r="Y23" s="108"/>
+      <c r="Z23" s="108"/>
+      <c r="AA23" s="108"/>
+      <c r="AB23" s="108"/>
+      <c r="AC23" s="108"/>
+      <c r="AD23" s="108"/>
+      <c r="AE23" s="108"/>
+      <c r="AF23" s="108"/>
+      <c r="AG23" s="108"/>
+      <c r="AH23" s="108"/>
+      <c r="AI23" s="108"/>
     </row>
     <row r="24" spans="2:35" ht="18.75">
-      <c r="B24" s="141" t="s">
+      <c r="B24" s="153" t="s">
         <v>193</v>
       </c>
-      <c r="C24" s="141"/>
+      <c r="C24" s="153"/>
       <c r="D24" s="34"/>
       <c r="E24" s="39">
         <f>SUM(E17:E19)</f>
@@ -45633,10 +45633,10 @@
       </c>
     </row>
     <row r="25" spans="2:35" ht="18.75">
-      <c r="B25" s="141" t="s">
+      <c r="B25" s="153" t="s">
         <v>194</v>
       </c>
-      <c r="C25" s="141"/>
+      <c r="C25" s="153"/>
       <c r="D25" s="34"/>
       <c r="E25" s="35">
         <v>7</v>
@@ -45733,10 +45733,10 @@
       </c>
     </row>
     <row r="26" spans="2:35" ht="18.75">
-      <c r="B26" s="141" t="s">
+      <c r="B26" s="153" t="s">
         <v>195</v>
       </c>
-      <c r="C26" s="141"/>
+      <c r="C26" s="153"/>
       <c r="D26" s="34"/>
       <c r="E26" s="35">
         <v>11</v>
@@ -45834,22 +45834,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="E23:AI23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
     <mergeCell ref="AN2:AN4"/>
     <mergeCell ref="AO2:AO4"/>
     <mergeCell ref="B9:C9"/>
@@ -45862,6 +45846,22 @@
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
+    <mergeCell ref="E23:AI23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
   </mergeCells>
   <conditionalFormatting sqref="E5:AH10">
     <cfRule type="containsText" dxfId="34" priority="23" operator="containsText" text="STN">
@@ -46014,6 +46014,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_activity xmlns="0ecd8b7c-869e-4f04-a6a3-066c3c63b311" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="مستند" ma:contentTypeID="0x01010053585A714B17B949862FA1B71BD97610" ma:contentTypeVersion="20" ma:contentTypeDescription="إنشاء مستند جديد." ma:contentTypeScope="" ma:versionID="dd8bd6d392f178541f6ccf1c351709a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns3="f1e9c892-1499-41bb-8a64-60ef909d8682" xmlns:ns4="0ecd8b7c-869e-4f04-a6a3-066c3c63b311" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9f246d41c9a2b9a4922388dcb99eeb28" ns1:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -46283,27 +46302,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_activity xmlns="0ecd8b7c-869e-4f04-a6a3-066c3c63b311" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57D06F05-5672-4668-89C3-4F6754D4BC82}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04335F04-3ECE-4043-846B-35335B1D83ED}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -46311,7 +46311,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04335F04-3ECE-4043-846B-35335B1D83ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57D06F05-5672-4668-89C3-4F6754D4BC82}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/rosters/.versions/2026-06/previous.xlsx
+++ b/rosters/.versions/2026-06/previous.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://omanair-my.sharepoint.com/personal/80235_hq_omanair_com/Documents/Desktop/Rosters/STAFF OPERATION SCHEDULE/Roster with 2 OFF/05June/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE75BAC3-01A8-4F4B-A53B-0B41260E82E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{CE75BAC3-01A8-4F4B-A53B-0B41260E82E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88B5E81A-A54C-44CD-A4F6-4E91E1F258F6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="2" activeTab="2" xr2:uid="{9736B67C-D61B-41E1-B07B-429B3D8AE9CC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="2" activeTab="4" xr2:uid="{9736B67C-D61B-41E1-B07B-429B3D8AE9CC}"/>
   </bookViews>
   <sheets>
     <sheet name="Setting " sheetId="1" state="hidden" r:id="rId1"/>
@@ -35689,13 +35689,13 @@
         <v>231</v>
       </c>
       <c r="I16" s="84" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J16" s="84" t="s">
         <v>230</v>
       </c>
       <c r="K16" s="84" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="L16" s="84" t="s">
         <v>234</v>
@@ -35780,11 +35780,11 @@
       </c>
       <c r="AN16" s="48">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO16" s="48">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP16" s="48">
         <f t="shared" si="4"/>
@@ -37240,7 +37240,7 @@
       </c>
       <c r="D29" s="107"/>
       <c r="F29" s="84" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="G29" s="84" t="s">
         <v>215</v>
@@ -37344,7 +37344,7 @@
       </c>
       <c r="AO29" s="48">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP29" s="48">
         <f t="shared" si="4"/>
@@ -37966,19 +37966,19 @@
         <v>215</v>
       </c>
       <c r="H35" s="84" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="I35" s="84" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="J35" s="84" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="K35" s="84" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="L35" s="84" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="M35" s="84" t="s">
         <v>215</v>
@@ -38056,11 +38056,11 @@
       </c>
       <c r="AM35" s="48">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AN35" s="48">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AO35" s="48">
         <f t="shared" si="3"/>
@@ -38200,13 +38200,13 @@
       </c>
       <c r="D37" s="117"/>
       <c r="F37" s="174" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="G37" s="174" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="H37" s="174" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="I37" s="174" t="s">
         <v>126</v>
@@ -38221,13 +38221,13 @@
         <v>215</v>
       </c>
       <c r="M37" s="174" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="N37" s="174" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="O37" s="174" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="P37" s="174" t="s">
         <v>231</v>
@@ -38242,13 +38242,13 @@
         <v>215</v>
       </c>
       <c r="T37" s="174" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="U37" s="174" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="V37" s="174" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="W37" s="174" t="s">
         <v>231</v>
@@ -38284,10 +38284,10 @@
         <v>215</v>
       </c>
       <c r="AH37" s="174" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="AI37" s="174" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="AJ37" s="174"/>
       <c r="AL37" s="48">
@@ -38365,11 +38365,11 @@
       </c>
       <c r="I39" s="37">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J39" s="37">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K39" s="37">
         <f t="shared" si="5"/>
@@ -38377,7 +38377,7 @@
       </c>
       <c r="L39" s="37">
         <f t="shared" si="5"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M39" s="37">
         <f t="shared" si="5"/>
@@ -38492,7 +38492,7 @@
       </c>
       <c r="H40" s="37">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I40" s="37">
         <f t="shared" si="6"/>
@@ -38615,7 +38615,7 @@
       <c r="E41" s="36"/>
       <c r="F41" s="37">
         <f t="shared" ref="F41:AJ41" si="7">COUNTIF(F$5:F$36,"N*")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G41" s="37">
         <f t="shared" si="7"/>
@@ -38635,7 +38635,7 @@
       </c>
       <c r="K41" s="37">
         <f t="shared" si="7"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L41" s="37">
         <f t="shared" si="7"/>
@@ -39139,7 +39139,7 @@
       <c r="E45" s="38"/>
       <c r="F45" s="50">
         <f>F47-F48</f>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G45" s="50">
         <f t="shared" ref="G45:AJ45" si="11">G47-G48</f>
@@ -39147,23 +39147,23 @@
       </c>
       <c r="H45" s="50">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I45" s="50">
         <f t="shared" si="11"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="J45" s="50">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K45" s="50">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L45" s="50">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M45" s="50">
         <f t="shared" si="11"/>
@@ -39306,7 +39306,7 @@
       <c r="E47" s="36"/>
       <c r="F47" s="41">
         <f>SUM(F39:F41)</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G47" s="41">
         <f t="shared" ref="G47:AI47" si="12">SUM(G39:G41)</f>
@@ -39314,23 +39314,23 @@
       </c>
       <c r="H47" s="41">
         <f t="shared" si="12"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I47" s="41">
         <f t="shared" si="12"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J47" s="41">
         <f t="shared" si="12"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K47" s="41">
         <f t="shared" si="12"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L47" s="41">
         <f t="shared" si="12"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M47" s="41">
         <f t="shared" si="12"/>
@@ -39536,7 +39536,7 @@
       <c r="E49" s="36"/>
       <c r="F49" s="37">
         <f>SUM(F39,F40,F41,F42,F44)</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G49" s="37">
         <f t="shared" ref="G49:AI49" si="13">SUM(G39,G40,G41,G42,G44)</f>
@@ -39544,23 +39544,23 @@
       </c>
       <c r="H49" s="37">
         <f t="shared" si="13"/>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I49" s="37">
         <f t="shared" si="13"/>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J49" s="37">
         <f t="shared" si="13"/>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K49" s="37">
         <f t="shared" si="13"/>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L49" s="37">
         <f t="shared" si="13"/>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M49" s="37">
         <f t="shared" si="13"/>
